--- a/Другое/2026/Доходы-Расходы.xlsx
+++ b/Другое/2026/Доходы-Расходы.xlsx
@@ -1,13 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROG\Git\Repository_1\Другое\2026\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10980" tabRatio="672" activeTab="9"/>
   </bookViews>
@@ -23,7 +18,7 @@
     <sheet name="Сентябрь 2026" sheetId="10" r:id="rId9"/>
     <sheet name="Октябрь 2026" sheetId="11" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="125725"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -46,7 +41,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="S3" authorId="0" shapeId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -69,7 +64,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P11" authorId="0" shapeId="0">
+    <comment ref="P11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -92,7 +87,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R16" authorId="0" shapeId="0">
+    <comment ref="R16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -115,7 +110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P20" authorId="0" shapeId="0">
+    <comment ref="P20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -137,7 +132,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P24" authorId="0" shapeId="0">
+    <comment ref="P24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -159,7 +154,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H25" authorId="0" shapeId="0">
+    <comment ref="H25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -182,7 +177,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J25" authorId="0" shapeId="0">
+    <comment ref="J25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -204,7 +199,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J26" authorId="0" shapeId="0">
+    <comment ref="J26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -226,7 +221,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L26" authorId="0" shapeId="0">
+    <comment ref="L26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -248,7 +243,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P26" authorId="0" shapeId="0">
+    <comment ref="P26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -270,7 +265,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J27" authorId="0" shapeId="0">
+    <comment ref="J27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -302,7 +297,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="R3" authorId="0" shapeId="0">
+    <comment ref="R3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -324,7 +319,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F4" authorId="0" shapeId="0">
+    <comment ref="F4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -346,7 +341,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R4" authorId="0" shapeId="0">
+    <comment ref="R4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -369,7 +364,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0" shapeId="0">
+    <comment ref="S4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -391,7 +386,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T4" authorId="0" shapeId="0">
+    <comment ref="T4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -413,7 +408,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G5" authorId="0" shapeId="0">
+    <comment ref="G5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -435,7 +430,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P5" authorId="0" shapeId="0">
+    <comment ref="P5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -457,7 +452,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P6" authorId="0" shapeId="0">
+    <comment ref="P6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -480,7 +475,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S10" authorId="0" shapeId="0">
+    <comment ref="S10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -502,7 +497,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A11" authorId="0" shapeId="0">
+    <comment ref="A11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -524,7 +519,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R18" authorId="0" shapeId="0">
+    <comment ref="R18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -547,7 +542,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S18" authorId="0" shapeId="0">
+    <comment ref="S18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -569,7 +564,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R19" authorId="0" shapeId="0">
+    <comment ref="R19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -592,7 +587,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S19" authorId="0" shapeId="0">
+    <comment ref="S19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -614,7 +609,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S20" authorId="0" shapeId="0">
+    <comment ref="S20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -636,7 +631,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T20" authorId="0" shapeId="0">
+    <comment ref="T20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -658,7 +653,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S22" authorId="0" shapeId="0">
+    <comment ref="S22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -680,7 +675,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S26" authorId="0" shapeId="0">
+    <comment ref="S26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -712,7 +707,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="Q3" authorId="0" shapeId="0">
+    <comment ref="Q3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -726,7 +721,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0" shapeId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -749,7 +744,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0" shapeId="0">
+    <comment ref="T3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -772,7 +767,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U3" authorId="0" shapeId="0">
+    <comment ref="U3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -794,7 +789,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0" shapeId="0">
+    <comment ref="H4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -816,7 +811,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K4" authorId="0" shapeId="0">
+    <comment ref="K4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -838,7 +833,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N4" authorId="0" shapeId="0">
+    <comment ref="N4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -860,7 +855,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q4" authorId="0" shapeId="0">
+    <comment ref="Q4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -883,7 +878,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0" shapeId="0">
+    <comment ref="S4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -906,7 +901,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U4" authorId="0" shapeId="0">
+    <comment ref="U4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -929,7 +924,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V4" authorId="0" shapeId="0">
+    <comment ref="V4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -951,7 +946,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I5" authorId="0" shapeId="0">
+    <comment ref="I5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -974,7 +969,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S5" authorId="0" shapeId="0">
+    <comment ref="S5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -996,7 +991,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K6" authorId="0" shapeId="0">
+    <comment ref="K6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1019,7 +1014,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S6" authorId="0" shapeId="0">
+    <comment ref="S6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1042,7 +1037,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H8" authorId="0" shapeId="0">
+    <comment ref="H8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1056,7 +1051,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0">
+    <comment ref="E10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1079,7 +1074,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X11" authorId="0" shapeId="0">
+    <comment ref="X11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1102,7 +1097,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X12" authorId="0" shapeId="0">
+    <comment ref="X12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1124,7 +1119,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H14" authorId="0" shapeId="0">
+    <comment ref="H14" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1147,7 +1142,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H15" authorId="0" shapeId="0">
+    <comment ref="H15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1161,7 +1156,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T15" authorId="0" shapeId="0">
+    <comment ref="T15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1174,7 +1169,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E17" authorId="0" shapeId="0">
+    <comment ref="E17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1196,7 +1191,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q17" authorId="0" shapeId="0">
+    <comment ref="Q17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1218,7 +1213,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S19" authorId="0" shapeId="0">
+    <comment ref="S19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1240,7 +1235,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S21" authorId="0" shapeId="0">
+    <comment ref="S21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1263,7 +1258,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T21" authorId="0" shapeId="0">
+    <comment ref="T21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1285,7 +1280,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F22" authorId="0" shapeId="0">
+    <comment ref="F22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1307,7 +1302,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H22" authorId="0" shapeId="0">
+    <comment ref="H22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1329,7 +1324,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T22" authorId="0" shapeId="0">
+    <comment ref="T22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1351,7 +1346,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E24" authorId="0" shapeId="0">
+    <comment ref="E24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1374,7 +1369,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F25" authorId="0" shapeId="0">
+    <comment ref="F25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1397,7 +1392,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E27" authorId="0" shapeId="0">
+    <comment ref="E27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1420,7 +1415,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H29" authorId="0" shapeId="0">
+    <comment ref="H29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1442,7 +1437,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S29" authorId="0" shapeId="0">
+    <comment ref="S29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1464,7 +1459,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F30" authorId="0" shapeId="0">
+    <comment ref="F30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1486,7 +1481,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X30" authorId="0" shapeId="0">
+    <comment ref="X30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1508,7 +1503,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H31" authorId="0" shapeId="0">
+    <comment ref="H31" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1530,7 +1525,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S33" authorId="0" shapeId="0">
+    <comment ref="S33" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1552,7 +1547,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X35" authorId="0" shapeId="0">
+    <comment ref="X35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1584,7 +1579,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="S3" authorId="0" shapeId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1606,7 +1601,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0" shapeId="0">
+    <comment ref="T3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1629,7 +1624,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0" shapeId="0">
+    <comment ref="H4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1651,7 +1646,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F5" authorId="0" shapeId="0">
+    <comment ref="F5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1673,7 +1668,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S5" authorId="0" shapeId="0">
+    <comment ref="S5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1695,7 +1690,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H6" authorId="0" shapeId="0">
+    <comment ref="H6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1717,7 +1712,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K7" authorId="0" shapeId="0">
+    <comment ref="K7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1739,7 +1734,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X7" authorId="0" shapeId="0">
+    <comment ref="X7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1761,7 +1756,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K8" authorId="0" shapeId="0">
+    <comment ref="K8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1783,7 +1778,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K9" authorId="0" shapeId="0">
+    <comment ref="K9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1805,7 +1800,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F10" authorId="0" shapeId="0">
+    <comment ref="F10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1828,7 +1823,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H11" authorId="0" shapeId="0">
+    <comment ref="H11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1850,7 +1845,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H13" authorId="0" shapeId="0">
+    <comment ref="H13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1873,7 +1868,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q19" authorId="0" shapeId="0">
+    <comment ref="Q19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1895,7 +1890,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S19" authorId="0" shapeId="0">
+    <comment ref="S19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1917,7 +1912,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T20" authorId="0" shapeId="0">
+    <comment ref="T20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1940,7 +1935,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H21" authorId="0" shapeId="0">
+    <comment ref="H21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1962,7 +1957,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T21" authorId="0" shapeId="0">
+    <comment ref="T21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1985,7 +1980,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X21" authorId="0" shapeId="0">
+    <comment ref="X21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2007,7 +2002,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J24" authorId="0" shapeId="0">
+    <comment ref="J24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2029,7 +2024,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S24" authorId="0" shapeId="0">
+    <comment ref="S24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2051,7 +2046,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V25" authorId="0" shapeId="0">
+    <comment ref="V25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2073,7 +2068,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H27" authorId="0" shapeId="0">
+    <comment ref="H27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2095,7 +2090,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S27" authorId="0" shapeId="0">
+    <comment ref="S27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2117,7 +2112,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H28" authorId="0" shapeId="0">
+    <comment ref="H28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2139,7 +2134,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V28" authorId="0" shapeId="0">
+    <comment ref="V28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2162,7 +2157,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X28" authorId="0" shapeId="0">
+    <comment ref="X28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2184,7 +2179,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E29" authorId="0" shapeId="0">
+    <comment ref="E29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2206,7 +2201,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X29" authorId="0" shapeId="0">
+    <comment ref="X29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2228,7 +2223,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S31" authorId="0" shapeId="0">
+    <comment ref="S31" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2250,7 +2245,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S33" authorId="0" shapeId="0">
+    <comment ref="S33" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2272,7 +2267,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X34" authorId="0" shapeId="0">
+    <comment ref="X34" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2305,7 +2300,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0" shapeId="0">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2327,7 +2322,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0" shapeId="0">
+    <comment ref="H3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2349,7 +2344,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0" shapeId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2371,7 +2366,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0" shapeId="0">
+    <comment ref="T3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2393,7 +2388,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V3" authorId="0" shapeId="0">
+    <comment ref="V3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2415,7 +2410,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0" shapeId="0">
+    <comment ref="H4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2437,7 +2432,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N4" authorId="0" shapeId="0">
+    <comment ref="N4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2459,7 +2454,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q4" authorId="0" shapeId="0">
+    <comment ref="Q4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2481,7 +2476,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0" shapeId="0">
+    <comment ref="S4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2503,7 +2498,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H5" authorId="0" shapeId="0">
+    <comment ref="H5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2525,7 +2520,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T5" authorId="0" shapeId="0">
+    <comment ref="T5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2547,7 +2542,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F6" authorId="0" shapeId="0">
+    <comment ref="F6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2569,7 +2564,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H6" authorId="0" shapeId="0">
+    <comment ref="H6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2591,7 +2586,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T6" authorId="0" shapeId="0">
+    <comment ref="T6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2613,7 +2608,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q7" authorId="0" shapeId="0">
+    <comment ref="Q7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2635,7 +2630,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F8" authorId="0" shapeId="0">
+    <comment ref="F8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2657,7 +2652,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q8" authorId="0" shapeId="0">
+    <comment ref="Q8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2679,7 +2674,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S8" authorId="0" shapeId="0">
+    <comment ref="S8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2701,7 +2696,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q9" authorId="0" shapeId="0">
+    <comment ref="Q9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2723,7 +2718,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X9" authorId="0" shapeId="0">
+    <comment ref="X9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2745,7 +2740,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0">
+    <comment ref="E10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2767,7 +2762,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E11" authorId="0" shapeId="0">
+    <comment ref="E11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2789,7 +2784,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I11" authorId="0" shapeId="0">
+    <comment ref="I11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2811,7 +2806,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q12" authorId="0" shapeId="0">
+    <comment ref="Q12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2834,7 +2829,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q13" authorId="0" shapeId="0">
+    <comment ref="Q13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2856,7 +2851,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S13" authorId="0" shapeId="0">
+    <comment ref="S13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2878,7 +2873,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X14" authorId="0" shapeId="0">
+    <comment ref="X14" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2900,7 +2895,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X16" authorId="0" shapeId="0">
+    <comment ref="X16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2922,7 +2917,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H17" authorId="0" shapeId="0">
+    <comment ref="H17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2945,7 +2940,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S17" authorId="0" shapeId="0">
+    <comment ref="S17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2967,7 +2962,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T17" authorId="0" shapeId="0">
+    <comment ref="T17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2989,7 +2984,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H19" authorId="0" shapeId="0">
+    <comment ref="H19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3011,7 +3006,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N19" authorId="0" shapeId="0">
+    <comment ref="N19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3043,7 +3038,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="Q3" authorId="0" shapeId="0">
+    <comment ref="Q3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3066,7 +3061,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0" shapeId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3088,7 +3083,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0" shapeId="0">
+    <comment ref="H4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3110,7 +3105,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S5" authorId="0" shapeId="0">
+    <comment ref="S5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3133,7 +3128,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V6" authorId="0" shapeId="0">
+    <comment ref="V6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3155,7 +3150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F7" authorId="0" shapeId="0">
+    <comment ref="F7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3177,7 +3172,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q8" authorId="0" shapeId="0">
+    <comment ref="Q8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3200,7 +3195,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S8" authorId="0" shapeId="0">
+    <comment ref="S8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3223,7 +3218,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S9" authorId="0" shapeId="0">
+    <comment ref="S9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3245,7 +3240,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0">
+    <comment ref="E10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3267,7 +3262,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S10" authorId="0" shapeId="0">
+    <comment ref="S10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3289,7 +3284,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q12" authorId="0" shapeId="0">
+    <comment ref="Q12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3311,7 +3306,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q13" authorId="0" shapeId="0">
+    <comment ref="Q13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3334,7 +3329,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S13" authorId="0" shapeId="0">
+    <comment ref="S13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3356,7 +3351,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y14" authorId="0" shapeId="0">
+    <comment ref="Y14" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3379,7 +3374,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q15" authorId="0" shapeId="0">
+    <comment ref="Q15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3401,7 +3396,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S15" authorId="0" shapeId="0">
+    <comment ref="S15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3423,7 +3418,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E16" authorId="0" shapeId="0">
+    <comment ref="E16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3445,7 +3440,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F16" authorId="0" shapeId="0">
+    <comment ref="F16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3467,7 +3462,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M16" authorId="0" shapeId="0">
+    <comment ref="M16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3490,7 +3485,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T16" authorId="0" shapeId="0">
+    <comment ref="T16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3503,7 +3498,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M17" authorId="0" shapeId="0">
+    <comment ref="M17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3525,7 +3520,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S17" authorId="0" shapeId="0">
+    <comment ref="S17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3547,7 +3542,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T17" authorId="0" shapeId="0">
+    <comment ref="T17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3569,7 +3564,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U17" authorId="0" shapeId="0">
+    <comment ref="U17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3591,7 +3586,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y17" authorId="0" shapeId="0">
+    <comment ref="Y17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3613,7 +3608,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S18" authorId="0" shapeId="0">
+    <comment ref="S18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3635,7 +3630,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U18" authorId="0" shapeId="0">
+    <comment ref="U18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3657,7 +3652,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E19" authorId="0" shapeId="0">
+    <comment ref="E19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3679,7 +3674,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V19" authorId="0" shapeId="0">
+    <comment ref="V19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3701,7 +3696,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y19" authorId="0" shapeId="0">
+    <comment ref="Y19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3714,7 +3709,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F21" authorId="0" shapeId="0">
+    <comment ref="F21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3736,7 +3731,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T21" authorId="0" shapeId="0">
+    <comment ref="T21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3759,7 +3754,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F23" authorId="0" shapeId="0">
+    <comment ref="F23" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3781,7 +3776,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S23" authorId="0" shapeId="0">
+    <comment ref="S23" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3803,7 +3798,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F24" authorId="0" shapeId="0">
+    <comment ref="F24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3825,7 +3820,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H25" authorId="0" shapeId="0">
+    <comment ref="H25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3847,7 +3842,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V25" authorId="0" shapeId="0">
+    <comment ref="V25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3869,7 +3864,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E27" authorId="0" shapeId="0">
+    <comment ref="E27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3891,7 +3886,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V27" authorId="0" shapeId="0">
+    <comment ref="V27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3913,7 +3908,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y27" authorId="0" shapeId="0">
+    <comment ref="Y27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3935,7 +3930,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S28" authorId="0" shapeId="0">
+    <comment ref="S28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3957,7 +3952,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T28" authorId="0" shapeId="0">
+    <comment ref="T28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3979,7 +3974,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q29" authorId="0" shapeId="0">
+    <comment ref="Q29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4001,7 +3996,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F30" authorId="0" shapeId="0">
+    <comment ref="F30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4014,7 +4009,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q30" authorId="0" shapeId="0">
+    <comment ref="Q30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4036,7 +4031,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y33" authorId="0" shapeId="0">
+    <comment ref="Y33" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4050,7 +4045,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S34" authorId="0" shapeId="0">
+    <comment ref="S34" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4064,7 +4059,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T34" authorId="0" shapeId="0">
+    <comment ref="T34" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4077,7 +4072,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E35" authorId="0" shapeId="0">
+    <comment ref="E35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4090,7 +4085,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F35" authorId="0" shapeId="0">
+    <comment ref="F35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4112,7 +4107,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S35" authorId="0" shapeId="0">
+    <comment ref="S35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4135,7 +4130,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H36" authorId="0" shapeId="0">
+    <comment ref="H36" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4157,7 +4152,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S36" authorId="0" shapeId="0">
+    <comment ref="S36" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4189,7 +4184,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="I4" authorId="0" shapeId="0">
+    <comment ref="I4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4202,7 +4197,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O4" authorId="0" shapeId="0">
+    <comment ref="O4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4214,7 +4209,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P4" authorId="0" shapeId="0">
+    <comment ref="P4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4237,7 +4232,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X4" authorId="0" shapeId="0">
+    <comment ref="X4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4250,7 +4245,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L5" authorId="0" shapeId="0">
+    <comment ref="L5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4274,7 +4269,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q5" authorId="0" shapeId="0">
+    <comment ref="Q5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4287,7 +4282,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W5" authorId="0" shapeId="0">
+    <comment ref="W5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4300,7 +4295,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J6" authorId="0" shapeId="0">
+    <comment ref="J6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4322,7 +4317,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I7" authorId="0" shapeId="0">
+    <comment ref="I7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4335,7 +4330,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J7" authorId="0" shapeId="0">
+    <comment ref="J7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4348,7 +4343,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O7" authorId="0" shapeId="0">
+    <comment ref="O7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4361,7 +4356,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z7" authorId="0" shapeId="0">
+    <comment ref="Z7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4375,7 +4370,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J8" authorId="0" shapeId="0">
+    <comment ref="J8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4397,7 +4392,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W8" authorId="0" shapeId="0">
+    <comment ref="W8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4410,7 +4405,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N9" authorId="0" shapeId="0">
+    <comment ref="N9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4423,7 +4418,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P9" authorId="0" shapeId="0">
+    <comment ref="P9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4436,7 +4431,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q10" authorId="0" shapeId="0">
+    <comment ref="Q10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4449,7 +4444,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W10" authorId="0" shapeId="0">
+    <comment ref="W10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4462,7 +4457,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X10" authorId="0" shapeId="0">
+    <comment ref="X10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4484,7 +4479,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W11" authorId="0" shapeId="0">
+    <comment ref="W11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4507,7 +4502,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K12" authorId="0" shapeId="0">
+    <comment ref="K12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4529,7 +4524,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W12" authorId="0" shapeId="0">
+    <comment ref="W12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4551,7 +4546,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I13" authorId="0" shapeId="0">
+    <comment ref="I13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4573,7 +4568,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W13" authorId="0" shapeId="0">
+    <comment ref="W13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4595,7 +4590,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H14" authorId="0" shapeId="0">
+    <comment ref="H14" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4608,7 +4603,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W14" authorId="0" shapeId="0">
+    <comment ref="W14" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4630,7 +4625,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D15" authorId="0" shapeId="0">
+    <comment ref="D15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4643,7 +4638,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J15" authorId="0" shapeId="0">
+    <comment ref="J15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4657,7 +4652,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W15" authorId="0" shapeId="0">
+    <comment ref="W15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4671,7 +4666,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X15" authorId="0" shapeId="0">
+    <comment ref="X15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4684,7 +4679,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z15" authorId="0" shapeId="0">
+    <comment ref="Z15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4697,7 +4692,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I16" authorId="0" shapeId="0">
+    <comment ref="I16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4710,7 +4705,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N16" authorId="0" shapeId="0">
+    <comment ref="N16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4724,7 +4719,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X16" authorId="0" shapeId="0">
+    <comment ref="X16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4737,7 +4732,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X18" authorId="0" shapeId="0">
+    <comment ref="X18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4750,7 +4745,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K20" authorId="0" shapeId="0">
+    <comment ref="K20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4763,7 +4758,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W20" authorId="0" shapeId="0">
+    <comment ref="W20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4777,7 +4772,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I21" authorId="0" shapeId="0">
+    <comment ref="I21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4790,7 +4785,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC21" authorId="0" shapeId="0">
+    <comment ref="AC21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4803,7 +4798,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J23" authorId="0" shapeId="0">
+    <comment ref="J23" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4816,7 +4811,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W23" authorId="0" shapeId="0">
+    <comment ref="W23" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4829,7 +4824,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H24" authorId="0" shapeId="0">
+    <comment ref="H24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4842,7 +4837,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K24" authorId="0" shapeId="0">
+    <comment ref="K24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4864,7 +4859,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K25" authorId="0" shapeId="0">
+    <comment ref="K25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4877,7 +4872,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W25" authorId="0" shapeId="0">
+    <comment ref="W25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4890,7 +4885,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N26" authorId="0" shapeId="0">
+    <comment ref="N26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4903,7 +4898,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W26" authorId="0" shapeId="0">
+    <comment ref="W26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4926,7 +4921,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X26" authorId="0" shapeId="0">
+    <comment ref="X26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4948,7 +4943,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K27" authorId="0" shapeId="0">
+    <comment ref="K27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4961,7 +4956,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X27" authorId="0" shapeId="0">
+    <comment ref="X27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4974,7 +4969,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W28" authorId="0" shapeId="0">
+    <comment ref="W28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4987,7 +4982,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z28" authorId="0" shapeId="0">
+    <comment ref="Z28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5000,7 +4995,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J29" authorId="0" shapeId="0">
+    <comment ref="J29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5022,7 +5017,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z29" authorId="0" shapeId="0">
+    <comment ref="Z29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5035,7 +5030,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC29" authorId="0" shapeId="0">
+    <comment ref="AC29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5048,7 +5043,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J30" authorId="0" shapeId="0">
+    <comment ref="J30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5061,7 +5056,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N30" authorId="0" shapeId="0">
+    <comment ref="N30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5074,7 +5069,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K31" authorId="0" shapeId="0">
+    <comment ref="K31" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5087,7 +5082,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K32" authorId="0" shapeId="0">
+    <comment ref="K32" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5100,7 +5095,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W32" authorId="0" shapeId="0">
+    <comment ref="W32" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5113,7 +5108,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N33" authorId="0" shapeId="0">
+    <comment ref="N33" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5126,7 +5121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W34" authorId="0" shapeId="0">
+    <comment ref="W34" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5140,7 +5135,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC34" authorId="0" shapeId="0">
+    <comment ref="AC34" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5165,7 +5160,7 @@
     <author>SABEN_MUSIC</author>
   </authors>
   <commentList>
-    <comment ref="X4" authorId="0" shapeId="0">
+    <comment ref="X4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5185,7 +5180,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y4" authorId="0" shapeId="0">
+    <comment ref="Y4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5205,7 +5200,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z4" authorId="0" shapeId="0">
+    <comment ref="Z4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5225,7 +5220,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H5" authorId="0" shapeId="0">
+    <comment ref="H5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5245,7 +5240,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J5" authorId="0" shapeId="0">
+    <comment ref="J5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5265,7 +5260,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M5" authorId="0" shapeId="0">
+    <comment ref="M5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5285,7 +5280,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N5" authorId="0" shapeId="0">
+    <comment ref="N5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5305,7 +5300,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X5" authorId="0" shapeId="0">
+    <comment ref="X5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5325,7 +5320,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I6" authorId="0" shapeId="0">
+    <comment ref="I6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5345,7 +5340,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T6" authorId="0" shapeId="0">
+    <comment ref="T6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5365,7 +5360,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W6" authorId="0" shapeId="0">
+    <comment ref="W6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5385,7 +5380,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K7" authorId="0" shapeId="0">
+    <comment ref="K7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5406,7 +5401,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W7" authorId="0" shapeId="0">
+    <comment ref="W7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5426,7 +5421,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X7" authorId="0" shapeId="0">
+    <comment ref="X7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5446,7 +5441,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y7" authorId="0" shapeId="0">
+    <comment ref="Y7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5466,7 +5461,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H8" authorId="1" shapeId="0">
+    <comment ref="H8" authorId="1">
       <text>
         <r>
           <rPr>
@@ -5489,7 +5484,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K8" authorId="1" shapeId="0">
+    <comment ref="K8" authorId="1">
       <text>
         <r>
           <rPr>
@@ -5502,7 +5497,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M8" authorId="1" shapeId="0">
+    <comment ref="M8" authorId="1">
       <text>
         <r>
           <rPr>
@@ -5515,7 +5510,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O8" authorId="1" shapeId="0">
+    <comment ref="O8" authorId="1">
       <text>
         <r>
           <rPr>
@@ -5528,7 +5523,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W8" authorId="1" shapeId="0">
+    <comment ref="W8" authorId="1">
       <text>
         <r>
           <rPr>
@@ -5541,7 +5536,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K9" authorId="1" shapeId="0">
+    <comment ref="K9" authorId="1">
       <text>
         <r>
           <rPr>
@@ -5563,7 +5558,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W9" authorId="1" shapeId="0">
+    <comment ref="W9" authorId="1">
       <text>
         <r>
           <rPr>
@@ -5576,7 +5571,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N10" authorId="1" shapeId="0">
+    <comment ref="N10" authorId="1">
       <text>
         <r>
           <rPr>
@@ -5598,7 +5593,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K11" authorId="0" shapeId="0">
+    <comment ref="K11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5619,7 +5614,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N11" authorId="0" shapeId="0">
+    <comment ref="N11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5639,7 +5634,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z11" authorId="0" shapeId="0">
+    <comment ref="Z11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5659,7 +5654,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J12" authorId="0" shapeId="0">
+    <comment ref="J12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5679,7 +5674,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q12" authorId="0" shapeId="0">
+    <comment ref="Q12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5700,7 +5695,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T12" authorId="0" shapeId="0">
+    <comment ref="T12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5720,7 +5715,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X12" authorId="0" shapeId="0">
+    <comment ref="X12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5741,7 +5736,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I13" authorId="0" shapeId="0">
+    <comment ref="I13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5761,7 +5756,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J13" authorId="0" shapeId="0">
+    <comment ref="J13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5781,7 +5776,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R13" authorId="0" shapeId="0">
+    <comment ref="R13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5801,7 +5796,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W13" authorId="0" shapeId="0">
+    <comment ref="W13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5822,7 +5817,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I15" authorId="0" shapeId="0">
+    <comment ref="I15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5843,7 +5838,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J15" authorId="0" shapeId="0">
+    <comment ref="J15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5864,7 +5859,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W15" authorId="0" shapeId="0">
+    <comment ref="W15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5884,7 +5879,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N16" authorId="0" shapeId="0">
+    <comment ref="N16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5904,7 +5899,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W16" authorId="0" shapeId="0">
+    <comment ref="W16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5924,7 +5919,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC16" authorId="0" shapeId="0">
+    <comment ref="AC16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5944,7 +5939,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M17" authorId="0" shapeId="0">
+    <comment ref="M17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5964,7 +5959,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N17" authorId="0" shapeId="0">
+    <comment ref="N17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5984,7 +5979,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q17" authorId="0" shapeId="0">
+    <comment ref="Q17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -6004,7 +5999,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I19" authorId="0" shapeId="0">
+    <comment ref="I19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -6025,7 +6020,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X19" authorId="0" shapeId="0">
+    <comment ref="X19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -6045,7 +6040,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I20" authorId="2" shapeId="0">
+    <comment ref="I20" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6069,7 +6064,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M20" authorId="2" shapeId="0">
+    <comment ref="M20" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6093,7 +6088,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W20" authorId="2" shapeId="0">
+    <comment ref="W20" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6117,7 +6112,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC20" authorId="0" shapeId="0">
+    <comment ref="AC20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -6137,7 +6132,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I21" authorId="2" shapeId="0">
+    <comment ref="I21" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6161,7 +6156,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J22" authorId="2" shapeId="0">
+    <comment ref="J22" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6185,7 +6180,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K22" authorId="2" shapeId="0">
+    <comment ref="K22" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6210,7 +6205,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V22" authorId="2" shapeId="0">
+    <comment ref="V22" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6235,7 +6230,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I23" authorId="2" shapeId="0">
+    <comment ref="I23" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6259,7 +6254,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W23" authorId="2" shapeId="0">
+    <comment ref="W23" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6283,7 +6278,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA23" authorId="2" shapeId="0">
+    <comment ref="AA23" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6307,7 +6302,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC23" authorId="2" shapeId="0">
+    <comment ref="AC23" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6331,7 +6326,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J24" authorId="2" shapeId="0">
+    <comment ref="J24" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6356,7 +6351,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M24" authorId="2" shapeId="0">
+    <comment ref="M24" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6380,7 +6375,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X24" authorId="2" shapeId="0">
+    <comment ref="X24" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6404,7 +6399,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA24" authorId="2" shapeId="0">
+    <comment ref="AA24" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6428,7 +6423,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J26" authorId="2" shapeId="0">
+    <comment ref="J26" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6452,7 +6447,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K26" authorId="2" shapeId="0">
+    <comment ref="K26" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6476,7 +6471,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N26" authorId="2" shapeId="0">
+    <comment ref="N26" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6500,7 +6495,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M27" authorId="2" shapeId="0">
+    <comment ref="M27" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6524,7 +6519,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T27" authorId="2" shapeId="0">
+    <comment ref="T27" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6549,7 +6544,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W27" authorId="2" shapeId="0">
+    <comment ref="W27" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6573,7 +6568,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC28" authorId="2" shapeId="0">
+    <comment ref="AC28" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6597,7 +6592,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W29" authorId="2" shapeId="0">
+    <comment ref="W29" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6621,7 +6616,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J30" authorId="2" shapeId="0">
+    <comment ref="J30" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6645,7 +6640,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N30" authorId="2" shapeId="0">
+    <comment ref="N30" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6669,7 +6664,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O31" authorId="2" shapeId="0">
+    <comment ref="O31" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6693,7 +6688,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P31" authorId="2" shapeId="0">
+    <comment ref="P31" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6718,7 +6713,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T31" authorId="2" shapeId="0">
+    <comment ref="T31" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6742,7 +6737,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W31" authorId="2" shapeId="0">
+    <comment ref="W31" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6767,7 +6762,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A32" authorId="2" shapeId="0">
+    <comment ref="A32" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6791,7 +6786,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I32" authorId="2" shapeId="0">
+    <comment ref="I32" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6815,7 +6810,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J32" authorId="2" shapeId="0">
+    <comment ref="J32" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6839,7 +6834,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K32" authorId="2" shapeId="0">
+    <comment ref="K32" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6863,7 +6858,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O32" authorId="2" shapeId="0">
+    <comment ref="O32" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6888,7 +6883,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W32" authorId="2" shapeId="0">
+    <comment ref="W32" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6912,7 +6907,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z32" authorId="2" shapeId="0">
+    <comment ref="Z32" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6936,7 +6931,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I33" authorId="2" shapeId="0">
+    <comment ref="I33" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6960,7 +6955,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N33" authorId="2" shapeId="0">
+    <comment ref="N33" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6985,7 +6980,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R33" authorId="2" shapeId="0">
+    <comment ref="R33" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7009,7 +7004,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U33" authorId="2" shapeId="0">
+    <comment ref="U33" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7034,7 +7029,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H34" authorId="2" shapeId="0">
+    <comment ref="H34" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7058,7 +7053,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I34" authorId="2" shapeId="0">
+    <comment ref="I34" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7082,7 +7077,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J34" authorId="2" shapeId="0">
+    <comment ref="J34" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7107,7 +7102,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R34" authorId="2" shapeId="0">
+    <comment ref="R34" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7131,7 +7126,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W34" authorId="2" shapeId="0">
+    <comment ref="W34" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7155,7 +7150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X34" authorId="2" shapeId="0">
+    <comment ref="X34" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7179,7 +7174,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z34" authorId="2" shapeId="0">
+    <comment ref="Z34" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7203,7 +7198,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC34" authorId="2" shapeId="0">
+    <comment ref="AC34" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7227,7 +7222,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I35" authorId="2" shapeId="0">
+    <comment ref="I35" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7251,7 +7246,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N35" authorId="2" shapeId="0">
+    <comment ref="N35" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7275,7 +7270,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X35" authorId="2" shapeId="0">
+    <comment ref="X35" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7299,7 +7294,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z35" authorId="2" shapeId="0">
+    <comment ref="Z35" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7323,7 +7318,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC35" authorId="2" shapeId="0">
+    <comment ref="AC35" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7355,9 +7350,10 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>SABEN_MUSIC</author>
+    <author>Собянин Евгений Андреевич (new)</author>
   </authors>
   <commentList>
-    <comment ref="A4" authorId="0" shapeId="0">
+    <comment ref="A4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -7383,7 +7379,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I4" authorId="0" shapeId="0">
+    <comment ref="I4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -7409,7 +7405,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N4" authorId="0" shapeId="0">
+    <comment ref="N4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -7435,7 +7431,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U4" authorId="0" shapeId="0">
+    <comment ref="U4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -7461,7 +7457,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W4" authorId="0" shapeId="0">
+    <comment ref="W4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -7489,7 +7485,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X4" authorId="0" shapeId="0">
+    <comment ref="X4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -7515,7 +7511,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I5" authorId="0" shapeId="0">
+    <comment ref="I5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -7542,7 +7538,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O5" authorId="0" shapeId="0">
+    <comment ref="O5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -7569,7 +7565,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P5" authorId="0" shapeId="0">
+    <comment ref="P5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -7595,7 +7591,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U5" authorId="0" shapeId="0">
+    <comment ref="U5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -7621,7 +7617,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W5" authorId="0" shapeId="0">
+    <comment ref="W5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -7650,7 +7646,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z5" authorId="0" shapeId="0">
+    <comment ref="Z5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -7676,7 +7672,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I6" authorId="0" shapeId="0">
+    <comment ref="I6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -7702,7 +7698,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q6" authorId="0" shapeId="0">
+    <comment ref="Q6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -7728,7 +7724,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X6" authorId="0" shapeId="0">
+    <comment ref="X6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -7754,7 +7750,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M7" authorId="0" shapeId="0">
+    <comment ref="M7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -7780,7 +7776,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC7" authorId="0" shapeId="0">
+    <comment ref="AC7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -7806,7 +7802,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X9" authorId="0" shapeId="0">
+    <comment ref="X9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -7833,7 +7829,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0">
+    <comment ref="E10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -7857,7 +7853,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W10" authorId="0" shapeId="0">
+    <comment ref="W10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -7881,7 +7877,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X10" authorId="0" shapeId="0">
+    <comment ref="X10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -7906,7 +7902,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y10" authorId="0" shapeId="0">
+    <comment ref="Y10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -7930,7 +7926,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC10" authorId="0" shapeId="0">
+    <comment ref="AC10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -7954,7 +7950,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N11" authorId="0" shapeId="0">
+    <comment ref="N11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -7978,7 +7974,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X11" authorId="0" shapeId="0">
+    <comment ref="X11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8002,7 +7998,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC11" authorId="0" shapeId="0">
+    <comment ref="AC11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8026,7 +8022,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N12" authorId="0" shapeId="0">
+    <comment ref="N12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8050,7 +8046,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W12" authorId="0" shapeId="0">
+    <comment ref="W12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8075,7 +8071,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X12" authorId="0" shapeId="0">
+    <comment ref="X12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8099,7 +8095,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X13" authorId="0" shapeId="0">
+    <comment ref="X13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8123,7 +8119,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y13" authorId="0" shapeId="0">
+    <comment ref="Y13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8147,7 +8143,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N14" authorId="0" shapeId="0">
+    <comment ref="N14" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8171,7 +8167,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H15" authorId="0" shapeId="0">
+    <comment ref="H15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8195,7 +8191,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N15" authorId="0" shapeId="0">
+    <comment ref="N15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8219,7 +8215,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W15" authorId="0" shapeId="0">
+    <comment ref="W15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8243,7 +8239,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X15" authorId="0" shapeId="0">
+    <comment ref="X15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8267,7 +8263,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H16" authorId="0" shapeId="0">
+    <comment ref="H16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8291,7 +8287,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X16" authorId="0" shapeId="0">
+    <comment ref="X16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8312,6 +8308,78 @@
           </rPr>
           <t xml:space="preserve">
 Фикс прайс</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X17" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Собянин Евгений Андреевич (new):</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Зарядный провод</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W18" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Собянин Евгений Андреевич (new):</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+На йогу + сплит за сережки и браслет</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W34" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Собянин Евгений Андреевич (new):</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Сплит за серьги и браслет</t>
         </r>
       </text>
     </comment>
@@ -8631,7 +8699,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#\ ##0.00\ &quot;₽&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
@@ -8999,7 +9067,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -9225,6 +9293,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -9704,7 +9778,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="239">
+  <cellXfs count="240">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10260,6 +10334,9 @@
     <xf numFmtId="0" fontId="24" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -10270,24 +10347,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -10311,6 +10370,21 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -10332,11 +10406,34 @@
     <xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="52" fillId="39" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF57B418"/>
@@ -10661,7 +10758,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="C4:H17"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -10694,7 +10791,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="3:8" ht="15.75">
+    <row r="5" spans="3:8" ht="16.5">
       <c r="C5" s="131" t="s">
         <v>6</v>
       </c>
@@ -10714,7 +10811,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="3:8" ht="15.75">
+    <row r="6" spans="3:8" ht="16.5">
       <c r="C6" s="131" t="s">
         <v>8</v>
       </c>
@@ -10735,7 +10832,7 @@
         <v>1260.56</v>
       </c>
     </row>
-    <row r="7" spans="3:8" ht="15.75">
+    <row r="7" spans="3:8" ht="16.5">
       <c r="C7" s="131" t="s">
         <v>9</v>
       </c>
@@ -10756,7 +10853,7 @@
         <v>-11931.3</v>
       </c>
     </row>
-    <row r="8" spans="3:8" ht="15.75">
+    <row r="8" spans="3:8" ht="16.5">
       <c r="C8" s="131" t="s">
         <v>10</v>
       </c>
@@ -10777,7 +10874,7 @@
         <v>59.0599999999977</v>
       </c>
     </row>
-    <row r="9" spans="3:8" ht="15.75">
+    <row r="9" spans="3:8" ht="16.5">
       <c r="C9" s="131" t="s">
         <v>11</v>
       </c>
@@ -10802,7 +10899,7 @@
         <v>-2729.0099999999902</v>
       </c>
     </row>
-    <row r="10" spans="3:8" ht="15.75">
+    <row r="10" spans="3:8" ht="16.5">
       <c r="C10" s="131" t="s">
         <v>12</v>
       </c>
@@ -10827,7 +10924,7 @@
         <v>22238.47</v>
       </c>
     </row>
-    <row r="11" spans="3:8" ht="15.75">
+    <row r="11" spans="3:8" ht="16.5">
       <c r="C11" s="131" t="s">
         <v>13</v>
       </c>
@@ -10852,7 +10949,7 @@
         <v>103369.95</v>
       </c>
     </row>
-    <row r="12" spans="3:8" ht="15.75">
+    <row r="12" spans="3:8" ht="16.5">
       <c r="C12" s="131" t="s">
         <v>14</v>
       </c>
@@ -10877,7 +10974,7 @@
         <v>-1058.5799999999899</v>
       </c>
     </row>
-    <row r="13" spans="3:8" ht="15.75">
+    <row r="13" spans="3:8" ht="16.5">
       <c r="C13" s="131" t="s">
         <v>15</v>
       </c>
@@ -10890,7 +10987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="3:8" ht="15.75">
+    <row r="14" spans="3:8" ht="16.5">
       <c r="C14" s="131" t="s">
         <v>16</v>
       </c>
@@ -10903,7 +11000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="3:8" ht="15.75">
+    <row r="15" spans="3:8" ht="16.5">
       <c r="C15" s="131" t="s">
         <v>17</v>
       </c>
@@ -10916,7 +11013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="3:8" ht="15.75">
+    <row r="16" spans="3:8" ht="16.5">
       <c r="C16" s="134" t="s">
         <v>18</v>
       </c>
@@ -10929,7 +11026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="3:8" ht="15.75">
+    <row r="17" spans="3:8" ht="16.5">
       <c r="C17" s="136" t="s">
         <v>19</v>
       </c>
@@ -10941,18 +11038,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H17">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>H17&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="10" priority="2">
       <formula>H17&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:H16">
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="9" priority="3">
       <formula>H5&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="8" priority="4">
       <formula>H5&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10962,7 +11059,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AZ41"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -10976,78 +11073,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="34.5" customHeight="1">
-      <c r="A1" s="225" t="s">
+      <c r="A1" s="220" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="225"/>
-      <c r="C1" s="225"/>
-      <c r="D1" s="225"/>
-      <c r="E1" s="225"/>
-      <c r="F1" s="225"/>
-      <c r="G1" s="225"/>
-      <c r="H1" s="225"/>
-      <c r="I1" s="225"/>
-      <c r="J1" s="225"/>
-      <c r="K1" s="225"/>
-      <c r="L1" s="225"/>
-      <c r="M1" s="225"/>
-      <c r="N1" s="225"/>
-      <c r="O1" s="225"/>
-      <c r="P1" s="225"/>
-      <c r="Q1" s="225"/>
-      <c r="R1" s="225"/>
-      <c r="S1" s="225"/>
-      <c r="T1" s="225"/>
-      <c r="U1" s="225"/>
-      <c r="V1" s="225"/>
-      <c r="W1" s="225"/>
-      <c r="X1" s="225"/>
-      <c r="Y1" s="225"/>
-      <c r="Z1" s="225"/>
-      <c r="AA1" s="225"/>
-      <c r="AB1" s="225"/>
-      <c r="AC1" s="225"/>
-      <c r="AD1" s="225"/>
+      <c r="B1" s="220"/>
+      <c r="C1" s="220"/>
+      <c r="D1" s="220"/>
+      <c r="E1" s="220"/>
+      <c r="F1" s="220"/>
+      <c r="G1" s="220"/>
+      <c r="H1" s="220"/>
+      <c r="I1" s="220"/>
+      <c r="J1" s="220"/>
+      <c r="K1" s="220"/>
+      <c r="L1" s="220"/>
+      <c r="M1" s="220"/>
+      <c r="N1" s="220"/>
+      <c r="O1" s="220"/>
+      <c r="P1" s="220"/>
+      <c r="Q1" s="220"/>
+      <c r="R1" s="220"/>
+      <c r="S1" s="220"/>
+      <c r="T1" s="220"/>
+      <c r="U1" s="220"/>
+      <c r="V1" s="220"/>
+      <c r="W1" s="220"/>
+      <c r="X1" s="220"/>
+      <c r="Y1" s="220"/>
+      <c r="Z1" s="220"/>
+      <c r="AA1" s="220"/>
+      <c r="AB1" s="220"/>
+      <c r="AC1" s="220"/>
+      <c r="AD1" s="220"/>
     </row>
     <row r="2" spans="1:52" ht="26.25">
-      <c r="A2" s="226"/>
-      <c r="B2" s="227"/>
-      <c r="C2" s="228" t="s">
+      <c r="A2" s="221"/>
+      <c r="B2" s="222"/>
+      <c r="C2" s="223" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="228"/>
-      <c r="E2" s="228"/>
-      <c r="F2" s="228"/>
-      <c r="G2" s="228"/>
-      <c r="H2" s="228"/>
-      <c r="I2" s="228"/>
-      <c r="J2" s="228"/>
-      <c r="K2" s="228"/>
-      <c r="L2" s="229" t="s">
+      <c r="D2" s="223"/>
+      <c r="E2" s="223"/>
+      <c r="F2" s="223"/>
+      <c r="G2" s="223"/>
+      <c r="H2" s="223"/>
+      <c r="I2" s="223"/>
+      <c r="J2" s="223"/>
+      <c r="K2" s="223"/>
+      <c r="L2" s="224" t="s">
         <v>68</v>
       </c>
-      <c r="M2" s="229"/>
-      <c r="N2" s="229"/>
-      <c r="O2" s="229"/>
-      <c r="P2" s="229"/>
-      <c r="Q2" s="229"/>
-      <c r="R2" s="230" t="s">
+      <c r="M2" s="224"/>
+      <c r="N2" s="224"/>
+      <c r="O2" s="224"/>
+      <c r="P2" s="224"/>
+      <c r="Q2" s="224"/>
+      <c r="R2" s="225" t="s">
         <v>69</v>
       </c>
-      <c r="S2" s="230"/>
-      <c r="T2" s="230"/>
-      <c r="U2" s="230"/>
-      <c r="V2" s="230"/>
-      <c r="W2" s="230"/>
-      <c r="X2" s="230"/>
-      <c r="Y2" s="230"/>
-      <c r="Z2" s="230"/>
-      <c r="AA2" s="230"/>
-      <c r="AB2" s="231" t="s">
+      <c r="S2" s="225"/>
+      <c r="T2" s="225"/>
+      <c r="U2" s="225"/>
+      <c r="V2" s="225"/>
+      <c r="W2" s="225"/>
+      <c r="X2" s="225"/>
+      <c r="Y2" s="225"/>
+      <c r="Z2" s="225"/>
+      <c r="AA2" s="225"/>
+      <c r="AB2" s="226" t="s">
         <v>70</v>
       </c>
-      <c r="AC2" s="231"/>
-      <c r="AD2" s="231"/>
+      <c r="AC2" s="226"/>
+      <c r="AD2" s="226"/>
     </row>
     <row r="3" spans="1:52" ht="45" customHeight="1" thickBot="1">
       <c r="A3" s="184" t="s">
@@ -11217,7 +11314,7 @@
       <c r="AC4" s="166">
         <v>142200.85999999999</v>
       </c>
-      <c r="AD4" s="223"/>
+      <c r="AD4" s="230"/>
     </row>
     <row r="5" spans="1:52" ht="15.75">
       <c r="A5" s="199">
@@ -11273,7 +11370,7 @@
         <v>47667</v>
       </c>
       <c r="AC5" s="168"/>
-      <c r="AD5" s="223"/>
+      <c r="AD5" s="230"/>
     </row>
     <row r="6" spans="1:52" ht="16.5" thickBot="1">
       <c r="A6" s="197">
@@ -11327,7 +11424,7 @@
         <v>9459</v>
       </c>
       <c r="AC6" s="168"/>
-      <c r="AD6" s="223"/>
+      <c r="AD6" s="230"/>
     </row>
     <row r="7" spans="1:52" ht="15.75">
       <c r="A7" s="189">
@@ -11380,7 +11477,7 @@
       <c r="AC7" s="168">
         <v>2000</v>
       </c>
-      <c r="AD7" s="223"/>
+      <c r="AD7" s="230"/>
     </row>
     <row r="8" spans="1:52" ht="15" customHeight="1">
       <c r="A8" s="11">
@@ -11422,7 +11519,7 @@
         <v>2946.51</v>
       </c>
       <c r="AC8" s="168"/>
-      <c r="AD8" s="223"/>
+      <c r="AD8" s="230"/>
     </row>
     <row r="9" spans="1:52" ht="15.75">
       <c r="A9" s="17">
@@ -11467,7 +11564,7 @@
         <v>1677.84</v>
       </c>
       <c r="AC9" s="168"/>
-      <c r="AD9" s="223"/>
+      <c r="AD9" s="230"/>
     </row>
     <row r="10" spans="1:52" ht="15.75">
       <c r="A10" s="11">
@@ -11533,7 +11630,7 @@
       <c r="AC10" s="168">
         <v>55867</v>
       </c>
-      <c r="AD10" s="223"/>
+      <c r="AD10" s="230"/>
     </row>
     <row r="11" spans="1:52" ht="15.75">
       <c r="A11" s="17">
@@ -11580,14 +11677,14 @@
       <c r="AC11" s="168">
         <v>3000</v>
       </c>
-      <c r="AD11" s="223"/>
-      <c r="AH11" s="224" t="s">
+      <c r="AD11" s="230"/>
+      <c r="AH11" s="231" t="s">
         <v>83</v>
       </c>
-      <c r="AI11" s="224"/>
-      <c r="AJ11" s="224"/>
-      <c r="AK11" s="224"/>
-      <c r="AL11" s="224"/>
+      <c r="AI11" s="231"/>
+      <c r="AJ11" s="231"/>
+      <c r="AK11" s="231"/>
+      <c r="AL11" s="231"/>
     </row>
     <row r="12" spans="1:52" ht="15.75">
       <c r="A12" s="11">
@@ -11636,12 +11733,12 @@
         <v>6686</v>
       </c>
       <c r="AC12" s="168"/>
-      <c r="AD12" s="223"/>
-      <c r="AH12" s="224"/>
-      <c r="AI12" s="224"/>
-      <c r="AJ12" s="224"/>
-      <c r="AK12" s="224"/>
-      <c r="AL12" s="224"/>
+      <c r="AD12" s="230"/>
+      <c r="AH12" s="231"/>
+      <c r="AI12" s="231"/>
+      <c r="AJ12" s="231"/>
+      <c r="AK12" s="231"/>
+      <c r="AL12" s="231"/>
     </row>
     <row r="13" spans="1:52" ht="15.75">
       <c r="A13" s="17">
@@ -11688,12 +11785,12 @@
         <v>3935</v>
       </c>
       <c r="AC13" s="168"/>
-      <c r="AD13" s="223"/>
-      <c r="AH13" s="224"/>
-      <c r="AI13" s="224"/>
-      <c r="AJ13" s="224"/>
-      <c r="AK13" s="224"/>
-      <c r="AL13" s="224"/>
+      <c r="AD13" s="230"/>
+      <c r="AH13" s="231"/>
+      <c r="AI13" s="231"/>
+      <c r="AJ13" s="231"/>
+      <c r="AK13" s="231"/>
+      <c r="AL13" s="231"/>
     </row>
     <row r="14" spans="1:52" ht="18">
       <c r="A14" s="11">
@@ -11734,13 +11831,13 @@
         <v>750</v>
       </c>
       <c r="AC14" s="168"/>
-      <c r="AD14" s="223"/>
-      <c r="AH14" s="220" t="s">
+      <c r="AD14" s="230"/>
+      <c r="AH14" s="227" t="s">
         <v>62</v>
       </c>
-      <c r="AI14" s="220"/>
-      <c r="AJ14" s="220"/>
-      <c r="AK14" s="220"/>
+      <c r="AI14" s="227"/>
+      <c r="AJ14" s="227"/>
+      <c r="AK14" s="227"/>
       <c r="AL14" s="22">
         <f>AC4+AC20+AC24+AC10</f>
         <v>198067.86</v>
@@ -11795,13 +11892,13 @@
         <v>10319</v>
       </c>
       <c r="AC15" s="166"/>
-      <c r="AD15" s="223"/>
-      <c r="AH15" s="220" t="s">
+      <c r="AD15" s="230"/>
+      <c r="AH15" s="227" t="s">
         <v>2</v>
       </c>
-      <c r="AI15" s="220"/>
-      <c r="AJ15" s="220"/>
-      <c r="AK15" s="220"/>
+      <c r="AI15" s="227"/>
+      <c r="AJ15" s="227"/>
+      <c r="AK15" s="227"/>
       <c r="AL15" s="22">
         <f>AC21</f>
         <v>0</v>
@@ -11856,13 +11953,13 @@
         <v>7901.26</v>
       </c>
       <c r="AC16" s="166"/>
-      <c r="AD16" s="223"/>
-      <c r="AH16" s="220" t="s">
+      <c r="AD16" s="230"/>
+      <c r="AH16" s="227" t="s">
         <v>63</v>
       </c>
-      <c r="AI16" s="220"/>
-      <c r="AJ16" s="220"/>
-      <c r="AK16" s="220"/>
+      <c r="AI16" s="227"/>
+      <c r="AJ16" s="227"/>
+      <c r="AK16" s="227"/>
       <c r="AL16" s="22" t="e">
         <f>AC16+AC29+AC35+#REF!</f>
         <v>#REF!</v>
@@ -11875,8 +11972,13 @@
       <c r="B17" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="178"/>
-      <c r="D17" s="178"/>
+      <c r="C17" s="178">
+        <v>267.94</v>
+      </c>
+      <c r="D17" s="178">
+        <f>215.78+383.95</f>
+        <v>599.73</v>
+      </c>
       <c r="E17" s="178"/>
       <c r="F17" s="178"/>
       <c r="G17" s="178"/>
@@ -11896,16 +11998,18 @@
       <c r="U17" s="178"/>
       <c r="V17" s="178"/>
       <c r="W17" s="178"/>
-      <c r="X17" s="178"/>
+      <c r="X17" s="178">
+        <v>899</v>
+      </c>
       <c r="Y17" s="178"/>
       <c r="Z17" s="178"/>
       <c r="AA17" s="179"/>
       <c r="AB17" s="15">
         <f>SUM(C17:AA17)</f>
-        <v>0</v>
+        <v>1766.67</v>
       </c>
       <c r="AC17" s="166"/>
-      <c r="AD17" s="223"/>
+      <c r="AD17" s="230"/>
       <c r="AH17" s="232" t="s">
         <v>67</v>
       </c>
@@ -11914,7 +12018,7 @@
       <c r="AK17" s="234"/>
       <c r="AL17" s="22">
         <f>SUM(C37:K37)</f>
-        <v>44045.09</v>
+        <v>58912.759999999995</v>
       </c>
     </row>
     <row r="18" spans="1:38" ht="18">
@@ -11944,17 +12048,20 @@
       <c r="T18" s="176"/>
       <c r="U18" s="176"/>
       <c r="V18" s="176"/>
-      <c r="W18" s="176"/>
+      <c r="W18" s="176">
+        <f>8000+11525</f>
+        <v>19525</v>
+      </c>
       <c r="X18" s="176"/>
       <c r="Y18" s="176"/>
       <c r="Z18" s="176"/>
       <c r="AA18" s="177"/>
       <c r="AB18" s="15">
         <f>SUM(C18:AA18)</f>
-        <v>0</v>
+        <v>19525</v>
       </c>
       <c r="AC18" s="166"/>
-      <c r="AD18" s="223"/>
+      <c r="AD18" s="230"/>
       <c r="AH18" s="139"/>
       <c r="AI18" s="140"/>
       <c r="AJ18" s="140"/>
@@ -11968,11 +12075,11 @@
       <c r="B19" s="238"/>
       <c r="C19" s="23">
         <f>SUM(C4:C18)</f>
-        <v>2624.79</v>
+        <v>2892.73</v>
       </c>
       <c r="D19" s="23">
         <f t="shared" ref="D19:K19" si="1">SUM(D4:D18)</f>
-        <v>1883.79</v>
+        <v>2483.52</v>
       </c>
       <c r="E19" s="23">
         <f t="shared" si="1"/>
@@ -12048,11 +12155,11 @@
       </c>
       <c r="W19" s="25">
         <f t="shared" si="3"/>
-        <v>29624</v>
+        <v>49149</v>
       </c>
       <c r="X19" s="25">
         <f t="shared" si="3"/>
-        <v>50764.5</v>
+        <v>51663.5</v>
       </c>
       <c r="Y19" s="25">
         <f t="shared" si="3"/>
@@ -12068,7 +12175,7 @@
       </c>
       <c r="AB19" s="26">
         <f>SUM(AB4:AB18)</f>
-        <v>157057.46000000002</v>
+        <v>178349.13000000003</v>
       </c>
       <c r="AC19" s="27">
         <f t="shared" ref="AC19" si="4">SUM(AC4:AC17)</f>
@@ -12076,14 +12183,14 @@
       </c>
       <c r="AD19" s="167">
         <f>AC19-AB19</f>
-        <v>46010.399999999965</v>
-      </c>
-      <c r="AH19" s="220" t="s">
+        <v>24718.729999999952</v>
+      </c>
+      <c r="AH19" s="227" t="s">
         <v>84</v>
       </c>
-      <c r="AI19" s="220"/>
-      <c r="AJ19" s="220"/>
-      <c r="AK19" s="220"/>
+      <c r="AI19" s="227"/>
+      <c r="AJ19" s="227"/>
+      <c r="AK19" s="227"/>
       <c r="AL19" s="22">
         <f>SUM(L37:Q37)</f>
         <v>21802</v>
@@ -12125,17 +12232,19 @@
         <f>SUM(C20:AA20)</f>
         <v>0</v>
       </c>
-      <c r="AC20" s="16"/>
-      <c r="AD20" s="223"/>
-      <c r="AH20" s="220" t="s">
+      <c r="AC20" s="16">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="230"/>
+      <c r="AH20" s="227" t="s">
         <v>85</v>
       </c>
-      <c r="AI20" s="220"/>
-      <c r="AJ20" s="220"/>
-      <c r="AK20" s="220"/>
+      <c r="AI20" s="227"/>
+      <c r="AJ20" s="227"/>
+      <c r="AK20" s="227"/>
       <c r="AL20" s="22">
         <f>W37</f>
-        <v>29624</v>
+        <v>60674</v>
       </c>
     </row>
     <row r="21" spans="1:38" ht="18">
@@ -12148,7 +12257,9 @@
       <c r="C21" s="178"/>
       <c r="D21" s="178"/>
       <c r="E21" s="178"/>
-      <c r="F21" s="178"/>
+      <c r="F21" s="239">
+        <v>3500</v>
+      </c>
       <c r="G21" s="178"/>
       <c r="H21" s="178"/>
       <c r="I21" s="178"/>
@@ -12172,17 +12283,17 @@
       <c r="AA21" s="179"/>
       <c r="AB21" s="15">
         <f>SUM(C21:AA21)</f>
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="AC21" s="21"/>
-      <c r="AD21" s="223"/>
+      <c r="AD21" s="230"/>
       <c r="AF21" s="29"/>
-      <c r="AH21" s="220" t="s">
+      <c r="AH21" s="227" t="s">
         <v>86</v>
       </c>
-      <c r="AI21" s="220"/>
-      <c r="AJ21" s="220"/>
-      <c r="AK21" s="220"/>
+      <c r="AI21" s="227"/>
+      <c r="AJ21" s="227"/>
+      <c r="AK21" s="227"/>
       <c r="AL21" s="22">
         <f>SUM(U37:V37)</f>
         <v>5082.03</v>
@@ -12225,7 +12336,7 @@
         <v>0</v>
       </c>
       <c r="AC22" s="21"/>
-      <c r="AD22" s="223"/>
+      <c r="AD22" s="230"/>
       <c r="AH22" s="235" t="s">
         <v>32</v>
       </c>
@@ -12274,7 +12385,7 @@
         <v>0</v>
       </c>
       <c r="AC23" s="21"/>
-      <c r="AD23" s="223"/>
+      <c r="AD23" s="230"/>
       <c r="AH23" s="236"/>
       <c r="AI23" s="236"/>
       <c r="AJ23" s="236"/>
@@ -12318,7 +12429,7 @@
         <v>0</v>
       </c>
       <c r="AC24" s="21"/>
-      <c r="AD24" s="223"/>
+      <c r="AD24" s="230"/>
     </row>
     <row r="25" spans="1:38" ht="15.75">
       <c r="A25" s="17">
@@ -12330,7 +12441,9 @@
       <c r="C25" s="178"/>
       <c r="D25" s="178"/>
       <c r="E25" s="178"/>
-      <c r="F25" s="178"/>
+      <c r="F25" s="239">
+        <v>3500</v>
+      </c>
       <c r="G25" s="178"/>
       <c r="H25" s="178"/>
       <c r="I25" s="178"/>
@@ -12354,10 +12467,10 @@
       <c r="AA25" s="179"/>
       <c r="AB25" s="15">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="AC25" s="21"/>
-      <c r="AD25" s="223"/>
+      <c r="AD25" s="230"/>
     </row>
     <row r="26" spans="1:38" ht="15.75">
       <c r="A26" s="11">
@@ -12396,7 +12509,7 @@
         <v>0</v>
       </c>
       <c r="AC26" s="16"/>
-      <c r="AD26" s="223"/>
+      <c r="AD26" s="230"/>
     </row>
     <row r="27" spans="1:38" ht="15.75">
       <c r="A27" s="17">
@@ -12435,7 +12548,7 @@
         <v>0</v>
       </c>
       <c r="AC27" s="21"/>
-      <c r="AD27" s="223"/>
+      <c r="AD27" s="230"/>
     </row>
     <row r="28" spans="1:38" ht="15.75">
       <c r="A28" s="11">
@@ -12474,7 +12587,7 @@
         <v>0</v>
       </c>
       <c r="AC28" s="21"/>
-      <c r="AD28" s="223"/>
+      <c r="AD28" s="230"/>
     </row>
     <row r="29" spans="1:38" ht="15.75">
       <c r="A29" s="17">
@@ -12486,7 +12599,9 @@
       <c r="C29" s="178"/>
       <c r="D29" s="178"/>
       <c r="E29" s="178"/>
-      <c r="F29" s="178"/>
+      <c r="F29" s="239">
+        <v>3500</v>
+      </c>
       <c r="G29" s="178"/>
       <c r="H29" s="178"/>
       <c r="I29" s="178"/>
@@ -12510,10 +12625,10 @@
       <c r="AA29" s="179"/>
       <c r="AB29" s="15">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="AC29" s="21"/>
-      <c r="AD29" s="223"/>
+      <c r="AD29" s="230"/>
     </row>
     <row r="30" spans="1:38" ht="15.75">
       <c r="A30" s="11">
@@ -12552,7 +12667,7 @@
         <v>0</v>
       </c>
       <c r="AC30" s="21"/>
-      <c r="AD30" s="223"/>
+      <c r="AD30" s="230"/>
     </row>
     <row r="31" spans="1:38" ht="15.75">
       <c r="A31" s="17">
@@ -12591,7 +12706,7 @@
         <v>0</v>
       </c>
       <c r="AC31" s="21"/>
-      <c r="AD31" s="223"/>
+      <c r="AD31" s="230"/>
     </row>
     <row r="32" spans="1:38" ht="15.75">
       <c r="A32" s="11">
@@ -12630,7 +12745,7 @@
         <v>0</v>
       </c>
       <c r="AC32" s="21"/>
-      <c r="AD32" s="223"/>
+      <c r="AD32" s="230"/>
     </row>
     <row r="33" spans="1:34" ht="15.75">
       <c r="A33" s="17">
@@ -12642,7 +12757,9 @@
       <c r="C33" s="182"/>
       <c r="D33" s="182"/>
       <c r="E33" s="182"/>
-      <c r="F33" s="182"/>
+      <c r="F33" s="239">
+        <v>3500</v>
+      </c>
       <c r="G33" s="182"/>
       <c r="H33" s="182"/>
       <c r="I33" s="182"/>
@@ -12666,10 +12783,10 @@
       <c r="AA33" s="182"/>
       <c r="AB33" s="174">
         <f t="shared" ref="AB33:AB35" si="6">SUM(C33:AA33)</f>
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="AC33" s="21"/>
-      <c r="AD33" s="223"/>
+      <c r="AD33" s="230"/>
     </row>
     <row r="34" spans="1:34" ht="15.75">
       <c r="A34" s="11">
@@ -12698,17 +12815,19 @@
       <c r="T34" s="183"/>
       <c r="U34" s="183"/>
       <c r="V34" s="183"/>
-      <c r="W34" s="183"/>
+      <c r="W34" s="239">
+        <v>11525</v>
+      </c>
       <c r="X34" s="183"/>
       <c r="Y34" s="183"/>
       <c r="Z34" s="183"/>
       <c r="AA34" s="183"/>
       <c r="AB34" s="174">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>11525</v>
       </c>
       <c r="AC34" s="21"/>
-      <c r="AD34" s="223"/>
+      <c r="AD34" s="230"/>
     </row>
     <row r="35" spans="1:34" ht="15.75">
       <c r="A35" s="17">
@@ -12747,7 +12866,7 @@
         <v>0</v>
       </c>
       <c r="AC35" s="21"/>
-      <c r="AD35" s="223"/>
+      <c r="AD35" s="230"/>
     </row>
     <row r="36" spans="1:34" ht="24" customHeight="1">
       <c r="A36" s="237" t="s">
@@ -12768,7 +12887,7 @@
       </c>
       <c r="F36" s="146">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="G36" s="146">
         <f t="shared" si="7"/>
@@ -12836,7 +12955,7 @@
       </c>
       <c r="W36" s="148">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>11525</v>
       </c>
       <c r="X36" s="148">
         <f t="shared" si="7"/>
@@ -12856,7 +12975,7 @@
       </c>
       <c r="AB36" s="26">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>25525</v>
       </c>
       <c r="AC36" s="27">
         <f t="shared" si="7"/>
@@ -12864,22 +12983,22 @@
       </c>
       <c r="AD36" s="28">
         <f>AC36-AB36</f>
-        <v>0</v>
+        <v>-25525</v>
       </c>
       <c r="AH36" s="165"/>
     </row>
     <row r="37" spans="1:34" ht="31.5" customHeight="1">
-      <c r="A37" s="222" t="s">
+      <c r="A37" s="229" t="s">
         <v>56</v>
       </c>
-      <c r="B37" s="222"/>
+      <c r="B37" s="229"/>
       <c r="C37" s="31">
         <f t="shared" ref="C37:R37" si="8">SUM(C19,C36)</f>
-        <v>2624.79</v>
+        <v>2892.73</v>
       </c>
       <c r="D37" s="31">
         <f t="shared" si="8"/>
-        <v>1883.79</v>
+        <v>2483.52</v>
       </c>
       <c r="E37" s="31">
         <f t="shared" si="8"/>
@@ -12887,7 +13006,7 @@
       </c>
       <c r="F37" s="31">
         <f t="shared" si="8"/>
-        <v>8254.85</v>
+        <v>22254.85</v>
       </c>
       <c r="G37" s="31">
         <f t="shared" si="8"/>
@@ -12952,11 +13071,11 @@
       </c>
       <c r="W37" s="31">
         <f t="shared" si="9"/>
-        <v>29624</v>
+        <v>60674</v>
       </c>
       <c r="X37" s="31">
         <f t="shared" si="9"/>
-        <v>50764.5</v>
+        <v>51663.5</v>
       </c>
       <c r="Y37" s="31">
         <f t="shared" si="9"/>
@@ -12972,7 +13091,7 @@
       </c>
       <c r="AB37" s="33">
         <f t="shared" si="9"/>
-        <v>157057.46000000002</v>
+        <v>203874.13000000003</v>
       </c>
       <c r="AC37" s="34">
         <f t="shared" si="9"/>
@@ -12980,7 +13099,7 @@
       </c>
       <c r="AD37" s="169">
         <f t="shared" si="9"/>
-        <v>46010.399999999965</v>
+        <v>-806.27000000004773</v>
       </c>
     </row>
     <row r="41" spans="1:34">
@@ -13003,6 +13122,12 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="AD4:AD18"/>
@@ -13018,13 +13143,15 @@
     <mergeCell ref="AH15:AK15"/>
     <mergeCell ref="AH16:AK16"/>
     <mergeCell ref="AH17:AK17"/>
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:K2"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
   </mergeCells>
+  <conditionalFormatting sqref="AD37">
+    <cfRule type="expression" dxfId="3" priority="2">
+      <formula>$AD$37&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>$AD$37&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -13032,7 +13159,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AT35"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -14382,7 +14509,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AT36"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -15744,7 +15871,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AU41"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -17542,7 +17669,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AU40"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -19259,10 +19386,10 @@
     <mergeCell ref="A36:B36"/>
   </mergeCells>
   <conditionalFormatting sqref="Y18:Y36">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>Y18&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>Y18&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19273,7 +19400,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AU40"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -20914,10 +21041,10 @@
     <mergeCell ref="A36:B36"/>
   </mergeCells>
   <conditionalFormatting sqref="Y18:Y36">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>Y18&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>Y18&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20928,7 +21055,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AV42"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -20940,34 +21067,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="60.75" customHeight="1">
-      <c r="A1" s="219" t="s">
+      <c r="A1" s="215" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="219"/>
-      <c r="C1" s="219"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
-      <c r="F1" s="219"/>
-      <c r="G1" s="219"/>
-      <c r="H1" s="219"/>
-      <c r="I1" s="219"/>
-      <c r="J1" s="219"/>
-      <c r="K1" s="219"/>
-      <c r="L1" s="219"/>
-      <c r="M1" s="219"/>
-      <c r="N1" s="219"/>
-      <c r="O1" s="219"/>
-      <c r="P1" s="219"/>
-      <c r="Q1" s="219"/>
-      <c r="R1" s="219"/>
-      <c r="S1" s="219"/>
-      <c r="T1" s="219"/>
-      <c r="U1" s="219"/>
-      <c r="V1" s="219"/>
-      <c r="W1" s="219"/>
-      <c r="X1" s="219"/>
-      <c r="Y1" s="219"/>
-      <c r="Z1" s="219"/>
+      <c r="B1" s="215"/>
+      <c r="C1" s="215"/>
+      <c r="D1" s="215"/>
+      <c r="E1" s="215"/>
+      <c r="F1" s="215"/>
+      <c r="G1" s="215"/>
+      <c r="H1" s="215"/>
+      <c r="I1" s="215"/>
+      <c r="J1" s="215"/>
+      <c r="K1" s="215"/>
+      <c r="L1" s="215"/>
+      <c r="M1" s="215"/>
+      <c r="N1" s="215"/>
+      <c r="O1" s="215"/>
+      <c r="P1" s="215"/>
+      <c r="Q1" s="215"/>
+      <c r="R1" s="215"/>
+      <c r="S1" s="215"/>
+      <c r="T1" s="215"/>
+      <c r="U1" s="215"/>
+      <c r="V1" s="215"/>
+      <c r="W1" s="215"/>
+      <c r="X1" s="215"/>
+      <c r="Y1" s="215"/>
+      <c r="Z1" s="215"/>
     </row>
     <row r="2" spans="1:48" ht="45" customHeight="1">
       <c r="A2" s="38" t="s">
@@ -21120,7 +21247,7 @@
         <f>(94085+57723.67)</f>
         <v>151808.67000000001</v>
       </c>
-      <c r="Z3" s="217"/>
+      <c r="Z3" s="218"/>
     </row>
     <row r="4" spans="1:48" ht="15.75">
       <c r="A4" s="52">
@@ -21170,7 +21297,7 @@
       </c>
       <c r="X4" s="50"/>
       <c r="Y4" s="56"/>
-      <c r="Z4" s="217"/>
+      <c r="Z4" s="218"/>
     </row>
     <row r="5" spans="1:48" ht="15.75">
       <c r="A5" s="45">
@@ -21210,7 +21337,7 @@
       </c>
       <c r="X5" s="50"/>
       <c r="Y5" s="56"/>
-      <c r="Z5" s="217"/>
+      <c r="Z5" s="218"/>
     </row>
     <row r="6" spans="1:48" ht="15.75">
       <c r="A6" s="52">
@@ -21251,7 +21378,7 @@
       </c>
       <c r="X6" s="50"/>
       <c r="Y6" s="56"/>
-      <c r="Z6" s="217"/>
+      <c r="Z6" s="218"/>
     </row>
     <row r="7" spans="1:48" ht="15" customHeight="1">
       <c r="A7" s="45">
@@ -21295,7 +21422,7 @@
       </c>
       <c r="X7" s="50"/>
       <c r="Y7" s="56"/>
-      <c r="Z7" s="217"/>
+      <c r="Z7" s="218"/>
     </row>
     <row r="8" spans="1:48" ht="15.75">
       <c r="A8" s="52">
@@ -21337,14 +21464,14 @@
       </c>
       <c r="X8" s="50"/>
       <c r="Y8" s="56"/>
-      <c r="Z8" s="217"/>
-      <c r="AC8" s="218" t="s">
+      <c r="Z8" s="218"/>
+      <c r="AC8" s="219" t="s">
         <v>61</v>
       </c>
-      <c r="AD8" s="218"/>
-      <c r="AE8" s="218"/>
-      <c r="AF8" s="218"/>
-      <c r="AG8" s="218"/>
+      <c r="AD8" s="219"/>
+      <c r="AE8" s="219"/>
+      <c r="AF8" s="219"/>
+      <c r="AG8" s="219"/>
     </row>
     <row r="9" spans="1:48" ht="15.75">
       <c r="A9" s="45">
@@ -21383,12 +21510,12 @@
       </c>
       <c r="X9" s="50"/>
       <c r="Y9" s="56"/>
-      <c r="Z9" s="217"/>
-      <c r="AC9" s="218"/>
-      <c r="AD9" s="218"/>
-      <c r="AE9" s="218"/>
-      <c r="AF9" s="218"/>
-      <c r="AG9" s="218"/>
+      <c r="Z9" s="218"/>
+      <c r="AC9" s="219"/>
+      <c r="AD9" s="219"/>
+      <c r="AE9" s="219"/>
+      <c r="AF9" s="219"/>
+      <c r="AG9" s="219"/>
     </row>
     <row r="10" spans="1:48" ht="15.75">
       <c r="A10" s="52">
@@ -21432,12 +21559,12 @@
       </c>
       <c r="X10" s="50"/>
       <c r="Y10" s="56"/>
-      <c r="Z10" s="217"/>
-      <c r="AC10" s="218"/>
-      <c r="AD10" s="218"/>
-      <c r="AE10" s="218"/>
-      <c r="AF10" s="218"/>
-      <c r="AG10" s="218"/>
+      <c r="Z10" s="218"/>
+      <c r="AC10" s="219"/>
+      <c r="AD10" s="219"/>
+      <c r="AE10" s="219"/>
+      <c r="AF10" s="219"/>
+      <c r="AG10" s="219"/>
     </row>
     <row r="11" spans="1:48" ht="15.75">
       <c r="A11" s="45">
@@ -21477,13 +21604,13 @@
       </c>
       <c r="X11" s="50"/>
       <c r="Y11" s="56"/>
-      <c r="Z11" s="217"/>
-      <c r="AC11" s="215" t="s">
+      <c r="Z11" s="218"/>
+      <c r="AC11" s="216" t="s">
         <v>62</v>
       </c>
-      <c r="AD11" s="215"/>
-      <c r="AE11" s="215"/>
-      <c r="AF11" s="215"/>
+      <c r="AD11" s="216"/>
+      <c r="AE11" s="216"/>
+      <c r="AF11" s="216"/>
       <c r="AG11" s="57">
         <f>Y3+Y14+Y21</f>
         <v>226341.31</v>
@@ -21524,13 +21651,13 @@
       </c>
       <c r="X12" s="50"/>
       <c r="Y12" s="56"/>
-      <c r="Z12" s="217"/>
-      <c r="AC12" s="215" t="s">
+      <c r="Z12" s="218"/>
+      <c r="AC12" s="216" t="s">
         <v>2</v>
       </c>
-      <c r="AD12" s="215"/>
-      <c r="AE12" s="215"/>
-      <c r="AF12" s="215"/>
+      <c r="AD12" s="216"/>
+      <c r="AE12" s="216"/>
+      <c r="AF12" s="216"/>
       <c r="AG12" s="57">
         <f>Y27</f>
         <v>20000</v>
@@ -21575,13 +21702,13 @@
       </c>
       <c r="X13" s="50"/>
       <c r="Y13" s="56"/>
-      <c r="Z13" s="217"/>
-      <c r="AC13" s="215" t="s">
+      <c r="Z13" s="218"/>
+      <c r="AC13" s="216" t="s">
         <v>63</v>
       </c>
-      <c r="AD13" s="215"/>
-      <c r="AE13" s="215"/>
-      <c r="AF13" s="215"/>
+      <c r="AD13" s="216"/>
+      <c r="AE13" s="216"/>
+      <c r="AF13" s="216"/>
       <c r="AG13" s="57">
         <f>Y17+Y19</f>
         <v>25000</v>
@@ -21627,13 +21754,13 @@
       <c r="Y14" s="51">
         <v>37634</v>
       </c>
-      <c r="Z14" s="217"/>
-      <c r="AC14" s="215" t="s">
+      <c r="Z14" s="218"/>
+      <c r="AC14" s="216" t="s">
         <v>64</v>
       </c>
-      <c r="AD14" s="215"/>
-      <c r="AE14" s="215"/>
-      <c r="AF14" s="215"/>
+      <c r="AD14" s="216"/>
+      <c r="AE14" s="216"/>
+      <c r="AF14" s="216"/>
       <c r="AG14" s="57">
         <f>W38</f>
         <v>177971.36</v>
@@ -21683,13 +21810,13 @@
       </c>
       <c r="X15" s="50"/>
       <c r="Y15" s="56"/>
-      <c r="Z15" s="217"/>
-      <c r="AC15" s="215" t="s">
+      <c r="Z15" s="218"/>
+      <c r="AC15" s="216" t="s">
         <v>65</v>
       </c>
-      <c r="AD15" s="215"/>
-      <c r="AE15" s="215"/>
-      <c r="AF15" s="215"/>
+      <c r="AD15" s="216"/>
+      <c r="AE15" s="216"/>
+      <c r="AF15" s="216"/>
       <c r="AG15" s="57">
         <f>SUM(C38:H38)</f>
         <v>55416.04</v>
@@ -21738,13 +21865,13 @@
       </c>
       <c r="X16" s="50"/>
       <c r="Y16" s="56"/>
-      <c r="Z16" s="217"/>
-      <c r="AC16" s="215" t="s">
+      <c r="Z16" s="218"/>
+      <c r="AC16" s="216" t="s">
         <v>85</v>
       </c>
-      <c r="AD16" s="215"/>
-      <c r="AE16" s="215"/>
-      <c r="AF16" s="215"/>
+      <c r="AD16" s="216"/>
+      <c r="AE16" s="216"/>
+      <c r="AF16" s="216"/>
       <c r="AG16" s="57">
         <f>Q38</f>
         <v>27468.98</v>
@@ -21800,7 +21927,7 @@
       <c r="Y17" s="59">
         <v>15000</v>
       </c>
-      <c r="Z17" s="217"/>
+      <c r="Z17" s="218"/>
     </row>
     <row r="18" spans="1:28" ht="15.75">
       <c r="A18" s="52">
@@ -21841,7 +21968,7 @@
       </c>
       <c r="X18" s="50"/>
       <c r="Y18" s="56"/>
-      <c r="Z18" s="217"/>
+      <c r="Z18" s="218"/>
     </row>
     <row r="19" spans="1:28" ht="15.75">
       <c r="A19" s="45">
@@ -21885,7 +22012,7 @@
       <c r="Y19" s="59">
         <v>10000</v>
       </c>
-      <c r="Z19" s="217"/>
+      <c r="Z19" s="218"/>
     </row>
     <row r="20" spans="1:28" ht="14.25" customHeight="1">
       <c r="A20" s="213" t="s">
@@ -22034,7 +22161,7 @@
       <c r="Y21" s="51">
         <v>36898.639999999999</v>
       </c>
-      <c r="Z21" s="217"/>
+      <c r="Z21" s="218"/>
     </row>
     <row r="22" spans="1:28" ht="15.75">
       <c r="A22" s="52">
@@ -22080,7 +22207,7 @@
         <v>23662.84</v>
       </c>
       <c r="Y22" s="56"/>
-      <c r="Z22" s="217"/>
+      <c r="Z22" s="218"/>
       <c r="AB22" s="29"/>
     </row>
     <row r="23" spans="1:28" ht="15.75">
@@ -22124,7 +22251,7 @@
       </c>
       <c r="X23" s="50"/>
       <c r="Y23" s="56"/>
-      <c r="Z23" s="217"/>
+      <c r="Z23" s="218"/>
     </row>
     <row r="24" spans="1:28" ht="15.75">
       <c r="A24" s="52">
@@ -22168,7 +22295,7 @@
       </c>
       <c r="X24" s="50"/>
       <c r="Y24" s="56"/>
-      <c r="Z24" s="217"/>
+      <c r="Z24" s="218"/>
     </row>
     <row r="25" spans="1:28" ht="15.75">
       <c r="A25" s="45">
@@ -22212,7 +22339,7 @@
       </c>
       <c r="X25" s="50"/>
       <c r="Y25" s="56"/>
-      <c r="Z25" s="217"/>
+      <c r="Z25" s="218"/>
     </row>
     <row r="26" spans="1:28" ht="15.75">
       <c r="A26" s="52">
@@ -22251,7 +22378,7 @@
       </c>
       <c r="X26" s="50"/>
       <c r="Y26" s="56"/>
-      <c r="Z26" s="217"/>
+      <c r="Z26" s="218"/>
     </row>
     <row r="27" spans="1:28" ht="15.75">
       <c r="A27" s="45">
@@ -22296,7 +22423,7 @@
       <c r="Y27" s="66">
         <v>20000</v>
       </c>
-      <c r="Z27" s="217"/>
+      <c r="Z27" s="218"/>
     </row>
     <row r="28" spans="1:28" ht="15.75">
       <c r="A28" s="52">
@@ -22338,7 +22465,7 @@
       </c>
       <c r="X28" s="50"/>
       <c r="Y28" s="56"/>
-      <c r="Z28" s="217"/>
+      <c r="Z28" s="218"/>
     </row>
     <row r="29" spans="1:28" ht="15.75">
       <c r="A29" s="45">
@@ -22377,7 +22504,7 @@
       </c>
       <c r="X29" s="50"/>
       <c r="Y29" s="56"/>
-      <c r="Z29" s="217"/>
+      <c r="Z29" s="218"/>
     </row>
     <row r="30" spans="1:28" ht="15.75">
       <c r="A30" s="52">
@@ -22417,7 +22544,7 @@
       </c>
       <c r="X30" s="50"/>
       <c r="Y30" s="56"/>
-      <c r="Z30" s="217"/>
+      <c r="Z30" s="218"/>
     </row>
     <row r="31" spans="1:28" ht="15.75">
       <c r="A31" s="45">
@@ -22452,7 +22579,7 @@
       </c>
       <c r="X31" s="50"/>
       <c r="Y31" s="56"/>
-      <c r="Z31" s="217"/>
+      <c r="Z31" s="218"/>
     </row>
     <row r="32" spans="1:28" ht="15.75">
       <c r="A32" s="52">
@@ -22487,7 +22614,7 @@
       </c>
       <c r="X32" s="50"/>
       <c r="Y32" s="56"/>
-      <c r="Z32" s="217"/>
+      <c r="Z32" s="218"/>
     </row>
     <row r="33" spans="1:26" ht="15.75">
       <c r="A33" s="45">
@@ -22524,7 +22651,7 @@
       <c r="Y33" s="67">
         <v>10000</v>
       </c>
-      <c r="Z33" s="217"/>
+      <c r="Z33" s="218"/>
     </row>
     <row r="34" spans="1:26" ht="15.75">
       <c r="A34" s="52">
@@ -22563,7 +22690,7 @@
       </c>
       <c r="X34" s="50"/>
       <c r="Y34" s="56"/>
-      <c r="Z34" s="217"/>
+      <c r="Z34" s="218"/>
     </row>
     <row r="35" spans="1:26" ht="15.75">
       <c r="A35" s="45">
@@ -22607,7 +22734,7 @@
       </c>
       <c r="X35" s="50"/>
       <c r="Y35" s="56"/>
-      <c r="Z35" s="217"/>
+      <c r="Z35" s="218"/>
     </row>
     <row r="36" spans="1:26" ht="15.75">
       <c r="A36" s="52">
@@ -22648,7 +22775,7 @@
       </c>
       <c r="X36" s="50"/>
       <c r="Y36" s="56"/>
-      <c r="Z36" s="217"/>
+      <c r="Z36" s="218"/>
     </row>
     <row r="37" spans="1:26">
       <c r="A37" s="213" t="s">
@@ -22753,10 +22880,10 @@
       </c>
     </row>
     <row r="38" spans="1:26" ht="31.5" customHeight="1">
-      <c r="A38" s="216" t="s">
+      <c r="A38" s="217" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="216"/>
+      <c r="B38" s="217"/>
       <c r="C38" s="69">
         <f>SUM(C20,C37)</f>
         <v>14335.99</v>
@@ -22868,11 +22995,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:Z1"/>
-    <mergeCell ref="AC11:AF11"/>
-    <mergeCell ref="AC12:AF12"/>
-    <mergeCell ref="AC13:AF13"/>
-    <mergeCell ref="AC14:AF14"/>
     <mergeCell ref="AC15:AF15"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A37:B37"/>
@@ -22881,6 +23003,11 @@
     <mergeCell ref="Z21:Z36"/>
     <mergeCell ref="AC8:AG10"/>
     <mergeCell ref="AC16:AF16"/>
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="AC11:AF11"/>
+    <mergeCell ref="AC12:AF12"/>
+    <mergeCell ref="AC13:AF13"/>
+    <mergeCell ref="AC14:AF14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -22889,7 +23016,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AZ40"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -22901,78 +23028,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="34.5" customHeight="1">
-      <c r="A1" s="225" t="s">
+      <c r="A1" s="220" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="225"/>
-      <c r="C1" s="225"/>
-      <c r="D1" s="225"/>
-      <c r="E1" s="225"/>
-      <c r="F1" s="225"/>
-      <c r="G1" s="225"/>
-      <c r="H1" s="225"/>
-      <c r="I1" s="225"/>
-      <c r="J1" s="225"/>
-      <c r="K1" s="225"/>
-      <c r="L1" s="225"/>
-      <c r="M1" s="225"/>
-      <c r="N1" s="225"/>
-      <c r="O1" s="225"/>
-      <c r="P1" s="225"/>
-      <c r="Q1" s="225"/>
-      <c r="R1" s="225"/>
-      <c r="S1" s="225"/>
-      <c r="T1" s="225"/>
-      <c r="U1" s="225"/>
-      <c r="V1" s="225"/>
-      <c r="W1" s="225"/>
-      <c r="X1" s="225"/>
-      <c r="Y1" s="225"/>
-      <c r="Z1" s="225"/>
-      <c r="AA1" s="225"/>
-      <c r="AB1" s="225"/>
-      <c r="AC1" s="225"/>
-      <c r="AD1" s="225"/>
+      <c r="B1" s="220"/>
+      <c r="C1" s="220"/>
+      <c r="D1" s="220"/>
+      <c r="E1" s="220"/>
+      <c r="F1" s="220"/>
+      <c r="G1" s="220"/>
+      <c r="H1" s="220"/>
+      <c r="I1" s="220"/>
+      <c r="J1" s="220"/>
+      <c r="K1" s="220"/>
+      <c r="L1" s="220"/>
+      <c r="M1" s="220"/>
+      <c r="N1" s="220"/>
+      <c r="O1" s="220"/>
+      <c r="P1" s="220"/>
+      <c r="Q1" s="220"/>
+      <c r="R1" s="220"/>
+      <c r="S1" s="220"/>
+      <c r="T1" s="220"/>
+      <c r="U1" s="220"/>
+      <c r="V1" s="220"/>
+      <c r="W1" s="220"/>
+      <c r="X1" s="220"/>
+      <c r="Y1" s="220"/>
+      <c r="Z1" s="220"/>
+      <c r="AA1" s="220"/>
+      <c r="AB1" s="220"/>
+      <c r="AC1" s="220"/>
+      <c r="AD1" s="220"/>
     </row>
     <row r="2" spans="1:52" ht="26.25">
-      <c r="A2" s="226"/>
-      <c r="B2" s="227"/>
-      <c r="C2" s="228" t="s">
+      <c r="A2" s="221"/>
+      <c r="B2" s="222"/>
+      <c r="C2" s="223" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="228"/>
-      <c r="E2" s="228"/>
-      <c r="F2" s="228"/>
-      <c r="G2" s="228"/>
-      <c r="H2" s="228"/>
-      <c r="I2" s="228"/>
-      <c r="J2" s="228"/>
-      <c r="K2" s="228"/>
-      <c r="L2" s="229" t="s">
+      <c r="D2" s="223"/>
+      <c r="E2" s="223"/>
+      <c r="F2" s="223"/>
+      <c r="G2" s="223"/>
+      <c r="H2" s="223"/>
+      <c r="I2" s="223"/>
+      <c r="J2" s="223"/>
+      <c r="K2" s="223"/>
+      <c r="L2" s="224" t="s">
         <v>68</v>
       </c>
-      <c r="M2" s="229"/>
-      <c r="N2" s="229"/>
-      <c r="O2" s="229"/>
-      <c r="P2" s="229"/>
-      <c r="Q2" s="229"/>
-      <c r="R2" s="230" t="s">
+      <c r="M2" s="224"/>
+      <c r="N2" s="224"/>
+      <c r="O2" s="224"/>
+      <c r="P2" s="224"/>
+      <c r="Q2" s="224"/>
+      <c r="R2" s="225" t="s">
         <v>69</v>
       </c>
-      <c r="S2" s="230"/>
-      <c r="T2" s="230"/>
-      <c r="U2" s="230"/>
-      <c r="V2" s="230"/>
-      <c r="W2" s="230"/>
-      <c r="X2" s="230"/>
-      <c r="Y2" s="230"/>
-      <c r="Z2" s="230"/>
-      <c r="AA2" s="230"/>
-      <c r="AB2" s="231" t="s">
+      <c r="S2" s="225"/>
+      <c r="T2" s="225"/>
+      <c r="U2" s="225"/>
+      <c r="V2" s="225"/>
+      <c r="W2" s="225"/>
+      <c r="X2" s="225"/>
+      <c r="Y2" s="225"/>
+      <c r="Z2" s="225"/>
+      <c r="AA2" s="225"/>
+      <c r="AB2" s="226" t="s">
         <v>70</v>
       </c>
-      <c r="AC2" s="231"/>
-      <c r="AD2" s="231"/>
+      <c r="AC2" s="226"/>
+      <c r="AD2" s="226"/>
     </row>
     <row r="3" spans="1:52" ht="45" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -23139,7 +23266,7 @@
         <f>37635+40252.26+18817.85</f>
         <v>96705.11</v>
       </c>
-      <c r="AD4" s="223"/>
+      <c r="AD4" s="230"/>
     </row>
     <row r="5" spans="1:52" ht="15.75">
       <c r="A5" s="17">
@@ -23189,7 +23316,7 @@
         <v>16503.13</v>
       </c>
       <c r="AC5" s="21"/>
-      <c r="AD5" s="223"/>
+      <c r="AD5" s="230"/>
     </row>
     <row r="6" spans="1:52" ht="15.75">
       <c r="A6" s="11">
@@ -23232,7 +23359,7 @@
         <v>996.61</v>
       </c>
       <c r="AC6" s="21"/>
-      <c r="AD6" s="223"/>
+      <c r="AD6" s="230"/>
     </row>
     <row r="7" spans="1:52" ht="15.75">
       <c r="A7" s="17">
@@ -23285,7 +23412,7 @@
         <v>5968</v>
       </c>
       <c r="AC7" s="21"/>
-      <c r="AD7" s="223"/>
+      <c r="AD7" s="230"/>
     </row>
     <row r="8" spans="1:52" ht="15" customHeight="1">
       <c r="A8" s="11">
@@ -23331,7 +23458,7 @@
         <v>12168.98</v>
       </c>
       <c r="AC8" s="21"/>
-      <c r="AD8" s="223"/>
+      <c r="AD8" s="230"/>
     </row>
     <row r="9" spans="1:52" ht="15.75">
       <c r="A9" s="17">
@@ -23379,7 +23506,7 @@
         <v>5970</v>
       </c>
       <c r="AC9" s="21"/>
-      <c r="AD9" s="223"/>
+      <c r="AD9" s="230"/>
     </row>
     <row r="10" spans="1:52" ht="15.75">
       <c r="A10" s="11">
@@ -23427,7 +23554,7 @@
         <v>3257</v>
       </c>
       <c r="AC10" s="21"/>
-      <c r="AD10" s="223"/>
+      <c r="AD10" s="230"/>
     </row>
     <row r="11" spans="1:52" ht="15.75">
       <c r="A11" s="17">
@@ -23471,14 +23598,14 @@
         <v>1034</v>
       </c>
       <c r="AC11" s="21"/>
-      <c r="AD11" s="223"/>
-      <c r="AH11" s="224" t="s">
+      <c r="AD11" s="230"/>
+      <c r="AH11" s="231" t="s">
         <v>83</v>
       </c>
-      <c r="AI11" s="224"/>
-      <c r="AJ11" s="224"/>
-      <c r="AK11" s="224"/>
-      <c r="AL11" s="224"/>
+      <c r="AI11" s="231"/>
+      <c r="AJ11" s="231"/>
+      <c r="AK11" s="231"/>
+      <c r="AL11" s="231"/>
     </row>
     <row r="12" spans="1:52" ht="15.75">
       <c r="A12" s="11">
@@ -23525,12 +23652,12 @@
         <v>3586</v>
       </c>
       <c r="AC12" s="21"/>
-      <c r="AD12" s="223"/>
-      <c r="AH12" s="224"/>
-      <c r="AI12" s="224"/>
-      <c r="AJ12" s="224"/>
-      <c r="AK12" s="224"/>
-      <c r="AL12" s="224"/>
+      <c r="AD12" s="230"/>
+      <c r="AH12" s="231"/>
+      <c r="AI12" s="231"/>
+      <c r="AJ12" s="231"/>
+      <c r="AK12" s="231"/>
+      <c r="AL12" s="231"/>
     </row>
     <row r="13" spans="1:52" ht="15.75">
       <c r="A13" s="17">
@@ -23577,12 +23704,12 @@
         <v>5889</v>
       </c>
       <c r="AC13" s="21"/>
-      <c r="AD13" s="223"/>
-      <c r="AH13" s="224"/>
-      <c r="AI13" s="224"/>
-      <c r="AJ13" s="224"/>
-      <c r="AK13" s="224"/>
-      <c r="AL13" s="224"/>
+      <c r="AD13" s="230"/>
+      <c r="AH13" s="231"/>
+      <c r="AI13" s="231"/>
+      <c r="AJ13" s="231"/>
+      <c r="AK13" s="231"/>
+      <c r="AL13" s="231"/>
     </row>
     <row r="14" spans="1:52" ht="18">
       <c r="A14" s="11">
@@ -23628,13 +23755,13 @@
         <v>7092.93</v>
       </c>
       <c r="AC14" s="21"/>
-      <c r="AD14" s="223"/>
-      <c r="AH14" s="220" t="s">
+      <c r="AD14" s="230"/>
+      <c r="AH14" s="227" t="s">
         <v>62</v>
       </c>
-      <c r="AI14" s="220"/>
-      <c r="AJ14" s="220"/>
-      <c r="AK14" s="220"/>
+      <c r="AI14" s="227"/>
+      <c r="AJ14" s="227"/>
+      <c r="AK14" s="227"/>
       <c r="AL14" s="22">
         <f>AC4+AC20</f>
         <v>133443.15</v>
@@ -23692,13 +23819,13 @@
         <v>6644.28</v>
       </c>
       <c r="AC15" s="16"/>
-      <c r="AD15" s="223"/>
-      <c r="AH15" s="220" t="s">
+      <c r="AD15" s="230"/>
+      <c r="AH15" s="227" t="s">
         <v>2</v>
       </c>
-      <c r="AI15" s="220"/>
-      <c r="AJ15" s="220"/>
-      <c r="AK15" s="220"/>
+      <c r="AI15" s="227"/>
+      <c r="AJ15" s="227"/>
+      <c r="AK15" s="227"/>
       <c r="AL15" s="22">
         <f>AC29</f>
         <v>1000</v>
@@ -23753,13 +23880,13 @@
         <v>5105.1899999999996</v>
       </c>
       <c r="AC16" s="21"/>
-      <c r="AD16" s="223"/>
-      <c r="AH16" s="220" t="s">
+      <c r="AD16" s="230"/>
+      <c r="AH16" s="227" t="s">
         <v>63</v>
       </c>
-      <c r="AI16" s="220"/>
-      <c r="AJ16" s="220"/>
-      <c r="AK16" s="220"/>
+      <c r="AI16" s="227"/>
+      <c r="AJ16" s="227"/>
+      <c r="AK16" s="227"/>
       <c r="AL16" s="22">
         <f>AC21+AC34</f>
         <v>11000</v>
@@ -23804,13 +23931,13 @@
         <v>280.97000000000003</v>
       </c>
       <c r="AC17" s="21"/>
-      <c r="AD17" s="223"/>
-      <c r="AH17" s="220" t="s">
+      <c r="AD17" s="230"/>
+      <c r="AH17" s="227" t="s">
         <v>64</v>
       </c>
-      <c r="AI17" s="220"/>
-      <c r="AJ17" s="220"/>
-      <c r="AK17" s="220"/>
+      <c r="AI17" s="227"/>
+      <c r="AJ17" s="227"/>
+      <c r="AK17" s="227"/>
       <c r="AL17" s="22">
         <f>AB36</f>
         <v>146501.73000000001</v>
@@ -23859,23 +23986,23 @@
         <v>956.98</v>
       </c>
       <c r="AC18" s="21"/>
-      <c r="AD18" s="223"/>
-      <c r="AH18" s="220" t="s">
+      <c r="AD18" s="230"/>
+      <c r="AH18" s="227" t="s">
         <v>65</v>
       </c>
-      <c r="AI18" s="220"/>
-      <c r="AJ18" s="220"/>
-      <c r="AK18" s="220"/>
+      <c r="AI18" s="227"/>
+      <c r="AJ18" s="227"/>
+      <c r="AK18" s="227"/>
       <c r="AL18" s="22">
         <f>SUM(C36:K36)</f>
         <v>56967.92</v>
       </c>
     </row>
     <row r="19" spans="1:38" ht="19.5" customHeight="1">
-      <c r="A19" s="221" t="s">
+      <c r="A19" s="228" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="221"/>
+      <c r="B19" s="228"/>
       <c r="C19" s="23">
         <f>SUM(C4:C18)</f>
         <v>1403.89</v>
@@ -23988,12 +24115,12 @@
         <f>AC19-AB19</f>
         <v>4280.0900000000101</v>
       </c>
-      <c r="AH19" s="220" t="s">
+      <c r="AH19" s="227" t="s">
         <v>84</v>
       </c>
-      <c r="AI19" s="220"/>
-      <c r="AJ19" s="220"/>
-      <c r="AK19" s="220"/>
+      <c r="AI19" s="227"/>
+      <c r="AJ19" s="227"/>
+      <c r="AK19" s="227"/>
       <c r="AL19" s="22">
         <f>SUM(L36:Q36)</f>
         <v>31394.13</v>
@@ -24054,13 +24181,13 @@
       <c r="AC20" s="16">
         <v>36738.04</v>
       </c>
-      <c r="AD20" s="223"/>
-      <c r="AH20" s="220" t="s">
+      <c r="AD20" s="230"/>
+      <c r="AH20" s="227" t="s">
         <v>85</v>
       </c>
-      <c r="AI20" s="220"/>
-      <c r="AJ20" s="220"/>
-      <c r="AK20" s="220"/>
+      <c r="AI20" s="227"/>
+      <c r="AJ20" s="227"/>
+      <c r="AK20" s="227"/>
       <c r="AL20" s="22">
         <f>W36</f>
         <v>35678.97</v>
@@ -24115,14 +24242,14 @@
       <c r="AC21" s="37">
         <v>10000</v>
       </c>
-      <c r="AD21" s="223"/>
+      <c r="AD21" s="230"/>
       <c r="AF21" s="29"/>
-      <c r="AH21" s="220" t="s">
+      <c r="AH21" s="227" t="s">
         <v>86</v>
       </c>
-      <c r="AI21" s="220"/>
-      <c r="AJ21" s="220"/>
-      <c r="AK21" s="220"/>
+      <c r="AI21" s="227"/>
+      <c r="AJ21" s="227"/>
+      <c r="AK21" s="227"/>
       <c r="AL21" s="22">
         <f>SUM(U36:V36)</f>
         <v>11008.46</v>
@@ -24165,13 +24292,13 @@
         <v>0</v>
       </c>
       <c r="AC22" s="21"/>
-      <c r="AD22" s="223"/>
-      <c r="AH22" s="220" t="s">
+      <c r="AD22" s="230"/>
+      <c r="AH22" s="227" t="s">
         <v>32</v>
       </c>
-      <c r="AI22" s="220"/>
-      <c r="AJ22" s="220"/>
-      <c r="AK22" s="220"/>
+      <c r="AI22" s="227"/>
+      <c r="AJ22" s="227"/>
+      <c r="AK22" s="227"/>
       <c r="AL22" s="22">
         <f>T36</f>
         <v>0</v>
@@ -24226,13 +24353,13 @@
         <v>6881.28</v>
       </c>
       <c r="AC23" s="21"/>
-      <c r="AD23" s="223"/>
-      <c r="AH23" s="220" t="s">
+      <c r="AD23" s="230"/>
+      <c r="AH23" s="227" t="s">
         <v>87</v>
       </c>
-      <c r="AI23" s="220"/>
-      <c r="AJ23" s="220"/>
-      <c r="AK23" s="220"/>
+      <c r="AI23" s="227"/>
+      <c r="AJ23" s="227"/>
+      <c r="AK23" s="227"/>
       <c r="AL23" s="22">
         <f>X36</f>
         <v>5267.98</v>
@@ -24287,7 +24414,7 @@
         <v>6126.69</v>
       </c>
       <c r="AC24" s="21"/>
-      <c r="AD24" s="223"/>
+      <c r="AD24" s="230"/>
     </row>
     <row r="25" spans="1:38" ht="15.75">
       <c r="A25" s="17">
@@ -24331,7 +24458,7 @@
         <v>7750</v>
       </c>
       <c r="AC25" s="21"/>
-      <c r="AD25" s="223"/>
+      <c r="AD25" s="230"/>
     </row>
     <row r="26" spans="1:38" ht="15.75">
       <c r="A26" s="11">
@@ -24378,7 +24505,7 @@
         <v>2803</v>
       </c>
       <c r="AC26" s="16"/>
-      <c r="AD26" s="223"/>
+      <c r="AD26" s="230"/>
     </row>
     <row r="27" spans="1:38" ht="15.75">
       <c r="A27" s="17">
@@ -24426,7 +24553,7 @@
         <v>2088.96</v>
       </c>
       <c r="AC27" s="21"/>
-      <c r="AD27" s="223"/>
+      <c r="AD27" s="230"/>
     </row>
     <row r="28" spans="1:38" ht="15.75">
       <c r="A28" s="11">
@@ -24472,7 +24599,7 @@
         <v>3468</v>
       </c>
       <c r="AC28" s="21"/>
-      <c r="AD28" s="223"/>
+      <c r="AD28" s="230"/>
     </row>
     <row r="29" spans="1:38" ht="15.75">
       <c r="A29" s="17">
@@ -24525,7 +24652,7 @@
       <c r="AC29" s="21">
         <v>1000</v>
       </c>
-      <c r="AD29" s="223"/>
+      <c r="AD29" s="230"/>
     </row>
     <row r="30" spans="1:38" ht="15.75">
       <c r="A30" s="11">
@@ -24573,7 +24700,7 @@
         <v>4016.5</v>
       </c>
       <c r="AC30" s="21"/>
-      <c r="AD30" s="223"/>
+      <c r="AD30" s="230"/>
     </row>
     <row r="31" spans="1:38" ht="15.75">
       <c r="A31" s="17">
@@ -24617,7 +24744,7 @@
         <v>2801.78</v>
       </c>
       <c r="AC31" s="21"/>
-      <c r="AD31" s="223"/>
+      <c r="AD31" s="230"/>
     </row>
     <row r="32" spans="1:38" ht="15.75">
       <c r="A32" s="11">
@@ -24666,7 +24793,7 @@
         <v>3807.11</v>
       </c>
       <c r="AC32" s="21"/>
-      <c r="AD32" s="223"/>
+      <c r="AD32" s="230"/>
     </row>
     <row r="33" spans="1:30" ht="15.75">
       <c r="A33" s="17">
@@ -24710,7 +24837,7 @@
         <v>675.44</v>
       </c>
       <c r="AC33" s="21"/>
-      <c r="AD33" s="223"/>
+      <c r="AD33" s="230"/>
     </row>
     <row r="34" spans="1:30" ht="15.75">
       <c r="A34" s="11">
@@ -24754,13 +24881,13 @@
       <c r="AC34" s="37">
         <v>1000</v>
       </c>
-      <c r="AD34" s="223"/>
+      <c r="AD34" s="230"/>
     </row>
     <row r="35" spans="1:30" ht="14.25" customHeight="1">
-      <c r="A35" s="221" t="s">
+      <c r="A35" s="228" t="s">
         <v>55</v>
       </c>
-      <c r="B35" s="221"/>
+      <c r="B35" s="228"/>
       <c r="C35" s="23">
         <f t="shared" ref="C35:AC35" si="3">SUM(C20:C34)</f>
         <v>2169.6999999999998</v>
@@ -24875,10 +25002,10 @@
       </c>
     </row>
     <row r="36" spans="1:30" ht="31.5" customHeight="1">
-      <c r="A36" s="222" t="s">
+      <c r="A36" s="229" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="222"/>
+      <c r="B36" s="229"/>
       <c r="C36" s="31">
         <f>SUM(C19,C35)</f>
         <v>3573.59</v>
@@ -25009,12 +25136,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:K2"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="AH23:AK23"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="A36:B36"/>
@@ -25031,6 +25152,12 @@
     <mergeCell ref="AH16:AK16"/>
     <mergeCell ref="AH17:AK17"/>
     <mergeCell ref="AH18:AK18"/>
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -25039,7 +25166,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AZ41"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -25051,78 +25178,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="34.5" customHeight="1">
-      <c r="A1" s="225" t="s">
+      <c r="A1" s="220" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="225"/>
-      <c r="C1" s="225"/>
-      <c r="D1" s="225"/>
-      <c r="E1" s="225"/>
-      <c r="F1" s="225"/>
-      <c r="G1" s="225"/>
-      <c r="H1" s="225"/>
-      <c r="I1" s="225"/>
-      <c r="J1" s="225"/>
-      <c r="K1" s="225"/>
-      <c r="L1" s="225"/>
-      <c r="M1" s="225"/>
-      <c r="N1" s="225"/>
-      <c r="O1" s="225"/>
-      <c r="P1" s="225"/>
-      <c r="Q1" s="225"/>
-      <c r="R1" s="225"/>
-      <c r="S1" s="225"/>
-      <c r="T1" s="225"/>
-      <c r="U1" s="225"/>
-      <c r="V1" s="225"/>
-      <c r="W1" s="225"/>
-      <c r="X1" s="225"/>
-      <c r="Y1" s="225"/>
-      <c r="Z1" s="225"/>
-      <c r="AA1" s="225"/>
-      <c r="AB1" s="225"/>
-      <c r="AC1" s="225"/>
-      <c r="AD1" s="225"/>
+      <c r="B1" s="220"/>
+      <c r="C1" s="220"/>
+      <c r="D1" s="220"/>
+      <c r="E1" s="220"/>
+      <c r="F1" s="220"/>
+      <c r="G1" s="220"/>
+      <c r="H1" s="220"/>
+      <c r="I1" s="220"/>
+      <c r="J1" s="220"/>
+      <c r="K1" s="220"/>
+      <c r="L1" s="220"/>
+      <c r="M1" s="220"/>
+      <c r="N1" s="220"/>
+      <c r="O1" s="220"/>
+      <c r="P1" s="220"/>
+      <c r="Q1" s="220"/>
+      <c r="R1" s="220"/>
+      <c r="S1" s="220"/>
+      <c r="T1" s="220"/>
+      <c r="U1" s="220"/>
+      <c r="V1" s="220"/>
+      <c r="W1" s="220"/>
+      <c r="X1" s="220"/>
+      <c r="Y1" s="220"/>
+      <c r="Z1" s="220"/>
+      <c r="AA1" s="220"/>
+      <c r="AB1" s="220"/>
+      <c r="AC1" s="220"/>
+      <c r="AD1" s="220"/>
     </row>
     <row r="2" spans="1:52" ht="26.25">
-      <c r="A2" s="226"/>
-      <c r="B2" s="227"/>
-      <c r="C2" s="228" t="s">
+      <c r="A2" s="221"/>
+      <c r="B2" s="222"/>
+      <c r="C2" s="223" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="228"/>
-      <c r="E2" s="228"/>
-      <c r="F2" s="228"/>
-      <c r="G2" s="228"/>
-      <c r="H2" s="228"/>
-      <c r="I2" s="228"/>
-      <c r="J2" s="228"/>
-      <c r="K2" s="228"/>
-      <c r="L2" s="229" t="s">
+      <c r="D2" s="223"/>
+      <c r="E2" s="223"/>
+      <c r="F2" s="223"/>
+      <c r="G2" s="223"/>
+      <c r="H2" s="223"/>
+      <c r="I2" s="223"/>
+      <c r="J2" s="223"/>
+      <c r="K2" s="223"/>
+      <c r="L2" s="224" t="s">
         <v>68</v>
       </c>
-      <c r="M2" s="229"/>
-      <c r="N2" s="229"/>
-      <c r="O2" s="229"/>
-      <c r="P2" s="229"/>
-      <c r="Q2" s="229"/>
-      <c r="R2" s="230" t="s">
+      <c r="M2" s="224"/>
+      <c r="N2" s="224"/>
+      <c r="O2" s="224"/>
+      <c r="P2" s="224"/>
+      <c r="Q2" s="224"/>
+      <c r="R2" s="225" t="s">
         <v>69</v>
       </c>
-      <c r="S2" s="230"/>
-      <c r="T2" s="230"/>
-      <c r="U2" s="230"/>
-      <c r="V2" s="230"/>
-      <c r="W2" s="230"/>
-      <c r="X2" s="230"/>
-      <c r="Y2" s="230"/>
-      <c r="Z2" s="230"/>
-      <c r="AA2" s="230"/>
-      <c r="AB2" s="231" t="s">
+      <c r="S2" s="225"/>
+      <c r="T2" s="225"/>
+      <c r="U2" s="225"/>
+      <c r="V2" s="225"/>
+      <c r="W2" s="225"/>
+      <c r="X2" s="225"/>
+      <c r="Y2" s="225"/>
+      <c r="Z2" s="225"/>
+      <c r="AA2" s="225"/>
+      <c r="AB2" s="226" t="s">
         <v>70</v>
       </c>
-      <c r="AC2" s="231"/>
-      <c r="AD2" s="231"/>
+      <c r="AC2" s="226"/>
+      <c r="AD2" s="226"/>
     </row>
     <row r="3" spans="1:52" ht="45" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -25287,7 +25414,7 @@
         <f>66577.47+18817</f>
         <v>85394.47</v>
       </c>
-      <c r="AD4" s="223"/>
+      <c r="AD4" s="230"/>
     </row>
     <row r="5" spans="1:52" ht="15.75">
       <c r="A5" s="17">
@@ -25342,7 +25469,7 @@
         <v>7116</v>
       </c>
       <c r="AC5" s="168"/>
-      <c r="AD5" s="223"/>
+      <c r="AD5" s="230"/>
     </row>
     <row r="6" spans="1:52" ht="15.75">
       <c r="A6" s="11">
@@ -25390,7 +25517,7 @@
         <v>17146</v>
       </c>
       <c r="AC6" s="168"/>
-      <c r="AD6" s="223"/>
+      <c r="AD6" s="230"/>
     </row>
     <row r="7" spans="1:52" ht="15.75">
       <c r="A7" s="17">
@@ -25447,7 +25574,7 @@
         <v>6206.84</v>
       </c>
       <c r="AC7" s="168"/>
-      <c r="AD7" s="223"/>
+      <c r="AD7" s="230"/>
     </row>
     <row r="8" spans="1:52" ht="15" customHeight="1">
       <c r="A8" s="11">
@@ -25506,7 +25633,7 @@
         <v>8204</v>
       </c>
       <c r="AC8" s="168"/>
-      <c r="AD8" s="223"/>
+      <c r="AD8" s="230"/>
     </row>
     <row r="9" spans="1:52" ht="15.75">
       <c r="A9" s="17">
@@ -25555,7 +25682,7 @@
         <v>8276</v>
       </c>
       <c r="AC9" s="168"/>
-      <c r="AD9" s="223"/>
+      <c r="AD9" s="230"/>
     </row>
     <row r="10" spans="1:52" ht="15.75">
       <c r="A10" s="11">
@@ -25603,7 +25730,7 @@
       <c r="AC10" s="168">
         <v>28225.5</v>
       </c>
-      <c r="AD10" s="223"/>
+      <c r="AD10" s="230"/>
     </row>
     <row r="11" spans="1:52" ht="15.75">
       <c r="A11" s="17">
@@ -25653,14 +25780,14 @@
         <v>5638.53</v>
       </c>
       <c r="AC11" s="168"/>
-      <c r="AD11" s="223"/>
-      <c r="AH11" s="224" t="s">
+      <c r="AD11" s="230"/>
+      <c r="AH11" s="231" t="s">
         <v>83</v>
       </c>
-      <c r="AI11" s="224"/>
-      <c r="AJ11" s="224"/>
-      <c r="AK11" s="224"/>
-      <c r="AL11" s="224"/>
+      <c r="AI11" s="231"/>
+      <c r="AJ11" s="231"/>
+      <c r="AK11" s="231"/>
+      <c r="AL11" s="231"/>
     </row>
     <row r="12" spans="1:52" ht="15.75">
       <c r="A12" s="11">
@@ -25714,12 +25841,12 @@
         <v>33365</v>
       </c>
       <c r="AC12" s="168"/>
-      <c r="AD12" s="223"/>
-      <c r="AH12" s="224"/>
-      <c r="AI12" s="224"/>
-      <c r="AJ12" s="224"/>
-      <c r="AK12" s="224"/>
-      <c r="AL12" s="224"/>
+      <c r="AD12" s="230"/>
+      <c r="AH12" s="231"/>
+      <c r="AI12" s="231"/>
+      <c r="AJ12" s="231"/>
+      <c r="AK12" s="231"/>
+      <c r="AL12" s="231"/>
     </row>
     <row r="13" spans="1:52" ht="15.75">
       <c r="A13" s="17">
@@ -25777,12 +25904,12 @@
         <v>10965.96</v>
       </c>
       <c r="AC13" s="168"/>
-      <c r="AD13" s="223"/>
-      <c r="AH13" s="224"/>
-      <c r="AI13" s="224"/>
-      <c r="AJ13" s="224"/>
-      <c r="AK13" s="224"/>
-      <c r="AL13" s="224"/>
+      <c r="AD13" s="230"/>
+      <c r="AH13" s="231"/>
+      <c r="AI13" s="231"/>
+      <c r="AJ13" s="231"/>
+      <c r="AK13" s="231"/>
+      <c r="AL13" s="231"/>
     </row>
     <row r="14" spans="1:52" ht="18">
       <c r="A14" s="11">
@@ -25830,13 +25957,13 @@
         <v>1614.53</v>
       </c>
       <c r="AC14" s="168"/>
-      <c r="AD14" s="223"/>
-      <c r="AH14" s="220" t="s">
+      <c r="AD14" s="230"/>
+      <c r="AH14" s="227" t="s">
         <v>62</v>
       </c>
-      <c r="AI14" s="220"/>
-      <c r="AJ14" s="220"/>
-      <c r="AK14" s="220"/>
+      <c r="AI14" s="227"/>
+      <c r="AJ14" s="227"/>
+      <c r="AK14" s="227"/>
       <c r="AL14" s="22">
         <f>AC4+AC19+AC23+AC10</f>
         <v>287751.42</v>
@@ -25894,13 +26021,13 @@
         <v>6960.82</v>
       </c>
       <c r="AC15" s="166"/>
-      <c r="AD15" s="223"/>
-      <c r="AH15" s="220" t="s">
+      <c r="AD15" s="230"/>
+      <c r="AH15" s="227" t="s">
         <v>2</v>
       </c>
-      <c r="AI15" s="220"/>
-      <c r="AJ15" s="220"/>
-      <c r="AK15" s="220"/>
+      <c r="AI15" s="227"/>
+      <c r="AJ15" s="227"/>
+      <c r="AK15" s="227"/>
       <c r="AL15" s="22">
         <f>AC20</f>
         <v>1000</v>
@@ -25954,13 +26081,13 @@
       <c r="AC16" s="170">
         <v>5000</v>
       </c>
-      <c r="AD16" s="223"/>
-      <c r="AH16" s="220" t="s">
+      <c r="AD16" s="230"/>
+      <c r="AH16" s="227" t="s">
         <v>63</v>
       </c>
-      <c r="AI16" s="220"/>
-      <c r="AJ16" s="220"/>
-      <c r="AK16" s="220"/>
+      <c r="AI16" s="227"/>
+      <c r="AJ16" s="227"/>
+      <c r="AK16" s="227"/>
       <c r="AL16" s="22">
         <f>AC16+AC28+AC34+AC35</f>
         <v>60000</v>
@@ -26018,7 +26145,7 @@
         <v>5002</v>
       </c>
       <c r="AC17" s="166"/>
-      <c r="AD17" s="223"/>
+      <c r="AD17" s="230"/>
       <c r="AH17" s="232" t="s">
         <v>67</v>
       </c>
@@ -26147,12 +26274,12 @@
         <f>AC18-AB18</f>
         <v>-900.67000000001281</v>
       </c>
-      <c r="AH18" s="220" t="s">
+      <c r="AH18" s="227" t="s">
         <v>84</v>
       </c>
-      <c r="AI18" s="220"/>
-      <c r="AJ18" s="220"/>
-      <c r="AK18" s="220"/>
+      <c r="AI18" s="227"/>
+      <c r="AJ18" s="227"/>
+      <c r="AK18" s="227"/>
       <c r="AL18" s="22">
         <f>SUM(L37:Q37)</f>
         <v>35695</v>
@@ -26206,13 +26333,13 @@
       <c r="AC19" s="16">
         <v>38575.449999999997</v>
       </c>
-      <c r="AD19" s="223"/>
-      <c r="AH19" s="220" t="s">
+      <c r="AD19" s="230"/>
+      <c r="AH19" s="227" t="s">
         <v>85</v>
       </c>
-      <c r="AI19" s="220"/>
-      <c r="AJ19" s="220"/>
-      <c r="AK19" s="220"/>
+      <c r="AI19" s="227"/>
+      <c r="AJ19" s="227"/>
+      <c r="AK19" s="227"/>
       <c r="AL19" s="22">
         <f>W37</f>
         <v>38934</v>
@@ -26269,14 +26396,14 @@
       <c r="AC20" s="21">
         <v>1000</v>
       </c>
-      <c r="AD20" s="223"/>
+      <c r="AD20" s="230"/>
       <c r="AF20" s="29"/>
-      <c r="AH20" s="220" t="s">
+      <c r="AH20" s="227" t="s">
         <v>86</v>
       </c>
-      <c r="AI20" s="220"/>
-      <c r="AJ20" s="220"/>
-      <c r="AK20" s="220"/>
+      <c r="AI20" s="227"/>
+      <c r="AJ20" s="227"/>
+      <c r="AK20" s="227"/>
       <c r="AL20" s="22">
         <f>SUM(U37:V37)</f>
         <v>15264.08</v>
@@ -26322,7 +26449,7 @@
         <v>1980</v>
       </c>
       <c r="AC21" s="21"/>
-      <c r="AD21" s="223"/>
+      <c r="AD21" s="230"/>
       <c r="AH21" s="235" t="s">
         <v>32</v>
       </c>
@@ -26383,7 +26510,7 @@
         <v>3710.54</v>
       </c>
       <c r="AC22" s="21"/>
-      <c r="AD22" s="223"/>
+      <c r="AD22" s="230"/>
       <c r="AH22" s="236"/>
       <c r="AI22" s="236"/>
       <c r="AJ22" s="236"/>
@@ -26439,7 +26566,7 @@
         <f>21986+70637+42933</f>
         <v>135556</v>
       </c>
-      <c r="AD23" s="223"/>
+      <c r="AD23" s="230"/>
     </row>
     <row r="24" spans="1:38" ht="15.75">
       <c r="A24" s="17">
@@ -26499,7 +26626,7 @@
         <v>26293.41</v>
       </c>
       <c r="AC24" s="21"/>
-      <c r="AD24" s="223"/>
+      <c r="AD24" s="230"/>
     </row>
     <row r="25" spans="1:38" ht="15.75">
       <c r="A25" s="11">
@@ -26544,7 +26671,7 @@
         <v>542</v>
       </c>
       <c r="AC25" s="16"/>
-      <c r="AD25" s="223"/>
+      <c r="AD25" s="230"/>
     </row>
     <row r="26" spans="1:38" ht="15.75">
       <c r="A26" s="17">
@@ -26604,7 +26731,7 @@
         <v>5856.07</v>
       </c>
       <c r="AC26" s="21"/>
-      <c r="AD26" s="223"/>
+      <c r="AD26" s="230"/>
     </row>
     <row r="27" spans="1:38" ht="15.75">
       <c r="A27" s="11">
@@ -26658,7 +26785,7 @@
         <v>14081.2</v>
       </c>
       <c r="AC27" s="21"/>
-      <c r="AD27" s="223"/>
+      <c r="AD27" s="230"/>
     </row>
     <row r="28" spans="1:38" ht="15.75">
       <c r="A28" s="17">
@@ -26702,7 +26829,7 @@
       <c r="AC28" s="21">
         <v>20000</v>
       </c>
-      <c r="AD28" s="223"/>
+      <c r="AD28" s="230"/>
     </row>
     <row r="29" spans="1:38" ht="15.75">
       <c r="A29" s="11">
@@ -26751,7 +26878,7 @@
         <v>4019.84</v>
       </c>
       <c r="AC29" s="21"/>
-      <c r="AD29" s="223"/>
+      <c r="AD29" s="230"/>
     </row>
     <row r="30" spans="1:38" ht="15.75">
       <c r="A30" s="17">
@@ -26802,7 +26929,7 @@
         <v>2628.39</v>
       </c>
       <c r="AC30" s="21"/>
-      <c r="AD30" s="223"/>
+      <c r="AD30" s="230"/>
     </row>
     <row r="31" spans="1:38" ht="16.5" thickBot="1">
       <c r="A31" s="142">
@@ -26858,7 +26985,7 @@
         <v>12589</v>
       </c>
       <c r="AC31" s="21"/>
-      <c r="AD31" s="223"/>
+      <c r="AD31" s="230"/>
     </row>
     <row r="32" spans="1:38" ht="15.75">
       <c r="A32" s="150">
@@ -26920,7 +27047,7 @@
         <v>18544.419999999998</v>
       </c>
       <c r="AC32" s="21"/>
-      <c r="AD32" s="223"/>
+      <c r="AD32" s="230"/>
     </row>
     <row r="33" spans="1:34" ht="15.75">
       <c r="A33" s="157">
@@ -26971,7 +27098,7 @@
         <v>9526.09</v>
       </c>
       <c r="AC33" s="21"/>
-      <c r="AD33" s="223"/>
+      <c r="AD33" s="230"/>
     </row>
     <row r="34" spans="1:34" ht="15.75">
       <c r="A34" s="154">
@@ -27033,7 +27160,7 @@
       <c r="AC34" s="21">
         <v>20000</v>
       </c>
-      <c r="AD34" s="223"/>
+      <c r="AD34" s="230"/>
     </row>
     <row r="35" spans="1:34" ht="16.5" thickBot="1">
       <c r="A35" s="161">
@@ -27089,7 +27216,7 @@
       <c r="AC35" s="37">
         <v>15000</v>
       </c>
-      <c r="AD35" s="223"/>
+      <c r="AD35" s="230"/>
     </row>
     <row r="36" spans="1:34" ht="24" customHeight="1">
       <c r="A36" s="237" t="s">
@@ -27211,10 +27338,10 @@
       <c r="AH36" s="165"/>
     </row>
     <row r="37" spans="1:34" ht="31.5" customHeight="1">
-      <c r="A37" s="222" t="s">
+      <c r="A37" s="229" t="s">
         <v>56</v>
       </c>
-      <c r="B37" s="222"/>
+      <c r="B37" s="229"/>
       <c r="C37" s="31">
         <f t="shared" ref="C37:R37" si="7">SUM(C18,C36)</f>
         <v>1423.08</v>
@@ -27345,12 +27472,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:K2"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="AD19:AD35"/>
     <mergeCell ref="AH11:AL13"/>
@@ -27366,6 +27487,12 @@
     <mergeCell ref="AH16:AK16"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="AH18:AK18"/>
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Другое/2026/Доходы-Расходы.xlsx
+++ b/Другое/2026/Доходы-Расходы.xlsx
@@ -8332,6 +8332,20 @@
           </rPr>
           <t xml:space="preserve">
 Зарядный провод</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D18" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Хлеб и наполеон в Амбаре</t>
         </r>
       </text>
     </comment>
@@ -8704,7 +8718,7 @@
     <numFmt numFmtId="164" formatCode="#\ ##0.00\ &quot;₽&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="55">
+  <fonts count="58">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9065,6 +9079,32 @@
       <name val="Tahoma"/>
       <family val="2"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFC000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="40">
@@ -9778,7 +9818,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="240">
+  <cellXfs count="242">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10118,15 +10158,6 @@
     <xf numFmtId="0" fontId="40" fillId="31" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="41" fillId="31" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="41" fillId="31" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -10295,6 +10326,9 @@
     <xf numFmtId="164" fontId="52" fillId="37" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="52" fillId="39" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -10334,9 +10368,6 @@
     <xf numFmtId="0" fontId="24" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -10347,6 +10378,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -10370,21 +10419,6 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -10406,14 +10440,26 @@
     <xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="52" fillId="39" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="55" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="56" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="56" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="57" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="57" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="10">
     <dxf>
       <font>
         <color rgb="FF00B050"/>
@@ -10422,16 +10468,6 @@
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
       </font>
     </dxf>
     <dxf>
@@ -11038,18 +11074,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H17">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>H17&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="2">
+    <cfRule type="expression" dxfId="8" priority="2">
       <formula>H17&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:H16">
-    <cfRule type="expression" dxfId="9" priority="3">
+    <cfRule type="expression" dxfId="7" priority="3">
       <formula>H5&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="4">
+    <cfRule type="expression" dxfId="6" priority="4">
       <formula>H5&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11073,159 +11109,159 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="34.5" customHeight="1">
-      <c r="A1" s="220" t="s">
+      <c r="A1" s="223" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="220"/>
-      <c r="C1" s="220"/>
-      <c r="D1" s="220"/>
-      <c r="E1" s="220"/>
-      <c r="F1" s="220"/>
-      <c r="G1" s="220"/>
-      <c r="H1" s="220"/>
-      <c r="I1" s="220"/>
-      <c r="J1" s="220"/>
-      <c r="K1" s="220"/>
-      <c r="L1" s="220"/>
-      <c r="M1" s="220"/>
-      <c r="N1" s="220"/>
-      <c r="O1" s="220"/>
-      <c r="P1" s="220"/>
-      <c r="Q1" s="220"/>
-      <c r="R1" s="220"/>
-      <c r="S1" s="220"/>
-      <c r="T1" s="220"/>
-      <c r="U1" s="220"/>
-      <c r="V1" s="220"/>
-      <c r="W1" s="220"/>
-      <c r="X1" s="220"/>
-      <c r="Y1" s="220"/>
-      <c r="Z1" s="220"/>
-      <c r="AA1" s="220"/>
-      <c r="AB1" s="220"/>
-      <c r="AC1" s="220"/>
-      <c r="AD1" s="220"/>
+      <c r="B1" s="223"/>
+      <c r="C1" s="223"/>
+      <c r="D1" s="223"/>
+      <c r="E1" s="223"/>
+      <c r="F1" s="223"/>
+      <c r="G1" s="223"/>
+      <c r="H1" s="223"/>
+      <c r="I1" s="223"/>
+      <c r="J1" s="223"/>
+      <c r="K1" s="223"/>
+      <c r="L1" s="223"/>
+      <c r="M1" s="223"/>
+      <c r="N1" s="223"/>
+      <c r="O1" s="223"/>
+      <c r="P1" s="223"/>
+      <c r="Q1" s="223"/>
+      <c r="R1" s="223"/>
+      <c r="S1" s="223"/>
+      <c r="T1" s="223"/>
+      <c r="U1" s="223"/>
+      <c r="V1" s="223"/>
+      <c r="W1" s="223"/>
+      <c r="X1" s="223"/>
+      <c r="Y1" s="223"/>
+      <c r="Z1" s="223"/>
+      <c r="AA1" s="223"/>
+      <c r="AB1" s="223"/>
+      <c r="AC1" s="223"/>
+      <c r="AD1" s="223"/>
     </row>
     <row r="2" spans="1:52" ht="26.25">
-      <c r="A2" s="221"/>
-      <c r="B2" s="222"/>
-      <c r="C2" s="223" t="s">
+      <c r="A2" s="224"/>
+      <c r="B2" s="225"/>
+      <c r="C2" s="226" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="223"/>
-      <c r="E2" s="223"/>
-      <c r="F2" s="223"/>
-      <c r="G2" s="223"/>
-      <c r="H2" s="223"/>
-      <c r="I2" s="223"/>
-      <c r="J2" s="223"/>
-      <c r="K2" s="223"/>
-      <c r="L2" s="224" t="s">
+      <c r="D2" s="226"/>
+      <c r="E2" s="226"/>
+      <c r="F2" s="226"/>
+      <c r="G2" s="226"/>
+      <c r="H2" s="226"/>
+      <c r="I2" s="226"/>
+      <c r="J2" s="226"/>
+      <c r="K2" s="226"/>
+      <c r="L2" s="227" t="s">
         <v>68</v>
       </c>
-      <c r="M2" s="224"/>
-      <c r="N2" s="224"/>
-      <c r="O2" s="224"/>
-      <c r="P2" s="224"/>
-      <c r="Q2" s="224"/>
-      <c r="R2" s="225" t="s">
+      <c r="M2" s="227"/>
+      <c r="N2" s="227"/>
+      <c r="O2" s="227"/>
+      <c r="P2" s="227"/>
+      <c r="Q2" s="227"/>
+      <c r="R2" s="228" t="s">
         <v>69</v>
       </c>
-      <c r="S2" s="225"/>
-      <c r="T2" s="225"/>
-      <c r="U2" s="225"/>
-      <c r="V2" s="225"/>
-      <c r="W2" s="225"/>
-      <c r="X2" s="225"/>
-      <c r="Y2" s="225"/>
-      <c r="Z2" s="225"/>
-      <c r="AA2" s="225"/>
-      <c r="AB2" s="226" t="s">
+      <c r="S2" s="228"/>
+      <c r="T2" s="228"/>
+      <c r="U2" s="228"/>
+      <c r="V2" s="228"/>
+      <c r="W2" s="228"/>
+      <c r="X2" s="228"/>
+      <c r="Y2" s="228"/>
+      <c r="Z2" s="228"/>
+      <c r="AA2" s="228"/>
+      <c r="AB2" s="229" t="s">
         <v>70</v>
       </c>
-      <c r="AC2" s="226"/>
-      <c r="AD2" s="226"/>
+      <c r="AC2" s="229"/>
+      <c r="AD2" s="229"/>
     </row>
     <row r="3" spans="1:52" ht="45" customHeight="1" thickBot="1">
-      <c r="A3" s="184" t="s">
+      <c r="A3" s="181" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="184" t="s">
+      <c r="B3" s="181" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="185" t="s">
+      <c r="C3" s="182" t="s">
         <v>71</v>
       </c>
-      <c r="D3" s="185" t="s">
+      <c r="D3" s="182" t="s">
         <v>89</v>
       </c>
-      <c r="E3" s="185" t="s">
+      <c r="E3" s="182" t="s">
         <v>90</v>
       </c>
-      <c r="F3" s="185" t="s">
+      <c r="F3" s="182" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="185" t="s">
+      <c r="G3" s="182" t="s">
         <v>74</v>
       </c>
-      <c r="H3" s="185" t="s">
+      <c r="H3" s="182" t="s">
         <v>75</v>
       </c>
-      <c r="I3" s="185" t="s">
+      <c r="I3" s="182" t="s">
         <v>76</v>
       </c>
-      <c r="J3" s="185" t="s">
+      <c r="J3" s="182" t="s">
         <v>77</v>
       </c>
-      <c r="K3" s="185" t="s">
+      <c r="K3" s="182" t="s">
         <v>78</v>
       </c>
-      <c r="L3" s="186" t="s">
+      <c r="L3" s="183" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="186" t="s">
+      <c r="M3" s="183" t="s">
         <v>33</v>
       </c>
-      <c r="N3" s="186" t="s">
+      <c r="N3" s="183" t="s">
         <v>79</v>
       </c>
-      <c r="O3" s="186" t="s">
+      <c r="O3" s="183" t="s">
         <v>39</v>
       </c>
-      <c r="P3" s="186" t="s">
+      <c r="P3" s="183" t="s">
         <v>39</v>
       </c>
-      <c r="Q3" s="186" t="s">
+      <c r="Q3" s="183" t="s">
         <v>80</v>
       </c>
-      <c r="R3" s="187" t="s">
+      <c r="R3" s="184" t="s">
         <v>28</v>
       </c>
-      <c r="S3" s="187" t="s">
+      <c r="S3" s="184" t="s">
         <v>31</v>
       </c>
-      <c r="T3" s="187" t="s">
+      <c r="T3" s="184" t="s">
         <v>32</v>
       </c>
-      <c r="U3" s="187" t="s">
+      <c r="U3" s="184" t="s">
         <v>34</v>
       </c>
-      <c r="V3" s="187" t="s">
+      <c r="V3" s="184" t="s">
         <v>35</v>
       </c>
-      <c r="W3" s="187" t="s">
+      <c r="W3" s="184" t="s">
         <v>36</v>
       </c>
-      <c r="X3" s="187" t="s">
+      <c r="X3" s="184" t="s">
         <v>81</v>
       </c>
-      <c r="Y3" s="187" t="s">
+      <c r="Y3" s="184" t="s">
         <v>81</v>
       </c>
-      <c r="Z3" s="187" t="s">
+      <c r="Z3" s="184" t="s">
         <v>82</v>
       </c>
-      <c r="AA3" s="188" t="s">
+      <c r="AA3" s="185" t="s">
         <v>40</v>
       </c>
       <c r="AB3" s="7" t="s">
@@ -11234,7 +11270,7 @@
       <c r="AC3" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AD3" s="171" t="s">
+      <c r="AD3" s="168" t="s">
         <v>5</v>
       </c>
       <c r="AE3" s="10"/>
@@ -11261,223 +11297,223 @@
       <c r="AZ3" s="10"/>
     </row>
     <row r="4" spans="1:52" ht="15.75">
-      <c r="A4" s="150">
+      <c r="A4" s="147">
         <v>5</v>
       </c>
-      <c r="B4" s="151" t="s">
+      <c r="B4" s="148" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="193"/>
-      <c r="D4" s="193"/>
-      <c r="E4" s="193">
+      <c r="C4" s="190"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190">
         <v>300.95999999999998</v>
       </c>
-      <c r="F4" s="193"/>
-      <c r="G4" s="193"/>
-      <c r="H4" s="193"/>
-      <c r="I4" s="193">
+      <c r="F4" s="190"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="190">
         <f>5000+415.8</f>
         <v>5415.8</v>
       </c>
-      <c r="J4" s="193"/>
-      <c r="K4" s="193"/>
-      <c r="L4" s="193"/>
-      <c r="M4" s="193"/>
-      <c r="N4" s="193">
+      <c r="J4" s="190"/>
+      <c r="K4" s="190"/>
+      <c r="L4" s="190"/>
+      <c r="M4" s="190"/>
+      <c r="N4" s="190">
         <v>199</v>
       </c>
-      <c r="O4" s="193"/>
-      <c r="P4" s="193"/>
-      <c r="Q4" s="193"/>
-      <c r="R4" s="193"/>
-      <c r="S4" s="193"/>
-      <c r="T4" s="193"/>
-      <c r="U4" s="193">
+      <c r="O4" s="190"/>
+      <c r="P4" s="190"/>
+      <c r="Q4" s="190"/>
+      <c r="R4" s="190"/>
+      <c r="S4" s="190"/>
+      <c r="T4" s="190"/>
+      <c r="U4" s="190">
         <f>190+190</f>
         <v>380</v>
       </c>
-      <c r="V4" s="193"/>
-      <c r="W4" s="193">
+      <c r="V4" s="190"/>
+      <c r="W4" s="190">
         <f>1000+3865</f>
         <v>4865</v>
       </c>
-      <c r="X4" s="193">
+      <c r="X4" s="190">
         <v>20000</v>
       </c>
-      <c r="Y4" s="193"/>
-      <c r="Z4" s="193"/>
-      <c r="AA4" s="194"/>
-      <c r="AB4" s="174">
+      <c r="Y4" s="190"/>
+      <c r="Z4" s="190"/>
+      <c r="AA4" s="191"/>
+      <c r="AB4" s="171">
         <f>SUM(C4:AA4)</f>
         <v>31160.760000000002</v>
       </c>
-      <c r="AC4" s="166">
+      <c r="AC4" s="163">
         <v>142200.85999999999</v>
       </c>
-      <c r="AD4" s="230"/>
+      <c r="AD4" s="221"/>
     </row>
     <row r="5" spans="1:52" ht="15.75">
-      <c r="A5" s="199">
+      <c r="A5" s="196">
         <v>6</v>
       </c>
-      <c r="B5" s="175" t="s">
+      <c r="B5" s="172" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="200"/>
-      <c r="D5" s="200"/>
-      <c r="E5" s="200"/>
-      <c r="F5" s="200"/>
-      <c r="G5" s="200"/>
-      <c r="H5" s="200"/>
-      <c r="I5" s="200">
+      <c r="C5" s="197"/>
+      <c r="D5" s="197"/>
+      <c r="E5" s="197"/>
+      <c r="F5" s="197"/>
+      <c r="G5" s="197"/>
+      <c r="H5" s="197"/>
+      <c r="I5" s="197">
         <f>5020+655+6960+1134</f>
         <v>13769</v>
       </c>
-      <c r="J5" s="200"/>
-      <c r="K5" s="200"/>
-      <c r="L5" s="200"/>
-      <c r="M5" s="200"/>
-      <c r="N5" s="200"/>
-      <c r="O5" s="200">
+      <c r="J5" s="197"/>
+      <c r="K5" s="197"/>
+      <c r="L5" s="197"/>
+      <c r="M5" s="197"/>
+      <c r="N5" s="197"/>
+      <c r="O5" s="197">
         <f>1930+3470</f>
         <v>5400</v>
       </c>
-      <c r="P5" s="200">
+      <c r="P5" s="197">
         <v>11093</v>
       </c>
-      <c r="Q5" s="200"/>
-      <c r="R5" s="200"/>
-      <c r="S5" s="200"/>
-      <c r="T5" s="200"/>
-      <c r="U5" s="200">
+      <c r="Q5" s="197"/>
+      <c r="R5" s="197"/>
+      <c r="S5" s="197"/>
+      <c r="T5" s="197"/>
+      <c r="U5" s="197">
         <f>190+190</f>
         <v>380</v>
       </c>
-      <c r="V5" s="200"/>
-      <c r="W5" s="200">
+      <c r="V5" s="197"/>
+      <c r="W5" s="197">
         <f>4500+11525</f>
         <v>16025</v>
       </c>
-      <c r="X5" s="200"/>
-      <c r="Y5" s="200"/>
-      <c r="Z5" s="200">
+      <c r="X5" s="197"/>
+      <c r="Y5" s="197"/>
+      <c r="Z5" s="197">
         <f>1000</f>
         <v>1000</v>
       </c>
-      <c r="AA5" s="201"/>
-      <c r="AB5" s="174">
+      <c r="AA5" s="198"/>
+      <c r="AB5" s="171">
         <f>SUM(C5:AA5)</f>
         <v>47667</v>
       </c>
-      <c r="AC5" s="168"/>
-      <c r="AD5" s="230"/>
+      <c r="AC5" s="165"/>
+      <c r="AD5" s="221"/>
     </row>
     <row r="6" spans="1:52" ht="16.5" thickBot="1">
-      <c r="A6" s="197">
+      <c r="A6" s="194">
         <v>7</v>
       </c>
-      <c r="B6" s="198" t="s">
+      <c r="B6" s="195" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="195"/>
-      <c r="D6" s="195"/>
-      <c r="E6" s="195"/>
-      <c r="F6" s="195"/>
-      <c r="G6" s="195"/>
-      <c r="H6" s="195"/>
-      <c r="I6" s="195">
+      <c r="C6" s="192"/>
+      <c r="D6" s="192"/>
+      <c r="E6" s="192"/>
+      <c r="F6" s="192"/>
+      <c r="G6" s="192"/>
+      <c r="H6" s="192"/>
+      <c r="I6" s="192">
         <f>4210+461</f>
         <v>4671</v>
       </c>
-      <c r="J6" s="195">
+      <c r="J6" s="192">
         <f>290</f>
         <v>290</v>
       </c>
-      <c r="K6" s="195"/>
-      <c r="L6" s="195"/>
-      <c r="M6" s="195"/>
-      <c r="N6" s="195"/>
-      <c r="O6" s="195"/>
-      <c r="P6" s="195"/>
-      <c r="Q6" s="195">
+      <c r="K6" s="192"/>
+      <c r="L6" s="192"/>
+      <c r="M6" s="192"/>
+      <c r="N6" s="192"/>
+      <c r="O6" s="192"/>
+      <c r="P6" s="192"/>
+      <c r="Q6" s="192">
         <f>300</f>
         <v>300</v>
       </c>
-      <c r="R6" s="195"/>
-      <c r="S6" s="195"/>
-      <c r="T6" s="195"/>
-      <c r="U6" s="195">
+      <c r="R6" s="192"/>
+      <c r="S6" s="192"/>
+      <c r="T6" s="192"/>
+      <c r="U6" s="192">
         <f>391</f>
         <v>391</v>
       </c>
-      <c r="V6" s="195"/>
-      <c r="W6" s="195"/>
-      <c r="X6" s="195">
+      <c r="V6" s="192"/>
+      <c r="W6" s="192"/>
+      <c r="X6" s="192">
         <f>3807</f>
         <v>3807</v>
       </c>
-      <c r="Y6" s="195"/>
-      <c r="Z6" s="195"/>
-      <c r="AA6" s="196"/>
-      <c r="AB6" s="174">
+      <c r="Y6" s="192"/>
+      <c r="Z6" s="192"/>
+      <c r="AA6" s="193"/>
+      <c r="AB6" s="171">
         <f t="shared" ref="AB6:AB16" si="0">SUM(C6:AA6)</f>
         <v>9459</v>
       </c>
-      <c r="AC6" s="168"/>
-      <c r="AD6" s="230"/>
+      <c r="AC6" s="165"/>
+      <c r="AD6" s="221"/>
     </row>
     <row r="7" spans="1:52" ht="15.75">
-      <c r="A7" s="189">
+      <c r="A7" s="186">
         <v>8</v>
       </c>
-      <c r="B7" s="190" t="s">
+      <c r="B7" s="187" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="191">
+      <c r="C7" s="188">
         <f>273.98</f>
         <v>273.98</v>
       </c>
-      <c r="D7" s="191">
+      <c r="D7" s="188">
         <f>556.94</f>
         <v>556.94000000000005</v>
       </c>
-      <c r="E7" s="191"/>
-      <c r="F7" s="191"/>
-      <c r="G7" s="191"/>
-      <c r="H7" s="191"/>
-      <c r="I7" s="191"/>
-      <c r="J7" s="191"/>
-      <c r="K7" s="191"/>
-      <c r="L7" s="191"/>
-      <c r="M7" s="191">
+      <c r="E7" s="188"/>
+      <c r="F7" s="188"/>
+      <c r="G7" s="188"/>
+      <c r="H7" s="188"/>
+      <c r="I7" s="188"/>
+      <c r="J7" s="188"/>
+      <c r="K7" s="188"/>
+      <c r="L7" s="188"/>
+      <c r="M7" s="188">
         <f>2001+69</f>
         <v>2070</v>
       </c>
-      <c r="N7" s="191"/>
-      <c r="O7" s="191"/>
-      <c r="P7" s="191"/>
-      <c r="Q7" s="191"/>
-      <c r="R7" s="191"/>
-      <c r="S7" s="191"/>
-      <c r="T7" s="191"/>
-      <c r="U7" s="191">
+      <c r="N7" s="188"/>
+      <c r="O7" s="188"/>
+      <c r="P7" s="188"/>
+      <c r="Q7" s="188"/>
+      <c r="R7" s="188"/>
+      <c r="S7" s="188"/>
+      <c r="T7" s="188"/>
+      <c r="U7" s="188">
         <f>182</f>
         <v>182</v>
       </c>
-      <c r="V7" s="191"/>
-      <c r="W7" s="191"/>
-      <c r="X7" s="191"/>
-      <c r="Y7" s="191"/>
-      <c r="Z7" s="191"/>
-      <c r="AA7" s="192"/>
+      <c r="V7" s="188"/>
+      <c r="W7" s="188"/>
+      <c r="X7" s="188"/>
+      <c r="Y7" s="188"/>
+      <c r="Z7" s="188"/>
+      <c r="AA7" s="189"/>
       <c r="AB7" s="15">
         <f t="shared" si="0"/>
         <v>3082.92</v>
       </c>
-      <c r="AC7" s="168">
+      <c r="AC7" s="165">
         <v>2000</v>
       </c>
-      <c r="AD7" s="230"/>
+      <c r="AD7" s="221"/>
     </row>
     <row r="8" spans="1:52" ht="15" customHeight="1">
       <c r="A8" s="11">
@@ -11486,40 +11522,40 @@
       <c r="B8" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="176"/>
-      <c r="D8" s="176"/>
-      <c r="E8" s="176"/>
-      <c r="F8" s="176">
+      <c r="C8" s="173"/>
+      <c r="D8" s="173"/>
+      <c r="E8" s="173"/>
+      <c r="F8" s="173">
         <f>2946.51</f>
         <v>2946.51</v>
       </c>
-      <c r="G8" s="176"/>
-      <c r="H8" s="176"/>
-      <c r="I8" s="176"/>
-      <c r="J8" s="176"/>
-      <c r="K8" s="176"/>
-      <c r="L8" s="176"/>
-      <c r="M8" s="176"/>
-      <c r="N8" s="176"/>
-      <c r="O8" s="176"/>
-      <c r="P8" s="176"/>
-      <c r="Q8" s="176"/>
-      <c r="R8" s="176"/>
-      <c r="S8" s="176"/>
-      <c r="T8" s="176"/>
-      <c r="U8" s="176"/>
-      <c r="V8" s="176"/>
-      <c r="W8" s="176"/>
-      <c r="X8" s="176"/>
-      <c r="Y8" s="176"/>
-      <c r="Z8" s="176"/>
-      <c r="AA8" s="177"/>
+      <c r="G8" s="173"/>
+      <c r="H8" s="173"/>
+      <c r="I8" s="173"/>
+      <c r="J8" s="173"/>
+      <c r="K8" s="173"/>
+      <c r="L8" s="173"/>
+      <c r="M8" s="173"/>
+      <c r="N8" s="173"/>
+      <c r="O8" s="173"/>
+      <c r="P8" s="173"/>
+      <c r="Q8" s="173"/>
+      <c r="R8" s="173"/>
+      <c r="S8" s="173"/>
+      <c r="T8" s="173"/>
+      <c r="U8" s="173"/>
+      <c r="V8" s="173"/>
+      <c r="W8" s="173"/>
+      <c r="X8" s="173"/>
+      <c r="Y8" s="173"/>
+      <c r="Z8" s="173"/>
+      <c r="AA8" s="174"/>
       <c r="AB8" s="15">
         <f t="shared" si="0"/>
         <v>2946.51</v>
       </c>
-      <c r="AC8" s="168"/>
-      <c r="AD8" s="230"/>
+      <c r="AC8" s="165"/>
+      <c r="AD8" s="221"/>
     </row>
     <row r="9" spans="1:52" ht="15.75">
       <c r="A9" s="17">
@@ -11528,43 +11564,43 @@
       <c r="B9" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="178">
+      <c r="C9" s="175">
         <f>1177.84</f>
         <v>1177.8399999999999</v>
       </c>
-      <c r="D9" s="178"/>
-      <c r="E9" s="178"/>
-      <c r="F9" s="178"/>
-      <c r="G9" s="178"/>
-      <c r="H9" s="178"/>
-      <c r="I9" s="178"/>
-      <c r="J9" s="178"/>
-      <c r="K9" s="178"/>
-      <c r="L9" s="178"/>
-      <c r="M9" s="178"/>
-      <c r="N9" s="178"/>
-      <c r="O9" s="178"/>
-      <c r="P9" s="178"/>
-      <c r="Q9" s="178"/>
-      <c r="R9" s="178"/>
-      <c r="S9" s="178"/>
-      <c r="T9" s="178"/>
-      <c r="U9" s="178"/>
-      <c r="V9" s="178"/>
-      <c r="W9" s="178"/>
-      <c r="X9" s="178">
+      <c r="D9" s="175"/>
+      <c r="E9" s="175"/>
+      <c r="F9" s="175"/>
+      <c r="G9" s="175"/>
+      <c r="H9" s="175"/>
+      <c r="I9" s="175"/>
+      <c r="J9" s="175"/>
+      <c r="K9" s="175"/>
+      <c r="L9" s="175"/>
+      <c r="M9" s="175"/>
+      <c r="N9" s="175"/>
+      <c r="O9" s="175"/>
+      <c r="P9" s="175"/>
+      <c r="Q9" s="175"/>
+      <c r="R9" s="175"/>
+      <c r="S9" s="175"/>
+      <c r="T9" s="175"/>
+      <c r="U9" s="175"/>
+      <c r="V9" s="175"/>
+      <c r="W9" s="175"/>
+      <c r="X9" s="175">
         <f>500</f>
         <v>500</v>
       </c>
-      <c r="Y9" s="178"/>
-      <c r="Z9" s="178"/>
-      <c r="AA9" s="179"/>
+      <c r="Y9" s="175"/>
+      <c r="Z9" s="175"/>
+      <c r="AA9" s="176"/>
       <c r="AB9" s="15">
         <f t="shared" si="0"/>
         <v>1677.84</v>
       </c>
-      <c r="AC9" s="168"/>
-      <c r="AD9" s="230"/>
+      <c r="AC9" s="165"/>
+      <c r="AD9" s="221"/>
     </row>
     <row r="10" spans="1:52" ht="15.75">
       <c r="A10" s="11">
@@ -11573,64 +11609,64 @@
       <c r="B10" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="176">
+      <c r="C10" s="173">
         <f>1172.97</f>
         <v>1172.97</v>
       </c>
-      <c r="D10" s="176">
+      <c r="D10" s="173">
         <f>818.93</f>
         <v>818.93</v>
       </c>
-      <c r="E10" s="176">
+      <c r="E10" s="173">
         <v>1549.9</v>
       </c>
-      <c r="F10" s="176">
+      <c r="F10" s="173">
         <f>1640</f>
         <v>1640</v>
       </c>
-      <c r="G10" s="176"/>
-      <c r="H10" s="176"/>
-      <c r="I10" s="176"/>
-      <c r="J10" s="176"/>
-      <c r="K10" s="176"/>
-      <c r="L10" s="176"/>
-      <c r="M10" s="176"/>
-      <c r="N10" s="176"/>
-      <c r="O10" s="176"/>
-      <c r="P10" s="176"/>
-      <c r="Q10" s="176"/>
-      <c r="R10" s="176">
+      <c r="G10" s="173"/>
+      <c r="H10" s="173"/>
+      <c r="I10" s="173"/>
+      <c r="J10" s="173"/>
+      <c r="K10" s="173"/>
+      <c r="L10" s="173"/>
+      <c r="M10" s="173"/>
+      <c r="N10" s="173"/>
+      <c r="O10" s="173"/>
+      <c r="P10" s="173"/>
+      <c r="Q10" s="173"/>
+      <c r="R10" s="173">
         <f>1554.88</f>
         <v>1554.88</v>
       </c>
-      <c r="S10" s="176"/>
-      <c r="T10" s="176"/>
-      <c r="U10" s="176"/>
-      <c r="V10" s="176">
+      <c r="S10" s="173"/>
+      <c r="T10" s="173"/>
+      <c r="U10" s="173"/>
+      <c r="V10" s="173">
         <v>2160</v>
       </c>
-      <c r="W10" s="176">
+      <c r="W10" s="173">
         <f>137+132+5+132+5</f>
         <v>411</v>
       </c>
-      <c r="X10" s="176">
+      <c r="X10" s="173">
         <f>363.5</f>
         <v>363.5</v>
       </c>
-      <c r="Y10" s="176">
+      <c r="Y10" s="173">
         <f>810.96</f>
         <v>810.96</v>
       </c>
-      <c r="Z10" s="176"/>
-      <c r="AA10" s="177"/>
+      <c r="Z10" s="173"/>
+      <c r="AA10" s="174"/>
       <c r="AB10" s="15">
         <f t="shared" si="0"/>
         <v>10482.14</v>
       </c>
-      <c r="AC10" s="168">
+      <c r="AC10" s="165">
         <v>55867</v>
       </c>
-      <c r="AD10" s="230"/>
+      <c r="AD10" s="221"/>
     </row>
     <row r="11" spans="1:52" ht="15.75">
       <c r="A11" s="17">
@@ -11639,52 +11675,52 @@
       <c r="B11" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="178"/>
-      <c r="D11" s="178"/>
-      <c r="E11" s="178"/>
-      <c r="F11" s="178"/>
-      <c r="G11" s="178"/>
-      <c r="H11" s="178"/>
-      <c r="I11" s="178"/>
-      <c r="J11" s="178"/>
-      <c r="K11" s="178"/>
-      <c r="L11" s="178"/>
-      <c r="M11" s="178"/>
-      <c r="N11" s="178">
+      <c r="C11" s="175"/>
+      <c r="D11" s="175"/>
+      <c r="E11" s="175"/>
+      <c r="F11" s="175"/>
+      <c r="G11" s="175"/>
+      <c r="H11" s="175"/>
+      <c r="I11" s="175"/>
+      <c r="J11" s="175"/>
+      <c r="K11" s="175"/>
+      <c r="L11" s="175"/>
+      <c r="M11" s="175"/>
+      <c r="N11" s="175">
         <v>700</v>
       </c>
-      <c r="O11" s="178"/>
-      <c r="P11" s="178"/>
-      <c r="Q11" s="178"/>
-      <c r="R11" s="178"/>
-      <c r="S11" s="178"/>
-      <c r="T11" s="178"/>
-      <c r="U11" s="178"/>
-      <c r="V11" s="178">
+      <c r="O11" s="175"/>
+      <c r="P11" s="175"/>
+      <c r="Q11" s="175"/>
+      <c r="R11" s="175"/>
+      <c r="S11" s="175"/>
+      <c r="T11" s="175"/>
+      <c r="U11" s="175"/>
+      <c r="V11" s="175">
         <v>290.02999999999997</v>
       </c>
-      <c r="W11" s="178"/>
-      <c r="X11" s="178">
+      <c r="W11" s="175"/>
+      <c r="X11" s="175">
         <v>20000</v>
       </c>
-      <c r="Y11" s="178"/>
-      <c r="Z11" s="178"/>
-      <c r="AA11" s="179"/>
+      <c r="Y11" s="175"/>
+      <c r="Z11" s="175"/>
+      <c r="AA11" s="176"/>
       <c r="AB11" s="15">
         <f t="shared" si="0"/>
         <v>20990.03</v>
       </c>
-      <c r="AC11" s="168">
+      <c r="AC11" s="165">
         <v>3000</v>
       </c>
-      <c r="AD11" s="230"/>
-      <c r="AH11" s="231" t="s">
+      <c r="AD11" s="221"/>
+      <c r="AH11" s="222" t="s">
         <v>83</v>
       </c>
-      <c r="AI11" s="231"/>
-      <c r="AJ11" s="231"/>
-      <c r="AK11" s="231"/>
-      <c r="AL11" s="231"/>
+      <c r="AI11" s="222"/>
+      <c r="AJ11" s="222"/>
+      <c r="AK11" s="222"/>
+      <c r="AL11" s="222"/>
     </row>
     <row r="12" spans="1:52" ht="15.75">
       <c r="A12" s="11">
@@ -11693,52 +11729,52 @@
       <c r="B12" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="176"/>
-      <c r="D12" s="176"/>
-      <c r="E12" s="176"/>
-      <c r="F12" s="176"/>
-      <c r="G12" s="176"/>
-      <c r="H12" s="176"/>
-      <c r="I12" s="176"/>
-      <c r="J12" s="176"/>
-      <c r="K12" s="176"/>
-      <c r="L12" s="176"/>
-      <c r="M12" s="176"/>
-      <c r="N12" s="176">
+      <c r="C12" s="173"/>
+      <c r="D12" s="173"/>
+      <c r="E12" s="173"/>
+      <c r="F12" s="173"/>
+      <c r="G12" s="173"/>
+      <c r="H12" s="173"/>
+      <c r="I12" s="173"/>
+      <c r="J12" s="173"/>
+      <c r="K12" s="173"/>
+      <c r="L12" s="173"/>
+      <c r="M12" s="173"/>
+      <c r="N12" s="173">
         <v>990</v>
       </c>
-      <c r="O12" s="176"/>
-      <c r="P12" s="176"/>
-      <c r="Q12" s="176"/>
-      <c r="R12" s="176"/>
-      <c r="S12" s="176"/>
-      <c r="T12" s="176"/>
-      <c r="U12" s="176">
+      <c r="O12" s="173"/>
+      <c r="P12" s="173"/>
+      <c r="Q12" s="173"/>
+      <c r="R12" s="173"/>
+      <c r="S12" s="173"/>
+      <c r="T12" s="173"/>
+      <c r="U12" s="173">
         <v>529</v>
       </c>
-      <c r="V12" s="176"/>
-      <c r="W12" s="176">
+      <c r="V12" s="173"/>
+      <c r="W12" s="173">
         <f>2500+623+200</f>
         <v>3323</v>
       </c>
-      <c r="X12" s="176">
+      <c r="X12" s="173">
         <f>1844</f>
         <v>1844</v>
       </c>
-      <c r="Y12" s="176"/>
-      <c r="Z12" s="176"/>
-      <c r="AA12" s="177"/>
+      <c r="Y12" s="173"/>
+      <c r="Z12" s="173"/>
+      <c r="AA12" s="174"/>
       <c r="AB12" s="15">
         <f t="shared" si="0"/>
         <v>6686</v>
       </c>
-      <c r="AC12" s="168"/>
-      <c r="AD12" s="230"/>
-      <c r="AH12" s="231"/>
-      <c r="AI12" s="231"/>
-      <c r="AJ12" s="231"/>
-      <c r="AK12" s="231"/>
-      <c r="AL12" s="231"/>
+      <c r="AC12" s="165"/>
+      <c r="AD12" s="221"/>
+      <c r="AH12" s="222"/>
+      <c r="AI12" s="222"/>
+      <c r="AJ12" s="222"/>
+      <c r="AK12" s="222"/>
+      <c r="AL12" s="222"/>
     </row>
     <row r="13" spans="1:52" ht="15.75">
       <c r="A13" s="17">
@@ -11747,50 +11783,50 @@
       <c r="B13" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="178"/>
-      <c r="D13" s="178"/>
-      <c r="E13" s="178"/>
-      <c r="F13" s="178"/>
-      <c r="G13" s="178"/>
-      <c r="H13" s="178"/>
-      <c r="I13" s="178"/>
-      <c r="J13" s="178"/>
-      <c r="K13" s="178"/>
-      <c r="L13" s="178"/>
-      <c r="M13" s="178"/>
-      <c r="N13" s="178"/>
-      <c r="O13" s="178"/>
-      <c r="P13" s="178"/>
-      <c r="Q13" s="178"/>
-      <c r="R13" s="178"/>
-      <c r="S13" s="178"/>
-      <c r="T13" s="178"/>
-      <c r="U13" s="178">
+      <c r="C13" s="175"/>
+      <c r="D13" s="175"/>
+      <c r="E13" s="175"/>
+      <c r="F13" s="175"/>
+      <c r="G13" s="175"/>
+      <c r="H13" s="175"/>
+      <c r="I13" s="175"/>
+      <c r="J13" s="175"/>
+      <c r="K13" s="175"/>
+      <c r="L13" s="175"/>
+      <c r="M13" s="175"/>
+      <c r="N13" s="175"/>
+      <c r="O13" s="175"/>
+      <c r="P13" s="175"/>
+      <c r="Q13" s="175"/>
+      <c r="R13" s="175"/>
+      <c r="S13" s="175"/>
+      <c r="T13" s="175"/>
+      <c r="U13" s="175">
         <v>770</v>
       </c>
-      <c r="V13" s="178"/>
-      <c r="W13" s="178"/>
-      <c r="X13" s="178">
+      <c r="V13" s="175"/>
+      <c r="W13" s="175"/>
+      <c r="X13" s="175">
         <f>990</f>
         <v>990</v>
       </c>
-      <c r="Y13" s="178">
+      <c r="Y13" s="175">
         <f>2175</f>
         <v>2175</v>
       </c>
-      <c r="Z13" s="178"/>
-      <c r="AA13" s="179"/>
+      <c r="Z13" s="175"/>
+      <c r="AA13" s="176"/>
       <c r="AB13" s="15">
         <f t="shared" si="0"/>
         <v>3935</v>
       </c>
-      <c r="AC13" s="168"/>
-      <c r="AD13" s="230"/>
-      <c r="AH13" s="231"/>
-      <c r="AI13" s="231"/>
-      <c r="AJ13" s="231"/>
-      <c r="AK13" s="231"/>
-      <c r="AL13" s="231"/>
+      <c r="AC13" s="165"/>
+      <c r="AD13" s="221"/>
+      <c r="AH13" s="222"/>
+      <c r="AI13" s="222"/>
+      <c r="AJ13" s="222"/>
+      <c r="AK13" s="222"/>
+      <c r="AL13" s="222"/>
     </row>
     <row r="14" spans="1:52" ht="18">
       <c r="A14" s="11">
@@ -11799,45 +11835,45 @@
       <c r="B14" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="176"/>
-      <c r="D14" s="176"/>
-      <c r="E14" s="176"/>
-      <c r="F14" s="176"/>
-      <c r="G14" s="176"/>
-      <c r="H14" s="176"/>
-      <c r="I14" s="176"/>
-      <c r="J14" s="176"/>
-      <c r="K14" s="176"/>
-      <c r="L14" s="176"/>
-      <c r="M14" s="176"/>
-      <c r="N14" s="176">
+      <c r="C14" s="173"/>
+      <c r="D14" s="173"/>
+      <c r="E14" s="173"/>
+      <c r="F14" s="173"/>
+      <c r="G14" s="173"/>
+      <c r="H14" s="173"/>
+      <c r="I14" s="173"/>
+      <c r="J14" s="173"/>
+      <c r="K14" s="173"/>
+      <c r="L14" s="173"/>
+      <c r="M14" s="173"/>
+      <c r="N14" s="173">
         <v>750</v>
       </c>
-      <c r="O14" s="176"/>
-      <c r="P14" s="176"/>
-      <c r="Q14" s="176"/>
-      <c r="R14" s="176"/>
-      <c r="S14" s="176"/>
-      <c r="T14" s="176"/>
-      <c r="U14" s="176"/>
-      <c r="V14" s="176"/>
-      <c r="W14" s="176"/>
-      <c r="X14" s="176"/>
-      <c r="Y14" s="176"/>
-      <c r="Z14" s="176"/>
-      <c r="AA14" s="177"/>
+      <c r="O14" s="173"/>
+      <c r="P14" s="173"/>
+      <c r="Q14" s="173"/>
+      <c r="R14" s="173"/>
+      <c r="S14" s="173"/>
+      <c r="T14" s="173"/>
+      <c r="U14" s="173"/>
+      <c r="V14" s="173"/>
+      <c r="W14" s="173"/>
+      <c r="X14" s="173"/>
+      <c r="Y14" s="173"/>
+      <c r="Z14" s="173"/>
+      <c r="AA14" s="174"/>
       <c r="AB14" s="15">
         <f t="shared" si="0"/>
         <v>750</v>
       </c>
-      <c r="AC14" s="168"/>
-      <c r="AD14" s="230"/>
-      <c r="AH14" s="227" t="s">
+      <c r="AC14" s="165"/>
+      <c r="AD14" s="221"/>
+      <c r="AH14" s="218" t="s">
         <v>62</v>
       </c>
-      <c r="AI14" s="227"/>
-      <c r="AJ14" s="227"/>
-      <c r="AK14" s="227"/>
+      <c r="AI14" s="218"/>
+      <c r="AJ14" s="218"/>
+      <c r="AK14" s="218"/>
       <c r="AL14" s="22">
         <f>AC4+AC20+AC24+AC10</f>
         <v>198067.86</v>
@@ -11850,58 +11886,58 @@
       <c r="B15" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="178"/>
-      <c r="D15" s="178"/>
-      <c r="E15" s="178"/>
-      <c r="F15" s="178"/>
-      <c r="G15" s="178"/>
-      <c r="H15" s="178">
+      <c r="C15" s="175"/>
+      <c r="D15" s="175"/>
+      <c r="E15" s="175"/>
+      <c r="F15" s="175"/>
+      <c r="G15" s="175"/>
+      <c r="H15" s="175">
         <f>2520</f>
         <v>2520</v>
       </c>
-      <c r="I15" s="178"/>
-      <c r="J15" s="178"/>
-      <c r="K15" s="178"/>
-      <c r="L15" s="178"/>
-      <c r="M15" s="178"/>
-      <c r="N15" s="178">
+      <c r="I15" s="175"/>
+      <c r="J15" s="175"/>
+      <c r="K15" s="175"/>
+      <c r="L15" s="175"/>
+      <c r="M15" s="175"/>
+      <c r="N15" s="175">
         <f>499</f>
         <v>499</v>
       </c>
-      <c r="O15" s="178"/>
-      <c r="P15" s="178"/>
-      <c r="Q15" s="178"/>
-      <c r="R15" s="178"/>
-      <c r="S15" s="178"/>
-      <c r="T15" s="178"/>
-      <c r="U15" s="178"/>
-      <c r="V15" s="178"/>
-      <c r="W15" s="178">
+      <c r="O15" s="175"/>
+      <c r="P15" s="175"/>
+      <c r="Q15" s="175"/>
+      <c r="R15" s="175"/>
+      <c r="S15" s="175"/>
+      <c r="T15" s="175"/>
+      <c r="U15" s="175"/>
+      <c r="V15" s="175"/>
+      <c r="W15" s="175">
         <f>2000+3000</f>
         <v>5000</v>
       </c>
-      <c r="X15" s="178">
+      <c r="X15" s="175">
         <f>2300</f>
         <v>2300</v>
       </c>
-      <c r="Y15" s="178"/>
-      <c r="Z15" s="178"/>
-      <c r="AA15" s="179"/>
+      <c r="Y15" s="175"/>
+      <c r="Z15" s="175"/>
+      <c r="AA15" s="176"/>
       <c r="AB15" s="15">
         <f t="shared" si="0"/>
         <v>10319</v>
       </c>
-      <c r="AC15" s="166"/>
-      <c r="AD15" s="230"/>
-      <c r="AH15" s="227" t="s">
+      <c r="AC15" s="163"/>
+      <c r="AD15" s="221"/>
+      <c r="AH15" s="218" t="s">
         <v>2</v>
       </c>
-      <c r="AI15" s="227"/>
-      <c r="AJ15" s="227"/>
-      <c r="AK15" s="227"/>
+      <c r="AI15" s="218"/>
+      <c r="AJ15" s="218"/>
+      <c r="AK15" s="218"/>
       <c r="AL15" s="22">
-        <f>AC21</f>
-        <v>0</v>
+        <f>SUM(AC7,AC11)</f>
+        <v>5000</v>
       </c>
     </row>
     <row r="16" spans="1:52" ht="18">
@@ -11911,58 +11947,57 @@
       <c r="B16" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="176"/>
-      <c r="D16" s="176">
+      <c r="C16" s="173"/>
+      <c r="D16" s="173">
         <f>131.97+375.95</f>
         <v>507.91999999999996</v>
       </c>
-      <c r="E16" s="176"/>
-      <c r="F16" s="176">
+      <c r="E16" s="173"/>
+      <c r="F16" s="173">
         <f>3668.34</f>
         <v>3668.34</v>
       </c>
-      <c r="G16" s="176"/>
-      <c r="H16" s="176">
+      <c r="G16" s="173"/>
+      <c r="H16" s="173">
         <f>50+1619+1096</f>
         <v>2765</v>
       </c>
-      <c r="I16" s="176"/>
-      <c r="J16" s="176"/>
-      <c r="K16" s="176"/>
-      <c r="L16" s="176"/>
-      <c r="M16" s="176"/>
-      <c r="N16" s="176"/>
-      <c r="O16" s="176"/>
-      <c r="P16" s="176"/>
-      <c r="Q16" s="176"/>
-      <c r="R16" s="176"/>
-      <c r="S16" s="176"/>
-      <c r="T16" s="176"/>
-      <c r="U16" s="176"/>
-      <c r="V16" s="176"/>
-      <c r="W16" s="176"/>
-      <c r="X16" s="176">
+      <c r="I16" s="173"/>
+      <c r="J16" s="173"/>
+      <c r="K16" s="173"/>
+      <c r="L16" s="173"/>
+      <c r="M16" s="173"/>
+      <c r="N16" s="173"/>
+      <c r="O16" s="173"/>
+      <c r="P16" s="173"/>
+      <c r="Q16" s="173"/>
+      <c r="R16" s="173"/>
+      <c r="S16" s="173"/>
+      <c r="T16" s="173"/>
+      <c r="U16" s="173"/>
+      <c r="V16" s="173"/>
+      <c r="W16" s="173"/>
+      <c r="X16" s="173">
         <f>960</f>
         <v>960</v>
       </c>
-      <c r="Y16" s="176"/>
-      <c r="Z16" s="176"/>
-      <c r="AA16" s="177"/>
+      <c r="Y16" s="173"/>
+      <c r="Z16" s="173"/>
+      <c r="AA16" s="174"/>
       <c r="AB16" s="15">
         <f t="shared" si="0"/>
         <v>7901.26</v>
       </c>
-      <c r="AC16" s="166"/>
-      <c r="AD16" s="230"/>
-      <c r="AH16" s="227" t="s">
+      <c r="AC16" s="163"/>
+      <c r="AD16" s="221"/>
+      <c r="AH16" s="218" t="s">
         <v>63</v>
       </c>
-      <c r="AI16" s="227"/>
-      <c r="AJ16" s="227"/>
-      <c r="AK16" s="227"/>
-      <c r="AL16" s="22" t="e">
-        <f>AC16+AC29+AC35+#REF!</f>
-        <v>#REF!</v>
+      <c r="AI16" s="218"/>
+      <c r="AJ16" s="218"/>
+      <c r="AK16" s="218"/>
+      <c r="AL16" s="22">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:38" ht="18">
@@ -11972,53 +12007,53 @@
       <c r="B17" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="178">
+      <c r="C17" s="175">
         <v>267.94</v>
       </c>
-      <c r="D17" s="178">
+      <c r="D17" s="175">
         <f>215.78+383.95</f>
         <v>599.73</v>
       </c>
-      <c r="E17" s="178"/>
-      <c r="F17" s="178"/>
-      <c r="G17" s="178"/>
-      <c r="H17" s="178"/>
-      <c r="I17" s="178"/>
-      <c r="J17" s="178"/>
-      <c r="K17" s="178"/>
-      <c r="L17" s="178"/>
-      <c r="M17" s="178"/>
-      <c r="N17" s="178"/>
-      <c r="O17" s="178"/>
-      <c r="P17" s="178"/>
-      <c r="Q17" s="178"/>
-      <c r="R17" s="178"/>
-      <c r="S17" s="178"/>
-      <c r="T17" s="178"/>
-      <c r="U17" s="178"/>
-      <c r="V17" s="178"/>
-      <c r="W17" s="178"/>
-      <c r="X17" s="178">
+      <c r="E17" s="175"/>
+      <c r="F17" s="175"/>
+      <c r="G17" s="175"/>
+      <c r="H17" s="175"/>
+      <c r="I17" s="175"/>
+      <c r="J17" s="175"/>
+      <c r="K17" s="175"/>
+      <c r="L17" s="175"/>
+      <c r="M17" s="175"/>
+      <c r="N17" s="175"/>
+      <c r="O17" s="175"/>
+      <c r="P17" s="175"/>
+      <c r="Q17" s="175"/>
+      <c r="R17" s="175"/>
+      <c r="S17" s="175"/>
+      <c r="T17" s="175"/>
+      <c r="U17" s="175"/>
+      <c r="V17" s="175"/>
+      <c r="W17" s="175"/>
+      <c r="X17" s="175">
         <v>899</v>
       </c>
-      <c r="Y17" s="178"/>
-      <c r="Z17" s="178"/>
-      <c r="AA17" s="179"/>
+      <c r="Y17" s="175"/>
+      <c r="Z17" s="175"/>
+      <c r="AA17" s="176"/>
       <c r="AB17" s="15">
         <f>SUM(C17:AA17)</f>
         <v>1766.67</v>
       </c>
-      <c r="AC17" s="166"/>
-      <c r="AD17" s="230"/>
-      <c r="AH17" s="232" t="s">
+      <c r="AC17" s="163"/>
+      <c r="AD17" s="221"/>
+      <c r="AH17" s="230" t="s">
         <v>67</v>
       </c>
-      <c r="AI17" s="233"/>
-      <c r="AJ17" s="233"/>
-      <c r="AK17" s="234"/>
+      <c r="AI17" s="231"/>
+      <c r="AJ17" s="231"/>
+      <c r="AK17" s="232"/>
       <c r="AL17" s="22">
         <f>SUM(C37:K37)</f>
-        <v>58912.759999999995</v>
+        <v>58461.880000000005</v>
       </c>
     </row>
     <row r="18" spans="1:38" ht="18">
@@ -12028,58 +12063,66 @@
       <c r="B18" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="176"/>
-      <c r="D18" s="176"/>
-      <c r="E18" s="176"/>
-      <c r="F18" s="176"/>
-      <c r="G18" s="176"/>
-      <c r="H18" s="176"/>
-      <c r="I18" s="176"/>
-      <c r="J18" s="176"/>
-      <c r="K18" s="176"/>
-      <c r="L18" s="176"/>
-      <c r="M18" s="176"/>
-      <c r="N18" s="176"/>
-      <c r="O18" s="176"/>
-      <c r="P18" s="176"/>
-      <c r="Q18" s="176"/>
-      <c r="R18" s="176"/>
-      <c r="S18" s="176"/>
-      <c r="T18" s="176"/>
-      <c r="U18" s="176"/>
-      <c r="V18" s="176"/>
-      <c r="W18" s="176">
+      <c r="C18" s="173"/>
+      <c r="D18" s="173">
+        <f>1115.4</f>
+        <v>1115.4000000000001</v>
+      </c>
+      <c r="E18" s="173"/>
+      <c r="F18" s="173"/>
+      <c r="G18" s="173"/>
+      <c r="H18" s="173"/>
+      <c r="I18" s="173"/>
+      <c r="J18" s="173"/>
+      <c r="K18" s="173"/>
+      <c r="L18" s="173"/>
+      <c r="M18" s="173"/>
+      <c r="N18" s="173"/>
+      <c r="O18" s="173"/>
+      <c r="P18" s="173"/>
+      <c r="Q18" s="173"/>
+      <c r="R18" s="173"/>
+      <c r="S18" s="173"/>
+      <c r="T18" s="173"/>
+      <c r="U18" s="173"/>
+      <c r="V18" s="173"/>
+      <c r="W18" s="173">
         <f>8000+11525</f>
         <v>19525</v>
       </c>
-      <c r="X18" s="176"/>
-      <c r="Y18" s="176"/>
-      <c r="Z18" s="176"/>
-      <c r="AA18" s="177"/>
+      <c r="X18" s="173"/>
+      <c r="Y18" s="173"/>
+      <c r="Z18" s="173"/>
+      <c r="AA18" s="174"/>
       <c r="AB18" s="15">
         <f>SUM(C18:AA18)</f>
-        <v>19525</v>
-      </c>
-      <c r="AC18" s="166"/>
-      <c r="AD18" s="230"/>
-      <c r="AH18" s="139"/>
-      <c r="AI18" s="140"/>
-      <c r="AJ18" s="140"/>
-      <c r="AK18" s="141"/>
-      <c r="AL18" s="22"/>
+        <v>20640.400000000001</v>
+      </c>
+      <c r="AC18" s="163"/>
+      <c r="AD18" s="221"/>
+      <c r="AH18" s="230" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI18" s="231"/>
+      <c r="AJ18" s="231"/>
+      <c r="AK18" s="232"/>
+      <c r="AL18" s="22">
+        <f>SUM(L37:Q37)</f>
+        <v>21802</v>
+      </c>
     </row>
     <row r="19" spans="1:38" ht="19.5" customHeight="1">
-      <c r="A19" s="238" t="s">
+      <c r="A19" s="236" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="238"/>
+      <c r="B19" s="236"/>
       <c r="C19" s="23">
         <f>SUM(C4:C18)</f>
         <v>2892.73</v>
       </c>
       <c r="D19" s="23">
         <f t="shared" ref="D19:K19" si="1">SUM(D4:D18)</f>
-        <v>2483.52</v>
+        <v>3598.92</v>
       </c>
       <c r="E19" s="23">
         <f t="shared" si="1"/>
@@ -12175,25 +12218,25 @@
       </c>
       <c r="AB19" s="26">
         <f>SUM(AB4:AB18)</f>
-        <v>178349.13000000003</v>
+        <v>179464.53000000003</v>
       </c>
       <c r="AC19" s="27">
         <f t="shared" ref="AC19" si="4">SUM(AC4:AC17)</f>
         <v>203067.86</v>
       </c>
-      <c r="AD19" s="167">
+      <c r="AD19" s="239">
         <f>AC19-AB19</f>
-        <v>24718.729999999952</v>
-      </c>
-      <c r="AH19" s="227" t="s">
-        <v>84</v>
-      </c>
-      <c r="AI19" s="227"/>
-      <c r="AJ19" s="227"/>
-      <c r="AK19" s="227"/>
+        <v>23603.329999999958</v>
+      </c>
+      <c r="AH19" s="230" t="s">
+        <v>85</v>
+      </c>
+      <c r="AI19" s="231"/>
+      <c r="AJ19" s="231"/>
+      <c r="AK19" s="232"/>
       <c r="AL19" s="22">
-        <f>SUM(L37:Q37)</f>
-        <v>21802</v>
+        <f>W37</f>
+        <v>60674</v>
       </c>
     </row>
     <row r="20" spans="1:38" ht="18">
@@ -12203,48 +12246,50 @@
       <c r="B20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="176"/>
-      <c r="D20" s="176"/>
-      <c r="E20" s="176"/>
-      <c r="F20" s="176"/>
-      <c r="G20" s="176"/>
-      <c r="H20" s="176"/>
-      <c r="I20" s="176"/>
-      <c r="J20" s="176"/>
-      <c r="K20" s="176"/>
-      <c r="L20" s="176"/>
-      <c r="M20" s="176"/>
-      <c r="N20" s="176"/>
-      <c r="O20" s="176"/>
-      <c r="P20" s="176"/>
-      <c r="Q20" s="176"/>
-      <c r="R20" s="176"/>
-      <c r="S20" s="176"/>
-      <c r="T20" s="176"/>
-      <c r="U20" s="176"/>
-      <c r="V20" s="176"/>
-      <c r="W20" s="176"/>
-      <c r="X20" s="176"/>
-      <c r="Y20" s="176"/>
-      <c r="Z20" s="176"/>
-      <c r="AA20" s="177"/>
+      <c r="C20" s="173"/>
+      <c r="D20" s="173"/>
+      <c r="E20" s="173"/>
+      <c r="F20" s="173">
+        <v>1933.72</v>
+      </c>
+      <c r="G20" s="173"/>
+      <c r="H20" s="173"/>
+      <c r="I20" s="173"/>
+      <c r="J20" s="173"/>
+      <c r="K20" s="173"/>
+      <c r="L20" s="173"/>
+      <c r="M20" s="173"/>
+      <c r="N20" s="173"/>
+      <c r="O20" s="173"/>
+      <c r="P20" s="173"/>
+      <c r="Q20" s="173"/>
+      <c r="R20" s="173"/>
+      <c r="S20" s="173"/>
+      <c r="T20" s="173"/>
+      <c r="U20" s="173"/>
+      <c r="V20" s="173"/>
+      <c r="W20" s="173"/>
+      <c r="X20" s="173"/>
+      <c r="Y20" s="173"/>
+      <c r="Z20" s="173"/>
+      <c r="AA20" s="174"/>
       <c r="AB20" s="15">
         <f>SUM(C20:AA20)</f>
-        <v>0</v>
+        <v>1933.72</v>
       </c>
       <c r="AC20" s="16">
         <v>0</v>
       </c>
-      <c r="AD20" s="230"/>
-      <c r="AH20" s="227" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI20" s="227"/>
-      <c r="AJ20" s="227"/>
-      <c r="AK20" s="227"/>
+      <c r="AD20" s="221"/>
+      <c r="AH20" s="230" t="s">
+        <v>86</v>
+      </c>
+      <c r="AI20" s="231"/>
+      <c r="AJ20" s="231"/>
+      <c r="AK20" s="232"/>
       <c r="AL20" s="22">
-        <f>W37</f>
-        <v>60674</v>
+        <f>SUM(U37:V37)</f>
+        <v>5082.03</v>
       </c>
     </row>
     <row r="21" spans="1:38" ht="18">
@@ -12254,99 +12299,87 @@
       <c r="B21" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="178"/>
-      <c r="D21" s="178"/>
-      <c r="E21" s="178"/>
-      <c r="F21" s="239">
-        <v>3500</v>
-      </c>
-      <c r="G21" s="178"/>
-      <c r="H21" s="178"/>
-      <c r="I21" s="178"/>
-      <c r="J21" s="178"/>
-      <c r="K21" s="178"/>
-      <c r="L21" s="178"/>
-      <c r="M21" s="178"/>
-      <c r="N21" s="178"/>
-      <c r="O21" s="178"/>
-      <c r="P21" s="178"/>
-      <c r="Q21" s="178"/>
-      <c r="R21" s="178"/>
-      <c r="S21" s="178"/>
-      <c r="T21" s="178"/>
-      <c r="U21" s="178"/>
-      <c r="V21" s="178"/>
-      <c r="W21" s="178"/>
-      <c r="X21" s="178"/>
-      <c r="Y21" s="178"/>
-      <c r="Z21" s="178"/>
-      <c r="AA21" s="179"/>
+      <c r="C21" s="175"/>
+      <c r="D21" s="175"/>
+      <c r="E21" s="175"/>
+      <c r="F21" s="175"/>
+      <c r="G21" s="175"/>
+      <c r="H21" s="175"/>
+      <c r="I21" s="175"/>
+      <c r="J21" s="175"/>
+      <c r="K21" s="175"/>
+      <c r="L21" s="175"/>
+      <c r="M21" s="175"/>
+      <c r="N21" s="175"/>
+      <c r="O21" s="175"/>
+      <c r="P21" s="175"/>
+      <c r="Q21" s="175"/>
+      <c r="R21" s="175"/>
+      <c r="S21" s="175"/>
+      <c r="T21" s="175"/>
+      <c r="U21" s="175"/>
+      <c r="V21" s="175"/>
+      <c r="W21" s="175"/>
+      <c r="X21" s="175"/>
+      <c r="Y21" s="175"/>
+      <c r="Z21" s="175"/>
+      <c r="AA21" s="176"/>
       <c r="AB21" s="15">
         <f>SUM(C21:AA21)</f>
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="AC21" s="21"/>
-      <c r="AD21" s="230"/>
+      <c r="AD21" s="221"/>
       <c r="AF21" s="29"/>
-      <c r="AH21" s="227" t="s">
-        <v>86</v>
-      </c>
-      <c r="AI21" s="227"/>
-      <c r="AJ21" s="227"/>
-      <c r="AK21" s="227"/>
-      <c r="AL21" s="22">
-        <f>SUM(U37:V37)</f>
-        <v>5082.03</v>
-      </c>
-    </row>
-    <row r="22" spans="1:38" ht="18">
+      <c r="AH21" s="233" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI21" s="233"/>
+      <c r="AJ21" s="233"/>
+      <c r="AK21" s="233"/>
+      <c r="AL21" s="169">
+        <f>T37</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:38" ht="15.75">
       <c r="A22" s="11">
         <v>22</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="176"/>
-      <c r="D22" s="176"/>
-      <c r="E22" s="176"/>
-      <c r="F22" s="176"/>
-      <c r="G22" s="176"/>
-      <c r="H22" s="176"/>
-      <c r="I22" s="176"/>
-      <c r="J22" s="176"/>
-      <c r="K22" s="176"/>
-      <c r="L22" s="176"/>
-      <c r="M22" s="176"/>
-      <c r="N22" s="176"/>
-      <c r="O22" s="176"/>
-      <c r="P22" s="176"/>
-      <c r="Q22" s="176"/>
-      <c r="R22" s="176"/>
-      <c r="S22" s="176"/>
-      <c r="T22" s="176"/>
-      <c r="U22" s="176"/>
-      <c r="V22" s="176"/>
-      <c r="W22" s="176"/>
-      <c r="X22" s="176"/>
-      <c r="Y22" s="176"/>
-      <c r="Z22" s="176"/>
-      <c r="AA22" s="177"/>
+      <c r="C22" s="173"/>
+      <c r="D22" s="173"/>
+      <c r="E22" s="173"/>
+      <c r="F22" s="173"/>
+      <c r="G22" s="173"/>
+      <c r="H22" s="173"/>
+      <c r="I22" s="173"/>
+      <c r="J22" s="173"/>
+      <c r="K22" s="173"/>
+      <c r="L22" s="173"/>
+      <c r="M22" s="173"/>
+      <c r="N22" s="173"/>
+      <c r="O22" s="173"/>
+      <c r="P22" s="173"/>
+      <c r="Q22" s="173"/>
+      <c r="R22" s="173"/>
+      <c r="S22" s="173"/>
+      <c r="T22" s="173"/>
+      <c r="U22" s="173"/>
+      <c r="V22" s="173"/>
+      <c r="W22" s="173"/>
+      <c r="X22" s="173"/>
+      <c r="Y22" s="173"/>
+      <c r="Z22" s="173"/>
+      <c r="AA22" s="174"/>
       <c r="AB22" s="15">
         <f t="shared" ref="AB22:AB31" si="5">SUM(C22:AA22)</f>
         <v>0</v>
       </c>
       <c r="AC22" s="21"/>
-      <c r="AD22" s="230"/>
-      <c r="AH22" s="235" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI22" s="235"/>
-      <c r="AJ22" s="235"/>
-      <c r="AK22" s="235"/>
-      <c r="AL22" s="172">
-        <f>T37</f>
-        <v>0</v>
-      </c>
+      <c r="AD22" s="221"/>
     </row>
     <row r="23" spans="1:38" ht="18">
       <c r="A23" s="17">
@@ -12355,42 +12388,42 @@
       <c r="B23" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="178"/>
-      <c r="D23" s="178"/>
-      <c r="E23" s="178"/>
-      <c r="F23" s="178"/>
-      <c r="G23" s="178"/>
-      <c r="H23" s="178"/>
-      <c r="I23" s="178"/>
-      <c r="J23" s="178"/>
-      <c r="K23" s="178"/>
-      <c r="L23" s="178"/>
-      <c r="M23" s="178"/>
-      <c r="N23" s="178"/>
-      <c r="O23" s="178"/>
-      <c r="P23" s="178"/>
-      <c r="Q23" s="178"/>
-      <c r="R23" s="178"/>
-      <c r="S23" s="178"/>
-      <c r="T23" s="178"/>
-      <c r="U23" s="178"/>
-      <c r="V23" s="178"/>
-      <c r="W23" s="178"/>
-      <c r="X23" s="178"/>
-      <c r="Y23" s="178"/>
-      <c r="Z23" s="178"/>
-      <c r="AA23" s="179"/>
+      <c r="C23" s="175"/>
+      <c r="D23" s="175"/>
+      <c r="E23" s="175"/>
+      <c r="F23" s="175"/>
+      <c r="G23" s="175"/>
+      <c r="H23" s="175"/>
+      <c r="I23" s="175"/>
+      <c r="J23" s="175"/>
+      <c r="K23" s="175"/>
+      <c r="L23" s="175"/>
+      <c r="M23" s="175"/>
+      <c r="N23" s="175"/>
+      <c r="O23" s="175"/>
+      <c r="P23" s="175"/>
+      <c r="Q23" s="175"/>
+      <c r="R23" s="175"/>
+      <c r="S23" s="175"/>
+      <c r="T23" s="175"/>
+      <c r="U23" s="175"/>
+      <c r="V23" s="175"/>
+      <c r="W23" s="175"/>
+      <c r="X23" s="175"/>
+      <c r="Y23" s="175"/>
+      <c r="Z23" s="175"/>
+      <c r="AA23" s="176"/>
       <c r="AB23" s="15">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AC23" s="21"/>
-      <c r="AD23" s="230"/>
-      <c r="AH23" s="236"/>
-      <c r="AI23" s="236"/>
-      <c r="AJ23" s="236"/>
-      <c r="AK23" s="236"/>
-      <c r="AL23" s="173"/>
+      <c r="AD23" s="221"/>
+      <c r="AH23" s="234"/>
+      <c r="AI23" s="234"/>
+      <c r="AJ23" s="234"/>
+      <c r="AK23" s="234"/>
+      <c r="AL23" s="170"/>
     </row>
     <row r="24" spans="1:38" ht="15.75">
       <c r="A24" s="11">
@@ -12399,37 +12432,37 @@
       <c r="B24" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="176"/>
-      <c r="D24" s="176"/>
-      <c r="E24" s="176"/>
-      <c r="F24" s="176"/>
-      <c r="G24" s="176"/>
-      <c r="H24" s="176"/>
-      <c r="I24" s="176"/>
-      <c r="J24" s="176"/>
-      <c r="K24" s="176"/>
-      <c r="L24" s="176"/>
-      <c r="M24" s="176"/>
-      <c r="N24" s="176"/>
-      <c r="O24" s="176"/>
-      <c r="P24" s="176"/>
-      <c r="Q24" s="176"/>
-      <c r="R24" s="176"/>
-      <c r="S24" s="176"/>
-      <c r="T24" s="176"/>
-      <c r="U24" s="176"/>
-      <c r="V24" s="176"/>
-      <c r="W24" s="176"/>
-      <c r="X24" s="176"/>
-      <c r="Y24" s="176"/>
-      <c r="Z24" s="176"/>
-      <c r="AA24" s="177"/>
+      <c r="C24" s="173"/>
+      <c r="D24" s="173"/>
+      <c r="E24" s="173"/>
+      <c r="F24" s="173"/>
+      <c r="G24" s="173"/>
+      <c r="H24" s="173"/>
+      <c r="I24" s="173"/>
+      <c r="J24" s="173"/>
+      <c r="K24" s="173"/>
+      <c r="L24" s="173"/>
+      <c r="M24" s="173"/>
+      <c r="N24" s="173"/>
+      <c r="O24" s="173"/>
+      <c r="P24" s="173"/>
+      <c r="Q24" s="173"/>
+      <c r="R24" s="173"/>
+      <c r="S24" s="173"/>
+      <c r="T24" s="173"/>
+      <c r="U24" s="173"/>
+      <c r="V24" s="173"/>
+      <c r="W24" s="173"/>
+      <c r="X24" s="173"/>
+      <c r="Y24" s="173"/>
+      <c r="Z24" s="173"/>
+      <c r="AA24" s="174"/>
       <c r="AB24" s="15">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AC24" s="21"/>
-      <c r="AD24" s="230"/>
+      <c r="AD24" s="221"/>
     </row>
     <row r="25" spans="1:38" ht="15.75">
       <c r="A25" s="17">
@@ -12438,39 +12471,39 @@
       <c r="B25" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="178"/>
-      <c r="D25" s="178"/>
-      <c r="E25" s="178"/>
-      <c r="F25" s="239">
+      <c r="C25" s="175"/>
+      <c r="D25" s="175"/>
+      <c r="E25" s="175"/>
+      <c r="F25" s="199">
         <v>3500</v>
       </c>
-      <c r="G25" s="178"/>
-      <c r="H25" s="178"/>
-      <c r="I25" s="178"/>
-      <c r="J25" s="178"/>
-      <c r="K25" s="178"/>
-      <c r="L25" s="178"/>
-      <c r="M25" s="178"/>
-      <c r="N25" s="178"/>
-      <c r="O25" s="178"/>
-      <c r="P25" s="178"/>
-      <c r="Q25" s="178"/>
-      <c r="R25" s="178"/>
-      <c r="S25" s="178"/>
-      <c r="T25" s="178"/>
-      <c r="U25" s="178"/>
-      <c r="V25" s="178"/>
-      <c r="W25" s="178"/>
-      <c r="X25" s="178"/>
-      <c r="Y25" s="178"/>
-      <c r="Z25" s="178"/>
-      <c r="AA25" s="179"/>
+      <c r="G25" s="175"/>
+      <c r="H25" s="175"/>
+      <c r="I25" s="175"/>
+      <c r="J25" s="175"/>
+      <c r="K25" s="175"/>
+      <c r="L25" s="175"/>
+      <c r="M25" s="175"/>
+      <c r="N25" s="175"/>
+      <c r="O25" s="175"/>
+      <c r="P25" s="175"/>
+      <c r="Q25" s="175"/>
+      <c r="R25" s="175"/>
+      <c r="S25" s="175"/>
+      <c r="T25" s="175"/>
+      <c r="U25" s="175"/>
+      <c r="V25" s="175"/>
+      <c r="W25" s="175"/>
+      <c r="X25" s="175"/>
+      <c r="Y25" s="175"/>
+      <c r="Z25" s="175"/>
+      <c r="AA25" s="176"/>
       <c r="AB25" s="15">
         <f t="shared" si="5"/>
         <v>3500</v>
       </c>
       <c r="AC25" s="21"/>
-      <c r="AD25" s="230"/>
+      <c r="AD25" s="221"/>
     </row>
     <row r="26" spans="1:38" ht="15.75">
       <c r="A26" s="11">
@@ -12479,37 +12512,37 @@
       <c r="B26" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="176"/>
-      <c r="D26" s="176"/>
-      <c r="E26" s="176"/>
-      <c r="F26" s="176"/>
-      <c r="G26" s="176"/>
-      <c r="H26" s="176"/>
-      <c r="I26" s="176"/>
-      <c r="J26" s="176"/>
-      <c r="K26" s="176"/>
-      <c r="L26" s="176"/>
-      <c r="M26" s="176"/>
-      <c r="N26" s="176"/>
-      <c r="O26" s="176"/>
-      <c r="P26" s="176"/>
-      <c r="Q26" s="176"/>
-      <c r="R26" s="176"/>
-      <c r="S26" s="176"/>
-      <c r="T26" s="176"/>
-      <c r="U26" s="176"/>
-      <c r="V26" s="176"/>
-      <c r="W26" s="176"/>
-      <c r="X26" s="176"/>
-      <c r="Y26" s="176"/>
-      <c r="Z26" s="176"/>
-      <c r="AA26" s="177"/>
+      <c r="C26" s="173"/>
+      <c r="D26" s="173"/>
+      <c r="E26" s="173"/>
+      <c r="F26" s="173"/>
+      <c r="G26" s="173"/>
+      <c r="H26" s="173"/>
+      <c r="I26" s="173"/>
+      <c r="J26" s="173"/>
+      <c r="K26" s="173"/>
+      <c r="L26" s="173"/>
+      <c r="M26" s="173"/>
+      <c r="N26" s="173"/>
+      <c r="O26" s="173"/>
+      <c r="P26" s="173"/>
+      <c r="Q26" s="173"/>
+      <c r="R26" s="173"/>
+      <c r="S26" s="173"/>
+      <c r="T26" s="173"/>
+      <c r="U26" s="173"/>
+      <c r="V26" s="173"/>
+      <c r="W26" s="173"/>
+      <c r="X26" s="173"/>
+      <c r="Y26" s="173"/>
+      <c r="Z26" s="173"/>
+      <c r="AA26" s="174"/>
       <c r="AB26" s="15">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AC26" s="16"/>
-      <c r="AD26" s="230"/>
+      <c r="AD26" s="221"/>
     </row>
     <row r="27" spans="1:38" ht="15.75">
       <c r="A27" s="17">
@@ -12518,37 +12551,37 @@
       <c r="B27" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="178"/>
-      <c r="D27" s="178"/>
-      <c r="E27" s="178"/>
-      <c r="F27" s="178"/>
-      <c r="G27" s="178"/>
-      <c r="H27" s="178"/>
-      <c r="I27" s="178"/>
-      <c r="J27" s="178"/>
-      <c r="K27" s="178"/>
-      <c r="L27" s="178"/>
-      <c r="M27" s="178"/>
-      <c r="N27" s="178"/>
-      <c r="O27" s="178"/>
-      <c r="P27" s="178"/>
-      <c r="Q27" s="178"/>
-      <c r="R27" s="178"/>
-      <c r="S27" s="178"/>
-      <c r="T27" s="178"/>
-      <c r="U27" s="178"/>
-      <c r="V27" s="178"/>
-      <c r="W27" s="178"/>
-      <c r="X27" s="178"/>
-      <c r="Y27" s="178"/>
-      <c r="Z27" s="178"/>
-      <c r="AA27" s="179"/>
+      <c r="C27" s="175"/>
+      <c r="D27" s="175"/>
+      <c r="E27" s="175"/>
+      <c r="F27" s="175"/>
+      <c r="G27" s="175"/>
+      <c r="H27" s="175"/>
+      <c r="I27" s="175"/>
+      <c r="J27" s="175"/>
+      <c r="K27" s="175"/>
+      <c r="L27" s="175"/>
+      <c r="M27" s="175"/>
+      <c r="N27" s="175"/>
+      <c r="O27" s="175"/>
+      <c r="P27" s="175"/>
+      <c r="Q27" s="175"/>
+      <c r="R27" s="175"/>
+      <c r="S27" s="175"/>
+      <c r="T27" s="175"/>
+      <c r="U27" s="175"/>
+      <c r="V27" s="175"/>
+      <c r="W27" s="175"/>
+      <c r="X27" s="175"/>
+      <c r="Y27" s="175"/>
+      <c r="Z27" s="175"/>
+      <c r="AA27" s="176"/>
       <c r="AB27" s="15">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AC27" s="21"/>
-      <c r="AD27" s="230"/>
+      <c r="AD27" s="221"/>
     </row>
     <row r="28" spans="1:38" ht="15.75">
       <c r="A28" s="11">
@@ -12557,37 +12590,37 @@
       <c r="B28" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="176"/>
-      <c r="D28" s="176"/>
-      <c r="E28" s="176"/>
-      <c r="F28" s="176"/>
-      <c r="G28" s="176"/>
-      <c r="H28" s="176"/>
-      <c r="I28" s="176"/>
-      <c r="J28" s="176"/>
-      <c r="K28" s="176"/>
-      <c r="L28" s="176"/>
-      <c r="M28" s="176"/>
-      <c r="N28" s="176"/>
-      <c r="O28" s="176"/>
-      <c r="P28" s="176"/>
-      <c r="Q28" s="176"/>
-      <c r="R28" s="176"/>
-      <c r="S28" s="176"/>
-      <c r="T28" s="176"/>
-      <c r="U28" s="176"/>
-      <c r="V28" s="176"/>
-      <c r="W28" s="176"/>
-      <c r="X28" s="176"/>
-      <c r="Y28" s="176"/>
-      <c r="Z28" s="176"/>
-      <c r="AA28" s="177"/>
+      <c r="C28" s="173"/>
+      <c r="D28" s="173"/>
+      <c r="E28" s="173"/>
+      <c r="F28" s="173"/>
+      <c r="G28" s="173"/>
+      <c r="H28" s="173"/>
+      <c r="I28" s="173"/>
+      <c r="J28" s="173"/>
+      <c r="K28" s="173"/>
+      <c r="L28" s="173"/>
+      <c r="M28" s="173"/>
+      <c r="N28" s="173"/>
+      <c r="O28" s="173"/>
+      <c r="P28" s="173"/>
+      <c r="Q28" s="173"/>
+      <c r="R28" s="173"/>
+      <c r="S28" s="173"/>
+      <c r="T28" s="173"/>
+      <c r="U28" s="173"/>
+      <c r="V28" s="173"/>
+      <c r="W28" s="173"/>
+      <c r="X28" s="173"/>
+      <c r="Y28" s="173"/>
+      <c r="Z28" s="173"/>
+      <c r="AA28" s="174"/>
       <c r="AB28" s="15">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AC28" s="21"/>
-      <c r="AD28" s="230"/>
+      <c r="AD28" s="221"/>
     </row>
     <row r="29" spans="1:38" ht="15.75">
       <c r="A29" s="17">
@@ -12596,39 +12629,39 @@
       <c r="B29" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C29" s="178"/>
-      <c r="D29" s="178"/>
-      <c r="E29" s="178"/>
-      <c r="F29" s="239">
+      <c r="C29" s="175"/>
+      <c r="D29" s="175"/>
+      <c r="E29" s="175"/>
+      <c r="F29" s="199">
         <v>3500</v>
       </c>
-      <c r="G29" s="178"/>
-      <c r="H29" s="178"/>
-      <c r="I29" s="178"/>
-      <c r="J29" s="178"/>
-      <c r="K29" s="178"/>
-      <c r="L29" s="178"/>
-      <c r="M29" s="178"/>
-      <c r="N29" s="178"/>
-      <c r="O29" s="178"/>
-      <c r="P29" s="178"/>
-      <c r="Q29" s="178"/>
-      <c r="R29" s="178"/>
-      <c r="S29" s="178"/>
-      <c r="T29" s="178"/>
-      <c r="U29" s="178"/>
-      <c r="V29" s="178"/>
-      <c r="W29" s="178"/>
-      <c r="X29" s="178"/>
-      <c r="Y29" s="178"/>
-      <c r="Z29" s="178"/>
-      <c r="AA29" s="179"/>
+      <c r="G29" s="175"/>
+      <c r="H29" s="175"/>
+      <c r="I29" s="175"/>
+      <c r="J29" s="175"/>
+      <c r="K29" s="175"/>
+      <c r="L29" s="175"/>
+      <c r="M29" s="175"/>
+      <c r="N29" s="175"/>
+      <c r="O29" s="175"/>
+      <c r="P29" s="175"/>
+      <c r="Q29" s="175"/>
+      <c r="R29" s="175"/>
+      <c r="S29" s="175"/>
+      <c r="T29" s="175"/>
+      <c r="U29" s="175"/>
+      <c r="V29" s="175"/>
+      <c r="W29" s="175"/>
+      <c r="X29" s="175"/>
+      <c r="Y29" s="175"/>
+      <c r="Z29" s="175"/>
+      <c r="AA29" s="176"/>
       <c r="AB29" s="15">
         <f t="shared" si="5"/>
         <v>3500</v>
       </c>
       <c r="AC29" s="21"/>
-      <c r="AD29" s="230"/>
+      <c r="AD29" s="221"/>
     </row>
     <row r="30" spans="1:38" ht="15.75">
       <c r="A30" s="11">
@@ -12637,37 +12670,37 @@
       <c r="B30" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="176"/>
-      <c r="D30" s="176"/>
-      <c r="E30" s="176"/>
-      <c r="F30" s="176"/>
-      <c r="G30" s="176"/>
-      <c r="H30" s="176"/>
-      <c r="I30" s="176"/>
-      <c r="J30" s="176"/>
-      <c r="K30" s="176"/>
-      <c r="L30" s="176"/>
-      <c r="M30" s="176"/>
-      <c r="N30" s="176"/>
-      <c r="O30" s="176"/>
-      <c r="P30" s="176"/>
-      <c r="Q30" s="176"/>
-      <c r="R30" s="176"/>
-      <c r="S30" s="176"/>
-      <c r="T30" s="176"/>
-      <c r="U30" s="176"/>
-      <c r="V30" s="176"/>
-      <c r="W30" s="176"/>
-      <c r="X30" s="176"/>
-      <c r="Y30" s="176"/>
-      <c r="Z30" s="176"/>
-      <c r="AA30" s="177"/>
+      <c r="C30" s="173"/>
+      <c r="D30" s="173"/>
+      <c r="E30" s="173"/>
+      <c r="F30" s="173"/>
+      <c r="G30" s="173"/>
+      <c r="H30" s="173"/>
+      <c r="I30" s="173"/>
+      <c r="J30" s="173"/>
+      <c r="K30" s="173"/>
+      <c r="L30" s="173"/>
+      <c r="M30" s="173"/>
+      <c r="N30" s="173"/>
+      <c r="O30" s="173"/>
+      <c r="P30" s="173"/>
+      <c r="Q30" s="173"/>
+      <c r="R30" s="173"/>
+      <c r="S30" s="173"/>
+      <c r="T30" s="173"/>
+      <c r="U30" s="173"/>
+      <c r="V30" s="173"/>
+      <c r="W30" s="173"/>
+      <c r="X30" s="173"/>
+      <c r="Y30" s="173"/>
+      <c r="Z30" s="173"/>
+      <c r="AA30" s="174"/>
       <c r="AB30" s="15">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AC30" s="21"/>
-      <c r="AD30" s="230"/>
+      <c r="AD30" s="221"/>
     </row>
     <row r="31" spans="1:38" ht="15.75">
       <c r="A31" s="17">
@@ -12676,37 +12709,37 @@
       <c r="B31" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="178"/>
-      <c r="D31" s="178"/>
-      <c r="E31" s="178"/>
-      <c r="F31" s="178"/>
-      <c r="G31" s="178"/>
-      <c r="H31" s="178"/>
-      <c r="I31" s="178"/>
-      <c r="J31" s="178"/>
-      <c r="K31" s="178"/>
-      <c r="L31" s="178"/>
-      <c r="M31" s="178"/>
-      <c r="N31" s="178"/>
-      <c r="O31" s="178"/>
-      <c r="P31" s="178"/>
-      <c r="Q31" s="178"/>
-      <c r="R31" s="178"/>
-      <c r="S31" s="178"/>
-      <c r="T31" s="178"/>
-      <c r="U31" s="178"/>
-      <c r="V31" s="178"/>
-      <c r="W31" s="178"/>
-      <c r="X31" s="178"/>
-      <c r="Y31" s="178"/>
-      <c r="Z31" s="178"/>
-      <c r="AA31" s="179"/>
+      <c r="C31" s="175"/>
+      <c r="D31" s="175"/>
+      <c r="E31" s="175"/>
+      <c r="F31" s="175"/>
+      <c r="G31" s="175"/>
+      <c r="H31" s="175"/>
+      <c r="I31" s="175"/>
+      <c r="J31" s="175"/>
+      <c r="K31" s="175"/>
+      <c r="L31" s="175"/>
+      <c r="M31" s="175"/>
+      <c r="N31" s="175"/>
+      <c r="O31" s="175"/>
+      <c r="P31" s="175"/>
+      <c r="Q31" s="175"/>
+      <c r="R31" s="175"/>
+      <c r="S31" s="175"/>
+      <c r="T31" s="175"/>
+      <c r="U31" s="175"/>
+      <c r="V31" s="175"/>
+      <c r="W31" s="175"/>
+      <c r="X31" s="175"/>
+      <c r="Y31" s="175"/>
+      <c r="Z31" s="175"/>
+      <c r="AA31" s="176"/>
       <c r="AB31" s="15">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AC31" s="21"/>
-      <c r="AD31" s="230"/>
+      <c r="AD31" s="221"/>
     </row>
     <row r="32" spans="1:38" ht="15.75">
       <c r="A32" s="11">
@@ -12715,37 +12748,37 @@
       <c r="B32" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="180"/>
-      <c r="D32" s="180"/>
-      <c r="E32" s="180"/>
-      <c r="F32" s="180"/>
-      <c r="G32" s="180"/>
-      <c r="H32" s="180"/>
-      <c r="I32" s="180"/>
-      <c r="J32" s="180"/>
-      <c r="K32" s="180"/>
-      <c r="L32" s="180"/>
-      <c r="M32" s="180"/>
-      <c r="N32" s="180"/>
-      <c r="O32" s="180"/>
-      <c r="P32" s="180"/>
-      <c r="Q32" s="180"/>
-      <c r="R32" s="180"/>
-      <c r="S32" s="180"/>
-      <c r="T32" s="180"/>
-      <c r="U32" s="180"/>
-      <c r="V32" s="180"/>
-      <c r="W32" s="180"/>
-      <c r="X32" s="180"/>
-      <c r="Y32" s="180"/>
-      <c r="Z32" s="180"/>
-      <c r="AA32" s="181"/>
+      <c r="C32" s="177"/>
+      <c r="D32" s="177"/>
+      <c r="E32" s="177"/>
+      <c r="F32" s="177"/>
+      <c r="G32" s="177"/>
+      <c r="H32" s="177"/>
+      <c r="I32" s="177"/>
+      <c r="J32" s="177"/>
+      <c r="K32" s="177"/>
+      <c r="L32" s="177"/>
+      <c r="M32" s="177"/>
+      <c r="N32" s="177"/>
+      <c r="O32" s="177"/>
+      <c r="P32" s="177"/>
+      <c r="Q32" s="177"/>
+      <c r="R32" s="177"/>
+      <c r="S32" s="177"/>
+      <c r="T32" s="177"/>
+      <c r="U32" s="177"/>
+      <c r="V32" s="177"/>
+      <c r="W32" s="177"/>
+      <c r="X32" s="177"/>
+      <c r="Y32" s="177"/>
+      <c r="Z32" s="177"/>
+      <c r="AA32" s="178"/>
       <c r="AB32" s="15">
         <f>SUM(C32:AA32)</f>
         <v>0</v>
       </c>
       <c r="AC32" s="21"/>
-      <c r="AD32" s="230"/>
+      <c r="AD32" s="221"/>
     </row>
     <row r="33" spans="1:34" ht="15.75">
       <c r="A33" s="17">
@@ -12754,39 +12787,39 @@
       <c r="B33" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="182"/>
-      <c r="D33" s="182"/>
-      <c r="E33" s="182"/>
-      <c r="F33" s="239">
+      <c r="C33" s="179"/>
+      <c r="D33" s="179"/>
+      <c r="E33" s="179"/>
+      <c r="F33" s="199">
         <v>3500</v>
       </c>
-      <c r="G33" s="182"/>
-      <c r="H33" s="182"/>
-      <c r="I33" s="182"/>
-      <c r="J33" s="182"/>
-      <c r="K33" s="182"/>
-      <c r="L33" s="182"/>
-      <c r="M33" s="182"/>
-      <c r="N33" s="182"/>
-      <c r="O33" s="182"/>
-      <c r="P33" s="182"/>
-      <c r="Q33" s="182"/>
-      <c r="R33" s="182"/>
-      <c r="S33" s="182"/>
-      <c r="T33" s="182"/>
-      <c r="U33" s="182"/>
-      <c r="V33" s="182"/>
-      <c r="W33" s="182"/>
-      <c r="X33" s="182"/>
-      <c r="Y33" s="182"/>
-      <c r="Z33" s="182"/>
-      <c r="AA33" s="182"/>
-      <c r="AB33" s="174">
+      <c r="G33" s="179"/>
+      <c r="H33" s="179"/>
+      <c r="I33" s="179"/>
+      <c r="J33" s="179"/>
+      <c r="K33" s="179"/>
+      <c r="L33" s="179"/>
+      <c r="M33" s="179"/>
+      <c r="N33" s="179"/>
+      <c r="O33" s="179"/>
+      <c r="P33" s="179"/>
+      <c r="Q33" s="179"/>
+      <c r="R33" s="179"/>
+      <c r="S33" s="179"/>
+      <c r="T33" s="179"/>
+      <c r="U33" s="179"/>
+      <c r="V33" s="179"/>
+      <c r="W33" s="179"/>
+      <c r="X33" s="179"/>
+      <c r="Y33" s="179"/>
+      <c r="Z33" s="179"/>
+      <c r="AA33" s="179"/>
+      <c r="AB33" s="171">
         <f t="shared" ref="AB33:AB35" si="6">SUM(C33:AA33)</f>
         <v>3500</v>
       </c>
       <c r="AC33" s="21"/>
-      <c r="AD33" s="230"/>
+      <c r="AD33" s="221"/>
     </row>
     <row r="34" spans="1:34" ht="15.75">
       <c r="A34" s="11">
@@ -12795,39 +12828,39 @@
       <c r="B34" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C34" s="183"/>
-      <c r="D34" s="183"/>
-      <c r="E34" s="183"/>
-      <c r="F34" s="183"/>
-      <c r="G34" s="183"/>
-      <c r="H34" s="183"/>
-      <c r="I34" s="183"/>
-      <c r="J34" s="183"/>
-      <c r="K34" s="183"/>
-      <c r="L34" s="183"/>
-      <c r="M34" s="183"/>
-      <c r="N34" s="183"/>
-      <c r="O34" s="183"/>
-      <c r="P34" s="183"/>
-      <c r="Q34" s="183"/>
-      <c r="R34" s="183"/>
-      <c r="S34" s="183"/>
-      <c r="T34" s="183"/>
-      <c r="U34" s="183"/>
-      <c r="V34" s="183"/>
-      <c r="W34" s="239">
+      <c r="C34" s="180"/>
+      <c r="D34" s="180"/>
+      <c r="E34" s="180"/>
+      <c r="F34" s="180"/>
+      <c r="G34" s="180"/>
+      <c r="H34" s="180"/>
+      <c r="I34" s="180"/>
+      <c r="J34" s="180"/>
+      <c r="K34" s="180"/>
+      <c r="L34" s="180"/>
+      <c r="M34" s="180"/>
+      <c r="N34" s="180"/>
+      <c r="O34" s="180"/>
+      <c r="P34" s="180"/>
+      <c r="Q34" s="180"/>
+      <c r="R34" s="180"/>
+      <c r="S34" s="180"/>
+      <c r="T34" s="180"/>
+      <c r="U34" s="180"/>
+      <c r="V34" s="180"/>
+      <c r="W34" s="199">
         <v>11525</v>
       </c>
-      <c r="X34" s="183"/>
-      <c r="Y34" s="183"/>
-      <c r="Z34" s="183"/>
-      <c r="AA34" s="183"/>
-      <c r="AB34" s="174">
+      <c r="X34" s="180"/>
+      <c r="Y34" s="180"/>
+      <c r="Z34" s="180"/>
+      <c r="AA34" s="180"/>
+      <c r="AB34" s="171">
         <f t="shared" si="6"/>
         <v>11525</v>
       </c>
       <c r="AC34" s="21"/>
-      <c r="AD34" s="230"/>
+      <c r="AD34" s="221"/>
     </row>
     <row r="35" spans="1:34" ht="15.75">
       <c r="A35" s="17">
@@ -12836,169 +12869,169 @@
       <c r="B35" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="C35" s="182"/>
-      <c r="D35" s="182"/>
-      <c r="E35" s="182"/>
-      <c r="F35" s="182"/>
-      <c r="G35" s="182"/>
-      <c r="H35" s="182"/>
-      <c r="I35" s="182"/>
-      <c r="J35" s="182"/>
-      <c r="K35" s="182"/>
-      <c r="L35" s="182"/>
-      <c r="M35" s="182"/>
-      <c r="N35" s="182"/>
-      <c r="O35" s="182"/>
-      <c r="P35" s="182"/>
-      <c r="Q35" s="182"/>
-      <c r="R35" s="182"/>
-      <c r="S35" s="182"/>
-      <c r="T35" s="182"/>
-      <c r="U35" s="182"/>
-      <c r="V35" s="182"/>
-      <c r="W35" s="182"/>
-      <c r="X35" s="182"/>
-      <c r="Y35" s="182"/>
-      <c r="Z35" s="182"/>
-      <c r="AA35" s="182"/>
-      <c r="AB35" s="174">
+      <c r="C35" s="179"/>
+      <c r="D35" s="179"/>
+      <c r="E35" s="179"/>
+      <c r="F35" s="179"/>
+      <c r="G35" s="179"/>
+      <c r="H35" s="179"/>
+      <c r="I35" s="179"/>
+      <c r="J35" s="179"/>
+      <c r="K35" s="179"/>
+      <c r="L35" s="179"/>
+      <c r="M35" s="179"/>
+      <c r="N35" s="179"/>
+      <c r="O35" s="179"/>
+      <c r="P35" s="179"/>
+      <c r="Q35" s="179"/>
+      <c r="R35" s="179"/>
+      <c r="S35" s="179"/>
+      <c r="T35" s="179"/>
+      <c r="U35" s="179"/>
+      <c r="V35" s="179"/>
+      <c r="W35" s="179"/>
+      <c r="X35" s="179"/>
+      <c r="Y35" s="179"/>
+      <c r="Z35" s="179"/>
+      <c r="AA35" s="179"/>
+      <c r="AB35" s="171">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AC35" s="21"/>
-      <c r="AD35" s="230"/>
+      <c r="AD35" s="221"/>
     </row>
     <row r="36" spans="1:34" ht="24" customHeight="1">
-      <c r="A36" s="237" t="s">
+      <c r="A36" s="235" t="s">
         <v>55</v>
       </c>
-      <c r="B36" s="237"/>
-      <c r="C36" s="146">
+      <c r="B36" s="235"/>
+      <c r="C36" s="143">
         <f t="shared" ref="C36:AC36" si="7">SUM(C20:C35)</f>
         <v>0</v>
       </c>
-      <c r="D36" s="146">
+      <c r="D36" s="143">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E36" s="146">
+      <c r="E36" s="143">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="F36" s="146">
+      <c r="F36" s="143">
         <f t="shared" si="7"/>
-        <v>14000</v>
-      </c>
-      <c r="G36" s="146">
+        <v>12433.720000000001</v>
+      </c>
+      <c r="G36" s="143">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H36" s="146">
+      <c r="H36" s="143">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="I36" s="146">
+      <c r="I36" s="143">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J36" s="146">
+      <c r="J36" s="143">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="K36" s="146">
+      <c r="K36" s="143">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L36" s="147">
+      <c r="L36" s="144">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M36" s="147">
+      <c r="M36" s="144">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="N36" s="147">
+      <c r="N36" s="144">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="O36" s="147">
+      <c r="O36" s="144">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="P36" s="147">
+      <c r="P36" s="144">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="Q36" s="147">
+      <c r="Q36" s="144">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="R36" s="148">
+      <c r="R36" s="145">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="S36" s="148">
+      <c r="S36" s="145">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T36" s="148">
+      <c r="T36" s="145">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U36" s="148">
+      <c r="U36" s="145">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="V36" s="148">
+      <c r="V36" s="145">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="W36" s="148">
+      <c r="W36" s="145">
         <f t="shared" si="7"/>
         <v>11525</v>
       </c>
-      <c r="X36" s="148">
+      <c r="X36" s="145">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="Y36" s="148">
+      <c r="Y36" s="145">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="Z36" s="148">
+      <c r="Z36" s="145">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AA36" s="149">
+      <c r="AA36" s="146">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AB36" s="26">
         <f t="shared" si="7"/>
-        <v>25525</v>
+        <v>23958.720000000001</v>
       </c>
       <c r="AC36" s="27">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD36" s="28">
+      <c r="AD36" s="238">
         <f>AC36-AB36</f>
-        <v>-25525</v>
-      </c>
-      <c r="AH36" s="165"/>
+        <v>-23958.720000000001</v>
+      </c>
+      <c r="AH36" s="162"/>
     </row>
     <row r="37" spans="1:34" ht="31.5" customHeight="1">
-      <c r="A37" s="229" t="s">
+      <c r="A37" s="220" t="s">
         <v>56</v>
       </c>
-      <c r="B37" s="229"/>
+      <c r="B37" s="220"/>
       <c r="C37" s="31">
         <f t="shared" ref="C37:R37" si="8">SUM(C19,C36)</f>
         <v>2892.73</v>
       </c>
       <c r="D37" s="31">
         <f t="shared" si="8"/>
-        <v>2483.52</v>
+        <v>3598.92</v>
       </c>
       <c r="E37" s="31">
         <f t="shared" si="8"/>
@@ -13006,7 +13039,7 @@
       </c>
       <c r="F37" s="31">
         <f t="shared" si="8"/>
-        <v>22254.85</v>
+        <v>20688.57</v>
       </c>
       <c r="G37" s="31">
         <f t="shared" si="8"/>
@@ -13089,17 +13122,17 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AB37" s="33">
+      <c r="AB37" s="240">
         <f t="shared" si="9"/>
-        <v>203874.13000000003</v>
-      </c>
-      <c r="AC37" s="34">
+        <v>203423.25000000003</v>
+      </c>
+      <c r="AC37" s="241">
         <f t="shared" si="9"/>
         <v>203067.86</v>
       </c>
-      <c r="AD37" s="169">
+      <c r="AD37" s="237">
         <f t="shared" si="9"/>
-        <v>-806.27000000004773</v>
+        <v>-355.39000000004307</v>
       </c>
     </row>
     <row r="41" spans="1:34">
@@ -13122,12 +13155,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:K2"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="AD4:AD18"/>
@@ -13136,20 +13163,26 @@
     <mergeCell ref="AD20:AD35"/>
     <mergeCell ref="AH20:AK20"/>
     <mergeCell ref="AH21:AK21"/>
-    <mergeCell ref="AH22:AK22"/>
     <mergeCell ref="AH23:AK23"/>
     <mergeCell ref="AH11:AL13"/>
     <mergeCell ref="AH14:AK14"/>
     <mergeCell ref="AH15:AK15"/>
     <mergeCell ref="AH16:AK16"/>
     <mergeCell ref="AH17:AK17"/>
+    <mergeCell ref="AH18:AK18"/>
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
   </mergeCells>
   <conditionalFormatting sqref="AD37">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$AD$37&lt;0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>$AD$37&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="1">
-      <formula>$AD$37&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13169,8 +13202,1358 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
+      <c r="A1" s="200" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="200"/>
+      <c r="C1" s="200"/>
+      <c r="D1" s="200"/>
+      <c r="E1" s="200"/>
+      <c r="F1" s="200"/>
+      <c r="G1" s="200"/>
+      <c r="H1" s="200"/>
+      <c r="I1" s="200"/>
+      <c r="J1" s="200"/>
+      <c r="K1" s="200"/>
+      <c r="L1" s="200"/>
+      <c r="M1" s="200"/>
+      <c r="N1" s="200"/>
+      <c r="O1" s="200"/>
+      <c r="P1" s="200"/>
+      <c r="Q1" s="200"/>
+      <c r="R1" s="200"/>
+      <c r="S1" s="200"/>
+      <c r="T1" s="200"/>
+      <c r="U1" s="200"/>
+      <c r="V1" s="200"/>
+      <c r="W1" s="200"/>
+      <c r="X1" s="200"/>
+    </row>
+    <row r="2" spans="1:46" ht="45" customHeight="1">
+      <c r="A2" s="107" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="107" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="107" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="107" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="107" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="107" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="107" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="107" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="107" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" s="107" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" s="107" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" s="107" t="s">
+        <v>33</v>
+      </c>
+      <c r="N2" s="107" t="s">
+        <v>34</v>
+      </c>
+      <c r="O2" s="107" t="s">
+        <v>35</v>
+      </c>
+      <c r="P2" s="107" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q2" s="107" t="s">
+        <v>37</v>
+      </c>
+      <c r="R2" s="107" t="s">
+        <v>38</v>
+      </c>
+      <c r="S2" s="107" t="s">
+        <v>39</v>
+      </c>
+      <c r="T2" s="107" t="s">
+        <v>39</v>
+      </c>
+      <c r="U2" s="107" t="s">
+        <v>40</v>
+      </c>
+      <c r="V2" s="107" t="s">
+        <v>41</v>
+      </c>
+      <c r="W2" s="107" t="s">
+        <v>42</v>
+      </c>
+      <c r="X2" s="107" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y2" s="10"/>
+      <c r="Z2" s="10"/>
+      <c r="AA2" s="10"/>
+      <c r="AB2" s="10"/>
+      <c r="AC2" s="10"/>
+      <c r="AD2" s="10"/>
+      <c r="AE2" s="10"/>
+      <c r="AF2" s="10"/>
+      <c r="AG2" s="10"/>
+      <c r="AH2" s="10"/>
+      <c r="AI2" s="10"/>
+      <c r="AJ2" s="10"/>
+      <c r="AK2" s="10"/>
+      <c r="AL2" s="10"/>
+      <c r="AM2" s="10"/>
+      <c r="AN2" s="10"/>
+      <c r="AO2" s="10"/>
+      <c r="AP2" s="10"/>
+      <c r="AQ2" s="10"/>
+      <c r="AR2" s="10"/>
+      <c r="AS2" s="10"/>
+      <c r="AT2" s="10"/>
+    </row>
+    <row r="3" spans="1:46">
+      <c r="A3" s="108">
+        <v>5</v>
+      </c>
+      <c r="B3" s="108" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="109">
+        <f>183+2168</f>
+        <v>2351</v>
+      </c>
+      <c r="D3" s="109">
+        <v>3131</v>
+      </c>
+      <c r="E3" s="109"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="110"/>
+      <c r="H3" s="110"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="109">
+        <v>450</v>
+      </c>
+      <c r="K3" s="109"/>
+      <c r="L3" s="109"/>
+      <c r="M3" s="109"/>
+      <c r="N3" s="109">
+        <v>40</v>
+      </c>
+      <c r="O3" s="109"/>
+      <c r="P3" s="109"/>
+      <c r="Q3" s="109">
+        <v>14418</v>
+      </c>
+      <c r="R3" s="109"/>
+      <c r="S3" s="109">
+        <v>5000</v>
+      </c>
+      <c r="T3" s="109"/>
+      <c r="U3" s="109"/>
+      <c r="V3" s="111">
+        <f>SUM(C3:U3)</f>
+        <v>25390</v>
+      </c>
+      <c r="W3" s="112">
+        <v>53739.4</v>
+      </c>
+      <c r="X3" s="113"/>
+    </row>
+    <row r="4" spans="1:46">
+      <c r="A4" s="114">
+        <v>6</v>
+      </c>
+      <c r="B4" s="114" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="115"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="116"/>
+      <c r="L4" s="116"/>
+      <c r="M4" s="116"/>
+      <c r="N4" s="117">
+        <f>131+247</f>
+        <v>378</v>
+      </c>
+      <c r="O4" s="116"/>
+      <c r="P4" s="116"/>
+      <c r="Q4" s="116"/>
+      <c r="R4" s="116"/>
+      <c r="S4" s="116"/>
+      <c r="T4" s="116"/>
+      <c r="U4" s="116"/>
+      <c r="V4" s="118">
+        <f>SUM(C4:U4)</f>
+        <v>378</v>
+      </c>
+      <c r="W4" s="119"/>
+      <c r="X4" s="113"/>
+    </row>
+    <row r="5" spans="1:46">
+      <c r="A5" s="120">
+        <v>7</v>
+      </c>
+      <c r="B5" s="120" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="121"/>
+      <c r="D5" s="122">
+        <v>1110</v>
+      </c>
+      <c r="E5" s="122"/>
+      <c r="F5" s="122"/>
+      <c r="G5" s="121"/>
+      <c r="H5" s="121"/>
+      <c r="I5" s="123">
+        <v>840</v>
+      </c>
+      <c r="J5" s="123"/>
+      <c r="K5" s="123"/>
+      <c r="L5" s="123"/>
+      <c r="M5" s="123"/>
+      <c r="N5" s="123">
+        <f>197+259</f>
+        <v>456</v>
+      </c>
+      <c r="O5" s="123"/>
+      <c r="P5" s="123"/>
+      <c r="Q5" s="123"/>
+      <c r="R5" s="123"/>
+      <c r="S5" s="123"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="124">
+        <f>SUM(C5:U5)</f>
+        <v>2406</v>
+      </c>
+      <c r="W5" s="125"/>
+      <c r="X5" s="113"/>
+    </row>
+    <row r="6" spans="1:46">
+      <c r="A6" s="114">
+        <v>8</v>
+      </c>
+      <c r="B6" s="114" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="117">
+        <v>1006</v>
+      </c>
+      <c r="D6" s="115"/>
+      <c r="E6" s="115"/>
+      <c r="F6" s="115"/>
+      <c r="G6" s="115"/>
+      <c r="H6" s="115"/>
+      <c r="I6" s="116"/>
+      <c r="J6" s="116"/>
+      <c r="K6" s="116"/>
+      <c r="L6" s="116"/>
+      <c r="M6" s="116"/>
+      <c r="N6" s="117">
+        <f>221+171</f>
+        <v>392</v>
+      </c>
+      <c r="O6" s="116"/>
+      <c r="P6" s="115"/>
+      <c r="Q6" s="116"/>
+      <c r="R6" s="116"/>
+      <c r="S6" s="116"/>
+      <c r="T6" s="116"/>
+      <c r="U6" s="116"/>
+      <c r="V6" s="118">
+        <f t="shared" ref="V6:V19" si="0">SUM(C6:U6)</f>
+        <v>1398</v>
+      </c>
+      <c r="W6" s="119"/>
+      <c r="X6" s="113"/>
+    </row>
+    <row r="7" spans="1:46">
+      <c r="A7" s="120">
+        <v>9</v>
+      </c>
+      <c r="B7" s="120" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="122">
+        <v>1819</v>
+      </c>
+      <c r="D7" s="121"/>
+      <c r="E7" s="121"/>
+      <c r="F7" s="121"/>
+      <c r="G7" s="121"/>
+      <c r="H7" s="121"/>
+      <c r="I7" s="123"/>
+      <c r="J7" s="123"/>
+      <c r="K7" s="123"/>
+      <c r="L7" s="123"/>
+      <c r="M7" s="123"/>
+      <c r="N7" s="123">
+        <v>224</v>
+      </c>
+      <c r="O7" s="121"/>
+      <c r="P7" s="123"/>
+      <c r="Q7" s="123"/>
+      <c r="R7" s="123"/>
+      <c r="S7" s="123">
+        <v>1055</v>
+      </c>
+      <c r="T7" s="123"/>
+      <c r="U7" s="123"/>
+      <c r="V7" s="124">
+        <f t="shared" si="0"/>
+        <v>3098</v>
+      </c>
+      <c r="W7" s="125"/>
+      <c r="X7" s="113"/>
+    </row>
+    <row r="8" spans="1:46">
+      <c r="A8" s="114">
+        <v>10</v>
+      </c>
+      <c r="B8" s="114" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="116">
+        <v>1266.9000000000001</v>
+      </c>
+      <c r="D8" s="116">
+        <v>1345</v>
+      </c>
+      <c r="E8" s="116"/>
+      <c r="F8" s="116"/>
+      <c r="G8" s="115"/>
+      <c r="H8" s="115"/>
+      <c r="I8" s="116"/>
+      <c r="J8" s="116"/>
+      <c r="K8" s="116"/>
+      <c r="L8" s="116"/>
+      <c r="M8" s="116"/>
+      <c r="N8" s="116">
+        <v>172</v>
+      </c>
+      <c r="O8" s="116"/>
+      <c r="P8" s="116"/>
+      <c r="Q8" s="116"/>
+      <c r="R8" s="115"/>
+      <c r="S8" s="116"/>
+      <c r="T8" s="116"/>
+      <c r="U8" s="116"/>
+      <c r="V8" s="118">
+        <f t="shared" si="0"/>
+        <v>2783.9</v>
+      </c>
+      <c r="W8" s="119"/>
+      <c r="X8" s="113"/>
+    </row>
+    <row r="9" spans="1:46">
+      <c r="A9" s="120">
+        <v>11</v>
+      </c>
+      <c r="B9" s="120" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="123">
+        <v>1403.84</v>
+      </c>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="123"/>
+      <c r="J9" s="123"/>
+      <c r="K9" s="123"/>
+      <c r="L9" s="123"/>
+      <c r="M9" s="123"/>
+      <c r="N9" s="123"/>
+      <c r="O9" s="123"/>
+      <c r="P9" s="123"/>
+      <c r="Q9" s="123"/>
+      <c r="R9" s="121"/>
+      <c r="S9" s="123"/>
+      <c r="T9" s="123"/>
+      <c r="U9" s="123"/>
+      <c r="V9" s="124">
+        <f t="shared" si="0"/>
+        <v>1403.84</v>
+      </c>
+      <c r="W9" s="125"/>
+      <c r="X9" s="113"/>
+    </row>
+    <row r="10" spans="1:46">
+      <c r="A10" s="114">
+        <v>12</v>
+      </c>
+      <c r="B10" s="114" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="115"/>
+      <c r="D10" s="116">
+        <v>959</v>
+      </c>
+      <c r="E10" s="116"/>
+      <c r="F10" s="116"/>
+      <c r="G10" s="115"/>
+      <c r="H10" s="115"/>
+      <c r="I10" s="116"/>
+      <c r="J10" s="116"/>
+      <c r="K10" s="116"/>
+      <c r="L10" s="116"/>
+      <c r="M10" s="116"/>
+      <c r="N10" s="115"/>
+      <c r="O10" s="116"/>
+      <c r="P10" s="116"/>
+      <c r="Q10" s="116"/>
+      <c r="R10" s="115"/>
+      <c r="S10" s="116"/>
+      <c r="T10" s="116"/>
+      <c r="U10" s="116"/>
+      <c r="V10" s="118">
+        <f t="shared" si="0"/>
+        <v>959</v>
+      </c>
+      <c r="W10" s="119"/>
+      <c r="X10" s="113"/>
+    </row>
+    <row r="11" spans="1:46">
+      <c r="A11" s="120">
+        <v>13</v>
+      </c>
+      <c r="B11" s="120" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="123">
+        <f>342.99+1260.98</f>
+        <v>1603.97</v>
+      </c>
+      <c r="D11" s="121"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="123">
+        <f>3980+430</f>
+        <v>4410</v>
+      </c>
+      <c r="H11" s="123"/>
+      <c r="I11" s="123"/>
+      <c r="J11" s="123"/>
+      <c r="K11" s="123"/>
+      <c r="L11" s="123"/>
+      <c r="M11" s="123"/>
+      <c r="N11" s="123"/>
+      <c r="O11" s="123"/>
+      <c r="P11" s="123">
+        <f>773+2000+1767</f>
+        <v>4540</v>
+      </c>
+      <c r="Q11" s="123"/>
+      <c r="R11" s="121"/>
+      <c r="S11" s="123"/>
+      <c r="T11" s="123"/>
+      <c r="U11" s="123"/>
+      <c r="V11" s="124">
+        <f t="shared" si="0"/>
+        <v>10553.97</v>
+      </c>
+      <c r="W11" s="125"/>
+      <c r="X11" s="113"/>
+    </row>
+    <row r="12" spans="1:46">
+      <c r="A12" s="114">
+        <v>14</v>
+      </c>
+      <c r="B12" s="114" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="116">
+        <f>1260.98+678.97</f>
+        <v>1939.95</v>
+      </c>
+      <c r="D12" s="116">
+        <f>4500+149</f>
+        <v>4649</v>
+      </c>
+      <c r="E12" s="116"/>
+      <c r="F12" s="116"/>
+      <c r="G12" s="115"/>
+      <c r="H12" s="115"/>
+      <c r="I12" s="116"/>
+      <c r="J12" s="115"/>
+      <c r="K12" s="116"/>
+      <c r="L12" s="116"/>
+      <c r="M12" s="116"/>
+      <c r="N12" s="116">
+        <f>543+421</f>
+        <v>964</v>
+      </c>
+      <c r="O12" s="116"/>
+      <c r="P12" s="116">
+        <f>497</f>
+        <v>497</v>
+      </c>
+      <c r="Q12" s="116"/>
+      <c r="R12" s="116"/>
+      <c r="S12" s="116"/>
+      <c r="T12" s="116"/>
+      <c r="U12" s="116"/>
+      <c r="V12" s="118">
+        <f t="shared" si="0"/>
+        <v>8049.95</v>
+      </c>
+      <c r="W12" s="119"/>
+      <c r="X12" s="113"/>
+    </row>
+    <row r="13" spans="1:46">
+      <c r="A13" s="120">
+        <v>15</v>
+      </c>
+      <c r="B13" s="120" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="123">
+        <f>1569.79</f>
+        <v>1569.79</v>
+      </c>
+      <c r="D13" s="121"/>
+      <c r="E13" s="121"/>
+      <c r="F13" s="121"/>
+      <c r="G13" s="121"/>
+      <c r="H13" s="121"/>
+      <c r="I13" s="123"/>
+      <c r="J13" s="121"/>
+      <c r="K13" s="123"/>
+      <c r="L13" s="123"/>
+      <c r="M13" s="123"/>
+      <c r="N13" s="123">
+        <v>135</v>
+      </c>
+      <c r="O13" s="123"/>
+      <c r="P13" s="123"/>
+      <c r="Q13" s="123"/>
+      <c r="R13" s="123"/>
+      <c r="S13" s="123"/>
+      <c r="T13" s="123"/>
+      <c r="U13" s="123"/>
+      <c r="V13" s="124">
+        <f t="shared" si="0"/>
+        <v>1704.79</v>
+      </c>
+      <c r="W13" s="125"/>
+      <c r="X13" s="113"/>
+    </row>
+    <row r="14" spans="1:46">
+      <c r="A14" s="114">
+        <v>16</v>
+      </c>
+      <c r="B14" s="114" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="116">
+        <v>1170</v>
+      </c>
+      <c r="D14" s="115"/>
+      <c r="E14" s="115"/>
+      <c r="F14" s="115"/>
+      <c r="G14" s="115"/>
+      <c r="H14" s="115"/>
+      <c r="I14" s="116"/>
+      <c r="J14" s="115"/>
+      <c r="K14" s="116"/>
+      <c r="L14" s="116"/>
+      <c r="M14" s="116"/>
+      <c r="N14" s="116"/>
+      <c r="O14" s="115"/>
+      <c r="P14" s="116"/>
+      <c r="Q14" s="116"/>
+      <c r="R14" s="116"/>
+      <c r="S14" s="116"/>
+      <c r="T14" s="116"/>
+      <c r="U14" s="116"/>
+      <c r="V14" s="118">
+        <f t="shared" si="0"/>
+        <v>1170</v>
+      </c>
+      <c r="W14" s="119"/>
+      <c r="X14" s="113"/>
+    </row>
+    <row r="15" spans="1:46">
+      <c r="A15" s="120">
+        <v>17</v>
+      </c>
+      <c r="B15" s="120" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="121"/>
+      <c r="D15" s="121"/>
+      <c r="E15" s="121"/>
+      <c r="F15" s="121"/>
+      <c r="G15" s="121"/>
+      <c r="H15" s="121"/>
+      <c r="I15" s="123"/>
+      <c r="J15" s="123"/>
+      <c r="K15" s="123"/>
+      <c r="L15" s="123"/>
+      <c r="M15" s="123"/>
+      <c r="N15" s="121"/>
+      <c r="O15" s="123"/>
+      <c r="P15" s="123"/>
+      <c r="Q15" s="123"/>
+      <c r="R15" s="123"/>
+      <c r="S15" s="123"/>
+      <c r="T15" s="123"/>
+      <c r="U15" s="123"/>
+      <c r="V15" s="124">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="125"/>
+      <c r="X15" s="113"/>
+    </row>
+    <row r="16" spans="1:46">
+      <c r="A16" s="114">
+        <v>18</v>
+      </c>
+      <c r="B16" s="114" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="116">
+        <v>200</v>
+      </c>
+      <c r="D16" s="115"/>
+      <c r="E16" s="115"/>
+      <c r="F16" s="115"/>
+      <c r="G16" s="115"/>
+      <c r="H16" s="115"/>
+      <c r="I16" s="116"/>
+      <c r="J16" s="116"/>
+      <c r="K16" s="116"/>
+      <c r="L16" s="116"/>
+      <c r="M16" s="116"/>
+      <c r="N16" s="116">
+        <v>400</v>
+      </c>
+      <c r="O16" s="116"/>
+      <c r="P16" s="116"/>
+      <c r="Q16" s="116"/>
+      <c r="R16" s="116">
+        <v>499</v>
+      </c>
+      <c r="S16" s="116"/>
+      <c r="T16" s="116"/>
+      <c r="U16" s="116"/>
+      <c r="V16" s="118">
+        <f t="shared" si="0"/>
+        <v>1099</v>
+      </c>
+      <c r="W16" s="119"/>
+      <c r="X16" s="113"/>
+    </row>
+    <row r="17" spans="1:24">
+      <c r="A17" s="120">
+        <v>19</v>
+      </c>
+      <c r="B17" s="120" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="121"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="115"/>
+      <c r="H17" s="115"/>
+      <c r="I17" s="123"/>
+      <c r="J17" s="123"/>
+      <c r="K17" s="123"/>
+      <c r="L17" s="123"/>
+      <c r="M17" s="123"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="123"/>
+      <c r="P17" s="123"/>
+      <c r="Q17" s="123"/>
+      <c r="R17" s="123"/>
+      <c r="S17" s="123"/>
+      <c r="T17" s="123"/>
+      <c r="U17" s="123"/>
+      <c r="V17" s="124">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="125"/>
+      <c r="X17" s="113">
+        <f>W3-SUM(V3:V16)</f>
+        <v>-6655.05</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" ht="14.25" customHeight="1">
+      <c r="A18" s="108">
+        <v>20</v>
+      </c>
+      <c r="B18" s="108" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="109"/>
+      <c r="D18" s="110"/>
+      <c r="E18" s="110"/>
+      <c r="F18" s="110"/>
+      <c r="G18" s="110"/>
+      <c r="H18" s="110"/>
+      <c r="I18" s="109">
+        <v>1300</v>
+      </c>
+      <c r="J18" s="109"/>
+      <c r="K18" s="109"/>
+      <c r="L18" s="109"/>
+      <c r="M18" s="109"/>
+      <c r="N18" s="109">
+        <f>1587+618</f>
+        <v>2205</v>
+      </c>
+      <c r="O18" s="109"/>
+      <c r="P18" s="109"/>
+      <c r="Q18" s="109"/>
+      <c r="R18" s="109"/>
+      <c r="S18" s="109"/>
+      <c r="T18" s="109"/>
+      <c r="U18" s="109"/>
+      <c r="V18" s="111">
+        <f t="shared" si="0"/>
+        <v>3505</v>
+      </c>
+      <c r="W18" s="112">
+        <f>30304+16451</f>
+        <v>46755</v>
+      </c>
+      <c r="X18" s="126"/>
+    </row>
+    <row r="19" spans="1:24">
+      <c r="A19" s="120">
+        <v>21</v>
+      </c>
+      <c r="B19" s="120" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="123"/>
+      <c r="D19" s="123"/>
+      <c r="E19" s="123">
+        <v>2933.48</v>
+      </c>
+      <c r="F19" s="123"/>
+      <c r="G19" s="123">
+        <f>3700+435</f>
+        <v>4135</v>
+      </c>
+      <c r="H19" s="123"/>
+      <c r="I19" s="123"/>
+      <c r="J19" s="123"/>
+      <c r="K19" s="123"/>
+      <c r="L19" s="123"/>
+      <c r="M19" s="123"/>
+      <c r="N19" s="123">
+        <v>463</v>
+      </c>
+      <c r="O19" s="123"/>
+      <c r="P19" s="123"/>
+      <c r="Q19" s="123"/>
+      <c r="R19" s="123"/>
+      <c r="S19" s="123"/>
+      <c r="T19" s="123"/>
+      <c r="U19" s="123"/>
+      <c r="V19" s="124">
+        <f t="shared" si="0"/>
+        <v>7531.48</v>
+      </c>
+      <c r="W19" s="125"/>
+      <c r="X19" s="113"/>
+    </row>
+    <row r="20" spans="1:24">
+      <c r="A20" s="114">
+        <v>22</v>
+      </c>
+      <c r="B20" s="114" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="116">
+        <f>968+2181</f>
+        <v>3149</v>
+      </c>
+      <c r="D20" s="116"/>
+      <c r="E20" s="116"/>
+      <c r="F20" s="116"/>
+      <c r="G20" s="116"/>
+      <c r="H20" s="116"/>
+      <c r="I20" s="116"/>
+      <c r="J20" s="116"/>
+      <c r="K20" s="116"/>
+      <c r="L20" s="116"/>
+      <c r="M20" s="116"/>
+      <c r="N20" s="116"/>
+      <c r="O20" s="116"/>
+      <c r="P20" s="116">
+        <v>1300</v>
+      </c>
+      <c r="Q20" s="116"/>
+      <c r="R20" s="116"/>
+      <c r="S20" s="116"/>
+      <c r="T20" s="116"/>
+      <c r="U20" s="116"/>
+      <c r="V20" s="118">
+        <f t="shared" ref="V20:V30" si="1">SUM(C20:U20)</f>
+        <v>4449</v>
+      </c>
+      <c r="W20" s="119"/>
+      <c r="X20" s="113"/>
+    </row>
+    <row r="21" spans="1:24">
+      <c r="A21" s="120">
+        <v>23</v>
+      </c>
+      <c r="B21" s="120" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="123"/>
+      <c r="D21" s="123"/>
+      <c r="E21" s="123"/>
+      <c r="F21" s="123"/>
+      <c r="G21" s="123"/>
+      <c r="H21" s="123"/>
+      <c r="I21" s="123"/>
+      <c r="J21" s="123"/>
+      <c r="K21" s="123"/>
+      <c r="L21" s="123"/>
+      <c r="M21" s="123"/>
+      <c r="N21" s="123"/>
+      <c r="O21" s="123"/>
+      <c r="P21" s="123"/>
+      <c r="Q21" s="123"/>
+      <c r="R21" s="123"/>
+      <c r="S21" s="123"/>
+      <c r="T21" s="123"/>
+      <c r="U21" s="123"/>
+      <c r="V21" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="125">
+        <v>10000</v>
+      </c>
+      <c r="X21" s="113"/>
+    </row>
+    <row r="22" spans="1:24">
+      <c r="A22" s="114">
+        <v>24</v>
+      </c>
+      <c r="B22" s="114" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="116"/>
+      <c r="D22" s="116"/>
+      <c r="E22" s="116">
+        <v>1583</v>
+      </c>
+      <c r="F22" s="116">
+        <v>939</v>
+      </c>
+      <c r="G22" s="116"/>
+      <c r="H22" s="116"/>
+      <c r="I22" s="116"/>
+      <c r="J22" s="116"/>
+      <c r="K22" s="116"/>
+      <c r="L22" s="116"/>
+      <c r="M22" s="116"/>
+      <c r="N22" s="116">
+        <v>515</v>
+      </c>
+      <c r="O22" s="116"/>
+      <c r="P22" s="116"/>
+      <c r="Q22" s="116"/>
+      <c r="R22" s="116"/>
+      <c r="S22" s="116"/>
+      <c r="T22" s="116"/>
+      <c r="U22" s="116"/>
+      <c r="V22" s="118">
+        <f t="shared" si="1"/>
+        <v>3037</v>
+      </c>
+      <c r="W22" s="119"/>
+      <c r="X22" s="113"/>
+    </row>
+    <row r="23" spans="1:24">
+      <c r="A23" s="120">
+        <v>25</v>
+      </c>
+      <c r="B23" s="120" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="123">
+        <v>935</v>
+      </c>
+      <c r="D23" s="123"/>
+      <c r="E23" s="123"/>
+      <c r="F23" s="123">
+        <f>1118+770</f>
+        <v>1888</v>
+      </c>
+      <c r="G23" s="123"/>
+      <c r="H23" s="123"/>
+      <c r="I23" s="123"/>
+      <c r="J23" s="123"/>
+      <c r="K23" s="123"/>
+      <c r="L23" s="123"/>
+      <c r="M23" s="123"/>
+      <c r="N23" s="123">
+        <f>360+381</f>
+        <v>741</v>
+      </c>
+      <c r="O23" s="123"/>
+      <c r="P23" s="123">
+        <v>100</v>
+      </c>
+      <c r="Q23" s="123"/>
+      <c r="R23" s="123"/>
+      <c r="S23" s="123">
+        <f>100+650</f>
+        <v>750</v>
+      </c>
+      <c r="T23" s="123"/>
+      <c r="U23" s="123"/>
+      <c r="V23" s="124">
+        <f t="shared" si="1"/>
+        <v>4414</v>
+      </c>
+      <c r="W23" s="125"/>
+      <c r="X23" s="113"/>
+    </row>
+    <row r="24" spans="1:24">
+      <c r="A24" s="114">
+        <v>26</v>
+      </c>
+      <c r="B24" s="114" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="116"/>
+      <c r="D24" s="116"/>
+      <c r="E24" s="116">
+        <v>611</v>
+      </c>
+      <c r="F24" s="116"/>
+      <c r="G24" s="116"/>
+      <c r="H24" s="116"/>
+      <c r="I24" s="116"/>
+      <c r="J24" s="116"/>
+      <c r="K24" s="116"/>
+      <c r="L24" s="116"/>
+      <c r="M24" s="116"/>
+      <c r="N24" s="116">
+        <f>400+344</f>
+        <v>744</v>
+      </c>
+      <c r="O24" s="116"/>
+      <c r="P24" s="116">
+        <v>214</v>
+      </c>
+      <c r="Q24" s="116"/>
+      <c r="R24" s="116"/>
+      <c r="S24" s="116"/>
+      <c r="T24" s="116"/>
+      <c r="U24" s="116"/>
+      <c r="V24" s="118">
+        <f t="shared" si="1"/>
+        <v>1569</v>
+      </c>
+      <c r="W24" s="119"/>
+      <c r="X24" s="113"/>
+    </row>
+    <row r="25" spans="1:24">
+      <c r="A25" s="120">
+        <v>27</v>
+      </c>
+      <c r="B25" s="120" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="123"/>
+      <c r="D25" s="123"/>
+      <c r="E25" s="123"/>
+      <c r="F25" s="123">
+        <v>700</v>
+      </c>
+      <c r="G25" s="123"/>
+      <c r="H25" s="123">
+        <v>1239.99</v>
+      </c>
+      <c r="I25" s="123"/>
+      <c r="J25" s="123">
+        <v>3974.41</v>
+      </c>
+      <c r="K25" s="123"/>
+      <c r="L25" s="123"/>
+      <c r="M25" s="123"/>
+      <c r="N25" s="123">
+        <f>349+254+607+400</f>
+        <v>1610</v>
+      </c>
+      <c r="O25" s="123"/>
+      <c r="P25" s="123"/>
+      <c r="Q25" s="123"/>
+      <c r="R25" s="123"/>
+      <c r="S25" s="123"/>
+      <c r="T25" s="123"/>
+      <c r="U25" s="123">
+        <f>1100+1090+350</f>
+        <v>2540</v>
+      </c>
+      <c r="V25" s="124">
+        <f t="shared" si="1"/>
+        <v>10064.4</v>
+      </c>
+      <c r="W25" s="125"/>
+      <c r="X25" s="113"/>
+    </row>
+    <row r="26" spans="1:24">
+      <c r="A26" s="114">
+        <v>28</v>
+      </c>
+      <c r="B26" s="114" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="116">
+        <v>1577.82</v>
+      </c>
+      <c r="D26" s="116"/>
+      <c r="E26" s="116"/>
+      <c r="F26" s="116"/>
+      <c r="G26" s="116"/>
+      <c r="H26" s="116"/>
+      <c r="I26" s="116"/>
+      <c r="J26" s="116">
+        <v>3990.69</v>
+      </c>
+      <c r="K26" s="116"/>
+      <c r="L26" s="116">
+        <f>1896+3633</f>
+        <v>5529</v>
+      </c>
+      <c r="M26" s="116"/>
+      <c r="N26" s="116">
+        <f>233+539</f>
+        <v>772</v>
+      </c>
+      <c r="O26" s="116"/>
+      <c r="P26" s="116">
+        <v>2400</v>
+      </c>
+      <c r="Q26" s="116"/>
+      <c r="R26" s="116"/>
+      <c r="S26" s="116"/>
+      <c r="T26" s="116"/>
+      <c r="U26" s="116"/>
+      <c r="V26" s="118">
+        <f t="shared" si="1"/>
+        <v>14269.51</v>
+      </c>
+      <c r="W26" s="119"/>
+      <c r="X26" s="113"/>
+    </row>
+    <row r="27" spans="1:24">
+      <c r="A27" s="114">
+        <v>1</v>
+      </c>
+      <c r="B27" s="114" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="116"/>
+      <c r="D27" s="116">
+        <v>1294</v>
+      </c>
+      <c r="E27" s="116"/>
+      <c r="F27" s="116"/>
+      <c r="G27" s="116"/>
+      <c r="H27" s="116"/>
+      <c r="I27" s="116"/>
+      <c r="J27" s="116">
+        <v>1711.25</v>
+      </c>
+      <c r="K27" s="116"/>
+      <c r="L27" s="116"/>
+      <c r="M27" s="116"/>
+      <c r="N27" s="116">
+        <v>133</v>
+      </c>
+      <c r="O27" s="116"/>
+      <c r="P27" s="116"/>
+      <c r="Q27" s="116"/>
+      <c r="R27" s="116"/>
+      <c r="S27" s="116">
+        <f>414+449</f>
+        <v>863</v>
+      </c>
+      <c r="T27" s="116"/>
+      <c r="U27" s="116"/>
+      <c r="V27" s="124">
+        <f t="shared" si="1"/>
+        <v>4001.25</v>
+      </c>
+      <c r="W27" s="119"/>
+      <c r="X27" s="113"/>
+    </row>
+    <row r="28" spans="1:24">
+      <c r="A28" s="114">
+        <v>2</v>
+      </c>
+      <c r="B28" s="114" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" s="116"/>
+      <c r="D28" s="116"/>
+      <c r="E28" s="116"/>
+      <c r="F28" s="116">
+        <f>350+1510</f>
+        <v>1860</v>
+      </c>
+      <c r="G28" s="116"/>
+      <c r="H28" s="116"/>
+      <c r="I28" s="116"/>
+      <c r="J28" s="116"/>
+      <c r="K28" s="116"/>
+      <c r="L28" s="116"/>
+      <c r="M28" s="116"/>
+      <c r="N28" s="116">
+        <v>277</v>
+      </c>
+      <c r="O28" s="116"/>
+      <c r="P28" s="116"/>
+      <c r="Q28" s="116"/>
+      <c r="R28" s="116">
+        <v>700</v>
+      </c>
+      <c r="S28" s="116"/>
+      <c r="T28" s="116"/>
+      <c r="U28" s="116"/>
+      <c r="V28" s="118">
+        <f t="shared" si="1"/>
+        <v>2837</v>
+      </c>
+      <c r="W28" s="119"/>
+      <c r="X28" s="113"/>
+    </row>
+    <row r="29" spans="1:24">
+      <c r="A29" s="114">
+        <v>3</v>
+      </c>
+      <c r="B29" s="114" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="116"/>
+      <c r="D29" s="116"/>
+      <c r="E29" s="116"/>
+      <c r="F29" s="116"/>
+      <c r="G29" s="116"/>
+      <c r="H29" s="116"/>
+      <c r="I29" s="116"/>
+      <c r="J29" s="116"/>
+      <c r="K29" s="116"/>
+      <c r="L29" s="116"/>
+      <c r="M29" s="116"/>
+      <c r="N29" s="116"/>
+      <c r="O29" s="116"/>
+      <c r="P29" s="116"/>
+      <c r="Q29" s="116"/>
+      <c r="R29" s="116">
+        <v>799</v>
+      </c>
+      <c r="S29" s="116"/>
+      <c r="T29" s="116"/>
+      <c r="U29" s="116"/>
+      <c r="V29" s="124">
+        <f t="shared" si="1"/>
+        <v>799</v>
+      </c>
+      <c r="W29" s="119"/>
+      <c r="X29" s="113"/>
+    </row>
+    <row r="30" spans="1:24">
+      <c r="A30" s="114">
+        <v>4</v>
+      </c>
+      <c r="B30" s="114" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" s="115"/>
+      <c r="D30" s="115"/>
+      <c r="E30" s="116"/>
+      <c r="F30" s="116"/>
+      <c r="G30" s="115"/>
+      <c r="H30" s="116"/>
+      <c r="I30" s="116"/>
+      <c r="J30" s="115"/>
+      <c r="K30" s="116"/>
+      <c r="L30" s="116"/>
+      <c r="M30" s="116"/>
+      <c r="N30" s="115"/>
+      <c r="O30" s="116"/>
+      <c r="P30" s="116"/>
+      <c r="Q30" s="116"/>
+      <c r="R30" s="115"/>
+      <c r="S30" s="115"/>
+      <c r="T30" s="116"/>
+      <c r="U30" s="116"/>
+      <c r="V30" s="118">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W30" s="119"/>
+      <c r="X30" s="113">
+        <f>W18+W21-SUM(V18:V30)</f>
+        <v>278.36000000000098</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24">
+      <c r="A31" s="201" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31" s="201"/>
+      <c r="C31" s="127">
+        <f>SUM(C3:C30)</f>
+        <v>19992.27</v>
+      </c>
+      <c r="D31" s="127">
+        <f t="shared" ref="D31:U31" si="2">SUM(D3:D30)</f>
+        <v>12488</v>
+      </c>
+      <c r="E31" s="127">
+        <f t="shared" si="2"/>
+        <v>5127.4799999999996</v>
+      </c>
+      <c r="F31" s="127">
+        <f t="shared" si="2"/>
+        <v>5387</v>
+      </c>
+      <c r="G31" s="127">
+        <f t="shared" si="2"/>
+        <v>8545</v>
+      </c>
+      <c r="H31" s="127">
+        <f t="shared" si="2"/>
+        <v>1239.99</v>
+      </c>
+      <c r="I31" s="127">
+        <f t="shared" si="2"/>
+        <v>2140</v>
+      </c>
+      <c r="J31" s="127">
+        <f t="shared" si="2"/>
+        <v>10126.35</v>
+      </c>
+      <c r="K31" s="127">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="127">
+        <f t="shared" si="2"/>
+        <v>5529</v>
+      </c>
+      <c r="M31" s="127">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N31" s="127">
+        <f t="shared" si="2"/>
+        <v>10621</v>
+      </c>
+      <c r="O31" s="127">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P31" s="127">
+        <f t="shared" si="2"/>
+        <v>9051</v>
+      </c>
+      <c r="Q31" s="127">
+        <f t="shared" si="2"/>
+        <v>14418</v>
+      </c>
+      <c r="R31" s="127">
+        <f t="shared" si="2"/>
+        <v>1998</v>
+      </c>
+      <c r="S31" s="127">
+        <f t="shared" si="2"/>
+        <v>7668</v>
+      </c>
+      <c r="T31" s="127">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="127">
+        <f t="shared" si="2"/>
+        <v>2540</v>
+      </c>
+      <c r="V31" s="127">
+        <f t="shared" ref="V31:W31" si="3">SUM(V3:V26)</f>
+        <v>109233.84</v>
+      </c>
+      <c r="W31" s="127">
+        <f t="shared" si="3"/>
+        <v>110494.39999999999</v>
+      </c>
+      <c r="X31" s="128">
+        <f>W31-V31</f>
+        <v>1260.5600000000099</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10">
+      <c r="B35" s="36"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="36"/>
+      <c r="G35" s="36"/>
+      <c r="H35" s="36"/>
+      <c r="I35" s="36"/>
+      <c r="J35" s="36"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:X1"/>
+    <mergeCell ref="A31:B31"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AT36"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="24" width="20.7109375" style="1" customWidth="1"/>
+    <col min="25" max="36" width="12.7109375" style="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:46" ht="60.75" customHeight="1">
       <c r="A1" s="202" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="B1" s="202"/>
       <c r="C1" s="202"/>
@@ -13197,76 +14580,76 @@
       <c r="X1" s="202"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
-      <c r="A2" s="107" t="s">
+      <c r="A2" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="107" t="s">
+      <c r="B2" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="107" t="s">
+      <c r="C2" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="107" t="s">
+      <c r="D2" s="84" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="107" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="107" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="107" t="s">
+      <c r="F2" s="84" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="84" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="107" t="s">
+      <c r="H2" s="84" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="107" t="s">
+      <c r="I2" s="84" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="107" t="s">
+      <c r="J2" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="K2" s="107" t="s">
+      <c r="K2" s="84" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="107" t="s">
+      <c r="L2" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="M2" s="107" t="s">
+      <c r="M2" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="N2" s="107" t="s">
+      <c r="N2" s="84" t="s">
         <v>34</v>
       </c>
-      <c r="O2" s="107" t="s">
+      <c r="O2" s="84" t="s">
         <v>35</v>
       </c>
-      <c r="P2" s="107" t="s">
+      <c r="P2" s="84" t="s">
         <v>36</v>
       </c>
-      <c r="Q2" s="107" t="s">
+      <c r="Q2" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="R2" s="107" t="s">
+      <c r="R2" s="84" t="s">
         <v>38</v>
       </c>
-      <c r="S2" s="107" t="s">
+      <c r="S2" s="84" t="s">
         <v>39</v>
       </c>
-      <c r="T2" s="107" t="s">
+      <c r="T2" s="84" t="s">
         <v>39</v>
       </c>
-      <c r="U2" s="107" t="s">
+      <c r="U2" s="84" t="s">
         <v>40</v>
       </c>
-      <c r="V2" s="107" t="s">
+      <c r="V2" s="84" t="s">
         <v>41</v>
       </c>
-      <c r="W2" s="107" t="s">
+      <c r="W2" s="84" t="s">
         <v>42</v>
       </c>
-      <c r="X2" s="107" t="s">
+      <c r="X2" s="84" t="s">
         <v>5</v>
       </c>
       <c r="Y2" s="10"/>
@@ -13293,1356 +14676,6 @@
       <c r="AT2" s="10"/>
     </row>
     <row r="3" spans="1:46">
-      <c r="A3" s="108">
-        <v>5</v>
-      </c>
-      <c r="B3" s="108" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" s="109">
-        <f>183+2168</f>
-        <v>2351</v>
-      </c>
-      <c r="D3" s="109">
-        <v>3131</v>
-      </c>
-      <c r="E3" s="109"/>
-      <c r="F3" s="109"/>
-      <c r="G3" s="110"/>
-      <c r="H3" s="110"/>
-      <c r="I3" s="109"/>
-      <c r="J3" s="109">
-        <v>450</v>
-      </c>
-      <c r="K3" s="109"/>
-      <c r="L3" s="109"/>
-      <c r="M3" s="109"/>
-      <c r="N3" s="109">
-        <v>40</v>
-      </c>
-      <c r="O3" s="109"/>
-      <c r="P3" s="109"/>
-      <c r="Q3" s="109">
-        <v>14418</v>
-      </c>
-      <c r="R3" s="109"/>
-      <c r="S3" s="109">
-        <v>5000</v>
-      </c>
-      <c r="T3" s="109"/>
-      <c r="U3" s="109"/>
-      <c r="V3" s="111">
-        <f>SUM(C3:U3)</f>
-        <v>25390</v>
-      </c>
-      <c r="W3" s="112">
-        <v>53739.4</v>
-      </c>
-      <c r="X3" s="113"/>
-    </row>
-    <row r="4" spans="1:46">
-      <c r="A4" s="114">
-        <v>6</v>
-      </c>
-      <c r="B4" s="114" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="115"/>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116"/>
-      <c r="M4" s="116"/>
-      <c r="N4" s="117">
-        <f>131+247</f>
-        <v>378</v>
-      </c>
-      <c r="O4" s="116"/>
-      <c r="P4" s="116"/>
-      <c r="Q4" s="116"/>
-      <c r="R4" s="116"/>
-      <c r="S4" s="116"/>
-      <c r="T4" s="116"/>
-      <c r="U4" s="116"/>
-      <c r="V4" s="118">
-        <f>SUM(C4:U4)</f>
-        <v>378</v>
-      </c>
-      <c r="W4" s="119"/>
-      <c r="X4" s="113"/>
-    </row>
-    <row r="5" spans="1:46">
-      <c r="A5" s="120">
-        <v>7</v>
-      </c>
-      <c r="B5" s="120" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="121"/>
-      <c r="D5" s="122">
-        <v>1110</v>
-      </c>
-      <c r="E5" s="122"/>
-      <c r="F5" s="122"/>
-      <c r="G5" s="121"/>
-      <c r="H5" s="121"/>
-      <c r="I5" s="123">
-        <v>840</v>
-      </c>
-      <c r="J5" s="123"/>
-      <c r="K5" s="123"/>
-      <c r="L5" s="123"/>
-      <c r="M5" s="123"/>
-      <c r="N5" s="123">
-        <f>197+259</f>
-        <v>456</v>
-      </c>
-      <c r="O5" s="123"/>
-      <c r="P5" s="123"/>
-      <c r="Q5" s="123"/>
-      <c r="R5" s="123"/>
-      <c r="S5" s="123"/>
-      <c r="T5" s="123"/>
-      <c r="U5" s="123"/>
-      <c r="V5" s="124">
-        <f>SUM(C5:U5)</f>
-        <v>2406</v>
-      </c>
-      <c r="W5" s="125"/>
-      <c r="X5" s="113"/>
-    </row>
-    <row r="6" spans="1:46">
-      <c r="A6" s="114">
-        <v>8</v>
-      </c>
-      <c r="B6" s="114" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="117">
-        <v>1006</v>
-      </c>
-      <c r="D6" s="115"/>
-      <c r="E6" s="115"/>
-      <c r="F6" s="115"/>
-      <c r="G6" s="115"/>
-      <c r="H6" s="115"/>
-      <c r="I6" s="116"/>
-      <c r="J6" s="116"/>
-      <c r="K6" s="116"/>
-      <c r="L6" s="116"/>
-      <c r="M6" s="116"/>
-      <c r="N6" s="117">
-        <f>221+171</f>
-        <v>392</v>
-      </c>
-      <c r="O6" s="116"/>
-      <c r="P6" s="115"/>
-      <c r="Q6" s="116"/>
-      <c r="R6" s="116"/>
-      <c r="S6" s="116"/>
-      <c r="T6" s="116"/>
-      <c r="U6" s="116"/>
-      <c r="V6" s="118">
-        <f t="shared" ref="V6:V19" si="0">SUM(C6:U6)</f>
-        <v>1398</v>
-      </c>
-      <c r="W6" s="119"/>
-      <c r="X6" s="113"/>
-    </row>
-    <row r="7" spans="1:46">
-      <c r="A7" s="120">
-        <v>9</v>
-      </c>
-      <c r="B7" s="120" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="122">
-        <v>1819</v>
-      </c>
-      <c r="D7" s="121"/>
-      <c r="E7" s="121"/>
-      <c r="F7" s="121"/>
-      <c r="G7" s="121"/>
-      <c r="H7" s="121"/>
-      <c r="I7" s="123"/>
-      <c r="J7" s="123"/>
-      <c r="K7" s="123"/>
-      <c r="L7" s="123"/>
-      <c r="M7" s="123"/>
-      <c r="N7" s="123">
-        <v>224</v>
-      </c>
-      <c r="O7" s="121"/>
-      <c r="P7" s="123"/>
-      <c r="Q7" s="123"/>
-      <c r="R7" s="123"/>
-      <c r="S7" s="123">
-        <v>1055</v>
-      </c>
-      <c r="T7" s="123"/>
-      <c r="U7" s="123"/>
-      <c r="V7" s="124">
-        <f t="shared" si="0"/>
-        <v>3098</v>
-      </c>
-      <c r="W7" s="125"/>
-      <c r="X7" s="113"/>
-    </row>
-    <row r="8" spans="1:46">
-      <c r="A8" s="114">
-        <v>10</v>
-      </c>
-      <c r="B8" s="114" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="116">
-        <v>1266.9000000000001</v>
-      </c>
-      <c r="D8" s="116">
-        <v>1345</v>
-      </c>
-      <c r="E8" s="116"/>
-      <c r="F8" s="116"/>
-      <c r="G8" s="115"/>
-      <c r="H8" s="115"/>
-      <c r="I8" s="116"/>
-      <c r="J8" s="116"/>
-      <c r="K8" s="116"/>
-      <c r="L8" s="116"/>
-      <c r="M8" s="116"/>
-      <c r="N8" s="116">
-        <v>172</v>
-      </c>
-      <c r="O8" s="116"/>
-      <c r="P8" s="116"/>
-      <c r="Q8" s="116"/>
-      <c r="R8" s="115"/>
-      <c r="S8" s="116"/>
-      <c r="T8" s="116"/>
-      <c r="U8" s="116"/>
-      <c r="V8" s="118">
-        <f t="shared" si="0"/>
-        <v>2783.9</v>
-      </c>
-      <c r="W8" s="119"/>
-      <c r="X8" s="113"/>
-    </row>
-    <row r="9" spans="1:46">
-      <c r="A9" s="120">
-        <v>11</v>
-      </c>
-      <c r="B9" s="120" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="123">
-        <v>1403.84</v>
-      </c>
-      <c r="D9" s="121"/>
-      <c r="E9" s="121"/>
-      <c r="F9" s="121"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="121"/>
-      <c r="I9" s="123"/>
-      <c r="J9" s="123"/>
-      <c r="K9" s="123"/>
-      <c r="L9" s="123"/>
-      <c r="M9" s="123"/>
-      <c r="N9" s="123"/>
-      <c r="O9" s="123"/>
-      <c r="P9" s="123"/>
-      <c r="Q9" s="123"/>
-      <c r="R9" s="121"/>
-      <c r="S9" s="123"/>
-      <c r="T9" s="123"/>
-      <c r="U9" s="123"/>
-      <c r="V9" s="124">
-        <f t="shared" si="0"/>
-        <v>1403.84</v>
-      </c>
-      <c r="W9" s="125"/>
-      <c r="X9" s="113"/>
-    </row>
-    <row r="10" spans="1:46">
-      <c r="A10" s="114">
-        <v>12</v>
-      </c>
-      <c r="B10" s="114" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="115"/>
-      <c r="D10" s="116">
-        <v>959</v>
-      </c>
-      <c r="E10" s="116"/>
-      <c r="F10" s="116"/>
-      <c r="G10" s="115"/>
-      <c r="H10" s="115"/>
-      <c r="I10" s="116"/>
-      <c r="J10" s="116"/>
-      <c r="K10" s="116"/>
-      <c r="L10" s="116"/>
-      <c r="M10" s="116"/>
-      <c r="N10" s="115"/>
-      <c r="O10" s="116"/>
-      <c r="P10" s="116"/>
-      <c r="Q10" s="116"/>
-      <c r="R10" s="115"/>
-      <c r="S10" s="116"/>
-      <c r="T10" s="116"/>
-      <c r="U10" s="116"/>
-      <c r="V10" s="118">
-        <f t="shared" si="0"/>
-        <v>959</v>
-      </c>
-      <c r="W10" s="119"/>
-      <c r="X10" s="113"/>
-    </row>
-    <row r="11" spans="1:46">
-      <c r="A11" s="120">
-        <v>13</v>
-      </c>
-      <c r="B11" s="120" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="123">
-        <f>342.99+1260.98</f>
-        <v>1603.97</v>
-      </c>
-      <c r="D11" s="121"/>
-      <c r="E11" s="121"/>
-      <c r="F11" s="121"/>
-      <c r="G11" s="123">
-        <f>3980+430</f>
-        <v>4410</v>
-      </c>
-      <c r="H11" s="123"/>
-      <c r="I11" s="123"/>
-      <c r="J11" s="123"/>
-      <c r="K11" s="123"/>
-      <c r="L11" s="123"/>
-      <c r="M11" s="123"/>
-      <c r="N11" s="123"/>
-      <c r="O11" s="123"/>
-      <c r="P11" s="123">
-        <f>773+2000+1767</f>
-        <v>4540</v>
-      </c>
-      <c r="Q11" s="123"/>
-      <c r="R11" s="121"/>
-      <c r="S11" s="123"/>
-      <c r="T11" s="123"/>
-      <c r="U11" s="123"/>
-      <c r="V11" s="124">
-        <f t="shared" si="0"/>
-        <v>10553.97</v>
-      </c>
-      <c r="W11" s="125"/>
-      <c r="X11" s="113"/>
-    </row>
-    <row r="12" spans="1:46">
-      <c r="A12" s="114">
-        <v>14</v>
-      </c>
-      <c r="B12" s="114" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="116">
-        <f>1260.98+678.97</f>
-        <v>1939.95</v>
-      </c>
-      <c r="D12" s="116">
-        <f>4500+149</f>
-        <v>4649</v>
-      </c>
-      <c r="E12" s="116"/>
-      <c r="F12" s="116"/>
-      <c r="G12" s="115"/>
-      <c r="H12" s="115"/>
-      <c r="I12" s="116"/>
-      <c r="J12" s="115"/>
-      <c r="K12" s="116"/>
-      <c r="L12" s="116"/>
-      <c r="M12" s="116"/>
-      <c r="N12" s="116">
-        <f>543+421</f>
-        <v>964</v>
-      </c>
-      <c r="O12" s="116"/>
-      <c r="P12" s="116">
-        <f>497</f>
-        <v>497</v>
-      </c>
-      <c r="Q12" s="116"/>
-      <c r="R12" s="116"/>
-      <c r="S12" s="116"/>
-      <c r="T12" s="116"/>
-      <c r="U12" s="116"/>
-      <c r="V12" s="118">
-        <f t="shared" si="0"/>
-        <v>8049.95</v>
-      </c>
-      <c r="W12" s="119"/>
-      <c r="X12" s="113"/>
-    </row>
-    <row r="13" spans="1:46">
-      <c r="A13" s="120">
-        <v>15</v>
-      </c>
-      <c r="B13" s="120" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="123">
-        <f>1569.79</f>
-        <v>1569.79</v>
-      </c>
-      <c r="D13" s="121"/>
-      <c r="E13" s="121"/>
-      <c r="F13" s="121"/>
-      <c r="G13" s="121"/>
-      <c r="H13" s="121"/>
-      <c r="I13" s="123"/>
-      <c r="J13" s="121"/>
-      <c r="K13" s="123"/>
-      <c r="L13" s="123"/>
-      <c r="M13" s="123"/>
-      <c r="N13" s="123">
-        <v>135</v>
-      </c>
-      <c r="O13" s="123"/>
-      <c r="P13" s="123"/>
-      <c r="Q13" s="123"/>
-      <c r="R13" s="123"/>
-      <c r="S13" s="123"/>
-      <c r="T13" s="123"/>
-      <c r="U13" s="123"/>
-      <c r="V13" s="124">
-        <f t="shared" si="0"/>
-        <v>1704.79</v>
-      </c>
-      <c r="W13" s="125"/>
-      <c r="X13" s="113"/>
-    </row>
-    <row r="14" spans="1:46">
-      <c r="A14" s="114">
-        <v>16</v>
-      </c>
-      <c r="B14" s="114" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="116">
-        <v>1170</v>
-      </c>
-      <c r="D14" s="115"/>
-      <c r="E14" s="115"/>
-      <c r="F14" s="115"/>
-      <c r="G14" s="115"/>
-      <c r="H14" s="115"/>
-      <c r="I14" s="116"/>
-      <c r="J14" s="115"/>
-      <c r="K14" s="116"/>
-      <c r="L14" s="116"/>
-      <c r="M14" s="116"/>
-      <c r="N14" s="116"/>
-      <c r="O14" s="115"/>
-      <c r="P14" s="116"/>
-      <c r="Q14" s="116"/>
-      <c r="R14" s="116"/>
-      <c r="S14" s="116"/>
-      <c r="T14" s="116"/>
-      <c r="U14" s="116"/>
-      <c r="V14" s="118">
-        <f t="shared" si="0"/>
-        <v>1170</v>
-      </c>
-      <c r="W14" s="119"/>
-      <c r="X14" s="113"/>
-    </row>
-    <row r="15" spans="1:46">
-      <c r="A15" s="120">
-        <v>17</v>
-      </c>
-      <c r="B15" s="120" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="121"/>
-      <c r="D15" s="121"/>
-      <c r="E15" s="121"/>
-      <c r="F15" s="121"/>
-      <c r="G15" s="121"/>
-      <c r="H15" s="121"/>
-      <c r="I15" s="123"/>
-      <c r="J15" s="123"/>
-      <c r="K15" s="123"/>
-      <c r="L15" s="123"/>
-      <c r="M15" s="123"/>
-      <c r="N15" s="121"/>
-      <c r="O15" s="123"/>
-      <c r="P15" s="123"/>
-      <c r="Q15" s="123"/>
-      <c r="R15" s="123"/>
-      <c r="S15" s="123"/>
-      <c r="T15" s="123"/>
-      <c r="U15" s="123"/>
-      <c r="V15" s="124">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W15" s="125"/>
-      <c r="X15" s="113"/>
-    </row>
-    <row r="16" spans="1:46">
-      <c r="A16" s="114">
-        <v>18</v>
-      </c>
-      <c r="B16" s="114" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="116">
-        <v>200</v>
-      </c>
-      <c r="D16" s="115"/>
-      <c r="E16" s="115"/>
-      <c r="F16" s="115"/>
-      <c r="G16" s="115"/>
-      <c r="H16" s="115"/>
-      <c r="I16" s="116"/>
-      <c r="J16" s="116"/>
-      <c r="K16" s="116"/>
-      <c r="L16" s="116"/>
-      <c r="M16" s="116"/>
-      <c r="N16" s="116">
-        <v>400</v>
-      </c>
-      <c r="O16" s="116"/>
-      <c r="P16" s="116"/>
-      <c r="Q16" s="116"/>
-      <c r="R16" s="116">
-        <v>499</v>
-      </c>
-      <c r="S16" s="116"/>
-      <c r="T16" s="116"/>
-      <c r="U16" s="116"/>
-      <c r="V16" s="118">
-        <f t="shared" si="0"/>
-        <v>1099</v>
-      </c>
-      <c r="W16" s="119"/>
-      <c r="X16" s="113"/>
-    </row>
-    <row r="17" spans="1:24">
-      <c r="A17" s="120">
-        <v>19</v>
-      </c>
-      <c r="B17" s="120" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="121"/>
-      <c r="G17" s="115"/>
-      <c r="H17" s="115"/>
-      <c r="I17" s="123"/>
-      <c r="J17" s="123"/>
-      <c r="K17" s="123"/>
-      <c r="L17" s="123"/>
-      <c r="M17" s="123"/>
-      <c r="N17" s="121"/>
-      <c r="O17" s="123"/>
-      <c r="P17" s="123"/>
-      <c r="Q17" s="123"/>
-      <c r="R17" s="123"/>
-      <c r="S17" s="123"/>
-      <c r="T17" s="123"/>
-      <c r="U17" s="123"/>
-      <c r="V17" s="124">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W17" s="125"/>
-      <c r="X17" s="113">
-        <f>W3-SUM(V3:V16)</f>
-        <v>-6655.05</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24" ht="14.25" customHeight="1">
-      <c r="A18" s="108">
-        <v>20</v>
-      </c>
-      <c r="B18" s="108" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="109"/>
-      <c r="D18" s="110"/>
-      <c r="E18" s="110"/>
-      <c r="F18" s="110"/>
-      <c r="G18" s="110"/>
-      <c r="H18" s="110"/>
-      <c r="I18" s="109">
-        <v>1300</v>
-      </c>
-      <c r="J18" s="109"/>
-      <c r="K18" s="109"/>
-      <c r="L18" s="109"/>
-      <c r="M18" s="109"/>
-      <c r="N18" s="109">
-        <f>1587+618</f>
-        <v>2205</v>
-      </c>
-      <c r="O18" s="109"/>
-      <c r="P18" s="109"/>
-      <c r="Q18" s="109"/>
-      <c r="R18" s="109"/>
-      <c r="S18" s="109"/>
-      <c r="T18" s="109"/>
-      <c r="U18" s="109"/>
-      <c r="V18" s="111">
-        <f t="shared" si="0"/>
-        <v>3505</v>
-      </c>
-      <c r="W18" s="112">
-        <f>30304+16451</f>
-        <v>46755</v>
-      </c>
-      <c r="X18" s="126"/>
-    </row>
-    <row r="19" spans="1:24">
-      <c r="A19" s="120">
-        <v>21</v>
-      </c>
-      <c r="B19" s="120" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19" s="123"/>
-      <c r="D19" s="123"/>
-      <c r="E19" s="123">
-        <v>2933.48</v>
-      </c>
-      <c r="F19" s="123"/>
-      <c r="G19" s="123">
-        <f>3700+435</f>
-        <v>4135</v>
-      </c>
-      <c r="H19" s="123"/>
-      <c r="I19" s="123"/>
-      <c r="J19" s="123"/>
-      <c r="K19" s="123"/>
-      <c r="L19" s="123"/>
-      <c r="M19" s="123"/>
-      <c r="N19" s="123">
-        <v>463</v>
-      </c>
-      <c r="O19" s="123"/>
-      <c r="P19" s="123"/>
-      <c r="Q19" s="123"/>
-      <c r="R19" s="123"/>
-      <c r="S19" s="123"/>
-      <c r="T19" s="123"/>
-      <c r="U19" s="123"/>
-      <c r="V19" s="124">
-        <f t="shared" si="0"/>
-        <v>7531.48</v>
-      </c>
-      <c r="W19" s="125"/>
-      <c r="X19" s="113"/>
-    </row>
-    <row r="20" spans="1:24">
-      <c r="A20" s="114">
-        <v>22</v>
-      </c>
-      <c r="B20" s="114" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" s="116">
-        <f>968+2181</f>
-        <v>3149</v>
-      </c>
-      <c r="D20" s="116"/>
-      <c r="E20" s="116"/>
-      <c r="F20" s="116"/>
-      <c r="G20" s="116"/>
-      <c r="H20" s="116"/>
-      <c r="I20" s="116"/>
-      <c r="J20" s="116"/>
-      <c r="K20" s="116"/>
-      <c r="L20" s="116"/>
-      <c r="M20" s="116"/>
-      <c r="N20" s="116"/>
-      <c r="O20" s="116"/>
-      <c r="P20" s="116">
-        <v>1300</v>
-      </c>
-      <c r="Q20" s="116"/>
-      <c r="R20" s="116"/>
-      <c r="S20" s="116"/>
-      <c r="T20" s="116"/>
-      <c r="U20" s="116"/>
-      <c r="V20" s="118">
-        <f t="shared" ref="V20:V30" si="1">SUM(C20:U20)</f>
-        <v>4449</v>
-      </c>
-      <c r="W20" s="119"/>
-      <c r="X20" s="113"/>
-    </row>
-    <row r="21" spans="1:24">
-      <c r="A21" s="120">
-        <v>23</v>
-      </c>
-      <c r="B21" s="120" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="123"/>
-      <c r="D21" s="123"/>
-      <c r="E21" s="123"/>
-      <c r="F21" s="123"/>
-      <c r="G21" s="123"/>
-      <c r="H21" s="123"/>
-      <c r="I21" s="123"/>
-      <c r="J21" s="123"/>
-      <c r="K21" s="123"/>
-      <c r="L21" s="123"/>
-      <c r="M21" s="123"/>
-      <c r="N21" s="123"/>
-      <c r="O21" s="123"/>
-      <c r="P21" s="123"/>
-      <c r="Q21" s="123"/>
-      <c r="R21" s="123"/>
-      <c r="S21" s="123"/>
-      <c r="T21" s="123"/>
-      <c r="U21" s="123"/>
-      <c r="V21" s="124">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W21" s="125">
-        <v>10000</v>
-      </c>
-      <c r="X21" s="113"/>
-    </row>
-    <row r="22" spans="1:24">
-      <c r="A22" s="114">
-        <v>24</v>
-      </c>
-      <c r="B22" s="114" t="s">
-        <v>48</v>
-      </c>
-      <c r="C22" s="116"/>
-      <c r="D22" s="116"/>
-      <c r="E22" s="116">
-        <v>1583</v>
-      </c>
-      <c r="F22" s="116">
-        <v>939</v>
-      </c>
-      <c r="G22" s="116"/>
-      <c r="H22" s="116"/>
-      <c r="I22" s="116"/>
-      <c r="J22" s="116"/>
-      <c r="K22" s="116"/>
-      <c r="L22" s="116"/>
-      <c r="M22" s="116"/>
-      <c r="N22" s="116">
-        <v>515</v>
-      </c>
-      <c r="O22" s="116"/>
-      <c r="P22" s="116"/>
-      <c r="Q22" s="116"/>
-      <c r="R22" s="116"/>
-      <c r="S22" s="116"/>
-      <c r="T22" s="116"/>
-      <c r="U22" s="116"/>
-      <c r="V22" s="118">
-        <f t="shared" si="1"/>
-        <v>3037</v>
-      </c>
-      <c r="W22" s="119"/>
-      <c r="X22" s="113"/>
-    </row>
-    <row r="23" spans="1:24">
-      <c r="A23" s="120">
-        <v>25</v>
-      </c>
-      <c r="B23" s="120" t="s">
-        <v>49</v>
-      </c>
-      <c r="C23" s="123">
-        <v>935</v>
-      </c>
-      <c r="D23" s="123"/>
-      <c r="E23" s="123"/>
-      <c r="F23" s="123">
-        <f>1118+770</f>
-        <v>1888</v>
-      </c>
-      <c r="G23" s="123"/>
-      <c r="H23" s="123"/>
-      <c r="I23" s="123"/>
-      <c r="J23" s="123"/>
-      <c r="K23" s="123"/>
-      <c r="L23" s="123"/>
-      <c r="M23" s="123"/>
-      <c r="N23" s="123">
-        <f>360+381</f>
-        <v>741</v>
-      </c>
-      <c r="O23" s="123"/>
-      <c r="P23" s="123">
-        <v>100</v>
-      </c>
-      <c r="Q23" s="123"/>
-      <c r="R23" s="123"/>
-      <c r="S23" s="123">
-        <f>100+650</f>
-        <v>750</v>
-      </c>
-      <c r="T23" s="123"/>
-      <c r="U23" s="123"/>
-      <c r="V23" s="124">
-        <f t="shared" si="1"/>
-        <v>4414</v>
-      </c>
-      <c r="W23" s="125"/>
-      <c r="X23" s="113"/>
-    </row>
-    <row r="24" spans="1:24">
-      <c r="A24" s="114">
-        <v>26</v>
-      </c>
-      <c r="B24" s="114" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" s="116"/>
-      <c r="D24" s="116"/>
-      <c r="E24" s="116">
-        <v>611</v>
-      </c>
-      <c r="F24" s="116"/>
-      <c r="G24" s="116"/>
-      <c r="H24" s="116"/>
-      <c r="I24" s="116"/>
-      <c r="J24" s="116"/>
-      <c r="K24" s="116"/>
-      <c r="L24" s="116"/>
-      <c r="M24" s="116"/>
-      <c r="N24" s="116">
-        <f>400+344</f>
-        <v>744</v>
-      </c>
-      <c r="O24" s="116"/>
-      <c r="P24" s="116">
-        <v>214</v>
-      </c>
-      <c r="Q24" s="116"/>
-      <c r="R24" s="116"/>
-      <c r="S24" s="116"/>
-      <c r="T24" s="116"/>
-      <c r="U24" s="116"/>
-      <c r="V24" s="118">
-        <f t="shared" si="1"/>
-        <v>1569</v>
-      </c>
-      <c r="W24" s="119"/>
-      <c r="X24" s="113"/>
-    </row>
-    <row r="25" spans="1:24">
-      <c r="A25" s="120">
-        <v>27</v>
-      </c>
-      <c r="B25" s="120" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" s="123"/>
-      <c r="D25" s="123"/>
-      <c r="E25" s="123"/>
-      <c r="F25" s="123">
-        <v>700</v>
-      </c>
-      <c r="G25" s="123"/>
-      <c r="H25" s="123">
-        <v>1239.99</v>
-      </c>
-      <c r="I25" s="123"/>
-      <c r="J25" s="123">
-        <v>3974.41</v>
-      </c>
-      <c r="K25" s="123"/>
-      <c r="L25" s="123"/>
-      <c r="M25" s="123"/>
-      <c r="N25" s="123">
-        <f>349+254+607+400</f>
-        <v>1610</v>
-      </c>
-      <c r="O25" s="123"/>
-      <c r="P25" s="123"/>
-      <c r="Q25" s="123"/>
-      <c r="R25" s="123"/>
-      <c r="S25" s="123"/>
-      <c r="T25" s="123"/>
-      <c r="U25" s="123">
-        <f>1100+1090+350</f>
-        <v>2540</v>
-      </c>
-      <c r="V25" s="124">
-        <f t="shared" si="1"/>
-        <v>10064.4</v>
-      </c>
-      <c r="W25" s="125"/>
-      <c r="X25" s="113"/>
-    </row>
-    <row r="26" spans="1:24">
-      <c r="A26" s="114">
-        <v>28</v>
-      </c>
-      <c r="B26" s="114" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" s="116">
-        <v>1577.82</v>
-      </c>
-      <c r="D26" s="116"/>
-      <c r="E26" s="116"/>
-      <c r="F26" s="116"/>
-      <c r="G26" s="116"/>
-      <c r="H26" s="116"/>
-      <c r="I26" s="116"/>
-      <c r="J26" s="116">
-        <v>3990.69</v>
-      </c>
-      <c r="K26" s="116"/>
-      <c r="L26" s="116">
-        <f>1896+3633</f>
-        <v>5529</v>
-      </c>
-      <c r="M26" s="116"/>
-      <c r="N26" s="116">
-        <f>233+539</f>
-        <v>772</v>
-      </c>
-      <c r="O26" s="116"/>
-      <c r="P26" s="116">
-        <v>2400</v>
-      </c>
-      <c r="Q26" s="116"/>
-      <c r="R26" s="116"/>
-      <c r="S26" s="116"/>
-      <c r="T26" s="116"/>
-      <c r="U26" s="116"/>
-      <c r="V26" s="118">
-        <f t="shared" si="1"/>
-        <v>14269.51</v>
-      </c>
-      <c r="W26" s="119"/>
-      <c r="X26" s="113"/>
-    </row>
-    <row r="27" spans="1:24">
-      <c r="A27" s="114">
-        <v>1</v>
-      </c>
-      <c r="B27" s="114" t="s">
-        <v>46</v>
-      </c>
-      <c r="C27" s="116"/>
-      <c r="D27" s="116">
-        <v>1294</v>
-      </c>
-      <c r="E27" s="116"/>
-      <c r="F27" s="116"/>
-      <c r="G27" s="116"/>
-      <c r="H27" s="116"/>
-      <c r="I27" s="116"/>
-      <c r="J27" s="116">
-        <v>1711.25</v>
-      </c>
-      <c r="K27" s="116"/>
-      <c r="L27" s="116"/>
-      <c r="M27" s="116"/>
-      <c r="N27" s="116">
-        <v>133</v>
-      </c>
-      <c r="O27" s="116"/>
-      <c r="P27" s="116"/>
-      <c r="Q27" s="116"/>
-      <c r="R27" s="116"/>
-      <c r="S27" s="116">
-        <f>414+449</f>
-        <v>863</v>
-      </c>
-      <c r="T27" s="116"/>
-      <c r="U27" s="116"/>
-      <c r="V27" s="124">
-        <f t="shared" si="1"/>
-        <v>4001.25</v>
-      </c>
-      <c r="W27" s="119"/>
-      <c r="X27" s="113"/>
-    </row>
-    <row r="28" spans="1:24">
-      <c r="A28" s="114">
-        <v>2</v>
-      </c>
-      <c r="B28" s="114" t="s">
-        <v>47</v>
-      </c>
-      <c r="C28" s="116"/>
-      <c r="D28" s="116"/>
-      <c r="E28" s="116"/>
-      <c r="F28" s="116">
-        <f>350+1510</f>
-        <v>1860</v>
-      </c>
-      <c r="G28" s="116"/>
-      <c r="H28" s="116"/>
-      <c r="I28" s="116"/>
-      <c r="J28" s="116"/>
-      <c r="K28" s="116"/>
-      <c r="L28" s="116"/>
-      <c r="M28" s="116"/>
-      <c r="N28" s="116">
-        <v>277</v>
-      </c>
-      <c r="O28" s="116"/>
-      <c r="P28" s="116"/>
-      <c r="Q28" s="116"/>
-      <c r="R28" s="116">
-        <v>700</v>
-      </c>
-      <c r="S28" s="116"/>
-      <c r="T28" s="116"/>
-      <c r="U28" s="116"/>
-      <c r="V28" s="118">
-        <f t="shared" si="1"/>
-        <v>2837</v>
-      </c>
-      <c r="W28" s="119"/>
-      <c r="X28" s="113"/>
-    </row>
-    <row r="29" spans="1:24">
-      <c r="A29" s="114">
-        <v>3</v>
-      </c>
-      <c r="B29" s="114" t="s">
-        <v>48</v>
-      </c>
-      <c r="C29" s="116"/>
-      <c r="D29" s="116"/>
-      <c r="E29" s="116"/>
-      <c r="F29" s="116"/>
-      <c r="G29" s="116"/>
-      <c r="H29" s="116"/>
-      <c r="I29" s="116"/>
-      <c r="J29" s="116"/>
-      <c r="K29" s="116"/>
-      <c r="L29" s="116"/>
-      <c r="M29" s="116"/>
-      <c r="N29" s="116"/>
-      <c r="O29" s="116"/>
-      <c r="P29" s="116"/>
-      <c r="Q29" s="116"/>
-      <c r="R29" s="116">
-        <v>799</v>
-      </c>
-      <c r="S29" s="116"/>
-      <c r="T29" s="116"/>
-      <c r="U29" s="116"/>
-      <c r="V29" s="124">
-        <f t="shared" si="1"/>
-        <v>799</v>
-      </c>
-      <c r="W29" s="119"/>
-      <c r="X29" s="113"/>
-    </row>
-    <row r="30" spans="1:24">
-      <c r="A30" s="114">
-        <v>4</v>
-      </c>
-      <c r="B30" s="114" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" s="115"/>
-      <c r="D30" s="115"/>
-      <c r="E30" s="116"/>
-      <c r="F30" s="116"/>
-      <c r="G30" s="115"/>
-      <c r="H30" s="116"/>
-      <c r="I30" s="116"/>
-      <c r="J30" s="115"/>
-      <c r="K30" s="116"/>
-      <c r="L30" s="116"/>
-      <c r="M30" s="116"/>
-      <c r="N30" s="115"/>
-      <c r="O30" s="116"/>
-      <c r="P30" s="116"/>
-      <c r="Q30" s="116"/>
-      <c r="R30" s="115"/>
-      <c r="S30" s="115"/>
-      <c r="T30" s="116"/>
-      <c r="U30" s="116"/>
-      <c r="V30" s="118">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W30" s="119"/>
-      <c r="X30" s="113">
-        <f>W18+W21-SUM(V18:V30)</f>
-        <v>278.36000000000098</v>
-      </c>
-    </row>
-    <row r="31" spans="1:24">
-      <c r="A31" s="203" t="s">
-        <v>19</v>
-      </c>
-      <c r="B31" s="203"/>
-      <c r="C31" s="127">
-        <f>SUM(C3:C30)</f>
-        <v>19992.27</v>
-      </c>
-      <c r="D31" s="127">
-        <f t="shared" ref="D31:U31" si="2">SUM(D3:D30)</f>
-        <v>12488</v>
-      </c>
-      <c r="E31" s="127">
-        <f t="shared" si="2"/>
-        <v>5127.4799999999996</v>
-      </c>
-      <c r="F31" s="127">
-        <f t="shared" si="2"/>
-        <v>5387</v>
-      </c>
-      <c r="G31" s="127">
-        <f t="shared" si="2"/>
-        <v>8545</v>
-      </c>
-      <c r="H31" s="127">
-        <f t="shared" si="2"/>
-        <v>1239.99</v>
-      </c>
-      <c r="I31" s="127">
-        <f t="shared" si="2"/>
-        <v>2140</v>
-      </c>
-      <c r="J31" s="127">
-        <f t="shared" si="2"/>
-        <v>10126.35</v>
-      </c>
-      <c r="K31" s="127">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L31" s="127">
-        <f t="shared" si="2"/>
-        <v>5529</v>
-      </c>
-      <c r="M31" s="127">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N31" s="127">
-        <f t="shared" si="2"/>
-        <v>10621</v>
-      </c>
-      <c r="O31" s="127">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="P31" s="127">
-        <f t="shared" si="2"/>
-        <v>9051</v>
-      </c>
-      <c r="Q31" s="127">
-        <f t="shared" si="2"/>
-        <v>14418</v>
-      </c>
-      <c r="R31" s="127">
-        <f t="shared" si="2"/>
-        <v>1998</v>
-      </c>
-      <c r="S31" s="127">
-        <f t="shared" si="2"/>
-        <v>7668</v>
-      </c>
-      <c r="T31" s="127">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="U31" s="127">
-        <f t="shared" si="2"/>
-        <v>2540</v>
-      </c>
-      <c r="V31" s="127">
-        <f t="shared" ref="V31:W31" si="3">SUM(V3:V26)</f>
-        <v>109233.84</v>
-      </c>
-      <c r="W31" s="127">
-        <f t="shared" si="3"/>
-        <v>110494.39999999999</v>
-      </c>
-      <c r="X31" s="128">
-        <f>W31-V31</f>
-        <v>1260.5600000000099</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10">
-      <c r="B35" s="36"/>
-      <c r="C35" s="36"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="36"/>
-      <c r="I35" s="36"/>
-      <c r="J35" s="36"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:X1"/>
-    <mergeCell ref="A31:B31"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AT36"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="24" width="20.7109375" style="1" customWidth="1"/>
-    <col min="25" max="36" width="12.7109375" style="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="204" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="204"/>
-      <c r="C1" s="204"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="204"/>
-      <c r="F1" s="204"/>
-      <c r="G1" s="204"/>
-      <c r="H1" s="204"/>
-      <c r="I1" s="204"/>
-      <c r="J1" s="204"/>
-      <c r="K1" s="204"/>
-      <c r="L1" s="204"/>
-      <c r="M1" s="204"/>
-      <c r="N1" s="204"/>
-      <c r="O1" s="204"/>
-      <c r="P1" s="204"/>
-      <c r="Q1" s="204"/>
-      <c r="R1" s="204"/>
-      <c r="S1" s="204"/>
-      <c r="T1" s="204"/>
-      <c r="U1" s="204"/>
-      <c r="V1" s="204"/>
-      <c r="W1" s="204"/>
-      <c r="X1" s="204"/>
-    </row>
-    <row r="2" spans="1:46" ht="45" customHeight="1">
-      <c r="A2" s="84" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="84" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="84" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="84" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="84" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="84" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" s="84" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" s="84" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2" s="84" t="s">
-        <v>30</v>
-      </c>
-      <c r="K2" s="84" t="s">
-        <v>31</v>
-      </c>
-      <c r="L2" s="84" t="s">
-        <v>32</v>
-      </c>
-      <c r="M2" s="84" t="s">
-        <v>33</v>
-      </c>
-      <c r="N2" s="84" t="s">
-        <v>34</v>
-      </c>
-      <c r="O2" s="84" t="s">
-        <v>35</v>
-      </c>
-      <c r="P2" s="84" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q2" s="84" t="s">
-        <v>37</v>
-      </c>
-      <c r="R2" s="84" t="s">
-        <v>38</v>
-      </c>
-      <c r="S2" s="84" t="s">
-        <v>39</v>
-      </c>
-      <c r="T2" s="84" t="s">
-        <v>39</v>
-      </c>
-      <c r="U2" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="V2" s="84" t="s">
-        <v>41</v>
-      </c>
-      <c r="W2" s="84" t="s">
-        <v>42</v>
-      </c>
-      <c r="X2" s="84" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y2" s="10"/>
-      <c r="Z2" s="10"/>
-      <c r="AA2" s="10"/>
-      <c r="AB2" s="10"/>
-      <c r="AC2" s="10"/>
-      <c r="AD2" s="10"/>
-      <c r="AE2" s="10"/>
-      <c r="AF2" s="10"/>
-      <c r="AG2" s="10"/>
-      <c r="AH2" s="10"/>
-      <c r="AI2" s="10"/>
-      <c r="AJ2" s="10"/>
-      <c r="AK2" s="10"/>
-      <c r="AL2" s="10"/>
-      <c r="AM2" s="10"/>
-      <c r="AN2" s="10"/>
-      <c r="AO2" s="10"/>
-      <c r="AP2" s="10"/>
-      <c r="AQ2" s="10"/>
-      <c r="AR2" s="10"/>
-      <c r="AS2" s="10"/>
-      <c r="AT2" s="10"/>
-    </row>
-    <row r="3" spans="1:46">
       <c r="A3" s="85">
         <v>5</v>
       </c>
@@ -15755,10 +15788,10 @@
       <c r="X31" s="101"/>
     </row>
     <row r="32" spans="1:24">
-      <c r="A32" s="205" t="s">
+      <c r="A32" s="203" t="s">
         <v>19</v>
       </c>
-      <c r="B32" s="205"/>
+      <c r="B32" s="203"/>
       <c r="C32" s="100">
         <f>SUM(C3:C31)</f>
         <v>16843.349999999999</v>
@@ -15881,33 +15914,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="204" t="s">
+      <c r="A1" s="202" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="204"/>
-      <c r="C1" s="204"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="204"/>
-      <c r="F1" s="204"/>
-      <c r="G1" s="204"/>
-      <c r="H1" s="204"/>
-      <c r="I1" s="204"/>
-      <c r="J1" s="204"/>
-      <c r="K1" s="204"/>
-      <c r="L1" s="204"/>
-      <c r="M1" s="204"/>
-      <c r="N1" s="204"/>
-      <c r="O1" s="204"/>
-      <c r="P1" s="204"/>
-      <c r="Q1" s="204"/>
-      <c r="R1" s="204"/>
-      <c r="S1" s="204"/>
-      <c r="T1" s="204"/>
-      <c r="U1" s="204"/>
-      <c r="V1" s="204"/>
-      <c r="W1" s="204"/>
-      <c r="X1" s="204"/>
-      <c r="Y1" s="204"/>
+      <c r="B1" s="202"/>
+      <c r="C1" s="202"/>
+      <c r="D1" s="202"/>
+      <c r="E1" s="202"/>
+      <c r="F1" s="202"/>
+      <c r="G1" s="202"/>
+      <c r="H1" s="202"/>
+      <c r="I1" s="202"/>
+      <c r="J1" s="202"/>
+      <c r="K1" s="202"/>
+      <c r="L1" s="202"/>
+      <c r="M1" s="202"/>
+      <c r="N1" s="202"/>
+      <c r="O1" s="202"/>
+      <c r="P1" s="202"/>
+      <c r="Q1" s="202"/>
+      <c r="R1" s="202"/>
+      <c r="S1" s="202"/>
+      <c r="T1" s="202"/>
+      <c r="U1" s="202"/>
+      <c r="V1" s="202"/>
+      <c r="W1" s="202"/>
+      <c r="X1" s="202"/>
+      <c r="Y1" s="202"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="84" t="s">
@@ -16725,10 +16758,10 @@
       <c r="Y19" s="92"/>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="206" t="s">
+      <c r="A20" s="204" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="207"/>
+      <c r="B20" s="205"/>
       <c r="C20" s="93">
         <f>SUM(C3:C19)</f>
         <v>12278.83</v>
@@ -17448,10 +17481,10 @@
       <c r="Y35" s="92"/>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="206" t="s">
+      <c r="A36" s="204" t="s">
         <v>55</v>
       </c>
-      <c r="B36" s="207"/>
+      <c r="B36" s="205"/>
       <c r="C36" s="93">
         <f>SUM(C21:C35)</f>
         <v>11057.89</v>
@@ -17546,10 +17579,10 @@
       </c>
     </row>
     <row r="37" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A37" s="208" t="s">
+      <c r="A37" s="206" t="s">
         <v>56</v>
       </c>
-      <c r="B37" s="208"/>
+      <c r="B37" s="206"/>
       <c r="C37" s="97">
         <f>SUM(C20,C36)</f>
         <v>23336.720000000001</v>
@@ -17679,33 +17712,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="209" t="s">
+      <c r="A1" s="207" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="209"/>
-      <c r="C1" s="209"/>
-      <c r="D1" s="209"/>
-      <c r="E1" s="209"/>
-      <c r="F1" s="209"/>
-      <c r="G1" s="209"/>
-      <c r="H1" s="209"/>
-      <c r="I1" s="209"/>
-      <c r="J1" s="209"/>
-      <c r="K1" s="209"/>
-      <c r="L1" s="209"/>
-      <c r="M1" s="209"/>
-      <c r="N1" s="209"/>
-      <c r="O1" s="209"/>
-      <c r="P1" s="209"/>
-      <c r="Q1" s="209"/>
-      <c r="R1" s="209"/>
-      <c r="S1" s="209"/>
-      <c r="T1" s="209"/>
-      <c r="U1" s="209"/>
-      <c r="V1" s="209"/>
-      <c r="W1" s="209"/>
-      <c r="X1" s="209"/>
-      <c r="Y1" s="209"/>
+      <c r="B1" s="207"/>
+      <c r="C1" s="207"/>
+      <c r="D1" s="207"/>
+      <c r="E1" s="207"/>
+      <c r="F1" s="207"/>
+      <c r="G1" s="207"/>
+      <c r="H1" s="207"/>
+      <c r="I1" s="207"/>
+      <c r="J1" s="207"/>
+      <c r="K1" s="207"/>
+      <c r="L1" s="207"/>
+      <c r="M1" s="207"/>
+      <c r="N1" s="207"/>
+      <c r="O1" s="207"/>
+      <c r="P1" s="207"/>
+      <c r="Q1" s="207"/>
+      <c r="R1" s="207"/>
+      <c r="S1" s="207"/>
+      <c r="T1" s="207"/>
+      <c r="U1" s="207"/>
+      <c r="V1" s="207"/>
+      <c r="W1" s="207"/>
+      <c r="X1" s="207"/>
+      <c r="Y1" s="207"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="81" t="s">
@@ -18415,10 +18448,10 @@
       <c r="Y17" s="74"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="210" t="s">
+      <c r="A18" s="208" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="210"/>
+      <c r="B18" s="208"/>
       <c r="C18" s="82">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
         <v>8428.35</v>
@@ -19171,10 +19204,10 @@
       <c r="Y34" s="76"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="210" t="s">
+      <c r="A35" s="208" t="s">
         <v>55</v>
       </c>
-      <c r="B35" s="210"/>
+      <c r="B35" s="208"/>
       <c r="C35" s="82">
         <f>SUM(C19:C34)</f>
         <v>10739.46</v>
@@ -19269,10 +19302,10 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="211" t="s">
+      <c r="A36" s="209" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="211"/>
+      <c r="B36" s="209"/>
       <c r="C36" s="72">
         <f>SUM(C18,C35)</f>
         <v>19167.810000000001</v>
@@ -19386,10 +19419,10 @@
     <mergeCell ref="A36:B36"/>
   </mergeCells>
   <conditionalFormatting sqref="Y18:Y36">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>Y18&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>Y18&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19410,33 +19443,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="212" t="s">
+      <c r="A1" s="210" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="212"/>
-      <c r="C1" s="212"/>
-      <c r="D1" s="212"/>
-      <c r="E1" s="212"/>
-      <c r="F1" s="212"/>
-      <c r="G1" s="212"/>
-      <c r="H1" s="212"/>
-      <c r="I1" s="212"/>
-      <c r="J1" s="212"/>
-      <c r="K1" s="212"/>
-      <c r="L1" s="212"/>
-      <c r="M1" s="212"/>
-      <c r="N1" s="212"/>
-      <c r="O1" s="212"/>
-      <c r="P1" s="212"/>
-      <c r="Q1" s="212"/>
-      <c r="R1" s="212"/>
-      <c r="S1" s="212"/>
-      <c r="T1" s="212"/>
-      <c r="U1" s="212"/>
-      <c r="V1" s="212"/>
-      <c r="W1" s="212"/>
-      <c r="X1" s="212"/>
-      <c r="Y1" s="212"/>
+      <c r="B1" s="210"/>
+      <c r="C1" s="210"/>
+      <c r="D1" s="210"/>
+      <c r="E1" s="210"/>
+      <c r="F1" s="210"/>
+      <c r="G1" s="210"/>
+      <c r="H1" s="210"/>
+      <c r="I1" s="210"/>
+      <c r="J1" s="210"/>
+      <c r="K1" s="210"/>
+      <c r="L1" s="210"/>
+      <c r="M1" s="210"/>
+      <c r="N1" s="210"/>
+      <c r="O1" s="210"/>
+      <c r="P1" s="210"/>
+      <c r="Q1" s="210"/>
+      <c r="R1" s="210"/>
+      <c r="S1" s="210"/>
+      <c r="T1" s="210"/>
+      <c r="U1" s="210"/>
+      <c r="V1" s="210"/>
+      <c r="W1" s="210"/>
+      <c r="X1" s="210"/>
+      <c r="Y1" s="210"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="38" t="s">
@@ -20175,10 +20208,10 @@
       <c r="Y17" s="74"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="213" t="s">
+      <c r="A18" s="211" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="213"/>
+      <c r="B18" s="211"/>
       <c r="C18" s="60">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
         <v>7904</v>
@@ -20826,10 +20859,10 @@
       <c r="Y34" s="76"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="213" t="s">
+      <c r="A35" s="211" t="s">
         <v>55</v>
       </c>
-      <c r="B35" s="213"/>
+      <c r="B35" s="211"/>
       <c r="C35" s="60">
         <f>SUM(C19:C34)</f>
         <v>0</v>
@@ -20924,10 +20957,10 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="214" t="s">
+      <c r="A36" s="212" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="214"/>
+      <c r="B36" s="212"/>
       <c r="C36" s="80">
         <f>SUM(C18,C35)</f>
         <v>7904</v>
@@ -21041,10 +21074,10 @@
     <mergeCell ref="A36:B36"/>
   </mergeCells>
   <conditionalFormatting sqref="Y18:Y36">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>Y18&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>Y18&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21067,34 +21100,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="60.75" customHeight="1">
-      <c r="A1" s="215" t="s">
+      <c r="A1" s="217" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="215"/>
-      <c r="C1" s="215"/>
-      <c r="D1" s="215"/>
-      <c r="E1" s="215"/>
-      <c r="F1" s="215"/>
-      <c r="G1" s="215"/>
-      <c r="H1" s="215"/>
-      <c r="I1" s="215"/>
-      <c r="J1" s="215"/>
-      <c r="K1" s="215"/>
-      <c r="L1" s="215"/>
-      <c r="M1" s="215"/>
-      <c r="N1" s="215"/>
-      <c r="O1" s="215"/>
-      <c r="P1" s="215"/>
-      <c r="Q1" s="215"/>
-      <c r="R1" s="215"/>
-      <c r="S1" s="215"/>
-      <c r="T1" s="215"/>
-      <c r="U1" s="215"/>
-      <c r="V1" s="215"/>
-      <c r="W1" s="215"/>
-      <c r="X1" s="215"/>
-      <c r="Y1" s="215"/>
-      <c r="Z1" s="215"/>
+      <c r="B1" s="217"/>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="217"/>
+      <c r="F1" s="217"/>
+      <c r="G1" s="217"/>
+      <c r="H1" s="217"/>
+      <c r="I1" s="217"/>
+      <c r="J1" s="217"/>
+      <c r="K1" s="217"/>
+      <c r="L1" s="217"/>
+      <c r="M1" s="217"/>
+      <c r="N1" s="217"/>
+      <c r="O1" s="217"/>
+      <c r="P1" s="217"/>
+      <c r="Q1" s="217"/>
+      <c r="R1" s="217"/>
+      <c r="S1" s="217"/>
+      <c r="T1" s="217"/>
+      <c r="U1" s="217"/>
+      <c r="V1" s="217"/>
+      <c r="W1" s="217"/>
+      <c r="X1" s="217"/>
+      <c r="Y1" s="217"/>
+      <c r="Z1" s="217"/>
     </row>
     <row r="2" spans="1:48" ht="45" customHeight="1">
       <c r="A2" s="38" t="s">
@@ -21247,7 +21280,7 @@
         <f>(94085+57723.67)</f>
         <v>151808.67000000001</v>
       </c>
-      <c r="Z3" s="218"/>
+      <c r="Z3" s="215"/>
     </row>
     <row r="4" spans="1:48" ht="15.75">
       <c r="A4" s="52">
@@ -21297,7 +21330,7 @@
       </c>
       <c r="X4" s="50"/>
       <c r="Y4" s="56"/>
-      <c r="Z4" s="218"/>
+      <c r="Z4" s="215"/>
     </row>
     <row r="5" spans="1:48" ht="15.75">
       <c r="A5" s="45">
@@ -21337,7 +21370,7 @@
       </c>
       <c r="X5" s="50"/>
       <c r="Y5" s="56"/>
-      <c r="Z5" s="218"/>
+      <c r="Z5" s="215"/>
     </row>
     <row r="6" spans="1:48" ht="15.75">
       <c r="A6" s="52">
@@ -21378,7 +21411,7 @@
       </c>
       <c r="X6" s="50"/>
       <c r="Y6" s="56"/>
-      <c r="Z6" s="218"/>
+      <c r="Z6" s="215"/>
     </row>
     <row r="7" spans="1:48" ht="15" customHeight="1">
       <c r="A7" s="45">
@@ -21422,7 +21455,7 @@
       </c>
       <c r="X7" s="50"/>
       <c r="Y7" s="56"/>
-      <c r="Z7" s="218"/>
+      <c r="Z7" s="215"/>
     </row>
     <row r="8" spans="1:48" ht="15.75">
       <c r="A8" s="52">
@@ -21464,14 +21497,14 @@
       </c>
       <c r="X8" s="50"/>
       <c r="Y8" s="56"/>
-      <c r="Z8" s="218"/>
-      <c r="AC8" s="219" t="s">
+      <c r="Z8" s="215"/>
+      <c r="AC8" s="216" t="s">
         <v>61</v>
       </c>
-      <c r="AD8" s="219"/>
-      <c r="AE8" s="219"/>
-      <c r="AF8" s="219"/>
-      <c r="AG8" s="219"/>
+      <c r="AD8" s="216"/>
+      <c r="AE8" s="216"/>
+      <c r="AF8" s="216"/>
+      <c r="AG8" s="216"/>
     </row>
     <row r="9" spans="1:48" ht="15.75">
       <c r="A9" s="45">
@@ -21510,12 +21543,12 @@
       </c>
       <c r="X9" s="50"/>
       <c r="Y9" s="56"/>
-      <c r="Z9" s="218"/>
-      <c r="AC9" s="219"/>
-      <c r="AD9" s="219"/>
-      <c r="AE9" s="219"/>
-      <c r="AF9" s="219"/>
-      <c r="AG9" s="219"/>
+      <c r="Z9" s="215"/>
+      <c r="AC9" s="216"/>
+      <c r="AD9" s="216"/>
+      <c r="AE9" s="216"/>
+      <c r="AF9" s="216"/>
+      <c r="AG9" s="216"/>
     </row>
     <row r="10" spans="1:48" ht="15.75">
       <c r="A10" s="52">
@@ -21559,12 +21592,12 @@
       </c>
       <c r="X10" s="50"/>
       <c r="Y10" s="56"/>
-      <c r="Z10" s="218"/>
-      <c r="AC10" s="219"/>
-      <c r="AD10" s="219"/>
-      <c r="AE10" s="219"/>
-      <c r="AF10" s="219"/>
-      <c r="AG10" s="219"/>
+      <c r="Z10" s="215"/>
+      <c r="AC10" s="216"/>
+      <c r="AD10" s="216"/>
+      <c r="AE10" s="216"/>
+      <c r="AF10" s="216"/>
+      <c r="AG10" s="216"/>
     </row>
     <row r="11" spans="1:48" ht="15.75">
       <c r="A11" s="45">
@@ -21604,13 +21637,13 @@
       </c>
       <c r="X11" s="50"/>
       <c r="Y11" s="56"/>
-      <c r="Z11" s="218"/>
-      <c r="AC11" s="216" t="s">
+      <c r="Z11" s="215"/>
+      <c r="AC11" s="213" t="s">
         <v>62</v>
       </c>
-      <c r="AD11" s="216"/>
-      <c r="AE11" s="216"/>
-      <c r="AF11" s="216"/>
+      <c r="AD11" s="213"/>
+      <c r="AE11" s="213"/>
+      <c r="AF11" s="213"/>
       <c r="AG11" s="57">
         <f>Y3+Y14+Y21</f>
         <v>226341.31</v>
@@ -21651,13 +21684,13 @@
       </c>
       <c r="X12" s="50"/>
       <c r="Y12" s="56"/>
-      <c r="Z12" s="218"/>
-      <c r="AC12" s="216" t="s">
+      <c r="Z12" s="215"/>
+      <c r="AC12" s="213" t="s">
         <v>2</v>
       </c>
-      <c r="AD12" s="216"/>
-      <c r="AE12" s="216"/>
-      <c r="AF12" s="216"/>
+      <c r="AD12" s="213"/>
+      <c r="AE12" s="213"/>
+      <c r="AF12" s="213"/>
       <c r="AG12" s="57">
         <f>Y27</f>
         <v>20000</v>
@@ -21702,13 +21735,13 @@
       </c>
       <c r="X13" s="50"/>
       <c r="Y13" s="56"/>
-      <c r="Z13" s="218"/>
-      <c r="AC13" s="216" t="s">
+      <c r="Z13" s="215"/>
+      <c r="AC13" s="213" t="s">
         <v>63</v>
       </c>
-      <c r="AD13" s="216"/>
-      <c r="AE13" s="216"/>
-      <c r="AF13" s="216"/>
+      <c r="AD13" s="213"/>
+      <c r="AE13" s="213"/>
+      <c r="AF13" s="213"/>
       <c r="AG13" s="57">
         <f>Y17+Y19</f>
         <v>25000</v>
@@ -21754,13 +21787,13 @@
       <c r="Y14" s="51">
         <v>37634</v>
       </c>
-      <c r="Z14" s="218"/>
-      <c r="AC14" s="216" t="s">
+      <c r="Z14" s="215"/>
+      <c r="AC14" s="213" t="s">
         <v>64</v>
       </c>
-      <c r="AD14" s="216"/>
-      <c r="AE14" s="216"/>
-      <c r="AF14" s="216"/>
+      <c r="AD14" s="213"/>
+      <c r="AE14" s="213"/>
+      <c r="AF14" s="213"/>
       <c r="AG14" s="57">
         <f>W38</f>
         <v>177971.36</v>
@@ -21810,13 +21843,13 @@
       </c>
       <c r="X15" s="50"/>
       <c r="Y15" s="56"/>
-      <c r="Z15" s="218"/>
-      <c r="AC15" s="216" t="s">
+      <c r="Z15" s="215"/>
+      <c r="AC15" s="213" t="s">
         <v>65</v>
       </c>
-      <c r="AD15" s="216"/>
-      <c r="AE15" s="216"/>
-      <c r="AF15" s="216"/>
+      <c r="AD15" s="213"/>
+      <c r="AE15" s="213"/>
+      <c r="AF15" s="213"/>
       <c r="AG15" s="57">
         <f>SUM(C38:H38)</f>
         <v>55416.04</v>
@@ -21865,13 +21898,13 @@
       </c>
       <c r="X16" s="50"/>
       <c r="Y16" s="56"/>
-      <c r="Z16" s="218"/>
-      <c r="AC16" s="216" t="s">
+      <c r="Z16" s="215"/>
+      <c r="AC16" s="213" t="s">
         <v>85</v>
       </c>
-      <c r="AD16" s="216"/>
-      <c r="AE16" s="216"/>
-      <c r="AF16" s="216"/>
+      <c r="AD16" s="213"/>
+      <c r="AE16" s="213"/>
+      <c r="AF16" s="213"/>
       <c r="AG16" s="57">
         <f>Q38</f>
         <v>27468.98</v>
@@ -21927,7 +21960,7 @@
       <c r="Y17" s="59">
         <v>15000</v>
       </c>
-      <c r="Z17" s="218"/>
+      <c r="Z17" s="215"/>
     </row>
     <row r="18" spans="1:28" ht="15.75">
       <c r="A18" s="52">
@@ -21968,7 +22001,7 @@
       </c>
       <c r="X18" s="50"/>
       <c r="Y18" s="56"/>
-      <c r="Z18" s="218"/>
+      <c r="Z18" s="215"/>
     </row>
     <row r="19" spans="1:28" ht="15.75">
       <c r="A19" s="45">
@@ -22012,13 +22045,13 @@
       <c r="Y19" s="59">
         <v>10000</v>
       </c>
-      <c r="Z19" s="218"/>
+      <c r="Z19" s="215"/>
     </row>
     <row r="20" spans="1:28" ht="14.25" customHeight="1">
-      <c r="A20" s="213" t="s">
+      <c r="A20" s="211" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="213"/>
+      <c r="B20" s="211"/>
       <c r="C20" s="60">
         <f t="shared" ref="C20:V20" si="1">SUM(C3:C17)</f>
         <v>10942.99</v>
@@ -22161,7 +22194,7 @@
       <c r="Y21" s="51">
         <v>36898.639999999999</v>
       </c>
-      <c r="Z21" s="218"/>
+      <c r="Z21" s="215"/>
     </row>
     <row r="22" spans="1:28" ht="15.75">
       <c r="A22" s="52">
@@ -22207,7 +22240,7 @@
         <v>23662.84</v>
       </c>
       <c r="Y22" s="56"/>
-      <c r="Z22" s="218"/>
+      <c r="Z22" s="215"/>
       <c r="AB22" s="29"/>
     </row>
     <row r="23" spans="1:28" ht="15.75">
@@ -22251,7 +22284,7 @@
       </c>
       <c r="X23" s="50"/>
       <c r="Y23" s="56"/>
-      <c r="Z23" s="218"/>
+      <c r="Z23" s="215"/>
     </row>
     <row r="24" spans="1:28" ht="15.75">
       <c r="A24" s="52">
@@ -22295,7 +22328,7 @@
       </c>
       <c r="X24" s="50"/>
       <c r="Y24" s="56"/>
-      <c r="Z24" s="218"/>
+      <c r="Z24" s="215"/>
     </row>
     <row r="25" spans="1:28" ht="15.75">
       <c r="A25" s="45">
@@ -22339,7 +22372,7 @@
       </c>
       <c r="X25" s="50"/>
       <c r="Y25" s="56"/>
-      <c r="Z25" s="218"/>
+      <c r="Z25" s="215"/>
     </row>
     <row r="26" spans="1:28" ht="15.75">
       <c r="A26" s="52">
@@ -22378,7 +22411,7 @@
       </c>
       <c r="X26" s="50"/>
       <c r="Y26" s="56"/>
-      <c r="Z26" s="218"/>
+      <c r="Z26" s="215"/>
     </row>
     <row r="27" spans="1:28" ht="15.75">
       <c r="A27" s="45">
@@ -22423,7 +22456,7 @@
       <c r="Y27" s="66">
         <v>20000</v>
       </c>
-      <c r="Z27" s="218"/>
+      <c r="Z27" s="215"/>
     </row>
     <row r="28" spans="1:28" ht="15.75">
       <c r="A28" s="52">
@@ -22465,7 +22498,7 @@
       </c>
       <c r="X28" s="50"/>
       <c r="Y28" s="56"/>
-      <c r="Z28" s="218"/>
+      <c r="Z28" s="215"/>
     </row>
     <row r="29" spans="1:28" ht="15.75">
       <c r="A29" s="45">
@@ -22504,7 +22537,7 @@
       </c>
       <c r="X29" s="50"/>
       <c r="Y29" s="56"/>
-      <c r="Z29" s="218"/>
+      <c r="Z29" s="215"/>
     </row>
     <row r="30" spans="1:28" ht="15.75">
       <c r="A30" s="52">
@@ -22544,7 +22577,7 @@
       </c>
       <c r="X30" s="50"/>
       <c r="Y30" s="56"/>
-      <c r="Z30" s="218"/>
+      <c r="Z30" s="215"/>
     </row>
     <row r="31" spans="1:28" ht="15.75">
       <c r="A31" s="45">
@@ -22579,7 +22612,7 @@
       </c>
       <c r="X31" s="50"/>
       <c r="Y31" s="56"/>
-      <c r="Z31" s="218"/>
+      <c r="Z31" s="215"/>
     </row>
     <row r="32" spans="1:28" ht="15.75">
       <c r="A32" s="52">
@@ -22614,7 +22647,7 @@
       </c>
       <c r="X32" s="50"/>
       <c r="Y32" s="56"/>
-      <c r="Z32" s="218"/>
+      <c r="Z32" s="215"/>
     </row>
     <row r="33" spans="1:26" ht="15.75">
       <c r="A33" s="45">
@@ -22651,7 +22684,7 @@
       <c r="Y33" s="67">
         <v>10000</v>
       </c>
-      <c r="Z33" s="218"/>
+      <c r="Z33" s="215"/>
     </row>
     <row r="34" spans="1:26" ht="15.75">
       <c r="A34" s="52">
@@ -22690,7 +22723,7 @@
       </c>
       <c r="X34" s="50"/>
       <c r="Y34" s="56"/>
-      <c r="Z34" s="218"/>
+      <c r="Z34" s="215"/>
     </row>
     <row r="35" spans="1:26" ht="15.75">
       <c r="A35" s="45">
@@ -22734,7 +22767,7 @@
       </c>
       <c r="X35" s="50"/>
       <c r="Y35" s="56"/>
-      <c r="Z35" s="218"/>
+      <c r="Z35" s="215"/>
     </row>
     <row r="36" spans="1:26" ht="15.75">
       <c r="A36" s="52">
@@ -22775,13 +22808,13 @@
       </c>
       <c r="X36" s="50"/>
       <c r="Y36" s="56"/>
-      <c r="Z36" s="218"/>
+      <c r="Z36" s="215"/>
     </row>
     <row r="37" spans="1:26">
-      <c r="A37" s="213" t="s">
+      <c r="A37" s="211" t="s">
         <v>55</v>
       </c>
-      <c r="B37" s="213"/>
+      <c r="B37" s="211"/>
       <c r="C37" s="60">
         <f>SUM(C21:C36)</f>
         <v>3393</v>
@@ -22880,10 +22913,10 @@
       </c>
     </row>
     <row r="38" spans="1:26" ht="31.5" customHeight="1">
-      <c r="A38" s="217" t="s">
+      <c r="A38" s="214" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="217"/>
+      <c r="B38" s="214"/>
       <c r="C38" s="69">
         <f>SUM(C20,C37)</f>
         <v>14335.99</v>
@@ -22995,6 +23028,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="AC11:AF11"/>
+    <mergeCell ref="AC12:AF12"/>
+    <mergeCell ref="AC13:AF13"/>
+    <mergeCell ref="AC14:AF14"/>
     <mergeCell ref="AC15:AF15"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A37:B37"/>
@@ -23003,11 +23041,6 @@
     <mergeCell ref="Z21:Z36"/>
     <mergeCell ref="AC8:AG10"/>
     <mergeCell ref="AC16:AF16"/>
-    <mergeCell ref="A1:Z1"/>
-    <mergeCell ref="AC11:AF11"/>
-    <mergeCell ref="AC12:AF12"/>
-    <mergeCell ref="AC13:AF13"/>
-    <mergeCell ref="AC14:AF14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -23028,78 +23061,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="34.5" customHeight="1">
-      <c r="A1" s="220" t="s">
+      <c r="A1" s="223" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="220"/>
-      <c r="C1" s="220"/>
-      <c r="D1" s="220"/>
-      <c r="E1" s="220"/>
-      <c r="F1" s="220"/>
-      <c r="G1" s="220"/>
-      <c r="H1" s="220"/>
-      <c r="I1" s="220"/>
-      <c r="J1" s="220"/>
-      <c r="K1" s="220"/>
-      <c r="L1" s="220"/>
-      <c r="M1" s="220"/>
-      <c r="N1" s="220"/>
-      <c r="O1" s="220"/>
-      <c r="P1" s="220"/>
-      <c r="Q1" s="220"/>
-      <c r="R1" s="220"/>
-      <c r="S1" s="220"/>
-      <c r="T1" s="220"/>
-      <c r="U1" s="220"/>
-      <c r="V1" s="220"/>
-      <c r="W1" s="220"/>
-      <c r="X1" s="220"/>
-      <c r="Y1" s="220"/>
-      <c r="Z1" s="220"/>
-      <c r="AA1" s="220"/>
-      <c r="AB1" s="220"/>
-      <c r="AC1" s="220"/>
-      <c r="AD1" s="220"/>
+      <c r="B1" s="223"/>
+      <c r="C1" s="223"/>
+      <c r="D1" s="223"/>
+      <c r="E1" s="223"/>
+      <c r="F1" s="223"/>
+      <c r="G1" s="223"/>
+      <c r="H1" s="223"/>
+      <c r="I1" s="223"/>
+      <c r="J1" s="223"/>
+      <c r="K1" s="223"/>
+      <c r="L1" s="223"/>
+      <c r="M1" s="223"/>
+      <c r="N1" s="223"/>
+      <c r="O1" s="223"/>
+      <c r="P1" s="223"/>
+      <c r="Q1" s="223"/>
+      <c r="R1" s="223"/>
+      <c r="S1" s="223"/>
+      <c r="T1" s="223"/>
+      <c r="U1" s="223"/>
+      <c r="V1" s="223"/>
+      <c r="W1" s="223"/>
+      <c r="X1" s="223"/>
+      <c r="Y1" s="223"/>
+      <c r="Z1" s="223"/>
+      <c r="AA1" s="223"/>
+      <c r="AB1" s="223"/>
+      <c r="AC1" s="223"/>
+      <c r="AD1" s="223"/>
     </row>
     <row r="2" spans="1:52" ht="26.25">
-      <c r="A2" s="221"/>
-      <c r="B2" s="222"/>
-      <c r="C2" s="223" t="s">
+      <c r="A2" s="224"/>
+      <c r="B2" s="225"/>
+      <c r="C2" s="226" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="223"/>
-      <c r="E2" s="223"/>
-      <c r="F2" s="223"/>
-      <c r="G2" s="223"/>
-      <c r="H2" s="223"/>
-      <c r="I2" s="223"/>
-      <c r="J2" s="223"/>
-      <c r="K2" s="223"/>
-      <c r="L2" s="224" t="s">
+      <c r="D2" s="226"/>
+      <c r="E2" s="226"/>
+      <c r="F2" s="226"/>
+      <c r="G2" s="226"/>
+      <c r="H2" s="226"/>
+      <c r="I2" s="226"/>
+      <c r="J2" s="226"/>
+      <c r="K2" s="226"/>
+      <c r="L2" s="227" t="s">
         <v>68</v>
       </c>
-      <c r="M2" s="224"/>
-      <c r="N2" s="224"/>
-      <c r="O2" s="224"/>
-      <c r="P2" s="224"/>
-      <c r="Q2" s="224"/>
-      <c r="R2" s="225" t="s">
+      <c r="M2" s="227"/>
+      <c r="N2" s="227"/>
+      <c r="O2" s="227"/>
+      <c r="P2" s="227"/>
+      <c r="Q2" s="227"/>
+      <c r="R2" s="228" t="s">
         <v>69</v>
       </c>
-      <c r="S2" s="225"/>
-      <c r="T2" s="225"/>
-      <c r="U2" s="225"/>
-      <c r="V2" s="225"/>
-      <c r="W2" s="225"/>
-      <c r="X2" s="225"/>
-      <c r="Y2" s="225"/>
-      <c r="Z2" s="225"/>
-      <c r="AA2" s="225"/>
-      <c r="AB2" s="226" t="s">
+      <c r="S2" s="228"/>
+      <c r="T2" s="228"/>
+      <c r="U2" s="228"/>
+      <c r="V2" s="228"/>
+      <c r="W2" s="228"/>
+      <c r="X2" s="228"/>
+      <c r="Y2" s="228"/>
+      <c r="Z2" s="228"/>
+      <c r="AA2" s="228"/>
+      <c r="AB2" s="229" t="s">
         <v>70</v>
       </c>
-      <c r="AC2" s="226"/>
-      <c r="AD2" s="226"/>
+      <c r="AC2" s="229"/>
+      <c r="AD2" s="229"/>
     </row>
     <row r="3" spans="1:52" ht="45" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -23266,7 +23299,7 @@
         <f>37635+40252.26+18817.85</f>
         <v>96705.11</v>
       </c>
-      <c r="AD4" s="230"/>
+      <c r="AD4" s="221"/>
     </row>
     <row r="5" spans="1:52" ht="15.75">
       <c r="A5" s="17">
@@ -23316,7 +23349,7 @@
         <v>16503.13</v>
       </c>
       <c r="AC5" s="21"/>
-      <c r="AD5" s="230"/>
+      <c r="AD5" s="221"/>
     </row>
     <row r="6" spans="1:52" ht="15.75">
       <c r="A6" s="11">
@@ -23359,7 +23392,7 @@
         <v>996.61</v>
       </c>
       <c r="AC6" s="21"/>
-      <c r="AD6" s="230"/>
+      <c r="AD6" s="221"/>
     </row>
     <row r="7" spans="1:52" ht="15.75">
       <c r="A7" s="17">
@@ -23412,7 +23445,7 @@
         <v>5968</v>
       </c>
       <c r="AC7" s="21"/>
-      <c r="AD7" s="230"/>
+      <c r="AD7" s="221"/>
     </row>
     <row r="8" spans="1:52" ht="15" customHeight="1">
       <c r="A8" s="11">
@@ -23458,7 +23491,7 @@
         <v>12168.98</v>
       </c>
       <c r="AC8" s="21"/>
-      <c r="AD8" s="230"/>
+      <c r="AD8" s="221"/>
     </row>
     <row r="9" spans="1:52" ht="15.75">
       <c r="A9" s="17">
@@ -23506,7 +23539,7 @@
         <v>5970</v>
       </c>
       <c r="AC9" s="21"/>
-      <c r="AD9" s="230"/>
+      <c r="AD9" s="221"/>
     </row>
     <row r="10" spans="1:52" ht="15.75">
       <c r="A10" s="11">
@@ -23554,7 +23587,7 @@
         <v>3257</v>
       </c>
       <c r="AC10" s="21"/>
-      <c r="AD10" s="230"/>
+      <c r="AD10" s="221"/>
     </row>
     <row r="11" spans="1:52" ht="15.75">
       <c r="A11" s="17">
@@ -23598,14 +23631,14 @@
         <v>1034</v>
       </c>
       <c r="AC11" s="21"/>
-      <c r="AD11" s="230"/>
-      <c r="AH11" s="231" t="s">
+      <c r="AD11" s="221"/>
+      <c r="AH11" s="222" t="s">
         <v>83</v>
       </c>
-      <c r="AI11" s="231"/>
-      <c r="AJ11" s="231"/>
-      <c r="AK11" s="231"/>
-      <c r="AL11" s="231"/>
+      <c r="AI11" s="222"/>
+      <c r="AJ11" s="222"/>
+      <c r="AK11" s="222"/>
+      <c r="AL11" s="222"/>
     </row>
     <row r="12" spans="1:52" ht="15.75">
       <c r="A12" s="11">
@@ -23652,12 +23685,12 @@
         <v>3586</v>
       </c>
       <c r="AC12" s="21"/>
-      <c r="AD12" s="230"/>
-      <c r="AH12" s="231"/>
-      <c r="AI12" s="231"/>
-      <c r="AJ12" s="231"/>
-      <c r="AK12" s="231"/>
-      <c r="AL12" s="231"/>
+      <c r="AD12" s="221"/>
+      <c r="AH12" s="222"/>
+      <c r="AI12" s="222"/>
+      <c r="AJ12" s="222"/>
+      <c r="AK12" s="222"/>
+      <c r="AL12" s="222"/>
     </row>
     <row r="13" spans="1:52" ht="15.75">
       <c r="A13" s="17">
@@ -23704,12 +23737,12 @@
         <v>5889</v>
       </c>
       <c r="AC13" s="21"/>
-      <c r="AD13" s="230"/>
-      <c r="AH13" s="231"/>
-      <c r="AI13" s="231"/>
-      <c r="AJ13" s="231"/>
-      <c r="AK13" s="231"/>
-      <c r="AL13" s="231"/>
+      <c r="AD13" s="221"/>
+      <c r="AH13" s="222"/>
+      <c r="AI13" s="222"/>
+      <c r="AJ13" s="222"/>
+      <c r="AK13" s="222"/>
+      <c r="AL13" s="222"/>
     </row>
     <row r="14" spans="1:52" ht="18">
       <c r="A14" s="11">
@@ -23755,13 +23788,13 @@
         <v>7092.93</v>
       </c>
       <c r="AC14" s="21"/>
-      <c r="AD14" s="230"/>
-      <c r="AH14" s="227" t="s">
+      <c r="AD14" s="221"/>
+      <c r="AH14" s="218" t="s">
         <v>62</v>
       </c>
-      <c r="AI14" s="227"/>
-      <c r="AJ14" s="227"/>
-      <c r="AK14" s="227"/>
+      <c r="AI14" s="218"/>
+      <c r="AJ14" s="218"/>
+      <c r="AK14" s="218"/>
       <c r="AL14" s="22">
         <f>AC4+AC20</f>
         <v>133443.15</v>
@@ -23819,13 +23852,13 @@
         <v>6644.28</v>
       </c>
       <c r="AC15" s="16"/>
-      <c r="AD15" s="230"/>
-      <c r="AH15" s="227" t="s">
+      <c r="AD15" s="221"/>
+      <c r="AH15" s="218" t="s">
         <v>2</v>
       </c>
-      <c r="AI15" s="227"/>
-      <c r="AJ15" s="227"/>
-      <c r="AK15" s="227"/>
+      <c r="AI15" s="218"/>
+      <c r="AJ15" s="218"/>
+      <c r="AK15" s="218"/>
       <c r="AL15" s="22">
         <f>AC29</f>
         <v>1000</v>
@@ -23880,13 +23913,13 @@
         <v>5105.1899999999996</v>
       </c>
       <c r="AC16" s="21"/>
-      <c r="AD16" s="230"/>
-      <c r="AH16" s="227" t="s">
+      <c r="AD16" s="221"/>
+      <c r="AH16" s="218" t="s">
         <v>63</v>
       </c>
-      <c r="AI16" s="227"/>
-      <c r="AJ16" s="227"/>
-      <c r="AK16" s="227"/>
+      <c r="AI16" s="218"/>
+      <c r="AJ16" s="218"/>
+      <c r="AK16" s="218"/>
       <c r="AL16" s="22">
         <f>AC21+AC34</f>
         <v>11000</v>
@@ -23931,13 +23964,13 @@
         <v>280.97000000000003</v>
       </c>
       <c r="AC17" s="21"/>
-      <c r="AD17" s="230"/>
-      <c r="AH17" s="227" t="s">
+      <c r="AD17" s="221"/>
+      <c r="AH17" s="218" t="s">
         <v>64</v>
       </c>
-      <c r="AI17" s="227"/>
-      <c r="AJ17" s="227"/>
-      <c r="AK17" s="227"/>
+      <c r="AI17" s="218"/>
+      <c r="AJ17" s="218"/>
+      <c r="AK17" s="218"/>
       <c r="AL17" s="22">
         <f>AB36</f>
         <v>146501.73000000001</v>
@@ -23986,23 +24019,23 @@
         <v>956.98</v>
       </c>
       <c r="AC18" s="21"/>
-      <c r="AD18" s="230"/>
-      <c r="AH18" s="227" t="s">
+      <c r="AD18" s="221"/>
+      <c r="AH18" s="218" t="s">
         <v>65</v>
       </c>
-      <c r="AI18" s="227"/>
-      <c r="AJ18" s="227"/>
-      <c r="AK18" s="227"/>
+      <c r="AI18" s="218"/>
+      <c r="AJ18" s="218"/>
+      <c r="AK18" s="218"/>
       <c r="AL18" s="22">
         <f>SUM(C36:K36)</f>
         <v>56967.92</v>
       </c>
     </row>
     <row r="19" spans="1:38" ht="19.5" customHeight="1">
-      <c r="A19" s="228" t="s">
+      <c r="A19" s="219" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="228"/>
+      <c r="B19" s="219"/>
       <c r="C19" s="23">
         <f>SUM(C4:C18)</f>
         <v>1403.89</v>
@@ -24115,12 +24148,12 @@
         <f>AC19-AB19</f>
         <v>4280.0900000000101</v>
       </c>
-      <c r="AH19" s="227" t="s">
+      <c r="AH19" s="218" t="s">
         <v>84</v>
       </c>
-      <c r="AI19" s="227"/>
-      <c r="AJ19" s="227"/>
-      <c r="AK19" s="227"/>
+      <c r="AI19" s="218"/>
+      <c r="AJ19" s="218"/>
+      <c r="AK19" s="218"/>
       <c r="AL19" s="22">
         <f>SUM(L36:Q36)</f>
         <v>31394.13</v>
@@ -24181,13 +24214,13 @@
       <c r="AC20" s="16">
         <v>36738.04</v>
       </c>
-      <c r="AD20" s="230"/>
-      <c r="AH20" s="227" t="s">
+      <c r="AD20" s="221"/>
+      <c r="AH20" s="218" t="s">
         <v>85</v>
       </c>
-      <c r="AI20" s="227"/>
-      <c r="AJ20" s="227"/>
-      <c r="AK20" s="227"/>
+      <c r="AI20" s="218"/>
+      <c r="AJ20" s="218"/>
+      <c r="AK20" s="218"/>
       <c r="AL20" s="22">
         <f>W36</f>
         <v>35678.97</v>
@@ -24242,14 +24275,14 @@
       <c r="AC21" s="37">
         <v>10000</v>
       </c>
-      <c r="AD21" s="230"/>
+      <c r="AD21" s="221"/>
       <c r="AF21" s="29"/>
-      <c r="AH21" s="227" t="s">
+      <c r="AH21" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="AI21" s="227"/>
-      <c r="AJ21" s="227"/>
-      <c r="AK21" s="227"/>
+      <c r="AI21" s="218"/>
+      <c r="AJ21" s="218"/>
+      <c r="AK21" s="218"/>
       <c r="AL21" s="22">
         <f>SUM(U36:V36)</f>
         <v>11008.46</v>
@@ -24292,13 +24325,13 @@
         <v>0</v>
       </c>
       <c r="AC22" s="21"/>
-      <c r="AD22" s="230"/>
-      <c r="AH22" s="227" t="s">
+      <c r="AD22" s="221"/>
+      <c r="AH22" s="218" t="s">
         <v>32</v>
       </c>
-      <c r="AI22" s="227"/>
-      <c r="AJ22" s="227"/>
-      <c r="AK22" s="227"/>
+      <c r="AI22" s="218"/>
+      <c r="AJ22" s="218"/>
+      <c r="AK22" s="218"/>
       <c r="AL22" s="22">
         <f>T36</f>
         <v>0</v>
@@ -24353,13 +24386,13 @@
         <v>6881.28</v>
       </c>
       <c r="AC23" s="21"/>
-      <c r="AD23" s="230"/>
-      <c r="AH23" s="227" t="s">
+      <c r="AD23" s="221"/>
+      <c r="AH23" s="218" t="s">
         <v>87</v>
       </c>
-      <c r="AI23" s="227"/>
-      <c r="AJ23" s="227"/>
-      <c r="AK23" s="227"/>
+      <c r="AI23" s="218"/>
+      <c r="AJ23" s="218"/>
+      <c r="AK23" s="218"/>
       <c r="AL23" s="22">
         <f>X36</f>
         <v>5267.98</v>
@@ -24414,7 +24447,7 @@
         <v>6126.69</v>
       </c>
       <c r="AC24" s="21"/>
-      <c r="AD24" s="230"/>
+      <c r="AD24" s="221"/>
     </row>
     <row r="25" spans="1:38" ht="15.75">
       <c r="A25" s="17">
@@ -24458,7 +24491,7 @@
         <v>7750</v>
       </c>
       <c r="AC25" s="21"/>
-      <c r="AD25" s="230"/>
+      <c r="AD25" s="221"/>
     </row>
     <row r="26" spans="1:38" ht="15.75">
       <c r="A26" s="11">
@@ -24505,7 +24538,7 @@
         <v>2803</v>
       </c>
       <c r="AC26" s="16"/>
-      <c r="AD26" s="230"/>
+      <c r="AD26" s="221"/>
     </row>
     <row r="27" spans="1:38" ht="15.75">
       <c r="A27" s="17">
@@ -24553,7 +24586,7 @@
         <v>2088.96</v>
       </c>
       <c r="AC27" s="21"/>
-      <c r="AD27" s="230"/>
+      <c r="AD27" s="221"/>
     </row>
     <row r="28" spans="1:38" ht="15.75">
       <c r="A28" s="11">
@@ -24599,7 +24632,7 @@
         <v>3468</v>
       </c>
       <c r="AC28" s="21"/>
-      <c r="AD28" s="230"/>
+      <c r="AD28" s="221"/>
     </row>
     <row r="29" spans="1:38" ht="15.75">
       <c r="A29" s="17">
@@ -24652,7 +24685,7 @@
       <c r="AC29" s="21">
         <v>1000</v>
       </c>
-      <c r="AD29" s="230"/>
+      <c r="AD29" s="221"/>
     </row>
     <row r="30" spans="1:38" ht="15.75">
       <c r="A30" s="11">
@@ -24700,7 +24733,7 @@
         <v>4016.5</v>
       </c>
       <c r="AC30" s="21"/>
-      <c r="AD30" s="230"/>
+      <c r="AD30" s="221"/>
     </row>
     <row r="31" spans="1:38" ht="15.75">
       <c r="A31" s="17">
@@ -24744,7 +24777,7 @@
         <v>2801.78</v>
       </c>
       <c r="AC31" s="21"/>
-      <c r="AD31" s="230"/>
+      <c r="AD31" s="221"/>
     </row>
     <row r="32" spans="1:38" ht="15.75">
       <c r="A32" s="11">
@@ -24793,7 +24826,7 @@
         <v>3807.11</v>
       </c>
       <c r="AC32" s="21"/>
-      <c r="AD32" s="230"/>
+      <c r="AD32" s="221"/>
     </row>
     <row r="33" spans="1:30" ht="15.75">
       <c r="A33" s="17">
@@ -24837,7 +24870,7 @@
         <v>675.44</v>
       </c>
       <c r="AC33" s="21"/>
-      <c r="AD33" s="230"/>
+      <c r="AD33" s="221"/>
     </row>
     <row r="34" spans="1:30" ht="15.75">
       <c r="A34" s="11">
@@ -24881,13 +24914,13 @@
       <c r="AC34" s="37">
         <v>1000</v>
       </c>
-      <c r="AD34" s="230"/>
+      <c r="AD34" s="221"/>
     </row>
     <row r="35" spans="1:30" ht="14.25" customHeight="1">
-      <c r="A35" s="228" t="s">
+      <c r="A35" s="219" t="s">
         <v>55</v>
       </c>
-      <c r="B35" s="228"/>
+      <c r="B35" s="219"/>
       <c r="C35" s="23">
         <f t="shared" ref="C35:AC35" si="3">SUM(C20:C34)</f>
         <v>2169.6999999999998</v>
@@ -25002,10 +25035,10 @@
       </c>
     </row>
     <row r="36" spans="1:30" ht="31.5" customHeight="1">
-      <c r="A36" s="229" t="s">
+      <c r="A36" s="220" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="229"/>
+      <c r="B36" s="220"/>
       <c r="C36" s="31">
         <f>SUM(C19,C35)</f>
         <v>3573.59</v>
@@ -25136,6 +25169,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="AH23:AK23"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="A36:B36"/>
@@ -25152,12 +25191,6 @@
     <mergeCell ref="AH16:AK16"/>
     <mergeCell ref="AH17:AK17"/>
     <mergeCell ref="AH18:AK18"/>
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:K2"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -25178,78 +25211,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="34.5" customHeight="1">
-      <c r="A1" s="220" t="s">
+      <c r="A1" s="223" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="220"/>
-      <c r="C1" s="220"/>
-      <c r="D1" s="220"/>
-      <c r="E1" s="220"/>
-      <c r="F1" s="220"/>
-      <c r="G1" s="220"/>
-      <c r="H1" s="220"/>
-      <c r="I1" s="220"/>
-      <c r="J1" s="220"/>
-      <c r="K1" s="220"/>
-      <c r="L1" s="220"/>
-      <c r="M1" s="220"/>
-      <c r="N1" s="220"/>
-      <c r="O1" s="220"/>
-      <c r="P1" s="220"/>
-      <c r="Q1" s="220"/>
-      <c r="R1" s="220"/>
-      <c r="S1" s="220"/>
-      <c r="T1" s="220"/>
-      <c r="U1" s="220"/>
-      <c r="V1" s="220"/>
-      <c r="W1" s="220"/>
-      <c r="X1" s="220"/>
-      <c r="Y1" s="220"/>
-      <c r="Z1" s="220"/>
-      <c r="AA1" s="220"/>
-      <c r="AB1" s="220"/>
-      <c r="AC1" s="220"/>
-      <c r="AD1" s="220"/>
+      <c r="B1" s="223"/>
+      <c r="C1" s="223"/>
+      <c r="D1" s="223"/>
+      <c r="E1" s="223"/>
+      <c r="F1" s="223"/>
+      <c r="G1" s="223"/>
+      <c r="H1" s="223"/>
+      <c r="I1" s="223"/>
+      <c r="J1" s="223"/>
+      <c r="K1" s="223"/>
+      <c r="L1" s="223"/>
+      <c r="M1" s="223"/>
+      <c r="N1" s="223"/>
+      <c r="O1" s="223"/>
+      <c r="P1" s="223"/>
+      <c r="Q1" s="223"/>
+      <c r="R1" s="223"/>
+      <c r="S1" s="223"/>
+      <c r="T1" s="223"/>
+      <c r="U1" s="223"/>
+      <c r="V1" s="223"/>
+      <c r="W1" s="223"/>
+      <c r="X1" s="223"/>
+      <c r="Y1" s="223"/>
+      <c r="Z1" s="223"/>
+      <c r="AA1" s="223"/>
+      <c r="AB1" s="223"/>
+      <c r="AC1" s="223"/>
+      <c r="AD1" s="223"/>
     </row>
     <row r="2" spans="1:52" ht="26.25">
-      <c r="A2" s="221"/>
-      <c r="B2" s="222"/>
-      <c r="C2" s="223" t="s">
+      <c r="A2" s="224"/>
+      <c r="B2" s="225"/>
+      <c r="C2" s="226" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="223"/>
-      <c r="E2" s="223"/>
-      <c r="F2" s="223"/>
-      <c r="G2" s="223"/>
-      <c r="H2" s="223"/>
-      <c r="I2" s="223"/>
-      <c r="J2" s="223"/>
-      <c r="K2" s="223"/>
-      <c r="L2" s="224" t="s">
+      <c r="D2" s="226"/>
+      <c r="E2" s="226"/>
+      <c r="F2" s="226"/>
+      <c r="G2" s="226"/>
+      <c r="H2" s="226"/>
+      <c r="I2" s="226"/>
+      <c r="J2" s="226"/>
+      <c r="K2" s="226"/>
+      <c r="L2" s="227" t="s">
         <v>68</v>
       </c>
-      <c r="M2" s="224"/>
-      <c r="N2" s="224"/>
-      <c r="O2" s="224"/>
-      <c r="P2" s="224"/>
-      <c r="Q2" s="224"/>
-      <c r="R2" s="225" t="s">
+      <c r="M2" s="227"/>
+      <c r="N2" s="227"/>
+      <c r="O2" s="227"/>
+      <c r="P2" s="227"/>
+      <c r="Q2" s="227"/>
+      <c r="R2" s="228" t="s">
         <v>69</v>
       </c>
-      <c r="S2" s="225"/>
-      <c r="T2" s="225"/>
-      <c r="U2" s="225"/>
-      <c r="V2" s="225"/>
-      <c r="W2" s="225"/>
-      <c r="X2" s="225"/>
-      <c r="Y2" s="225"/>
-      <c r="Z2" s="225"/>
-      <c r="AA2" s="225"/>
-      <c r="AB2" s="226" t="s">
+      <c r="S2" s="228"/>
+      <c r="T2" s="228"/>
+      <c r="U2" s="228"/>
+      <c r="V2" s="228"/>
+      <c r="W2" s="228"/>
+      <c r="X2" s="228"/>
+      <c r="Y2" s="228"/>
+      <c r="Z2" s="228"/>
+      <c r="AA2" s="228"/>
+      <c r="AB2" s="229" t="s">
         <v>70</v>
       </c>
-      <c r="AC2" s="226"/>
-      <c r="AD2" s="226"/>
+      <c r="AC2" s="229"/>
+      <c r="AD2" s="229"/>
     </row>
     <row r="3" spans="1:52" ht="45" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -25339,7 +25372,7 @@
       <c r="AC3" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AD3" s="171" t="s">
+      <c r="AD3" s="168" t="s">
         <v>5</v>
       </c>
       <c r="AE3" s="10"/>
@@ -25410,11 +25443,11 @@
         <f>SUM(C4:AA4)</f>
         <v>4117.99</v>
       </c>
-      <c r="AC4" s="166">
+      <c r="AC4" s="163">
         <f>66577.47+18817</f>
         <v>85394.47</v>
       </c>
-      <c r="AD4" s="230"/>
+      <c r="AD4" s="221"/>
     </row>
     <row r="5" spans="1:52" ht="15.75">
       <c r="A5" s="17">
@@ -25468,8 +25501,8 @@
         <f>SUM(C5:AA5)</f>
         <v>7116</v>
       </c>
-      <c r="AC5" s="168"/>
-      <c r="AD5" s="230"/>
+      <c r="AC5" s="165"/>
+      <c r="AD5" s="221"/>
     </row>
     <row r="6" spans="1:52" ht="15.75">
       <c r="A6" s="11">
@@ -25516,8 +25549,8 @@
         <f t="shared" ref="AB6:AB16" si="0">SUM(C6:AA6)</f>
         <v>17146</v>
       </c>
-      <c r="AC6" s="168"/>
-      <c r="AD6" s="230"/>
+      <c r="AC6" s="165"/>
+      <c r="AD6" s="221"/>
     </row>
     <row r="7" spans="1:52" ht="15.75">
       <c r="A7" s="17">
@@ -25573,8 +25606,8 @@
         <f t="shared" si="0"/>
         <v>6206.84</v>
       </c>
-      <c r="AC7" s="168"/>
-      <c r="AD7" s="230"/>
+      <c r="AC7" s="165"/>
+      <c r="AD7" s="221"/>
     </row>
     <row r="8" spans="1:52" ht="15" customHeight="1">
       <c r="A8" s="11">
@@ -25632,8 +25665,8 @@
         <f t="shared" si="0"/>
         <v>8204</v>
       </c>
-      <c r="AC8" s="168"/>
-      <c r="AD8" s="230"/>
+      <c r="AC8" s="165"/>
+      <c r="AD8" s="221"/>
     </row>
     <row r="9" spans="1:52" ht="15.75">
       <c r="A9" s="17">
@@ -25681,8 +25714,8 @@
         <f t="shared" si="0"/>
         <v>8276</v>
       </c>
-      <c r="AC9" s="168"/>
-      <c r="AD9" s="230"/>
+      <c r="AC9" s="165"/>
+      <c r="AD9" s="221"/>
     </row>
     <row r="10" spans="1:52" ht="15.75">
       <c r="A10" s="11">
@@ -25727,10 +25760,10 @@
         <f t="shared" si="0"/>
         <v>1425</v>
       </c>
-      <c r="AC10" s="168">
+      <c r="AC10" s="165">
         <v>28225.5</v>
       </c>
-      <c r="AD10" s="230"/>
+      <c r="AD10" s="221"/>
     </row>
     <row r="11" spans="1:52" ht="15.75">
       <c r="A11" s="17">
@@ -25779,15 +25812,15 @@
         <f t="shared" si="0"/>
         <v>5638.53</v>
       </c>
-      <c r="AC11" s="168"/>
-      <c r="AD11" s="230"/>
-      <c r="AH11" s="231" t="s">
+      <c r="AC11" s="165"/>
+      <c r="AD11" s="221"/>
+      <c r="AH11" s="222" t="s">
         <v>83</v>
       </c>
-      <c r="AI11" s="231"/>
-      <c r="AJ11" s="231"/>
-      <c r="AK11" s="231"/>
-      <c r="AL11" s="231"/>
+      <c r="AI11" s="222"/>
+      <c r="AJ11" s="222"/>
+      <c r="AK11" s="222"/>
+      <c r="AL11" s="222"/>
     </row>
     <row r="12" spans="1:52" ht="15.75">
       <c r="A12" s="11">
@@ -25840,13 +25873,13 @@
         <f t="shared" si="0"/>
         <v>33365</v>
       </c>
-      <c r="AC12" s="168"/>
-      <c r="AD12" s="230"/>
-      <c r="AH12" s="231"/>
-      <c r="AI12" s="231"/>
-      <c r="AJ12" s="231"/>
-      <c r="AK12" s="231"/>
-      <c r="AL12" s="231"/>
+      <c r="AC12" s="165"/>
+      <c r="AD12" s="221"/>
+      <c r="AH12" s="222"/>
+      <c r="AI12" s="222"/>
+      <c r="AJ12" s="222"/>
+      <c r="AK12" s="222"/>
+      <c r="AL12" s="222"/>
     </row>
     <row r="13" spans="1:52" ht="15.75">
       <c r="A13" s="17">
@@ -25903,13 +25936,13 @@
         <f t="shared" si="0"/>
         <v>10965.96</v>
       </c>
-      <c r="AC13" s="168"/>
-      <c r="AD13" s="230"/>
-      <c r="AH13" s="231"/>
-      <c r="AI13" s="231"/>
-      <c r="AJ13" s="231"/>
-      <c r="AK13" s="231"/>
-      <c r="AL13" s="231"/>
+      <c r="AC13" s="165"/>
+      <c r="AD13" s="221"/>
+      <c r="AH13" s="222"/>
+      <c r="AI13" s="222"/>
+      <c r="AJ13" s="222"/>
+      <c r="AK13" s="222"/>
+      <c r="AL13" s="222"/>
     </row>
     <row r="14" spans="1:52" ht="18">
       <c r="A14" s="11">
@@ -25956,14 +25989,14 @@
         <f t="shared" si="0"/>
         <v>1614.53</v>
       </c>
-      <c r="AC14" s="168"/>
-      <c r="AD14" s="230"/>
-      <c r="AH14" s="227" t="s">
+      <c r="AC14" s="165"/>
+      <c r="AD14" s="221"/>
+      <c r="AH14" s="218" t="s">
         <v>62</v>
       </c>
-      <c r="AI14" s="227"/>
-      <c r="AJ14" s="227"/>
-      <c r="AK14" s="227"/>
+      <c r="AI14" s="218"/>
+      <c r="AJ14" s="218"/>
+      <c r="AK14" s="218"/>
       <c r="AL14" s="22">
         <f>AC4+AC19+AC23+AC10</f>
         <v>287751.42</v>
@@ -26020,14 +26053,14 @@
         <f t="shared" si="0"/>
         <v>6960.82</v>
       </c>
-      <c r="AC15" s="166"/>
-      <c r="AD15" s="230"/>
-      <c r="AH15" s="227" t="s">
+      <c r="AC15" s="163"/>
+      <c r="AD15" s="221"/>
+      <c r="AH15" s="218" t="s">
         <v>2</v>
       </c>
-      <c r="AI15" s="227"/>
-      <c r="AJ15" s="227"/>
-      <c r="AK15" s="227"/>
+      <c r="AI15" s="218"/>
+      <c r="AJ15" s="218"/>
+      <c r="AK15" s="218"/>
       <c r="AL15" s="22">
         <f>AC20</f>
         <v>1000</v>
@@ -26078,16 +26111,16 @@
         <f t="shared" si="0"/>
         <v>3481.97</v>
       </c>
-      <c r="AC16" s="170">
+      <c r="AC16" s="167">
         <v>5000</v>
       </c>
-      <c r="AD16" s="230"/>
-      <c r="AH16" s="227" t="s">
+      <c r="AD16" s="221"/>
+      <c r="AH16" s="218" t="s">
         <v>63</v>
       </c>
-      <c r="AI16" s="227"/>
-      <c r="AJ16" s="227"/>
-      <c r="AK16" s="227"/>
+      <c r="AI16" s="218"/>
+      <c r="AJ16" s="218"/>
+      <c r="AK16" s="218"/>
       <c r="AL16" s="22">
         <f>AC16+AC28+AC34+AC35</f>
         <v>60000</v>
@@ -26144,24 +26177,24 @@
         <f>SUM(C17:AA17)</f>
         <v>5002</v>
       </c>
-      <c r="AC17" s="166"/>
-      <c r="AD17" s="230"/>
-      <c r="AH17" s="232" t="s">
+      <c r="AC17" s="163"/>
+      <c r="AD17" s="221"/>
+      <c r="AH17" s="230" t="s">
         <v>67</v>
       </c>
-      <c r="AI17" s="233"/>
-      <c r="AJ17" s="233"/>
-      <c r="AK17" s="234"/>
+      <c r="AI17" s="231"/>
+      <c r="AJ17" s="231"/>
+      <c r="AK17" s="232"/>
       <c r="AL17" s="22">
         <f>SUM(C37:K37)</f>
         <v>121331.08</v>
       </c>
     </row>
     <row r="18" spans="1:38" ht="19.5" customHeight="1">
-      <c r="A18" s="238" t="s">
+      <c r="A18" s="236" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="238"/>
+      <c r="B18" s="236"/>
       <c r="C18" s="23">
         <f>SUM(C4:C17)</f>
         <v>129.99</v>
@@ -26270,16 +26303,16 @@
         <f t="shared" si="3"/>
         <v>118619.97</v>
       </c>
-      <c r="AD18" s="167">
+      <c r="AD18" s="164">
         <f>AC18-AB18</f>
         <v>-900.67000000001281</v>
       </c>
-      <c r="AH18" s="227" t="s">
+      <c r="AH18" s="218" t="s">
         <v>84</v>
       </c>
-      <c r="AI18" s="227"/>
-      <c r="AJ18" s="227"/>
-      <c r="AK18" s="227"/>
+      <c r="AI18" s="218"/>
+      <c r="AJ18" s="218"/>
+      <c r="AK18" s="218"/>
       <c r="AL18" s="22">
         <f>SUM(L37:Q37)</f>
         <v>35695</v>
@@ -26333,13 +26366,13 @@
       <c r="AC19" s="16">
         <v>38575.449999999997</v>
       </c>
-      <c r="AD19" s="230"/>
-      <c r="AH19" s="227" t="s">
+      <c r="AD19" s="221"/>
+      <c r="AH19" s="218" t="s">
         <v>85</v>
       </c>
-      <c r="AI19" s="227"/>
-      <c r="AJ19" s="227"/>
-      <c r="AK19" s="227"/>
+      <c r="AI19" s="218"/>
+      <c r="AJ19" s="218"/>
+      <c r="AK19" s="218"/>
       <c r="AL19" s="22">
         <f>W37</f>
         <v>38934</v>
@@ -26396,14 +26429,14 @@
       <c r="AC20" s="21">
         <v>1000</v>
       </c>
-      <c r="AD20" s="230"/>
+      <c r="AD20" s="221"/>
       <c r="AF20" s="29"/>
-      <c r="AH20" s="227" t="s">
+      <c r="AH20" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="AI20" s="227"/>
-      <c r="AJ20" s="227"/>
-      <c r="AK20" s="227"/>
+      <c r="AI20" s="218"/>
+      <c r="AJ20" s="218"/>
+      <c r="AK20" s="218"/>
       <c r="AL20" s="22">
         <f>SUM(U37:V37)</f>
         <v>15264.08</v>
@@ -26449,14 +26482,14 @@
         <v>1980</v>
       </c>
       <c r="AC21" s="21"/>
-      <c r="AD21" s="230"/>
-      <c r="AH21" s="235" t="s">
+      <c r="AD21" s="221"/>
+      <c r="AH21" s="233" t="s">
         <v>32</v>
       </c>
-      <c r="AI21" s="235"/>
-      <c r="AJ21" s="235"/>
-      <c r="AK21" s="235"/>
-      <c r="AL21" s="172">
+      <c r="AI21" s="233"/>
+      <c r="AJ21" s="233"/>
+      <c r="AK21" s="233"/>
+      <c r="AL21" s="169">
         <f>T37</f>
         <v>31093</v>
       </c>
@@ -26510,12 +26543,12 @@
         <v>3710.54</v>
       </c>
       <c r="AC22" s="21"/>
-      <c r="AD22" s="230"/>
-      <c r="AH22" s="236"/>
-      <c r="AI22" s="236"/>
-      <c r="AJ22" s="236"/>
-      <c r="AK22" s="236"/>
-      <c r="AL22" s="173"/>
+      <c r="AD22" s="221"/>
+      <c r="AH22" s="234"/>
+      <c r="AI22" s="234"/>
+      <c r="AJ22" s="234"/>
+      <c r="AK22" s="234"/>
+      <c r="AL22" s="170"/>
     </row>
     <row r="23" spans="1:38" ht="15.75">
       <c r="A23" s="11">
@@ -26566,7 +26599,7 @@
         <f>21986+70637+42933</f>
         <v>135556</v>
       </c>
-      <c r="AD23" s="230"/>
+      <c r="AD23" s="221"/>
     </row>
     <row r="24" spans="1:38" ht="15.75">
       <c r="A24" s="17">
@@ -26626,7 +26659,7 @@
         <v>26293.41</v>
       </c>
       <c r="AC24" s="21"/>
-      <c r="AD24" s="230"/>
+      <c r="AD24" s="221"/>
     </row>
     <row r="25" spans="1:38" ht="15.75">
       <c r="A25" s="11">
@@ -26671,7 +26704,7 @@
         <v>542</v>
       </c>
       <c r="AC25" s="16"/>
-      <c r="AD25" s="230"/>
+      <c r="AD25" s="221"/>
     </row>
     <row r="26" spans="1:38" ht="15.75">
       <c r="A26" s="17">
@@ -26731,7 +26764,7 @@
         <v>5856.07</v>
       </c>
       <c r="AC26" s="21"/>
-      <c r="AD26" s="230"/>
+      <c r="AD26" s="221"/>
     </row>
     <row r="27" spans="1:38" ht="15.75">
       <c r="A27" s="11">
@@ -26785,7 +26818,7 @@
         <v>14081.2</v>
       </c>
       <c r="AC27" s="21"/>
-      <c r="AD27" s="230"/>
+      <c r="AD27" s="221"/>
     </row>
     <row r="28" spans="1:38" ht="15.75">
       <c r="A28" s="17">
@@ -26829,7 +26862,7 @@
       <c r="AC28" s="21">
         <v>20000</v>
       </c>
-      <c r="AD28" s="230"/>
+      <c r="AD28" s="221"/>
     </row>
     <row r="29" spans="1:38" ht="15.75">
       <c r="A29" s="11">
@@ -26878,7 +26911,7 @@
         <v>4019.84</v>
       </c>
       <c r="AC29" s="21"/>
-      <c r="AD29" s="230"/>
+      <c r="AD29" s="221"/>
     </row>
     <row r="30" spans="1:38" ht="15.75">
       <c r="A30" s="17">
@@ -26929,182 +26962,182 @@
         <v>2628.39</v>
       </c>
       <c r="AC30" s="21"/>
-      <c r="AD30" s="230"/>
+      <c r="AD30" s="221"/>
     </row>
     <row r="31" spans="1:38" ht="16.5" thickBot="1">
-      <c r="A31" s="142">
+      <c r="A31" s="139">
         <v>30</v>
       </c>
-      <c r="B31" s="143" t="s">
+      <c r="B31" s="140" t="s">
         <v>49</v>
       </c>
-      <c r="C31" s="144"/>
-      <c r="D31" s="144"/>
-      <c r="E31" s="144"/>
-      <c r="F31" s="144">
+      <c r="C31" s="141"/>
+      <c r="D31" s="141"/>
+      <c r="E31" s="141"/>
+      <c r="F31" s="141">
         <f>586</f>
         <v>586</v>
       </c>
-      <c r="G31" s="144"/>
-      <c r="H31" s="144"/>
-      <c r="I31" s="144"/>
-      <c r="J31" s="144"/>
-      <c r="K31" s="144"/>
-      <c r="L31" s="144"/>
-      <c r="M31" s="144"/>
-      <c r="N31" s="144"/>
-      <c r="O31" s="144">
+      <c r="G31" s="141"/>
+      <c r="H31" s="141"/>
+      <c r="I31" s="141"/>
+      <c r="J31" s="141"/>
+      <c r="K31" s="141"/>
+      <c r="L31" s="141"/>
+      <c r="M31" s="141"/>
+      <c r="N31" s="141"/>
+      <c r="O31" s="141">
         <v>1200</v>
       </c>
-      <c r="P31" s="144">
+      <c r="P31" s="141">
         <f>389</f>
         <v>389</v>
       </c>
-      <c r="Q31" s="144"/>
-      <c r="R31" s="144"/>
-      <c r="S31" s="144"/>
-      <c r="T31" s="144">
+      <c r="Q31" s="141"/>
+      <c r="R31" s="141"/>
+      <c r="S31" s="141"/>
+      <c r="T31" s="141">
         <f>5593</f>
         <v>5593</v>
       </c>
-      <c r="U31" s="144"/>
-      <c r="V31" s="144">
+      <c r="U31" s="141"/>
+      <c r="V31" s="141">
         <f>2124</f>
         <v>2124</v>
       </c>
-      <c r="W31" s="144">
+      <c r="W31" s="141">
         <f>1515+934+248</f>
         <v>2697</v>
       </c>
-      <c r="X31" s="144"/>
-      <c r="Y31" s="144"/>
-      <c r="Z31" s="144"/>
-      <c r="AA31" s="145"/>
+      <c r="X31" s="141"/>
+      <c r="Y31" s="141"/>
+      <c r="Z31" s="141"/>
+      <c r="AA31" s="142"/>
       <c r="AB31" s="15">
         <f>SUM(C31:AA31)</f>
         <v>12589</v>
       </c>
       <c r="AC31" s="21"/>
-      <c r="AD31" s="230"/>
+      <c r="AD31" s="221"/>
     </row>
     <row r="32" spans="1:38" ht="15.75">
-      <c r="A32" s="150">
+      <c r="A32" s="147">
         <v>1</v>
       </c>
-      <c r="B32" s="151" t="s">
+      <c r="B32" s="148" t="s">
         <v>43</v>
       </c>
-      <c r="C32" s="152"/>
-      <c r="D32" s="152"/>
-      <c r="E32" s="152"/>
-      <c r="F32" s="152">
+      <c r="C32" s="149"/>
+      <c r="D32" s="149"/>
+      <c r="E32" s="149"/>
+      <c r="F32" s="149">
         <v>2323.1</v>
       </c>
-      <c r="G32" s="152"/>
-      <c r="H32" s="152"/>
-      <c r="I32" s="152">
+      <c r="G32" s="149"/>
+      <c r="H32" s="149"/>
+      <c r="I32" s="149">
         <f>4290+463.32</f>
         <v>4753.32</v>
       </c>
-      <c r="J32" s="152">
+      <c r="J32" s="149">
         <f>1360</f>
         <v>1360</v>
       </c>
-      <c r="K32" s="152">
+      <c r="K32" s="149">
         <f>980</f>
         <v>980</v>
       </c>
-      <c r="L32" s="152"/>
-      <c r="M32" s="152"/>
-      <c r="N32" s="152"/>
-      <c r="O32" s="152">
+      <c r="L32" s="149"/>
+      <c r="M32" s="149"/>
+      <c r="N32" s="149"/>
+      <c r="O32" s="149">
         <f>300</f>
         <v>300</v>
       </c>
-      <c r="P32" s="152"/>
-      <c r="Q32" s="152"/>
-      <c r="R32" s="152"/>
-      <c r="S32" s="152"/>
-      <c r="T32" s="152"/>
-      <c r="U32" s="152">
+      <c r="P32" s="149"/>
+      <c r="Q32" s="149"/>
+      <c r="R32" s="149"/>
+      <c r="S32" s="149"/>
+      <c r="T32" s="149"/>
+      <c r="U32" s="149">
         <f>337</f>
         <v>337</v>
       </c>
-      <c r="V32" s="152"/>
-      <c r="W32" s="152">
+      <c r="V32" s="149"/>
+      <c r="W32" s="149">
         <f>1289+1202</f>
         <v>2491</v>
       </c>
-      <c r="X32" s="152"/>
-      <c r="Y32" s="152"/>
-      <c r="Z32" s="152">
+      <c r="X32" s="149"/>
+      <c r="Y32" s="149"/>
+      <c r="Z32" s="149">
         <f>6000</f>
         <v>6000</v>
       </c>
-      <c r="AA32" s="153"/>
+      <c r="AA32" s="150"/>
       <c r="AB32" s="15">
         <f t="shared" ref="AB32:AB35" si="5">SUM(C32:AA32)</f>
         <v>18544.419999999998</v>
       </c>
       <c r="AC32" s="21"/>
-      <c r="AD32" s="230"/>
+      <c r="AD32" s="221"/>
     </row>
     <row r="33" spans="1:34" ht="15.75">
-      <c r="A33" s="157">
+      <c r="A33" s="154">
         <v>2</v>
       </c>
-      <c r="B33" s="158" t="s">
+      <c r="B33" s="155" t="s">
         <v>44</v>
       </c>
-      <c r="C33" s="159"/>
-      <c r="D33" s="159"/>
-      <c r="E33" s="159"/>
-      <c r="F33" s="159"/>
-      <c r="G33" s="159"/>
-      <c r="H33" s="159"/>
-      <c r="I33" s="159">
+      <c r="C33" s="156"/>
+      <c r="D33" s="156"/>
+      <c r="E33" s="156"/>
+      <c r="F33" s="156"/>
+      <c r="G33" s="156"/>
+      <c r="H33" s="156"/>
+      <c r="I33" s="156">
         <f>2839+4140+447.12</f>
         <v>7426.12</v>
       </c>
-      <c r="J33" s="159"/>
-      <c r="K33" s="159"/>
-      <c r="L33" s="159"/>
-      <c r="M33" s="159"/>
-      <c r="N33" s="159">
+      <c r="J33" s="156"/>
+      <c r="K33" s="156"/>
+      <c r="L33" s="156"/>
+      <c r="M33" s="156"/>
+      <c r="N33" s="156">
         <f>399</f>
         <v>399</v>
       </c>
-      <c r="O33" s="159"/>
-      <c r="P33" s="159"/>
-      <c r="Q33" s="159"/>
-      <c r="R33" s="159">
+      <c r="O33" s="156"/>
+      <c r="P33" s="156"/>
+      <c r="Q33" s="156"/>
+      <c r="R33" s="156">
         <f>1510.97</f>
         <v>1510.97</v>
       </c>
-      <c r="S33" s="159"/>
-      <c r="T33" s="159"/>
-      <c r="U33" s="159">
+      <c r="S33" s="156"/>
+      <c r="T33" s="156"/>
+      <c r="U33" s="156">
         <f>95+95</f>
         <v>190</v>
       </c>
-      <c r="V33" s="159"/>
-      <c r="W33" s="159"/>
-      <c r="X33" s="159"/>
-      <c r="Y33" s="159"/>
-      <c r="Z33" s="159"/>
-      <c r="AA33" s="160"/>
+      <c r="V33" s="156"/>
+      <c r="W33" s="156"/>
+      <c r="X33" s="156"/>
+      <c r="Y33" s="156"/>
+      <c r="Z33" s="156"/>
+      <c r="AA33" s="157"/>
       <c r="AB33" s="15">
         <f t="shared" si="5"/>
         <v>9526.09</v>
       </c>
       <c r="AC33" s="21"/>
-      <c r="AD33" s="230"/>
+      <c r="AD33" s="221"/>
     </row>
     <row r="34" spans="1:34" ht="15.75">
-      <c r="A34" s="154">
+      <c r="A34" s="151">
         <v>3</v>
       </c>
-      <c r="B34" s="155" t="s">
+      <c r="B34" s="152" t="s">
         <v>45</v>
       </c>
       <c r="C34" s="50"/>
@@ -27152,7 +27185,7 @@
         <f>1700</f>
         <v>1700</v>
       </c>
-      <c r="AA34" s="156"/>
+      <c r="AA34" s="153"/>
       <c r="AB34" s="15">
         <f t="shared" si="5"/>
         <v>22952</v>
@@ -27160,55 +27193,55 @@
       <c r="AC34" s="21">
         <v>20000</v>
       </c>
-      <c r="AD34" s="230"/>
+      <c r="AD34" s="221"/>
     </row>
     <row r="35" spans="1:34" ht="16.5" thickBot="1">
-      <c r="A35" s="161">
+      <c r="A35" s="158">
         <v>4</v>
       </c>
-      <c r="B35" s="162" t="s">
+      <c r="B35" s="159" t="s">
         <v>46</v>
       </c>
-      <c r="C35" s="163"/>
-      <c r="D35" s="163"/>
-      <c r="E35" s="163"/>
-      <c r="F35" s="163"/>
-      <c r="G35" s="163"/>
-      <c r="H35" s="163"/>
-      <c r="I35" s="163">
+      <c r="C35" s="160"/>
+      <c r="D35" s="160"/>
+      <c r="E35" s="160"/>
+      <c r="F35" s="160"/>
+      <c r="G35" s="160"/>
+      <c r="H35" s="160"/>
+      <c r="I35" s="160">
         <f>5900+651+13880+1508</f>
         <v>21939</v>
       </c>
-      <c r="J35" s="163"/>
-      <c r="K35" s="163"/>
-      <c r="L35" s="163"/>
-      <c r="M35" s="163"/>
-      <c r="N35" s="163">
+      <c r="J35" s="160"/>
+      <c r="K35" s="160"/>
+      <c r="L35" s="160"/>
+      <c r="M35" s="160"/>
+      <c r="N35" s="160">
         <f>300</f>
         <v>300</v>
       </c>
-      <c r="O35" s="163"/>
-      <c r="P35" s="163"/>
-      <c r="Q35" s="163"/>
-      <c r="R35" s="163"/>
-      <c r="S35" s="163"/>
-      <c r="T35" s="163"/>
-      <c r="U35" s="163">
+      <c r="O35" s="160"/>
+      <c r="P35" s="160"/>
+      <c r="Q35" s="160"/>
+      <c r="R35" s="160"/>
+      <c r="S35" s="160"/>
+      <c r="T35" s="160"/>
+      <c r="U35" s="160">
         <f>423+526+838</f>
         <v>1787</v>
       </c>
-      <c r="V35" s="163"/>
-      <c r="W35" s="163"/>
-      <c r="X35" s="163">
+      <c r="V35" s="160"/>
+      <c r="W35" s="160"/>
+      <c r="X35" s="160">
         <f>375</f>
         <v>375</v>
       </c>
-      <c r="Y35" s="163"/>
-      <c r="Z35" s="163">
+      <c r="Y35" s="160"/>
+      <c r="Z35" s="160">
         <f>1400</f>
         <v>1400</v>
       </c>
-      <c r="AA35" s="164"/>
+      <c r="AA35" s="161"/>
       <c r="AB35" s="15">
         <f t="shared" si="5"/>
         <v>25801</v>
@@ -27216,110 +27249,110 @@
       <c r="AC35" s="37">
         <v>15000</v>
       </c>
-      <c r="AD35" s="230"/>
+      <c r="AD35" s="221"/>
     </row>
     <row r="36" spans="1:34" ht="24" customHeight="1">
-      <c r="A36" s="237" t="s">
+      <c r="A36" s="235" t="s">
         <v>55</v>
       </c>
-      <c r="B36" s="237"/>
-      <c r="C36" s="146">
+      <c r="B36" s="235"/>
+      <c r="C36" s="143">
         <f t="shared" ref="C36:AC36" si="6">SUM(C19:C35)</f>
         <v>1293.0899999999999</v>
       </c>
-      <c r="D36" s="146">
+      <c r="D36" s="143">
         <f t="shared" si="6"/>
         <v>2055.8000000000002</v>
       </c>
-      <c r="E36" s="146">
+      <c r="E36" s="143">
         <f t="shared" si="6"/>
         <v>3550.01</v>
       </c>
-      <c r="F36" s="146">
+      <c r="F36" s="143">
         <f t="shared" si="6"/>
         <v>7603.8099999999995</v>
       </c>
-      <c r="G36" s="146">
+      <c r="G36" s="143">
         <f t="shared" si="6"/>
         <v>926</v>
       </c>
-      <c r="H36" s="146">
+      <c r="H36" s="143">
         <f t="shared" si="6"/>
         <v>9215</v>
       </c>
-      <c r="I36" s="146">
+      <c r="I36" s="143">
         <f t="shared" si="6"/>
         <v>49258.44</v>
       </c>
-      <c r="J36" s="146">
+      <c r="J36" s="143">
         <f t="shared" si="6"/>
         <v>6442</v>
       </c>
-      <c r="K36" s="146">
+      <c r="K36" s="143">
         <f t="shared" si="6"/>
         <v>4820</v>
       </c>
-      <c r="L36" s="147">
+      <c r="L36" s="144">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="M36" s="147">
+      <c r="M36" s="144">
         <f t="shared" si="6"/>
         <v>5345</v>
       </c>
-      <c r="N36" s="147">
+      <c r="N36" s="144">
         <f t="shared" si="6"/>
         <v>1747</v>
       </c>
-      <c r="O36" s="147">
+      <c r="O36" s="144">
         <f t="shared" si="6"/>
         <v>1500</v>
       </c>
-      <c r="P36" s="147">
+      <c r="P36" s="144">
         <f t="shared" si="6"/>
         <v>389</v>
       </c>
-      <c r="Q36" s="147">
+      <c r="Q36" s="144">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R36" s="148">
+      <c r="R36" s="145">
         <f t="shared" si="6"/>
         <v>6339.95</v>
       </c>
-      <c r="S36" s="148">
+      <c r="S36" s="145">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T36" s="148">
+      <c r="T36" s="145">
         <f t="shared" si="6"/>
         <v>11703</v>
       </c>
-      <c r="U36" s="148">
+      <c r="U36" s="145">
         <f t="shared" si="6"/>
         <v>3897</v>
       </c>
-      <c r="V36" s="148">
+      <c r="V36" s="145">
         <f t="shared" si="6"/>
         <v>5937.3499999999995</v>
       </c>
-      <c r="W36" s="148">
+      <c r="W36" s="145">
         <f t="shared" si="6"/>
         <v>18675</v>
       </c>
-      <c r="X36" s="148">
+      <c r="X36" s="145">
         <f t="shared" si="6"/>
         <v>4949</v>
       </c>
-      <c r="Y36" s="148">
+      <c r="Y36" s="145">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z36" s="148">
+      <c r="Z36" s="145">
         <f t="shared" si="6"/>
         <v>9100</v>
       </c>
-      <c r="AA36" s="149">
+      <c r="AA36" s="146">
         <f t="shared" si="6"/>
         <v>73610.12</v>
       </c>
@@ -27335,13 +27368,13 @@
         <f>AC36-AB36</f>
         <v>1774.8799999999756</v>
       </c>
-      <c r="AH36" s="165"/>
+      <c r="AH36" s="162"/>
     </row>
     <row r="37" spans="1:34" ht="31.5" customHeight="1">
-      <c r="A37" s="229" t="s">
+      <c r="A37" s="220" t="s">
         <v>56</v>
       </c>
-      <c r="B37" s="229"/>
+      <c r="B37" s="220"/>
       <c r="C37" s="31">
         <f t="shared" ref="C37:R37" si="7">SUM(C18,C36)</f>
         <v>1423.08</v>
@@ -27447,7 +27480,7 @@
         <f t="shared" si="8"/>
         <v>348751.42000000004</v>
       </c>
-      <c r="AD37" s="169">
+      <c r="AD37" s="166">
         <f>SUM(AD18,AD36)</f>
         <v>874.20999999996275</v>
       </c>
@@ -27472,6 +27505,12 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="AD19:AD35"/>
     <mergeCell ref="AH11:AL13"/>
@@ -27487,12 +27526,6 @@
     <mergeCell ref="AH16:AK16"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="AH18:AK18"/>
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:K2"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Другое/2026/Доходы-Расходы.xlsx
+++ b/Другое/2026/Доходы-Расходы.xlsx
@@ -8370,6 +8370,30 @@
           </rPr>
           <t xml:space="preserve">
 На йогу + сплит за сережки и браслет</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W22" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Собянин Евгений Андреевич (new):</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+На врача</t>
         </r>
       </text>
     </comment>
@@ -10329,6 +10353,21 @@
     <xf numFmtId="164" fontId="52" fillId="39" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="55" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="56" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="56" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="57" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="57" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -10368,6 +10407,9 @@
     <xf numFmtId="0" fontId="24" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -10378,24 +10420,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -10419,6 +10443,21 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -10438,21 +10477,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="55" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="56" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="56" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="57" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="57" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -11350,7 +11374,7 @@
       <c r="AC4" s="163">
         <v>142200.85999999999</v>
       </c>
-      <c r="AD4" s="221"/>
+      <c r="AD4" s="233"/>
     </row>
     <row r="5" spans="1:52" ht="15.75">
       <c r="A5" s="196">
@@ -11406,7 +11430,7 @@
         <v>47667</v>
       </c>
       <c r="AC5" s="165"/>
-      <c r="AD5" s="221"/>
+      <c r="AD5" s="233"/>
     </row>
     <row r="6" spans="1:52" ht="16.5" thickBot="1">
       <c r="A6" s="194">
@@ -11460,7 +11484,7 @@
         <v>9459</v>
       </c>
       <c r="AC6" s="165"/>
-      <c r="AD6" s="221"/>
+      <c r="AD6" s="233"/>
     </row>
     <row r="7" spans="1:52" ht="15.75">
       <c r="A7" s="186">
@@ -11513,7 +11537,7 @@
       <c r="AC7" s="165">
         <v>2000</v>
       </c>
-      <c r="AD7" s="221"/>
+      <c r="AD7" s="233"/>
     </row>
     <row r="8" spans="1:52" ht="15" customHeight="1">
       <c r="A8" s="11">
@@ -11555,7 +11579,7 @@
         <v>2946.51</v>
       </c>
       <c r="AC8" s="165"/>
-      <c r="AD8" s="221"/>
+      <c r="AD8" s="233"/>
     </row>
     <row r="9" spans="1:52" ht="15.75">
       <c r="A9" s="17">
@@ -11600,7 +11624,7 @@
         <v>1677.84</v>
       </c>
       <c r="AC9" s="165"/>
-      <c r="AD9" s="221"/>
+      <c r="AD9" s="233"/>
     </row>
     <row r="10" spans="1:52" ht="15.75">
       <c r="A10" s="11">
@@ -11666,7 +11690,7 @@
       <c r="AC10" s="165">
         <v>55867</v>
       </c>
-      <c r="AD10" s="221"/>
+      <c r="AD10" s="233"/>
     </row>
     <row r="11" spans="1:52" ht="15.75">
       <c r="A11" s="17">
@@ -11713,14 +11737,14 @@
       <c r="AC11" s="165">
         <v>3000</v>
       </c>
-      <c r="AD11" s="221"/>
-      <c r="AH11" s="222" t="s">
+      <c r="AD11" s="233"/>
+      <c r="AH11" s="234" t="s">
         <v>83</v>
       </c>
-      <c r="AI11" s="222"/>
-      <c r="AJ11" s="222"/>
-      <c r="AK11" s="222"/>
-      <c r="AL11" s="222"/>
+      <c r="AI11" s="234"/>
+      <c r="AJ11" s="234"/>
+      <c r="AK11" s="234"/>
+      <c r="AL11" s="234"/>
     </row>
     <row r="12" spans="1:52" ht="15.75">
       <c r="A12" s="11">
@@ -11769,12 +11793,12 @@
         <v>6686</v>
       </c>
       <c r="AC12" s="165"/>
-      <c r="AD12" s="221"/>
-      <c r="AH12" s="222"/>
-      <c r="AI12" s="222"/>
-      <c r="AJ12" s="222"/>
-      <c r="AK12" s="222"/>
-      <c r="AL12" s="222"/>
+      <c r="AD12" s="233"/>
+      <c r="AH12" s="234"/>
+      <c r="AI12" s="234"/>
+      <c r="AJ12" s="234"/>
+      <c r="AK12" s="234"/>
+      <c r="AL12" s="234"/>
     </row>
     <row r="13" spans="1:52" ht="15.75">
       <c r="A13" s="17">
@@ -11821,12 +11845,12 @@
         <v>3935</v>
       </c>
       <c r="AC13" s="165"/>
-      <c r="AD13" s="221"/>
-      <c r="AH13" s="222"/>
-      <c r="AI13" s="222"/>
-      <c r="AJ13" s="222"/>
-      <c r="AK13" s="222"/>
-      <c r="AL13" s="222"/>
+      <c r="AD13" s="233"/>
+      <c r="AH13" s="234"/>
+      <c r="AI13" s="234"/>
+      <c r="AJ13" s="234"/>
+      <c r="AK13" s="234"/>
+      <c r="AL13" s="234"/>
     </row>
     <row r="14" spans="1:52" ht="18">
       <c r="A14" s="11">
@@ -11867,13 +11891,13 @@
         <v>750</v>
       </c>
       <c r="AC14" s="165"/>
-      <c r="AD14" s="221"/>
-      <c r="AH14" s="218" t="s">
+      <c r="AD14" s="233"/>
+      <c r="AH14" s="230" t="s">
         <v>62</v>
       </c>
-      <c r="AI14" s="218"/>
-      <c r="AJ14" s="218"/>
-      <c r="AK14" s="218"/>
+      <c r="AI14" s="230"/>
+      <c r="AJ14" s="230"/>
+      <c r="AK14" s="230"/>
       <c r="AL14" s="22">
         <f>AC4+AC20+AC24+AC10</f>
         <v>198067.86</v>
@@ -11928,13 +11952,13 @@
         <v>10319</v>
       </c>
       <c r="AC15" s="163"/>
-      <c r="AD15" s="221"/>
-      <c r="AH15" s="218" t="s">
+      <c r="AD15" s="233"/>
+      <c r="AH15" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="AI15" s="218"/>
-      <c r="AJ15" s="218"/>
-      <c r="AK15" s="218"/>
+      <c r="AI15" s="230"/>
+      <c r="AJ15" s="230"/>
+      <c r="AK15" s="230"/>
       <c r="AL15" s="22">
         <f>SUM(AC7,AC11)</f>
         <v>5000</v>
@@ -11989,13 +12013,13 @@
         <v>7901.26</v>
       </c>
       <c r="AC16" s="163"/>
-      <c r="AD16" s="221"/>
-      <c r="AH16" s="218" t="s">
+      <c r="AD16" s="233"/>
+      <c r="AH16" s="230" t="s">
         <v>63</v>
       </c>
-      <c r="AI16" s="218"/>
-      <c r="AJ16" s="218"/>
-      <c r="AK16" s="218"/>
+      <c r="AI16" s="230"/>
+      <c r="AJ16" s="230"/>
+      <c r="AK16" s="230"/>
       <c r="AL16" s="22">
         <v>0</v>
       </c>
@@ -12044,16 +12068,16 @@
         <v>1766.67</v>
       </c>
       <c r="AC17" s="163"/>
-      <c r="AD17" s="221"/>
-      <c r="AH17" s="230" t="s">
+      <c r="AD17" s="233"/>
+      <c r="AH17" s="235" t="s">
         <v>67</v>
       </c>
-      <c r="AI17" s="231"/>
-      <c r="AJ17" s="231"/>
-      <c r="AK17" s="232"/>
+      <c r="AI17" s="236"/>
+      <c r="AJ17" s="236"/>
+      <c r="AK17" s="237"/>
       <c r="AL17" s="22">
         <f>SUM(C37:K37)</f>
-        <v>58461.880000000005</v>
+        <v>59012.880000000005</v>
       </c>
     </row>
     <row r="18" spans="1:38" ht="18">
@@ -12099,23 +12123,23 @@
         <v>20640.400000000001</v>
       </c>
       <c r="AC18" s="163"/>
-      <c r="AD18" s="221"/>
-      <c r="AH18" s="230" t="s">
+      <c r="AD18" s="233"/>
+      <c r="AH18" s="235" t="s">
         <v>84</v>
       </c>
-      <c r="AI18" s="231"/>
-      <c r="AJ18" s="231"/>
-      <c r="AK18" s="232"/>
+      <c r="AI18" s="236"/>
+      <c r="AJ18" s="236"/>
+      <c r="AK18" s="237"/>
       <c r="AL18" s="22">
         <f>SUM(L37:Q37)</f>
         <v>21802</v>
       </c>
     </row>
     <row r="19" spans="1:38" ht="19.5" customHeight="1">
-      <c r="A19" s="236" t="s">
+      <c r="A19" s="241" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="236"/>
+      <c r="B19" s="241"/>
       <c r="C19" s="23">
         <f>SUM(C4:C18)</f>
         <v>2892.73</v>
@@ -12224,19 +12248,19 @@
         <f t="shared" ref="AC19" si="4">SUM(AC4:AC17)</f>
         <v>203067.86</v>
       </c>
-      <c r="AD19" s="239">
+      <c r="AD19" s="202">
         <f>AC19-AB19</f>
         <v>23603.329999999958</v>
       </c>
-      <c r="AH19" s="230" t="s">
+      <c r="AH19" s="235" t="s">
         <v>85</v>
       </c>
-      <c r="AI19" s="231"/>
-      <c r="AJ19" s="231"/>
-      <c r="AK19" s="232"/>
+      <c r="AI19" s="236"/>
+      <c r="AJ19" s="236"/>
+      <c r="AK19" s="237"/>
       <c r="AL19" s="22">
         <f>W37</f>
-        <v>60674</v>
+        <v>62674</v>
       </c>
     </row>
     <row r="20" spans="1:38" ht="18">
@@ -12280,13 +12304,13 @@
       <c r="AC20" s="16">
         <v>0</v>
       </c>
-      <c r="AD20" s="221"/>
-      <c r="AH20" s="230" t="s">
+      <c r="AD20" s="233"/>
+      <c r="AH20" s="235" t="s">
         <v>86</v>
       </c>
-      <c r="AI20" s="231"/>
-      <c r="AJ20" s="231"/>
-      <c r="AK20" s="232"/>
+      <c r="AI20" s="236"/>
+      <c r="AJ20" s="236"/>
+      <c r="AK20" s="237"/>
       <c r="AL20" s="22">
         <f>SUM(U37:V37)</f>
         <v>5082.03</v>
@@ -12302,7 +12326,9 @@
       <c r="C21" s="175"/>
       <c r="D21" s="175"/>
       <c r="E21" s="175"/>
-      <c r="F21" s="175"/>
+      <c r="F21" s="175">
+        <v>551</v>
+      </c>
       <c r="G21" s="175"/>
       <c r="H21" s="175"/>
       <c r="I21" s="175"/>
@@ -12326,17 +12352,20 @@
       <c r="AA21" s="176"/>
       <c r="AB21" s="15">
         <f>SUM(C21:AA21)</f>
-        <v>0</v>
-      </c>
-      <c r="AC21" s="21"/>
-      <c r="AD21" s="221"/>
+        <v>551</v>
+      </c>
+      <c r="AC21" s="21">
+        <f>3175.8+7922.85</f>
+        <v>11098.650000000001</v>
+      </c>
+      <c r="AD21" s="233"/>
       <c r="AF21" s="29"/>
-      <c r="AH21" s="233" t="s">
+      <c r="AH21" s="238" t="s">
         <v>32</v>
       </c>
-      <c r="AI21" s="233"/>
-      <c r="AJ21" s="233"/>
-      <c r="AK21" s="233"/>
+      <c r="AI21" s="238"/>
+      <c r="AJ21" s="238"/>
+      <c r="AK21" s="238"/>
       <c r="AL21" s="169">
         <f>T37</f>
         <v>0</v>
@@ -12369,17 +12398,20 @@
       <c r="T22" s="173"/>
       <c r="U22" s="173"/>
       <c r="V22" s="173"/>
-      <c r="W22" s="173"/>
+      <c r="W22" s="173">
+        <f>2000</f>
+        <v>2000</v>
+      </c>
       <c r="X22" s="173"/>
       <c r="Y22" s="173"/>
       <c r="Z22" s="173"/>
       <c r="AA22" s="174"/>
       <c r="AB22" s="15">
         <f t="shared" ref="AB22:AB31" si="5">SUM(C22:AA22)</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="AC22" s="21"/>
-      <c r="AD22" s="221"/>
+      <c r="AD22" s="233"/>
     </row>
     <row r="23" spans="1:38" ht="18">
       <c r="A23" s="17">
@@ -12418,11 +12450,11 @@
         <v>0</v>
       </c>
       <c r="AC23" s="21"/>
-      <c r="AD23" s="221"/>
-      <c r="AH23" s="234"/>
-      <c r="AI23" s="234"/>
-      <c r="AJ23" s="234"/>
-      <c r="AK23" s="234"/>
+      <c r="AD23" s="233"/>
+      <c r="AH23" s="239"/>
+      <c r="AI23" s="239"/>
+      <c r="AJ23" s="239"/>
+      <c r="AK23" s="239"/>
       <c r="AL23" s="170"/>
     </row>
     <row r="24" spans="1:38" ht="15.75">
@@ -12462,7 +12494,7 @@
         <v>0</v>
       </c>
       <c r="AC24" s="21"/>
-      <c r="AD24" s="221"/>
+      <c r="AD24" s="233"/>
     </row>
     <row r="25" spans="1:38" ht="15.75">
       <c r="A25" s="17">
@@ -12503,7 +12535,7 @@
         <v>3500</v>
       </c>
       <c r="AC25" s="21"/>
-      <c r="AD25" s="221"/>
+      <c r="AD25" s="233"/>
     </row>
     <row r="26" spans="1:38" ht="15.75">
       <c r="A26" s="11">
@@ -12542,7 +12574,7 @@
         <v>0</v>
       </c>
       <c r="AC26" s="16"/>
-      <c r="AD26" s="221"/>
+      <c r="AD26" s="233"/>
     </row>
     <row r="27" spans="1:38" ht="15.75">
       <c r="A27" s="17">
@@ -12581,7 +12613,7 @@
         <v>0</v>
       </c>
       <c r="AC27" s="21"/>
-      <c r="AD27" s="221"/>
+      <c r="AD27" s="233"/>
     </row>
     <row r="28" spans="1:38" ht="15.75">
       <c r="A28" s="11">
@@ -12620,7 +12652,7 @@
         <v>0</v>
       </c>
       <c r="AC28" s="21"/>
-      <c r="AD28" s="221"/>
+      <c r="AD28" s="233"/>
     </row>
     <row r="29" spans="1:38" ht="15.75">
       <c r="A29" s="17">
@@ -12661,7 +12693,7 @@
         <v>3500</v>
       </c>
       <c r="AC29" s="21"/>
-      <c r="AD29" s="221"/>
+      <c r="AD29" s="233"/>
     </row>
     <row r="30" spans="1:38" ht="15.75">
       <c r="A30" s="11">
@@ -12700,7 +12732,7 @@
         <v>0</v>
       </c>
       <c r="AC30" s="21"/>
-      <c r="AD30" s="221"/>
+      <c r="AD30" s="233"/>
     </row>
     <row r="31" spans="1:38" ht="15.75">
       <c r="A31" s="17">
@@ -12739,7 +12771,7 @@
         <v>0</v>
       </c>
       <c r="AC31" s="21"/>
-      <c r="AD31" s="221"/>
+      <c r="AD31" s="233"/>
     </row>
     <row r="32" spans="1:38" ht="15.75">
       <c r="A32" s="11">
@@ -12778,7 +12810,7 @@
         <v>0</v>
       </c>
       <c r="AC32" s="21"/>
-      <c r="AD32" s="221"/>
+      <c r="AD32" s="233"/>
     </row>
     <row r="33" spans="1:34" ht="15.75">
       <c r="A33" s="17">
@@ -12819,7 +12851,7 @@
         <v>3500</v>
       </c>
       <c r="AC33" s="21"/>
-      <c r="AD33" s="221"/>
+      <c r="AD33" s="233"/>
     </row>
     <row r="34" spans="1:34" ht="15.75">
       <c r="A34" s="11">
@@ -12860,7 +12892,7 @@
         <v>11525</v>
       </c>
       <c r="AC34" s="21"/>
-      <c r="AD34" s="221"/>
+      <c r="AD34" s="233"/>
     </row>
     <row r="35" spans="1:34" ht="15.75">
       <c r="A35" s="17">
@@ -12899,13 +12931,13 @@
         <v>0</v>
       </c>
       <c r="AC35" s="21"/>
-      <c r="AD35" s="221"/>
+      <c r="AD35" s="233"/>
     </row>
     <row r="36" spans="1:34" ht="24" customHeight="1">
-      <c r="A36" s="235" t="s">
+      <c r="A36" s="240" t="s">
         <v>55</v>
       </c>
-      <c r="B36" s="235"/>
+      <c r="B36" s="240"/>
       <c r="C36" s="143">
         <f t="shared" ref="C36:AC36" si="7">SUM(C20:C35)</f>
         <v>0</v>
@@ -12920,7 +12952,7 @@
       </c>
       <c r="F36" s="143">
         <f t="shared" si="7"/>
-        <v>12433.720000000001</v>
+        <v>12984.720000000001</v>
       </c>
       <c r="G36" s="143">
         <f t="shared" si="7"/>
@@ -12988,7 +13020,7 @@
       </c>
       <c r="W36" s="145">
         <f t="shared" si="7"/>
-        <v>11525</v>
+        <v>13525</v>
       </c>
       <c r="X36" s="145">
         <f t="shared" si="7"/>
@@ -13008,23 +13040,23 @@
       </c>
       <c r="AB36" s="26">
         <f t="shared" si="7"/>
-        <v>23958.720000000001</v>
+        <v>26509.72</v>
       </c>
       <c r="AC36" s="27">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AD36" s="238">
+        <v>11098.650000000001</v>
+      </c>
+      <c r="AD36" s="201">
         <f>AC36-AB36</f>
-        <v>-23958.720000000001</v>
+        <v>-15411.07</v>
       </c>
       <c r="AH36" s="162"/>
     </row>
     <row r="37" spans="1:34" ht="31.5" customHeight="1">
-      <c r="A37" s="220" t="s">
+      <c r="A37" s="232" t="s">
         <v>56</v>
       </c>
-      <c r="B37" s="220"/>
+      <c r="B37" s="232"/>
       <c r="C37" s="31">
         <f t="shared" ref="C37:R37" si="8">SUM(C19,C36)</f>
         <v>2892.73</v>
@@ -13039,7 +13071,7 @@
       </c>
       <c r="F37" s="31">
         <f t="shared" si="8"/>
-        <v>20688.57</v>
+        <v>21239.57</v>
       </c>
       <c r="G37" s="31">
         <f t="shared" si="8"/>
@@ -13104,7 +13136,7 @@
       </c>
       <c r="W37" s="31">
         <f t="shared" si="9"/>
-        <v>60674</v>
+        <v>62674</v>
       </c>
       <c r="X37" s="31">
         <f t="shared" si="9"/>
@@ -13122,17 +13154,17 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AB37" s="240">
+      <c r="AB37" s="203">
         <f t="shared" si="9"/>
-        <v>203423.25000000003</v>
-      </c>
-      <c r="AC37" s="241">
+        <v>205974.25000000003</v>
+      </c>
+      <c r="AC37" s="204">
         <f t="shared" si="9"/>
-        <v>203067.86</v>
-      </c>
-      <c r="AD37" s="237">
+        <v>214166.50999999998</v>
+      </c>
+      <c r="AD37" s="200">
         <f t="shared" si="9"/>
-        <v>-355.39000000004307</v>
+        <v>8192.2599999999584</v>
       </c>
     </row>
     <row r="41" spans="1:34">
@@ -13155,6 +13187,12 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="AD4:AD18"/>
@@ -13170,12 +13208,6 @@
     <mergeCell ref="AH16:AK16"/>
     <mergeCell ref="AH17:AK17"/>
     <mergeCell ref="AH18:AK18"/>
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:K2"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
   </mergeCells>
   <conditionalFormatting sqref="AD37">
     <cfRule type="expression" dxfId="1" priority="1">
@@ -13202,32 +13234,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="200" t="s">
+      <c r="A1" s="205" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="200"/>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
-      <c r="G1" s="200"/>
-      <c r="H1" s="200"/>
-      <c r="I1" s="200"/>
-      <c r="J1" s="200"/>
-      <c r="K1" s="200"/>
-      <c r="L1" s="200"/>
-      <c r="M1" s="200"/>
-      <c r="N1" s="200"/>
-      <c r="O1" s="200"/>
-      <c r="P1" s="200"/>
-      <c r="Q1" s="200"/>
-      <c r="R1" s="200"/>
-      <c r="S1" s="200"/>
-      <c r="T1" s="200"/>
-      <c r="U1" s="200"/>
-      <c r="V1" s="200"/>
-      <c r="W1" s="200"/>
-      <c r="X1" s="200"/>
+      <c r="B1" s="205"/>
+      <c r="C1" s="205"/>
+      <c r="D1" s="205"/>
+      <c r="E1" s="205"/>
+      <c r="F1" s="205"/>
+      <c r="G1" s="205"/>
+      <c r="H1" s="205"/>
+      <c r="I1" s="205"/>
+      <c r="J1" s="205"/>
+      <c r="K1" s="205"/>
+      <c r="L1" s="205"/>
+      <c r="M1" s="205"/>
+      <c r="N1" s="205"/>
+      <c r="O1" s="205"/>
+      <c r="P1" s="205"/>
+      <c r="Q1" s="205"/>
+      <c r="R1" s="205"/>
+      <c r="S1" s="205"/>
+      <c r="T1" s="205"/>
+      <c r="U1" s="205"/>
+      <c r="V1" s="205"/>
+      <c r="W1" s="205"/>
+      <c r="X1" s="205"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="107" t="s">
@@ -14426,10 +14458,10 @@
       </c>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" s="201" t="s">
+      <c r="A31" s="206" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="201"/>
+      <c r="B31" s="206"/>
       <c r="C31" s="127">
         <f>SUM(C3:C30)</f>
         <v>19992.27</v>
@@ -14552,32 +14584,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="202" t="s">
+      <c r="A1" s="207" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="202"/>
-      <c r="C1" s="202"/>
-      <c r="D1" s="202"/>
-      <c r="E1" s="202"/>
-      <c r="F1" s="202"/>
-      <c r="G1" s="202"/>
-      <c r="H1" s="202"/>
-      <c r="I1" s="202"/>
-      <c r="J1" s="202"/>
-      <c r="K1" s="202"/>
-      <c r="L1" s="202"/>
-      <c r="M1" s="202"/>
-      <c r="N1" s="202"/>
-      <c r="O1" s="202"/>
-      <c r="P1" s="202"/>
-      <c r="Q1" s="202"/>
-      <c r="R1" s="202"/>
-      <c r="S1" s="202"/>
-      <c r="T1" s="202"/>
-      <c r="U1" s="202"/>
-      <c r="V1" s="202"/>
-      <c r="W1" s="202"/>
-      <c r="X1" s="202"/>
+      <c r="B1" s="207"/>
+      <c r="C1" s="207"/>
+      <c r="D1" s="207"/>
+      <c r="E1" s="207"/>
+      <c r="F1" s="207"/>
+      <c r="G1" s="207"/>
+      <c r="H1" s="207"/>
+      <c r="I1" s="207"/>
+      <c r="J1" s="207"/>
+      <c r="K1" s="207"/>
+      <c r="L1" s="207"/>
+      <c r="M1" s="207"/>
+      <c r="N1" s="207"/>
+      <c r="O1" s="207"/>
+      <c r="P1" s="207"/>
+      <c r="Q1" s="207"/>
+      <c r="R1" s="207"/>
+      <c r="S1" s="207"/>
+      <c r="T1" s="207"/>
+      <c r="U1" s="207"/>
+      <c r="V1" s="207"/>
+      <c r="W1" s="207"/>
+      <c r="X1" s="207"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="84" t="s">
@@ -15788,10 +15820,10 @@
       <c r="X31" s="101"/>
     </row>
     <row r="32" spans="1:24">
-      <c r="A32" s="203" t="s">
+      <c r="A32" s="208" t="s">
         <v>19</v>
       </c>
-      <c r="B32" s="203"/>
+      <c r="B32" s="208"/>
       <c r="C32" s="100">
         <f>SUM(C3:C31)</f>
         <v>16843.349999999999</v>
@@ -15914,33 +15946,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="202" t="s">
+      <c r="A1" s="207" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="202"/>
-      <c r="C1" s="202"/>
-      <c r="D1" s="202"/>
-      <c r="E1" s="202"/>
-      <c r="F1" s="202"/>
-      <c r="G1" s="202"/>
-      <c r="H1" s="202"/>
-      <c r="I1" s="202"/>
-      <c r="J1" s="202"/>
-      <c r="K1" s="202"/>
-      <c r="L1" s="202"/>
-      <c r="M1" s="202"/>
-      <c r="N1" s="202"/>
-      <c r="O1" s="202"/>
-      <c r="P1" s="202"/>
-      <c r="Q1" s="202"/>
-      <c r="R1" s="202"/>
-      <c r="S1" s="202"/>
-      <c r="T1" s="202"/>
-      <c r="U1" s="202"/>
-      <c r="V1" s="202"/>
-      <c r="W1" s="202"/>
-      <c r="X1" s="202"/>
-      <c r="Y1" s="202"/>
+      <c r="B1" s="207"/>
+      <c r="C1" s="207"/>
+      <c r="D1" s="207"/>
+      <c r="E1" s="207"/>
+      <c r="F1" s="207"/>
+      <c r="G1" s="207"/>
+      <c r="H1" s="207"/>
+      <c r="I1" s="207"/>
+      <c r="J1" s="207"/>
+      <c r="K1" s="207"/>
+      <c r="L1" s="207"/>
+      <c r="M1" s="207"/>
+      <c r="N1" s="207"/>
+      <c r="O1" s="207"/>
+      <c r="P1" s="207"/>
+      <c r="Q1" s="207"/>
+      <c r="R1" s="207"/>
+      <c r="S1" s="207"/>
+      <c r="T1" s="207"/>
+      <c r="U1" s="207"/>
+      <c r="V1" s="207"/>
+      <c r="W1" s="207"/>
+      <c r="X1" s="207"/>
+      <c r="Y1" s="207"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="84" t="s">
@@ -16758,10 +16790,10 @@
       <c r="Y19" s="92"/>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="204" t="s">
+      <c r="A20" s="209" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="205"/>
+      <c r="B20" s="210"/>
       <c r="C20" s="93">
         <f>SUM(C3:C19)</f>
         <v>12278.83</v>
@@ -17481,10 +17513,10 @@
       <c r="Y35" s="92"/>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="204" t="s">
+      <c r="A36" s="209" t="s">
         <v>55</v>
       </c>
-      <c r="B36" s="205"/>
+      <c r="B36" s="210"/>
       <c r="C36" s="93">
         <f>SUM(C21:C35)</f>
         <v>11057.89</v>
@@ -17579,10 +17611,10 @@
       </c>
     </row>
     <row r="37" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A37" s="206" t="s">
+      <c r="A37" s="211" t="s">
         <v>56</v>
       </c>
-      <c r="B37" s="206"/>
+      <c r="B37" s="211"/>
       <c r="C37" s="97">
         <f>SUM(C20,C36)</f>
         <v>23336.720000000001</v>
@@ -17712,33 +17744,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="207" t="s">
+      <c r="A1" s="212" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="207"/>
-      <c r="C1" s="207"/>
-      <c r="D1" s="207"/>
-      <c r="E1" s="207"/>
-      <c r="F1" s="207"/>
-      <c r="G1" s="207"/>
-      <c r="H1" s="207"/>
-      <c r="I1" s="207"/>
-      <c r="J1" s="207"/>
-      <c r="K1" s="207"/>
-      <c r="L1" s="207"/>
-      <c r="M1" s="207"/>
-      <c r="N1" s="207"/>
-      <c r="O1" s="207"/>
-      <c r="P1" s="207"/>
-      <c r="Q1" s="207"/>
-      <c r="R1" s="207"/>
-      <c r="S1" s="207"/>
-      <c r="T1" s="207"/>
-      <c r="U1" s="207"/>
-      <c r="V1" s="207"/>
-      <c r="W1" s="207"/>
-      <c r="X1" s="207"/>
-      <c r="Y1" s="207"/>
+      <c r="B1" s="212"/>
+      <c r="C1" s="212"/>
+      <c r="D1" s="212"/>
+      <c r="E1" s="212"/>
+      <c r="F1" s="212"/>
+      <c r="G1" s="212"/>
+      <c r="H1" s="212"/>
+      <c r="I1" s="212"/>
+      <c r="J1" s="212"/>
+      <c r="K1" s="212"/>
+      <c r="L1" s="212"/>
+      <c r="M1" s="212"/>
+      <c r="N1" s="212"/>
+      <c r="O1" s="212"/>
+      <c r="P1" s="212"/>
+      <c r="Q1" s="212"/>
+      <c r="R1" s="212"/>
+      <c r="S1" s="212"/>
+      <c r="T1" s="212"/>
+      <c r="U1" s="212"/>
+      <c r="V1" s="212"/>
+      <c r="W1" s="212"/>
+      <c r="X1" s="212"/>
+      <c r="Y1" s="212"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="81" t="s">
@@ -18448,10 +18480,10 @@
       <c r="Y17" s="74"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="208" t="s">
+      <c r="A18" s="213" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="208"/>
+      <c r="B18" s="213"/>
       <c r="C18" s="82">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
         <v>8428.35</v>
@@ -19204,10 +19236,10 @@
       <c r="Y34" s="76"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="208" t="s">
+      <c r="A35" s="213" t="s">
         <v>55</v>
       </c>
-      <c r="B35" s="208"/>
+      <c r="B35" s="213"/>
       <c r="C35" s="82">
         <f>SUM(C19:C34)</f>
         <v>10739.46</v>
@@ -19302,10 +19334,10 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="209" t="s">
+      <c r="A36" s="214" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="209"/>
+      <c r="B36" s="214"/>
       <c r="C36" s="72">
         <f>SUM(C18,C35)</f>
         <v>19167.810000000001</v>
@@ -19443,33 +19475,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="210" t="s">
+      <c r="A1" s="215" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="210"/>
-      <c r="C1" s="210"/>
-      <c r="D1" s="210"/>
-      <c r="E1" s="210"/>
-      <c r="F1" s="210"/>
-      <c r="G1" s="210"/>
-      <c r="H1" s="210"/>
-      <c r="I1" s="210"/>
-      <c r="J1" s="210"/>
-      <c r="K1" s="210"/>
-      <c r="L1" s="210"/>
-      <c r="M1" s="210"/>
-      <c r="N1" s="210"/>
-      <c r="O1" s="210"/>
-      <c r="P1" s="210"/>
-      <c r="Q1" s="210"/>
-      <c r="R1" s="210"/>
-      <c r="S1" s="210"/>
-      <c r="T1" s="210"/>
-      <c r="U1" s="210"/>
-      <c r="V1" s="210"/>
-      <c r="W1" s="210"/>
-      <c r="X1" s="210"/>
-      <c r="Y1" s="210"/>
+      <c r="B1" s="215"/>
+      <c r="C1" s="215"/>
+      <c r="D1" s="215"/>
+      <c r="E1" s="215"/>
+      <c r="F1" s="215"/>
+      <c r="G1" s="215"/>
+      <c r="H1" s="215"/>
+      <c r="I1" s="215"/>
+      <c r="J1" s="215"/>
+      <c r="K1" s="215"/>
+      <c r="L1" s="215"/>
+      <c r="M1" s="215"/>
+      <c r="N1" s="215"/>
+      <c r="O1" s="215"/>
+      <c r="P1" s="215"/>
+      <c r="Q1" s="215"/>
+      <c r="R1" s="215"/>
+      <c r="S1" s="215"/>
+      <c r="T1" s="215"/>
+      <c r="U1" s="215"/>
+      <c r="V1" s="215"/>
+      <c r="W1" s="215"/>
+      <c r="X1" s="215"/>
+      <c r="Y1" s="215"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="38" t="s">
@@ -20208,10 +20240,10 @@
       <c r="Y17" s="74"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="211" t="s">
+      <c r="A18" s="216" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="211"/>
+      <c r="B18" s="216"/>
       <c r="C18" s="60">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
         <v>7904</v>
@@ -20859,10 +20891,10 @@
       <c r="Y34" s="76"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="211" t="s">
+      <c r="A35" s="216" t="s">
         <v>55</v>
       </c>
-      <c r="B35" s="211"/>
+      <c r="B35" s="216"/>
       <c r="C35" s="60">
         <f>SUM(C19:C34)</f>
         <v>0</v>
@@ -20957,10 +20989,10 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="212" t="s">
+      <c r="A36" s="217" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="212"/>
+      <c r="B36" s="217"/>
       <c r="C36" s="80">
         <f>SUM(C18,C35)</f>
         <v>7904</v>
@@ -21100,34 +21132,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="60.75" customHeight="1">
-      <c r="A1" s="217" t="s">
+      <c r="A1" s="218" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="217"/>
-      <c r="C1" s="217"/>
-      <c r="D1" s="217"/>
-      <c r="E1" s="217"/>
-      <c r="F1" s="217"/>
-      <c r="G1" s="217"/>
-      <c r="H1" s="217"/>
-      <c r="I1" s="217"/>
-      <c r="J1" s="217"/>
-      <c r="K1" s="217"/>
-      <c r="L1" s="217"/>
-      <c r="M1" s="217"/>
-      <c r="N1" s="217"/>
-      <c r="O1" s="217"/>
-      <c r="P1" s="217"/>
-      <c r="Q1" s="217"/>
-      <c r="R1" s="217"/>
-      <c r="S1" s="217"/>
-      <c r="T1" s="217"/>
-      <c r="U1" s="217"/>
-      <c r="V1" s="217"/>
-      <c r="W1" s="217"/>
-      <c r="X1" s="217"/>
-      <c r="Y1" s="217"/>
-      <c r="Z1" s="217"/>
+      <c r="B1" s="218"/>
+      <c r="C1" s="218"/>
+      <c r="D1" s="218"/>
+      <c r="E1" s="218"/>
+      <c r="F1" s="218"/>
+      <c r="G1" s="218"/>
+      <c r="H1" s="218"/>
+      <c r="I1" s="218"/>
+      <c r="J1" s="218"/>
+      <c r="K1" s="218"/>
+      <c r="L1" s="218"/>
+      <c r="M1" s="218"/>
+      <c r="N1" s="218"/>
+      <c r="O1" s="218"/>
+      <c r="P1" s="218"/>
+      <c r="Q1" s="218"/>
+      <c r="R1" s="218"/>
+      <c r="S1" s="218"/>
+      <c r="T1" s="218"/>
+      <c r="U1" s="218"/>
+      <c r="V1" s="218"/>
+      <c r="W1" s="218"/>
+      <c r="X1" s="218"/>
+      <c r="Y1" s="218"/>
+      <c r="Z1" s="218"/>
     </row>
     <row r="2" spans="1:48" ht="45" customHeight="1">
       <c r="A2" s="38" t="s">
@@ -21280,7 +21312,7 @@
         <f>(94085+57723.67)</f>
         <v>151808.67000000001</v>
       </c>
-      <c r="Z3" s="215"/>
+      <c r="Z3" s="221"/>
     </row>
     <row r="4" spans="1:48" ht="15.75">
       <c r="A4" s="52">
@@ -21330,7 +21362,7 @@
       </c>
       <c r="X4" s="50"/>
       <c r="Y4" s="56"/>
-      <c r="Z4" s="215"/>
+      <c r="Z4" s="221"/>
     </row>
     <row r="5" spans="1:48" ht="15.75">
       <c r="A5" s="45">
@@ -21370,7 +21402,7 @@
       </c>
       <c r="X5" s="50"/>
       <c r="Y5" s="56"/>
-      <c r="Z5" s="215"/>
+      <c r="Z5" s="221"/>
     </row>
     <row r="6" spans="1:48" ht="15.75">
       <c r="A6" s="52">
@@ -21411,7 +21443,7 @@
       </c>
       <c r="X6" s="50"/>
       <c r="Y6" s="56"/>
-      <c r="Z6" s="215"/>
+      <c r="Z6" s="221"/>
     </row>
     <row r="7" spans="1:48" ht="15" customHeight="1">
       <c r="A7" s="45">
@@ -21455,7 +21487,7 @@
       </c>
       <c r="X7" s="50"/>
       <c r="Y7" s="56"/>
-      <c r="Z7" s="215"/>
+      <c r="Z7" s="221"/>
     </row>
     <row r="8" spans="1:48" ht="15.75">
       <c r="A8" s="52">
@@ -21497,14 +21529,14 @@
       </c>
       <c r="X8" s="50"/>
       <c r="Y8" s="56"/>
-      <c r="Z8" s="215"/>
-      <c r="AC8" s="216" t="s">
+      <c r="Z8" s="221"/>
+      <c r="AC8" s="222" t="s">
         <v>61</v>
       </c>
-      <c r="AD8" s="216"/>
-      <c r="AE8" s="216"/>
-      <c r="AF8" s="216"/>
-      <c r="AG8" s="216"/>
+      <c r="AD8" s="222"/>
+      <c r="AE8" s="222"/>
+      <c r="AF8" s="222"/>
+      <c r="AG8" s="222"/>
     </row>
     <row r="9" spans="1:48" ht="15.75">
       <c r="A9" s="45">
@@ -21543,12 +21575,12 @@
       </c>
       <c r="X9" s="50"/>
       <c r="Y9" s="56"/>
-      <c r="Z9" s="215"/>
-      <c r="AC9" s="216"/>
-      <c r="AD9" s="216"/>
-      <c r="AE9" s="216"/>
-      <c r="AF9" s="216"/>
-      <c r="AG9" s="216"/>
+      <c r="Z9" s="221"/>
+      <c r="AC9" s="222"/>
+      <c r="AD9" s="222"/>
+      <c r="AE9" s="222"/>
+      <c r="AF9" s="222"/>
+      <c r="AG9" s="222"/>
     </row>
     <row r="10" spans="1:48" ht="15.75">
       <c r="A10" s="52">
@@ -21592,12 +21624,12 @@
       </c>
       <c r="X10" s="50"/>
       <c r="Y10" s="56"/>
-      <c r="Z10" s="215"/>
-      <c r="AC10" s="216"/>
-      <c r="AD10" s="216"/>
-      <c r="AE10" s="216"/>
-      <c r="AF10" s="216"/>
-      <c r="AG10" s="216"/>
+      <c r="Z10" s="221"/>
+      <c r="AC10" s="222"/>
+      <c r="AD10" s="222"/>
+      <c r="AE10" s="222"/>
+      <c r="AF10" s="222"/>
+      <c r="AG10" s="222"/>
     </row>
     <row r="11" spans="1:48" ht="15.75">
       <c r="A11" s="45">
@@ -21637,13 +21669,13 @@
       </c>
       <c r="X11" s="50"/>
       <c r="Y11" s="56"/>
-      <c r="Z11" s="215"/>
-      <c r="AC11" s="213" t="s">
+      <c r="Z11" s="221"/>
+      <c r="AC11" s="219" t="s">
         <v>62</v>
       </c>
-      <c r="AD11" s="213"/>
-      <c r="AE11" s="213"/>
-      <c r="AF11" s="213"/>
+      <c r="AD11" s="219"/>
+      <c r="AE11" s="219"/>
+      <c r="AF11" s="219"/>
       <c r="AG11" s="57">
         <f>Y3+Y14+Y21</f>
         <v>226341.31</v>
@@ -21684,13 +21716,13 @@
       </c>
       <c r="X12" s="50"/>
       <c r="Y12" s="56"/>
-      <c r="Z12" s="215"/>
-      <c r="AC12" s="213" t="s">
+      <c r="Z12" s="221"/>
+      <c r="AC12" s="219" t="s">
         <v>2</v>
       </c>
-      <c r="AD12" s="213"/>
-      <c r="AE12" s="213"/>
-      <c r="AF12" s="213"/>
+      <c r="AD12" s="219"/>
+      <c r="AE12" s="219"/>
+      <c r="AF12" s="219"/>
       <c r="AG12" s="57">
         <f>Y27</f>
         <v>20000</v>
@@ -21735,13 +21767,13 @@
       </c>
       <c r="X13" s="50"/>
       <c r="Y13" s="56"/>
-      <c r="Z13" s="215"/>
-      <c r="AC13" s="213" t="s">
+      <c r="Z13" s="221"/>
+      <c r="AC13" s="219" t="s">
         <v>63</v>
       </c>
-      <c r="AD13" s="213"/>
-      <c r="AE13" s="213"/>
-      <c r="AF13" s="213"/>
+      <c r="AD13" s="219"/>
+      <c r="AE13" s="219"/>
+      <c r="AF13" s="219"/>
       <c r="AG13" s="57">
         <f>Y17+Y19</f>
         <v>25000</v>
@@ -21787,13 +21819,13 @@
       <c r="Y14" s="51">
         <v>37634</v>
       </c>
-      <c r="Z14" s="215"/>
-      <c r="AC14" s="213" t="s">
+      <c r="Z14" s="221"/>
+      <c r="AC14" s="219" t="s">
         <v>64</v>
       </c>
-      <c r="AD14" s="213"/>
-      <c r="AE14" s="213"/>
-      <c r="AF14" s="213"/>
+      <c r="AD14" s="219"/>
+      <c r="AE14" s="219"/>
+      <c r="AF14" s="219"/>
       <c r="AG14" s="57">
         <f>W38</f>
         <v>177971.36</v>
@@ -21843,13 +21875,13 @@
       </c>
       <c r="X15" s="50"/>
       <c r="Y15" s="56"/>
-      <c r="Z15" s="215"/>
-      <c r="AC15" s="213" t="s">
+      <c r="Z15" s="221"/>
+      <c r="AC15" s="219" t="s">
         <v>65</v>
       </c>
-      <c r="AD15" s="213"/>
-      <c r="AE15" s="213"/>
-      <c r="AF15" s="213"/>
+      <c r="AD15" s="219"/>
+      <c r="AE15" s="219"/>
+      <c r="AF15" s="219"/>
       <c r="AG15" s="57">
         <f>SUM(C38:H38)</f>
         <v>55416.04</v>
@@ -21898,13 +21930,13 @@
       </c>
       <c r="X16" s="50"/>
       <c r="Y16" s="56"/>
-      <c r="Z16" s="215"/>
-      <c r="AC16" s="213" t="s">
+      <c r="Z16" s="221"/>
+      <c r="AC16" s="219" t="s">
         <v>85</v>
       </c>
-      <c r="AD16" s="213"/>
-      <c r="AE16" s="213"/>
-      <c r="AF16" s="213"/>
+      <c r="AD16" s="219"/>
+      <c r="AE16" s="219"/>
+      <c r="AF16" s="219"/>
       <c r="AG16" s="57">
         <f>Q38</f>
         <v>27468.98</v>
@@ -21960,7 +21992,7 @@
       <c r="Y17" s="59">
         <v>15000</v>
       </c>
-      <c r="Z17" s="215"/>
+      <c r="Z17" s="221"/>
     </row>
     <row r="18" spans="1:28" ht="15.75">
       <c r="A18" s="52">
@@ -22001,7 +22033,7 @@
       </c>
       <c r="X18" s="50"/>
       <c r="Y18" s="56"/>
-      <c r="Z18" s="215"/>
+      <c r="Z18" s="221"/>
     </row>
     <row r="19" spans="1:28" ht="15.75">
       <c r="A19" s="45">
@@ -22045,13 +22077,13 @@
       <c r="Y19" s="59">
         <v>10000</v>
       </c>
-      <c r="Z19" s="215"/>
+      <c r="Z19" s="221"/>
     </row>
     <row r="20" spans="1:28" ht="14.25" customHeight="1">
-      <c r="A20" s="211" t="s">
+      <c r="A20" s="216" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="211"/>
+      <c r="B20" s="216"/>
       <c r="C20" s="60">
         <f t="shared" ref="C20:V20" si="1">SUM(C3:C17)</f>
         <v>10942.99</v>
@@ -22194,7 +22226,7 @@
       <c r="Y21" s="51">
         <v>36898.639999999999</v>
       </c>
-      <c r="Z21" s="215"/>
+      <c r="Z21" s="221"/>
     </row>
     <row r="22" spans="1:28" ht="15.75">
       <c r="A22" s="52">
@@ -22240,7 +22272,7 @@
         <v>23662.84</v>
       </c>
       <c r="Y22" s="56"/>
-      <c r="Z22" s="215"/>
+      <c r="Z22" s="221"/>
       <c r="AB22" s="29"/>
     </row>
     <row r="23" spans="1:28" ht="15.75">
@@ -22284,7 +22316,7 @@
       </c>
       <c r="X23" s="50"/>
       <c r="Y23" s="56"/>
-      <c r="Z23" s="215"/>
+      <c r="Z23" s="221"/>
     </row>
     <row r="24" spans="1:28" ht="15.75">
       <c r="A24" s="52">
@@ -22328,7 +22360,7 @@
       </c>
       <c r="X24" s="50"/>
       <c r="Y24" s="56"/>
-      <c r="Z24" s="215"/>
+      <c r="Z24" s="221"/>
     </row>
     <row r="25" spans="1:28" ht="15.75">
       <c r="A25" s="45">
@@ -22372,7 +22404,7 @@
       </c>
       <c r="X25" s="50"/>
       <c r="Y25" s="56"/>
-      <c r="Z25" s="215"/>
+      <c r="Z25" s="221"/>
     </row>
     <row r="26" spans="1:28" ht="15.75">
       <c r="A26" s="52">
@@ -22411,7 +22443,7 @@
       </c>
       <c r="X26" s="50"/>
       <c r="Y26" s="56"/>
-      <c r="Z26" s="215"/>
+      <c r="Z26" s="221"/>
     </row>
     <row r="27" spans="1:28" ht="15.75">
       <c r="A27" s="45">
@@ -22456,7 +22488,7 @@
       <c r="Y27" s="66">
         <v>20000</v>
       </c>
-      <c r="Z27" s="215"/>
+      <c r="Z27" s="221"/>
     </row>
     <row r="28" spans="1:28" ht="15.75">
       <c r="A28" s="52">
@@ -22498,7 +22530,7 @@
       </c>
       <c r="X28" s="50"/>
       <c r="Y28" s="56"/>
-      <c r="Z28" s="215"/>
+      <c r="Z28" s="221"/>
     </row>
     <row r="29" spans="1:28" ht="15.75">
       <c r="A29" s="45">
@@ -22537,7 +22569,7 @@
       </c>
       <c r="X29" s="50"/>
       <c r="Y29" s="56"/>
-      <c r="Z29" s="215"/>
+      <c r="Z29" s="221"/>
     </row>
     <row r="30" spans="1:28" ht="15.75">
       <c r="A30" s="52">
@@ -22577,7 +22609,7 @@
       </c>
       <c r="X30" s="50"/>
       <c r="Y30" s="56"/>
-      <c r="Z30" s="215"/>
+      <c r="Z30" s="221"/>
     </row>
     <row r="31" spans="1:28" ht="15.75">
       <c r="A31" s="45">
@@ -22612,7 +22644,7 @@
       </c>
       <c r="X31" s="50"/>
       <c r="Y31" s="56"/>
-      <c r="Z31" s="215"/>
+      <c r="Z31" s="221"/>
     </row>
     <row r="32" spans="1:28" ht="15.75">
       <c r="A32" s="52">
@@ -22647,7 +22679,7 @@
       </c>
       <c r="X32" s="50"/>
       <c r="Y32" s="56"/>
-      <c r="Z32" s="215"/>
+      <c r="Z32" s="221"/>
     </row>
     <row r="33" spans="1:26" ht="15.75">
       <c r="A33" s="45">
@@ -22684,7 +22716,7 @@
       <c r="Y33" s="67">
         <v>10000</v>
       </c>
-      <c r="Z33" s="215"/>
+      <c r="Z33" s="221"/>
     </row>
     <row r="34" spans="1:26" ht="15.75">
       <c r="A34" s="52">
@@ -22723,7 +22755,7 @@
       </c>
       <c r="X34" s="50"/>
       <c r="Y34" s="56"/>
-      <c r="Z34" s="215"/>
+      <c r="Z34" s="221"/>
     </row>
     <row r="35" spans="1:26" ht="15.75">
       <c r="A35" s="45">
@@ -22767,7 +22799,7 @@
       </c>
       <c r="X35" s="50"/>
       <c r="Y35" s="56"/>
-      <c r="Z35" s="215"/>
+      <c r="Z35" s="221"/>
     </row>
     <row r="36" spans="1:26" ht="15.75">
       <c r="A36" s="52">
@@ -22808,13 +22840,13 @@
       </c>
       <c r="X36" s="50"/>
       <c r="Y36" s="56"/>
-      <c r="Z36" s="215"/>
+      <c r="Z36" s="221"/>
     </row>
     <row r="37" spans="1:26">
-      <c r="A37" s="211" t="s">
+      <c r="A37" s="216" t="s">
         <v>55</v>
       </c>
-      <c r="B37" s="211"/>
+      <c r="B37" s="216"/>
       <c r="C37" s="60">
         <f>SUM(C21:C36)</f>
         <v>3393</v>
@@ -22913,10 +22945,10 @@
       </c>
     </row>
     <row r="38" spans="1:26" ht="31.5" customHeight="1">
-      <c r="A38" s="214" t="s">
+      <c r="A38" s="220" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="214"/>
+      <c r="B38" s="220"/>
       <c r="C38" s="69">
         <f>SUM(C20,C37)</f>
         <v>14335.99</v>
@@ -23028,11 +23060,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:Z1"/>
-    <mergeCell ref="AC11:AF11"/>
-    <mergeCell ref="AC12:AF12"/>
-    <mergeCell ref="AC13:AF13"/>
-    <mergeCell ref="AC14:AF14"/>
     <mergeCell ref="AC15:AF15"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A37:B37"/>
@@ -23041,6 +23068,11 @@
     <mergeCell ref="Z21:Z36"/>
     <mergeCell ref="AC8:AG10"/>
     <mergeCell ref="AC16:AF16"/>
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="AC11:AF11"/>
+    <mergeCell ref="AC12:AF12"/>
+    <mergeCell ref="AC13:AF13"/>
+    <mergeCell ref="AC14:AF14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -23299,7 +23331,7 @@
         <f>37635+40252.26+18817.85</f>
         <v>96705.11</v>
       </c>
-      <c r="AD4" s="221"/>
+      <c r="AD4" s="233"/>
     </row>
     <row r="5" spans="1:52" ht="15.75">
       <c r="A5" s="17">
@@ -23349,7 +23381,7 @@
         <v>16503.13</v>
       </c>
       <c r="AC5" s="21"/>
-      <c r="AD5" s="221"/>
+      <c r="AD5" s="233"/>
     </row>
     <row r="6" spans="1:52" ht="15.75">
       <c r="A6" s="11">
@@ -23392,7 +23424,7 @@
         <v>996.61</v>
       </c>
       <c r="AC6" s="21"/>
-      <c r="AD6" s="221"/>
+      <c r="AD6" s="233"/>
     </row>
     <row r="7" spans="1:52" ht="15.75">
       <c r="A7" s="17">
@@ -23445,7 +23477,7 @@
         <v>5968</v>
       </c>
       <c r="AC7" s="21"/>
-      <c r="AD7" s="221"/>
+      <c r="AD7" s="233"/>
     </row>
     <row r="8" spans="1:52" ht="15" customHeight="1">
       <c r="A8" s="11">
@@ -23491,7 +23523,7 @@
         <v>12168.98</v>
       </c>
       <c r="AC8" s="21"/>
-      <c r="AD8" s="221"/>
+      <c r="AD8" s="233"/>
     </row>
     <row r="9" spans="1:52" ht="15.75">
       <c r="A9" s="17">
@@ -23539,7 +23571,7 @@
         <v>5970</v>
       </c>
       <c r="AC9" s="21"/>
-      <c r="AD9" s="221"/>
+      <c r="AD9" s="233"/>
     </row>
     <row r="10" spans="1:52" ht="15.75">
       <c r="A10" s="11">
@@ -23587,7 +23619,7 @@
         <v>3257</v>
       </c>
       <c r="AC10" s="21"/>
-      <c r="AD10" s="221"/>
+      <c r="AD10" s="233"/>
     </row>
     <row r="11" spans="1:52" ht="15.75">
       <c r="A11" s="17">
@@ -23631,14 +23663,14 @@
         <v>1034</v>
       </c>
       <c r="AC11" s="21"/>
-      <c r="AD11" s="221"/>
-      <c r="AH11" s="222" t="s">
+      <c r="AD11" s="233"/>
+      <c r="AH11" s="234" t="s">
         <v>83</v>
       </c>
-      <c r="AI11" s="222"/>
-      <c r="AJ11" s="222"/>
-      <c r="AK11" s="222"/>
-      <c r="AL11" s="222"/>
+      <c r="AI11" s="234"/>
+      <c r="AJ11" s="234"/>
+      <c r="AK11" s="234"/>
+      <c r="AL11" s="234"/>
     </row>
     <row r="12" spans="1:52" ht="15.75">
       <c r="A12" s="11">
@@ -23685,12 +23717,12 @@
         <v>3586</v>
       </c>
       <c r="AC12" s="21"/>
-      <c r="AD12" s="221"/>
-      <c r="AH12" s="222"/>
-      <c r="AI12" s="222"/>
-      <c r="AJ12" s="222"/>
-      <c r="AK12" s="222"/>
-      <c r="AL12" s="222"/>
+      <c r="AD12" s="233"/>
+      <c r="AH12" s="234"/>
+      <c r="AI12" s="234"/>
+      <c r="AJ12" s="234"/>
+      <c r="AK12" s="234"/>
+      <c r="AL12" s="234"/>
     </row>
     <row r="13" spans="1:52" ht="15.75">
       <c r="A13" s="17">
@@ -23737,12 +23769,12 @@
         <v>5889</v>
       </c>
       <c r="AC13" s="21"/>
-      <c r="AD13" s="221"/>
-      <c r="AH13" s="222"/>
-      <c r="AI13" s="222"/>
-      <c r="AJ13" s="222"/>
-      <c r="AK13" s="222"/>
-      <c r="AL13" s="222"/>
+      <c r="AD13" s="233"/>
+      <c r="AH13" s="234"/>
+      <c r="AI13" s="234"/>
+      <c r="AJ13" s="234"/>
+      <c r="AK13" s="234"/>
+      <c r="AL13" s="234"/>
     </row>
     <row r="14" spans="1:52" ht="18">
       <c r="A14" s="11">
@@ -23788,13 +23820,13 @@
         <v>7092.93</v>
       </c>
       <c r="AC14" s="21"/>
-      <c r="AD14" s="221"/>
-      <c r="AH14" s="218" t="s">
+      <c r="AD14" s="233"/>
+      <c r="AH14" s="230" t="s">
         <v>62</v>
       </c>
-      <c r="AI14" s="218"/>
-      <c r="AJ14" s="218"/>
-      <c r="AK14" s="218"/>
+      <c r="AI14" s="230"/>
+      <c r="AJ14" s="230"/>
+      <c r="AK14" s="230"/>
       <c r="AL14" s="22">
         <f>AC4+AC20</f>
         <v>133443.15</v>
@@ -23852,13 +23884,13 @@
         <v>6644.28</v>
       </c>
       <c r="AC15" s="16"/>
-      <c r="AD15" s="221"/>
-      <c r="AH15" s="218" t="s">
+      <c r="AD15" s="233"/>
+      <c r="AH15" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="AI15" s="218"/>
-      <c r="AJ15" s="218"/>
-      <c r="AK15" s="218"/>
+      <c r="AI15" s="230"/>
+      <c r="AJ15" s="230"/>
+      <c r="AK15" s="230"/>
       <c r="AL15" s="22">
         <f>AC29</f>
         <v>1000</v>
@@ -23913,13 +23945,13 @@
         <v>5105.1899999999996</v>
       </c>
       <c r="AC16" s="21"/>
-      <c r="AD16" s="221"/>
-      <c r="AH16" s="218" t="s">
+      <c r="AD16" s="233"/>
+      <c r="AH16" s="230" t="s">
         <v>63</v>
       </c>
-      <c r="AI16" s="218"/>
-      <c r="AJ16" s="218"/>
-      <c r="AK16" s="218"/>
+      <c r="AI16" s="230"/>
+      <c r="AJ16" s="230"/>
+      <c r="AK16" s="230"/>
       <c r="AL16" s="22">
         <f>AC21+AC34</f>
         <v>11000</v>
@@ -23964,13 +23996,13 @@
         <v>280.97000000000003</v>
       </c>
       <c r="AC17" s="21"/>
-      <c r="AD17" s="221"/>
-      <c r="AH17" s="218" t="s">
+      <c r="AD17" s="233"/>
+      <c r="AH17" s="230" t="s">
         <v>64</v>
       </c>
-      <c r="AI17" s="218"/>
-      <c r="AJ17" s="218"/>
-      <c r="AK17" s="218"/>
+      <c r="AI17" s="230"/>
+      <c r="AJ17" s="230"/>
+      <c r="AK17" s="230"/>
       <c r="AL17" s="22">
         <f>AB36</f>
         <v>146501.73000000001</v>
@@ -24019,23 +24051,23 @@
         <v>956.98</v>
       </c>
       <c r="AC18" s="21"/>
-      <c r="AD18" s="221"/>
-      <c r="AH18" s="218" t="s">
+      <c r="AD18" s="233"/>
+      <c r="AH18" s="230" t="s">
         <v>65</v>
       </c>
-      <c r="AI18" s="218"/>
-      <c r="AJ18" s="218"/>
-      <c r="AK18" s="218"/>
+      <c r="AI18" s="230"/>
+      <c r="AJ18" s="230"/>
+      <c r="AK18" s="230"/>
       <c r="AL18" s="22">
         <f>SUM(C36:K36)</f>
         <v>56967.92</v>
       </c>
     </row>
     <row r="19" spans="1:38" ht="19.5" customHeight="1">
-      <c r="A19" s="219" t="s">
+      <c r="A19" s="231" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="219"/>
+      <c r="B19" s="231"/>
       <c r="C19" s="23">
         <f>SUM(C4:C18)</f>
         <v>1403.89</v>
@@ -24148,12 +24180,12 @@
         <f>AC19-AB19</f>
         <v>4280.0900000000101</v>
       </c>
-      <c r="AH19" s="218" t="s">
+      <c r="AH19" s="230" t="s">
         <v>84</v>
       </c>
-      <c r="AI19" s="218"/>
-      <c r="AJ19" s="218"/>
-      <c r="AK19" s="218"/>
+      <c r="AI19" s="230"/>
+      <c r="AJ19" s="230"/>
+      <c r="AK19" s="230"/>
       <c r="AL19" s="22">
         <f>SUM(L36:Q36)</f>
         <v>31394.13</v>
@@ -24214,13 +24246,13 @@
       <c r="AC20" s="16">
         <v>36738.04</v>
       </c>
-      <c r="AD20" s="221"/>
-      <c r="AH20" s="218" t="s">
+      <c r="AD20" s="233"/>
+      <c r="AH20" s="230" t="s">
         <v>85</v>
       </c>
-      <c r="AI20" s="218"/>
-      <c r="AJ20" s="218"/>
-      <c r="AK20" s="218"/>
+      <c r="AI20" s="230"/>
+      <c r="AJ20" s="230"/>
+      <c r="AK20" s="230"/>
       <c r="AL20" s="22">
         <f>W36</f>
         <v>35678.97</v>
@@ -24275,14 +24307,14 @@
       <c r="AC21" s="37">
         <v>10000</v>
       </c>
-      <c r="AD21" s="221"/>
+      <c r="AD21" s="233"/>
       <c r="AF21" s="29"/>
-      <c r="AH21" s="218" t="s">
+      <c r="AH21" s="230" t="s">
         <v>86</v>
       </c>
-      <c r="AI21" s="218"/>
-      <c r="AJ21" s="218"/>
-      <c r="AK21" s="218"/>
+      <c r="AI21" s="230"/>
+      <c r="AJ21" s="230"/>
+      <c r="AK21" s="230"/>
       <c r="AL21" s="22">
         <f>SUM(U36:V36)</f>
         <v>11008.46</v>
@@ -24325,13 +24357,13 @@
         <v>0</v>
       </c>
       <c r="AC22" s="21"/>
-      <c r="AD22" s="221"/>
-      <c r="AH22" s="218" t="s">
+      <c r="AD22" s="233"/>
+      <c r="AH22" s="230" t="s">
         <v>32</v>
       </c>
-      <c r="AI22" s="218"/>
-      <c r="AJ22" s="218"/>
-      <c r="AK22" s="218"/>
+      <c r="AI22" s="230"/>
+      <c r="AJ22" s="230"/>
+      <c r="AK22" s="230"/>
       <c r="AL22" s="22">
         <f>T36</f>
         <v>0</v>
@@ -24386,13 +24418,13 @@
         <v>6881.28</v>
       </c>
       <c r="AC23" s="21"/>
-      <c r="AD23" s="221"/>
-      <c r="AH23" s="218" t="s">
+      <c r="AD23" s="233"/>
+      <c r="AH23" s="230" t="s">
         <v>87</v>
       </c>
-      <c r="AI23" s="218"/>
-      <c r="AJ23" s="218"/>
-      <c r="AK23" s="218"/>
+      <c r="AI23" s="230"/>
+      <c r="AJ23" s="230"/>
+      <c r="AK23" s="230"/>
       <c r="AL23" s="22">
         <f>X36</f>
         <v>5267.98</v>
@@ -24447,7 +24479,7 @@
         <v>6126.69</v>
       </c>
       <c r="AC24" s="21"/>
-      <c r="AD24" s="221"/>
+      <c r="AD24" s="233"/>
     </row>
     <row r="25" spans="1:38" ht="15.75">
       <c r="A25" s="17">
@@ -24491,7 +24523,7 @@
         <v>7750</v>
       </c>
       <c r="AC25" s="21"/>
-      <c r="AD25" s="221"/>
+      <c r="AD25" s="233"/>
     </row>
     <row r="26" spans="1:38" ht="15.75">
       <c r="A26" s="11">
@@ -24538,7 +24570,7 @@
         <v>2803</v>
       </c>
       <c r="AC26" s="16"/>
-      <c r="AD26" s="221"/>
+      <c r="AD26" s="233"/>
     </row>
     <row r="27" spans="1:38" ht="15.75">
       <c r="A27" s="17">
@@ -24586,7 +24618,7 @@
         <v>2088.96</v>
       </c>
       <c r="AC27" s="21"/>
-      <c r="AD27" s="221"/>
+      <c r="AD27" s="233"/>
     </row>
     <row r="28" spans="1:38" ht="15.75">
       <c r="A28" s="11">
@@ -24632,7 +24664,7 @@
         <v>3468</v>
       </c>
       <c r="AC28" s="21"/>
-      <c r="AD28" s="221"/>
+      <c r="AD28" s="233"/>
     </row>
     <row r="29" spans="1:38" ht="15.75">
       <c r="A29" s="17">
@@ -24685,7 +24717,7 @@
       <c r="AC29" s="21">
         <v>1000</v>
       </c>
-      <c r="AD29" s="221"/>
+      <c r="AD29" s="233"/>
     </row>
     <row r="30" spans="1:38" ht="15.75">
       <c r="A30" s="11">
@@ -24733,7 +24765,7 @@
         <v>4016.5</v>
       </c>
       <c r="AC30" s="21"/>
-      <c r="AD30" s="221"/>
+      <c r="AD30" s="233"/>
     </row>
     <row r="31" spans="1:38" ht="15.75">
       <c r="A31" s="17">
@@ -24777,7 +24809,7 @@
         <v>2801.78</v>
       </c>
       <c r="AC31" s="21"/>
-      <c r="AD31" s="221"/>
+      <c r="AD31" s="233"/>
     </row>
     <row r="32" spans="1:38" ht="15.75">
       <c r="A32" s="11">
@@ -24826,7 +24858,7 @@
         <v>3807.11</v>
       </c>
       <c r="AC32" s="21"/>
-      <c r="AD32" s="221"/>
+      <c r="AD32" s="233"/>
     </row>
     <row r="33" spans="1:30" ht="15.75">
       <c r="A33" s="17">
@@ -24870,7 +24902,7 @@
         <v>675.44</v>
       </c>
       <c r="AC33" s="21"/>
-      <c r="AD33" s="221"/>
+      <c r="AD33" s="233"/>
     </row>
     <row r="34" spans="1:30" ht="15.75">
       <c r="A34" s="11">
@@ -24914,13 +24946,13 @@
       <c r="AC34" s="37">
         <v>1000</v>
       </c>
-      <c r="AD34" s="221"/>
+      <c r="AD34" s="233"/>
     </row>
     <row r="35" spans="1:30" ht="14.25" customHeight="1">
-      <c r="A35" s="219" t="s">
+      <c r="A35" s="231" t="s">
         <v>55</v>
       </c>
-      <c r="B35" s="219"/>
+      <c r="B35" s="231"/>
       <c r="C35" s="23">
         <f t="shared" ref="C35:AC35" si="3">SUM(C20:C34)</f>
         <v>2169.6999999999998</v>
@@ -25035,10 +25067,10 @@
       </c>
     </row>
     <row r="36" spans="1:30" ht="31.5" customHeight="1">
-      <c r="A36" s="220" t="s">
+      <c r="A36" s="232" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="220"/>
+      <c r="B36" s="232"/>
       <c r="C36" s="31">
         <f>SUM(C19,C35)</f>
         <v>3573.59</v>
@@ -25169,12 +25201,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:K2"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="AH23:AK23"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="A36:B36"/>
@@ -25191,6 +25217,12 @@
     <mergeCell ref="AH16:AK16"/>
     <mergeCell ref="AH17:AK17"/>
     <mergeCell ref="AH18:AK18"/>
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -25447,7 +25479,7 @@
         <f>66577.47+18817</f>
         <v>85394.47</v>
       </c>
-      <c r="AD4" s="221"/>
+      <c r="AD4" s="233"/>
     </row>
     <row r="5" spans="1:52" ht="15.75">
       <c r="A5" s="17">
@@ -25502,7 +25534,7 @@
         <v>7116</v>
       </c>
       <c r="AC5" s="165"/>
-      <c r="AD5" s="221"/>
+      <c r="AD5" s="233"/>
     </row>
     <row r="6" spans="1:52" ht="15.75">
       <c r="A6" s="11">
@@ -25550,7 +25582,7 @@
         <v>17146</v>
       </c>
       <c r="AC6" s="165"/>
-      <c r="AD6" s="221"/>
+      <c r="AD6" s="233"/>
     </row>
     <row r="7" spans="1:52" ht="15.75">
       <c r="A7" s="17">
@@ -25607,7 +25639,7 @@
         <v>6206.84</v>
       </c>
       <c r="AC7" s="165"/>
-      <c r="AD7" s="221"/>
+      <c r="AD7" s="233"/>
     </row>
     <row r="8" spans="1:52" ht="15" customHeight="1">
       <c r="A8" s="11">
@@ -25666,7 +25698,7 @@
         <v>8204</v>
       </c>
       <c r="AC8" s="165"/>
-      <c r="AD8" s="221"/>
+      <c r="AD8" s="233"/>
     </row>
     <row r="9" spans="1:52" ht="15.75">
       <c r="A9" s="17">
@@ -25715,7 +25747,7 @@
         <v>8276</v>
       </c>
       <c r="AC9" s="165"/>
-      <c r="AD9" s="221"/>
+      <c r="AD9" s="233"/>
     </row>
     <row r="10" spans="1:52" ht="15.75">
       <c r="A10" s="11">
@@ -25763,7 +25795,7 @@
       <c r="AC10" s="165">
         <v>28225.5</v>
       </c>
-      <c r="AD10" s="221"/>
+      <c r="AD10" s="233"/>
     </row>
     <row r="11" spans="1:52" ht="15.75">
       <c r="A11" s="17">
@@ -25813,14 +25845,14 @@
         <v>5638.53</v>
       </c>
       <c r="AC11" s="165"/>
-      <c r="AD11" s="221"/>
-      <c r="AH11" s="222" t="s">
+      <c r="AD11" s="233"/>
+      <c r="AH11" s="234" t="s">
         <v>83</v>
       </c>
-      <c r="AI11" s="222"/>
-      <c r="AJ11" s="222"/>
-      <c r="AK11" s="222"/>
-      <c r="AL11" s="222"/>
+      <c r="AI11" s="234"/>
+      <c r="AJ11" s="234"/>
+      <c r="AK11" s="234"/>
+      <c r="AL11" s="234"/>
     </row>
     <row r="12" spans="1:52" ht="15.75">
       <c r="A12" s="11">
@@ -25874,12 +25906,12 @@
         <v>33365</v>
       </c>
       <c r="AC12" s="165"/>
-      <c r="AD12" s="221"/>
-      <c r="AH12" s="222"/>
-      <c r="AI12" s="222"/>
-      <c r="AJ12" s="222"/>
-      <c r="AK12" s="222"/>
-      <c r="AL12" s="222"/>
+      <c r="AD12" s="233"/>
+      <c r="AH12" s="234"/>
+      <c r="AI12" s="234"/>
+      <c r="AJ12" s="234"/>
+      <c r="AK12" s="234"/>
+      <c r="AL12" s="234"/>
     </row>
     <row r="13" spans="1:52" ht="15.75">
       <c r="A13" s="17">
@@ -25937,12 +25969,12 @@
         <v>10965.96</v>
       </c>
       <c r="AC13" s="165"/>
-      <c r="AD13" s="221"/>
-      <c r="AH13" s="222"/>
-      <c r="AI13" s="222"/>
-      <c r="AJ13" s="222"/>
-      <c r="AK13" s="222"/>
-      <c r="AL13" s="222"/>
+      <c r="AD13" s="233"/>
+      <c r="AH13" s="234"/>
+      <c r="AI13" s="234"/>
+      <c r="AJ13" s="234"/>
+      <c r="AK13" s="234"/>
+      <c r="AL13" s="234"/>
     </row>
     <row r="14" spans="1:52" ht="18">
       <c r="A14" s="11">
@@ -25990,13 +26022,13 @@
         <v>1614.53</v>
       </c>
       <c r="AC14" s="165"/>
-      <c r="AD14" s="221"/>
-      <c r="AH14" s="218" t="s">
+      <c r="AD14" s="233"/>
+      <c r="AH14" s="230" t="s">
         <v>62</v>
       </c>
-      <c r="AI14" s="218"/>
-      <c r="AJ14" s="218"/>
-      <c r="AK14" s="218"/>
+      <c r="AI14" s="230"/>
+      <c r="AJ14" s="230"/>
+      <c r="AK14" s="230"/>
       <c r="AL14" s="22">
         <f>AC4+AC19+AC23+AC10</f>
         <v>287751.42</v>
@@ -26054,13 +26086,13 @@
         <v>6960.82</v>
       </c>
       <c r="AC15" s="163"/>
-      <c r="AD15" s="221"/>
-      <c r="AH15" s="218" t="s">
+      <c r="AD15" s="233"/>
+      <c r="AH15" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="AI15" s="218"/>
-      <c r="AJ15" s="218"/>
-      <c r="AK15" s="218"/>
+      <c r="AI15" s="230"/>
+      <c r="AJ15" s="230"/>
+      <c r="AK15" s="230"/>
       <c r="AL15" s="22">
         <f>AC20</f>
         <v>1000</v>
@@ -26114,13 +26146,13 @@
       <c r="AC16" s="167">
         <v>5000</v>
       </c>
-      <c r="AD16" s="221"/>
-      <c r="AH16" s="218" t="s">
+      <c r="AD16" s="233"/>
+      <c r="AH16" s="230" t="s">
         <v>63</v>
       </c>
-      <c r="AI16" s="218"/>
-      <c r="AJ16" s="218"/>
-      <c r="AK16" s="218"/>
+      <c r="AI16" s="230"/>
+      <c r="AJ16" s="230"/>
+      <c r="AK16" s="230"/>
       <c r="AL16" s="22">
         <f>AC16+AC28+AC34+AC35</f>
         <v>60000</v>
@@ -26178,23 +26210,23 @@
         <v>5002</v>
       </c>
       <c r="AC17" s="163"/>
-      <c r="AD17" s="221"/>
-      <c r="AH17" s="230" t="s">
+      <c r="AD17" s="233"/>
+      <c r="AH17" s="235" t="s">
         <v>67</v>
       </c>
-      <c r="AI17" s="231"/>
-      <c r="AJ17" s="231"/>
-      <c r="AK17" s="232"/>
+      <c r="AI17" s="236"/>
+      <c r="AJ17" s="236"/>
+      <c r="AK17" s="237"/>
       <c r="AL17" s="22">
         <f>SUM(C37:K37)</f>
         <v>121331.08</v>
       </c>
     </row>
     <row r="18" spans="1:38" ht="19.5" customHeight="1">
-      <c r="A18" s="236" t="s">
+      <c r="A18" s="241" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="236"/>
+      <c r="B18" s="241"/>
       <c r="C18" s="23">
         <f>SUM(C4:C17)</f>
         <v>129.99</v>
@@ -26307,12 +26339,12 @@
         <f>AC18-AB18</f>
         <v>-900.67000000001281</v>
       </c>
-      <c r="AH18" s="218" t="s">
+      <c r="AH18" s="230" t="s">
         <v>84</v>
       </c>
-      <c r="AI18" s="218"/>
-      <c r="AJ18" s="218"/>
-      <c r="AK18" s="218"/>
+      <c r="AI18" s="230"/>
+      <c r="AJ18" s="230"/>
+      <c r="AK18" s="230"/>
       <c r="AL18" s="22">
         <f>SUM(L37:Q37)</f>
         <v>35695</v>
@@ -26366,13 +26398,13 @@
       <c r="AC19" s="16">
         <v>38575.449999999997</v>
       </c>
-      <c r="AD19" s="221"/>
-      <c r="AH19" s="218" t="s">
+      <c r="AD19" s="233"/>
+      <c r="AH19" s="230" t="s">
         <v>85</v>
       </c>
-      <c r="AI19" s="218"/>
-      <c r="AJ19" s="218"/>
-      <c r="AK19" s="218"/>
+      <c r="AI19" s="230"/>
+      <c r="AJ19" s="230"/>
+      <c r="AK19" s="230"/>
       <c r="AL19" s="22">
         <f>W37</f>
         <v>38934</v>
@@ -26429,14 +26461,14 @@
       <c r="AC20" s="21">
         <v>1000</v>
       </c>
-      <c r="AD20" s="221"/>
+      <c r="AD20" s="233"/>
       <c r="AF20" s="29"/>
-      <c r="AH20" s="218" t="s">
+      <c r="AH20" s="230" t="s">
         <v>86</v>
       </c>
-      <c r="AI20" s="218"/>
-      <c r="AJ20" s="218"/>
-      <c r="AK20" s="218"/>
+      <c r="AI20" s="230"/>
+      <c r="AJ20" s="230"/>
+      <c r="AK20" s="230"/>
       <c r="AL20" s="22">
         <f>SUM(U37:V37)</f>
         <v>15264.08</v>
@@ -26482,13 +26514,13 @@
         <v>1980</v>
       </c>
       <c r="AC21" s="21"/>
-      <c r="AD21" s="221"/>
-      <c r="AH21" s="233" t="s">
+      <c r="AD21" s="233"/>
+      <c r="AH21" s="238" t="s">
         <v>32</v>
       </c>
-      <c r="AI21" s="233"/>
-      <c r="AJ21" s="233"/>
-      <c r="AK21" s="233"/>
+      <c r="AI21" s="238"/>
+      <c r="AJ21" s="238"/>
+      <c r="AK21" s="238"/>
       <c r="AL21" s="169">
         <f>T37</f>
         <v>31093</v>
@@ -26543,11 +26575,11 @@
         <v>3710.54</v>
       </c>
       <c r="AC22" s="21"/>
-      <c r="AD22" s="221"/>
-      <c r="AH22" s="234"/>
-      <c r="AI22" s="234"/>
-      <c r="AJ22" s="234"/>
-      <c r="AK22" s="234"/>
+      <c r="AD22" s="233"/>
+      <c r="AH22" s="239"/>
+      <c r="AI22" s="239"/>
+      <c r="AJ22" s="239"/>
+      <c r="AK22" s="239"/>
       <c r="AL22" s="170"/>
     </row>
     <row r="23" spans="1:38" ht="15.75">
@@ -26599,7 +26631,7 @@
         <f>21986+70637+42933</f>
         <v>135556</v>
       </c>
-      <c r="AD23" s="221"/>
+      <c r="AD23" s="233"/>
     </row>
     <row r="24" spans="1:38" ht="15.75">
       <c r="A24" s="17">
@@ -26659,7 +26691,7 @@
         <v>26293.41</v>
       </c>
       <c r="AC24" s="21"/>
-      <c r="AD24" s="221"/>
+      <c r="AD24" s="233"/>
     </row>
     <row r="25" spans="1:38" ht="15.75">
       <c r="A25" s="11">
@@ -26704,7 +26736,7 @@
         <v>542</v>
       </c>
       <c r="AC25" s="16"/>
-      <c r="AD25" s="221"/>
+      <c r="AD25" s="233"/>
     </row>
     <row r="26" spans="1:38" ht="15.75">
       <c r="A26" s="17">
@@ -26764,7 +26796,7 @@
         <v>5856.07</v>
       </c>
       <c r="AC26" s="21"/>
-      <c r="AD26" s="221"/>
+      <c r="AD26" s="233"/>
     </row>
     <row r="27" spans="1:38" ht="15.75">
       <c r="A27" s="11">
@@ -26818,7 +26850,7 @@
         <v>14081.2</v>
       </c>
       <c r="AC27" s="21"/>
-      <c r="AD27" s="221"/>
+      <c r="AD27" s="233"/>
     </row>
     <row r="28" spans="1:38" ht="15.75">
       <c r="A28" s="17">
@@ -26862,7 +26894,7 @@
       <c r="AC28" s="21">
         <v>20000</v>
       </c>
-      <c r="AD28" s="221"/>
+      <c r="AD28" s="233"/>
     </row>
     <row r="29" spans="1:38" ht="15.75">
       <c r="A29" s="11">
@@ -26911,7 +26943,7 @@
         <v>4019.84</v>
       </c>
       <c r="AC29" s="21"/>
-      <c r="AD29" s="221"/>
+      <c r="AD29" s="233"/>
     </row>
     <row r="30" spans="1:38" ht="15.75">
       <c r="A30" s="17">
@@ -26962,7 +26994,7 @@
         <v>2628.39</v>
       </c>
       <c r="AC30" s="21"/>
-      <c r="AD30" s="221"/>
+      <c r="AD30" s="233"/>
     </row>
     <row r="31" spans="1:38" ht="16.5" thickBot="1">
       <c r="A31" s="139">
@@ -27018,7 +27050,7 @@
         <v>12589</v>
       </c>
       <c r="AC31" s="21"/>
-      <c r="AD31" s="221"/>
+      <c r="AD31" s="233"/>
     </row>
     <row r="32" spans="1:38" ht="15.75">
       <c r="A32" s="147">
@@ -27080,7 +27112,7 @@
         <v>18544.419999999998</v>
       </c>
       <c r="AC32" s="21"/>
-      <c r="AD32" s="221"/>
+      <c r="AD32" s="233"/>
     </row>
     <row r="33" spans="1:34" ht="15.75">
       <c r="A33" s="154">
@@ -27131,7 +27163,7 @@
         <v>9526.09</v>
       </c>
       <c r="AC33" s="21"/>
-      <c r="AD33" s="221"/>
+      <c r="AD33" s="233"/>
     </row>
     <row r="34" spans="1:34" ht="15.75">
       <c r="A34" s="151">
@@ -27193,7 +27225,7 @@
       <c r="AC34" s="21">
         <v>20000</v>
       </c>
-      <c r="AD34" s="221"/>
+      <c r="AD34" s="233"/>
     </row>
     <row r="35" spans="1:34" ht="16.5" thickBot="1">
       <c r="A35" s="158">
@@ -27249,13 +27281,13 @@
       <c r="AC35" s="37">
         <v>15000</v>
       </c>
-      <c r="AD35" s="221"/>
+      <c r="AD35" s="233"/>
     </row>
     <row r="36" spans="1:34" ht="24" customHeight="1">
-      <c r="A36" s="235" t="s">
+      <c r="A36" s="240" t="s">
         <v>55</v>
       </c>
-      <c r="B36" s="235"/>
+      <c r="B36" s="240"/>
       <c r="C36" s="143">
         <f t="shared" ref="C36:AC36" si="6">SUM(C19:C35)</f>
         <v>1293.0899999999999</v>
@@ -27371,10 +27403,10 @@
       <c r="AH36" s="162"/>
     </row>
     <row r="37" spans="1:34" ht="31.5" customHeight="1">
-      <c r="A37" s="220" t="s">
+      <c r="A37" s="232" t="s">
         <v>56</v>
       </c>
-      <c r="B37" s="220"/>
+      <c r="B37" s="232"/>
       <c r="C37" s="31">
         <f t="shared" ref="C37:R37" si="7">SUM(C18,C36)</f>
         <v>1423.08</v>
@@ -27505,12 +27537,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:K2"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="AD19:AD35"/>
     <mergeCell ref="AH11:AL13"/>
@@ -27526,6 +27552,12 @@
     <mergeCell ref="AH16:AK16"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="AH18:AK18"/>
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Другое/2026/Доходы-Расходы.xlsx
+++ b/Другое/2026/Доходы-Расходы.xlsx
@@ -8373,6 +8373,19 @@
         </r>
       </text>
     </comment>
+    <comment ref="O22" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Губки для чистки обуви</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="W22" authorId="1">
       <text>
         <r>
@@ -8394,6 +8407,20 @@
           </rPr>
           <t xml:space="preserve">
 На врача</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W23" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">на косметолога
+</t>
         </r>
       </text>
     </comment>
@@ -10407,9 +10434,6 @@
     <xf numFmtId="0" fontId="24" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -10420,6 +10444,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -10441,21 +10483,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -11133,78 +11160,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="34.5" customHeight="1">
-      <c r="A1" s="223" t="s">
+      <c r="A1" s="228" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="223"/>
-      <c r="C1" s="223"/>
-      <c r="D1" s="223"/>
-      <c r="E1" s="223"/>
-      <c r="F1" s="223"/>
-      <c r="G1" s="223"/>
-      <c r="H1" s="223"/>
-      <c r="I1" s="223"/>
-      <c r="J1" s="223"/>
-      <c r="K1" s="223"/>
-      <c r="L1" s="223"/>
-      <c r="M1" s="223"/>
-      <c r="N1" s="223"/>
-      <c r="O1" s="223"/>
-      <c r="P1" s="223"/>
-      <c r="Q1" s="223"/>
-      <c r="R1" s="223"/>
-      <c r="S1" s="223"/>
-      <c r="T1" s="223"/>
-      <c r="U1" s="223"/>
-      <c r="V1" s="223"/>
-      <c r="W1" s="223"/>
-      <c r="X1" s="223"/>
-      <c r="Y1" s="223"/>
-      <c r="Z1" s="223"/>
-      <c r="AA1" s="223"/>
-      <c r="AB1" s="223"/>
-      <c r="AC1" s="223"/>
-      <c r="AD1" s="223"/>
+      <c r="B1" s="228"/>
+      <c r="C1" s="228"/>
+      <c r="D1" s="228"/>
+      <c r="E1" s="228"/>
+      <c r="F1" s="228"/>
+      <c r="G1" s="228"/>
+      <c r="H1" s="228"/>
+      <c r="I1" s="228"/>
+      <c r="J1" s="228"/>
+      <c r="K1" s="228"/>
+      <c r="L1" s="228"/>
+      <c r="M1" s="228"/>
+      <c r="N1" s="228"/>
+      <c r="O1" s="228"/>
+      <c r="P1" s="228"/>
+      <c r="Q1" s="228"/>
+      <c r="R1" s="228"/>
+      <c r="S1" s="228"/>
+      <c r="T1" s="228"/>
+      <c r="U1" s="228"/>
+      <c r="V1" s="228"/>
+      <c r="W1" s="228"/>
+      <c r="X1" s="228"/>
+      <c r="Y1" s="228"/>
+      <c r="Z1" s="228"/>
+      <c r="AA1" s="228"/>
+      <c r="AB1" s="228"/>
+      <c r="AC1" s="228"/>
+      <c r="AD1" s="228"/>
     </row>
     <row r="2" spans="1:52" ht="26.25">
-      <c r="A2" s="224"/>
-      <c r="B2" s="225"/>
-      <c r="C2" s="226" t="s">
+      <c r="A2" s="229"/>
+      <c r="B2" s="230"/>
+      <c r="C2" s="231" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="226"/>
-      <c r="E2" s="226"/>
-      <c r="F2" s="226"/>
-      <c r="G2" s="226"/>
-      <c r="H2" s="226"/>
-      <c r="I2" s="226"/>
-      <c r="J2" s="226"/>
-      <c r="K2" s="226"/>
-      <c r="L2" s="227" t="s">
+      <c r="D2" s="231"/>
+      <c r="E2" s="231"/>
+      <c r="F2" s="231"/>
+      <c r="G2" s="231"/>
+      <c r="H2" s="231"/>
+      <c r="I2" s="231"/>
+      <c r="J2" s="231"/>
+      <c r="K2" s="231"/>
+      <c r="L2" s="232" t="s">
         <v>68</v>
       </c>
-      <c r="M2" s="227"/>
-      <c r="N2" s="227"/>
-      <c r="O2" s="227"/>
-      <c r="P2" s="227"/>
-      <c r="Q2" s="227"/>
-      <c r="R2" s="228" t="s">
+      <c r="M2" s="232"/>
+      <c r="N2" s="232"/>
+      <c r="O2" s="232"/>
+      <c r="P2" s="232"/>
+      <c r="Q2" s="232"/>
+      <c r="R2" s="233" t="s">
         <v>69</v>
       </c>
-      <c r="S2" s="228"/>
-      <c r="T2" s="228"/>
-      <c r="U2" s="228"/>
-      <c r="V2" s="228"/>
-      <c r="W2" s="228"/>
-      <c r="X2" s="228"/>
-      <c r="Y2" s="228"/>
-      <c r="Z2" s="228"/>
-      <c r="AA2" s="228"/>
-      <c r="AB2" s="229" t="s">
+      <c r="S2" s="233"/>
+      <c r="T2" s="233"/>
+      <c r="U2" s="233"/>
+      <c r="V2" s="233"/>
+      <c r="W2" s="233"/>
+      <c r="X2" s="233"/>
+      <c r="Y2" s="233"/>
+      <c r="Z2" s="233"/>
+      <c r="AA2" s="233"/>
+      <c r="AB2" s="234" t="s">
         <v>70</v>
       </c>
-      <c r="AC2" s="229"/>
-      <c r="AD2" s="229"/>
+      <c r="AC2" s="234"/>
+      <c r="AD2" s="234"/>
     </row>
     <row r="3" spans="1:52" ht="45" customHeight="1" thickBot="1">
       <c r="A3" s="181" t="s">
@@ -11374,7 +11401,7 @@
       <c r="AC4" s="163">
         <v>142200.85999999999</v>
       </c>
-      <c r="AD4" s="233"/>
+      <c r="AD4" s="226"/>
     </row>
     <row r="5" spans="1:52" ht="15.75">
       <c r="A5" s="196">
@@ -11430,7 +11457,7 @@
         <v>47667</v>
       </c>
       <c r="AC5" s="165"/>
-      <c r="AD5" s="233"/>
+      <c r="AD5" s="226"/>
     </row>
     <row r="6" spans="1:52" ht="16.5" thickBot="1">
       <c r="A6" s="194">
@@ -11484,7 +11511,7 @@
         <v>9459</v>
       </c>
       <c r="AC6" s="165"/>
-      <c r="AD6" s="233"/>
+      <c r="AD6" s="226"/>
     </row>
     <row r="7" spans="1:52" ht="15.75">
       <c r="A7" s="186">
@@ -11537,7 +11564,7 @@
       <c r="AC7" s="165">
         <v>2000</v>
       </c>
-      <c r="AD7" s="233"/>
+      <c r="AD7" s="226"/>
     </row>
     <row r="8" spans="1:52" ht="15" customHeight="1">
       <c r="A8" s="11">
@@ -11579,7 +11606,7 @@
         <v>2946.51</v>
       </c>
       <c r="AC8" s="165"/>
-      <c r="AD8" s="233"/>
+      <c r="AD8" s="226"/>
     </row>
     <row r="9" spans="1:52" ht="15.75">
       <c r="A9" s="17">
@@ -11624,7 +11651,7 @@
         <v>1677.84</v>
       </c>
       <c r="AC9" s="165"/>
-      <c r="AD9" s="233"/>
+      <c r="AD9" s="226"/>
     </row>
     <row r="10" spans="1:52" ht="15.75">
       <c r="A10" s="11">
@@ -11690,7 +11717,7 @@
       <c r="AC10" s="165">
         <v>55867</v>
       </c>
-      <c r="AD10" s="233"/>
+      <c r="AD10" s="226"/>
     </row>
     <row r="11" spans="1:52" ht="15.75">
       <c r="A11" s="17">
@@ -11737,14 +11764,14 @@
       <c r="AC11" s="165">
         <v>3000</v>
       </c>
-      <c r="AD11" s="233"/>
-      <c r="AH11" s="234" t="s">
+      <c r="AD11" s="226"/>
+      <c r="AH11" s="227" t="s">
         <v>83</v>
       </c>
-      <c r="AI11" s="234"/>
-      <c r="AJ11" s="234"/>
-      <c r="AK11" s="234"/>
-      <c r="AL11" s="234"/>
+      <c r="AI11" s="227"/>
+      <c r="AJ11" s="227"/>
+      <c r="AK11" s="227"/>
+      <c r="AL11" s="227"/>
     </row>
     <row r="12" spans="1:52" ht="15.75">
       <c r="A12" s="11">
@@ -11793,12 +11820,12 @@
         <v>6686</v>
       </c>
       <c r="AC12" s="165"/>
-      <c r="AD12" s="233"/>
-      <c r="AH12" s="234"/>
-      <c r="AI12" s="234"/>
-      <c r="AJ12" s="234"/>
-      <c r="AK12" s="234"/>
-      <c r="AL12" s="234"/>
+      <c r="AD12" s="226"/>
+      <c r="AH12" s="227"/>
+      <c r="AI12" s="227"/>
+      <c r="AJ12" s="227"/>
+      <c r="AK12" s="227"/>
+      <c r="AL12" s="227"/>
     </row>
     <row r="13" spans="1:52" ht="15.75">
       <c r="A13" s="17">
@@ -11845,12 +11872,12 @@
         <v>3935</v>
       </c>
       <c r="AC13" s="165"/>
-      <c r="AD13" s="233"/>
-      <c r="AH13" s="234"/>
-      <c r="AI13" s="234"/>
-      <c r="AJ13" s="234"/>
-      <c r="AK13" s="234"/>
-      <c r="AL13" s="234"/>
+      <c r="AD13" s="226"/>
+      <c r="AH13" s="227"/>
+      <c r="AI13" s="227"/>
+      <c r="AJ13" s="227"/>
+      <c r="AK13" s="227"/>
+      <c r="AL13" s="227"/>
     </row>
     <row r="14" spans="1:52" ht="18">
       <c r="A14" s="11">
@@ -11891,13 +11918,13 @@
         <v>750</v>
       </c>
       <c r="AC14" s="165"/>
-      <c r="AD14" s="233"/>
-      <c r="AH14" s="230" t="s">
+      <c r="AD14" s="226"/>
+      <c r="AH14" s="223" t="s">
         <v>62</v>
       </c>
-      <c r="AI14" s="230"/>
-      <c r="AJ14" s="230"/>
-      <c r="AK14" s="230"/>
+      <c r="AI14" s="223"/>
+      <c r="AJ14" s="223"/>
+      <c r="AK14" s="223"/>
       <c r="AL14" s="22">
         <f>AC4+AC20+AC24+AC10</f>
         <v>198067.86</v>
@@ -11952,13 +11979,13 @@
         <v>10319</v>
       </c>
       <c r="AC15" s="163"/>
-      <c r="AD15" s="233"/>
-      <c r="AH15" s="230" t="s">
+      <c r="AD15" s="226"/>
+      <c r="AH15" s="223" t="s">
         <v>2</v>
       </c>
-      <c r="AI15" s="230"/>
-      <c r="AJ15" s="230"/>
-      <c r="AK15" s="230"/>
+      <c r="AI15" s="223"/>
+      <c r="AJ15" s="223"/>
+      <c r="AK15" s="223"/>
       <c r="AL15" s="22">
         <f>SUM(AC7,AC11)</f>
         <v>5000</v>
@@ -12013,13 +12040,13 @@
         <v>7901.26</v>
       </c>
       <c r="AC16" s="163"/>
-      <c r="AD16" s="233"/>
-      <c r="AH16" s="230" t="s">
+      <c r="AD16" s="226"/>
+      <c r="AH16" s="223" t="s">
         <v>63</v>
       </c>
-      <c r="AI16" s="230"/>
-      <c r="AJ16" s="230"/>
-      <c r="AK16" s="230"/>
+      <c r="AI16" s="223"/>
+      <c r="AJ16" s="223"/>
+      <c r="AK16" s="223"/>
       <c r="AL16" s="22">
         <v>0</v>
       </c>
@@ -12068,7 +12095,7 @@
         <v>1766.67</v>
       </c>
       <c r="AC17" s="163"/>
-      <c r="AD17" s="233"/>
+      <c r="AD17" s="226"/>
       <c r="AH17" s="235" t="s">
         <v>67</v>
       </c>
@@ -12077,7 +12104,7 @@
       <c r="AK17" s="237"/>
       <c r="AL17" s="22">
         <f>SUM(C37:K37)</f>
-        <v>59012.880000000005</v>
+        <v>61492.880000000005</v>
       </c>
     </row>
     <row r="18" spans="1:38" ht="18">
@@ -12123,7 +12150,7 @@
         <v>20640.400000000001</v>
       </c>
       <c r="AC18" s="163"/>
-      <c r="AD18" s="233"/>
+      <c r="AD18" s="226"/>
       <c r="AH18" s="235" t="s">
         <v>84</v>
       </c>
@@ -12132,7 +12159,7 @@
       <c r="AK18" s="237"/>
       <c r="AL18" s="22">
         <f>SUM(L37:Q37)</f>
-        <v>21802</v>
+        <v>22101.98</v>
       </c>
     </row>
     <row r="19" spans="1:38" ht="19.5" customHeight="1">
@@ -12260,7 +12287,7 @@
       <c r="AK19" s="237"/>
       <c r="AL19" s="22">
         <f>W37</f>
-        <v>62674</v>
+        <v>65674</v>
       </c>
     </row>
     <row r="20" spans="1:38" ht="18">
@@ -12304,7 +12331,7 @@
       <c r="AC20" s="16">
         <v>0</v>
       </c>
-      <c r="AD20" s="233"/>
+      <c r="AD20" s="226"/>
       <c r="AH20" s="235" t="s">
         <v>86</v>
       </c>
@@ -12313,7 +12340,7 @@
       <c r="AK20" s="237"/>
       <c r="AL20" s="22">
         <f>SUM(U37:V37)</f>
-        <v>5082.03</v>
+        <v>5324.03</v>
       </c>
     </row>
     <row r="21" spans="1:38" ht="18">
@@ -12358,7 +12385,7 @@
         <f>3175.8+7922.85</f>
         <v>11098.650000000001</v>
       </c>
-      <c r="AD21" s="233"/>
+      <c r="AD21" s="226"/>
       <c r="AF21" s="29"/>
       <c r="AH21" s="238" t="s">
         <v>32</v>
@@ -12381,7 +12408,9 @@
       <c r="C22" s="173"/>
       <c r="D22" s="173"/>
       <c r="E22" s="173"/>
-      <c r="F22" s="173"/>
+      <c r="F22" s="173">
+        <v>2480</v>
+      </c>
       <c r="G22" s="173"/>
       <c r="H22" s="173"/>
       <c r="I22" s="173"/>
@@ -12390,7 +12419,10 @@
       <c r="L22" s="173"/>
       <c r="M22" s="173"/>
       <c r="N22" s="173"/>
-      <c r="O22" s="173"/>
+      <c r="O22" s="173">
+        <f>109.99+189.99</f>
+        <v>299.98</v>
+      </c>
       <c r="P22" s="173"/>
       <c r="Q22" s="173"/>
       <c r="R22" s="173"/>
@@ -12408,10 +12440,10 @@
       <c r="AA22" s="174"/>
       <c r="AB22" s="15">
         <f t="shared" ref="AB22:AB31" si="5">SUM(C22:AA22)</f>
-        <v>2000</v>
+        <v>4779.9799999999996</v>
       </c>
       <c r="AC22" s="21"/>
-      <c r="AD22" s="233"/>
+      <c r="AD22" s="226"/>
     </row>
     <row r="23" spans="1:38" ht="18">
       <c r="A23" s="17">
@@ -12438,19 +12470,23 @@
       <c r="R23" s="175"/>
       <c r="S23" s="175"/>
       <c r="T23" s="175"/>
-      <c r="U23" s="175"/>
+      <c r="U23" s="175">
+        <v>242</v>
+      </c>
       <c r="V23" s="175"/>
-      <c r="W23" s="175"/>
+      <c r="W23" s="175">
+        <v>3000</v>
+      </c>
       <c r="X23" s="175"/>
       <c r="Y23" s="175"/>
       <c r="Z23" s="175"/>
       <c r="AA23" s="176"/>
       <c r="AB23" s="15">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3242</v>
       </c>
       <c r="AC23" s="21"/>
-      <c r="AD23" s="233"/>
+      <c r="AD23" s="226"/>
       <c r="AH23" s="239"/>
       <c r="AI23" s="239"/>
       <c r="AJ23" s="239"/>
@@ -12494,7 +12530,7 @@
         <v>0</v>
       </c>
       <c r="AC24" s="21"/>
-      <c r="AD24" s="233"/>
+      <c r="AD24" s="226"/>
     </row>
     <row r="25" spans="1:38" ht="15.75">
       <c r="A25" s="17">
@@ -12535,7 +12571,7 @@
         <v>3500</v>
       </c>
       <c r="AC25" s="21"/>
-      <c r="AD25" s="233"/>
+      <c r="AD25" s="226"/>
     </row>
     <row r="26" spans="1:38" ht="15.75">
       <c r="A26" s="11">
@@ -12574,7 +12610,7 @@
         <v>0</v>
       </c>
       <c r="AC26" s="16"/>
-      <c r="AD26" s="233"/>
+      <c r="AD26" s="226"/>
     </row>
     <row r="27" spans="1:38" ht="15.75">
       <c r="A27" s="17">
@@ -12613,7 +12649,7 @@
         <v>0</v>
       </c>
       <c r="AC27" s="21"/>
-      <c r="AD27" s="233"/>
+      <c r="AD27" s="226"/>
     </row>
     <row r="28" spans="1:38" ht="15.75">
       <c r="A28" s="11">
@@ -12652,7 +12688,7 @@
         <v>0</v>
       </c>
       <c r="AC28" s="21"/>
-      <c r="AD28" s="233"/>
+      <c r="AD28" s="226"/>
     </row>
     <row r="29" spans="1:38" ht="15.75">
       <c r="A29" s="17">
@@ -12693,7 +12729,7 @@
         <v>3500</v>
       </c>
       <c r="AC29" s="21"/>
-      <c r="AD29" s="233"/>
+      <c r="AD29" s="226"/>
     </row>
     <row r="30" spans="1:38" ht="15.75">
       <c r="A30" s="11">
@@ -12732,7 +12768,7 @@
         <v>0</v>
       </c>
       <c r="AC30" s="21"/>
-      <c r="AD30" s="233"/>
+      <c r="AD30" s="226"/>
     </row>
     <row r="31" spans="1:38" ht="15.75">
       <c r="A31" s="17">
@@ -12771,7 +12807,7 @@
         <v>0</v>
       </c>
       <c r="AC31" s="21"/>
-      <c r="AD31" s="233"/>
+      <c r="AD31" s="226"/>
     </row>
     <row r="32" spans="1:38" ht="15.75">
       <c r="A32" s="11">
@@ -12810,7 +12846,7 @@
         <v>0</v>
       </c>
       <c r="AC32" s="21"/>
-      <c r="AD32" s="233"/>
+      <c r="AD32" s="226"/>
     </row>
     <row r="33" spans="1:34" ht="15.75">
       <c r="A33" s="17">
@@ -12851,7 +12887,7 @@
         <v>3500</v>
       </c>
       <c r="AC33" s="21"/>
-      <c r="AD33" s="233"/>
+      <c r="AD33" s="226"/>
     </row>
     <row r="34" spans="1:34" ht="15.75">
       <c r="A34" s="11">
@@ -12892,7 +12928,7 @@
         <v>11525</v>
       </c>
       <c r="AC34" s="21"/>
-      <c r="AD34" s="233"/>
+      <c r="AD34" s="226"/>
     </row>
     <row r="35" spans="1:34" ht="15.75">
       <c r="A35" s="17">
@@ -12931,7 +12967,7 @@
         <v>0</v>
       </c>
       <c r="AC35" s="21"/>
-      <c r="AD35" s="233"/>
+      <c r="AD35" s="226"/>
     </row>
     <row r="36" spans="1:34" ht="24" customHeight="1">
       <c r="A36" s="240" t="s">
@@ -12952,7 +12988,7 @@
       </c>
       <c r="F36" s="143">
         <f t="shared" si="7"/>
-        <v>12984.720000000001</v>
+        <v>15464.720000000001</v>
       </c>
       <c r="G36" s="143">
         <f t="shared" si="7"/>
@@ -12988,7 +13024,7 @@
       </c>
       <c r="O36" s="144">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>299.98</v>
       </c>
       <c r="P36" s="144">
         <f t="shared" si="7"/>
@@ -13012,7 +13048,7 @@
       </c>
       <c r="U36" s="145">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="V36" s="145">
         <f t="shared" si="7"/>
@@ -13020,7 +13056,7 @@
       </c>
       <c r="W36" s="145">
         <f t="shared" si="7"/>
-        <v>13525</v>
+        <v>16525</v>
       </c>
       <c r="X36" s="145">
         <f t="shared" si="7"/>
@@ -13040,7 +13076,7 @@
       </c>
       <c r="AB36" s="26">
         <f t="shared" si="7"/>
-        <v>26509.72</v>
+        <v>32531.7</v>
       </c>
       <c r="AC36" s="27">
         <f t="shared" si="7"/>
@@ -13048,15 +13084,15 @@
       </c>
       <c r="AD36" s="201">
         <f>AC36-AB36</f>
-        <v>-15411.07</v>
+        <v>-21433.05</v>
       </c>
       <c r="AH36" s="162"/>
     </row>
     <row r="37" spans="1:34" ht="31.5" customHeight="1">
-      <c r="A37" s="232" t="s">
+      <c r="A37" s="225" t="s">
         <v>56</v>
       </c>
-      <c r="B37" s="232"/>
+      <c r="B37" s="225"/>
       <c r="C37" s="31">
         <f t="shared" ref="C37:R37" si="8">SUM(C19,C36)</f>
         <v>2892.73</v>
@@ -13071,7 +13107,7 @@
       </c>
       <c r="F37" s="31">
         <f t="shared" si="8"/>
-        <v>21239.57</v>
+        <v>23719.57</v>
       </c>
       <c r="G37" s="31">
         <f t="shared" si="8"/>
@@ -13107,7 +13143,7 @@
       </c>
       <c r="O37" s="31">
         <f t="shared" si="8"/>
-        <v>5400</v>
+        <v>5699.98</v>
       </c>
       <c r="P37" s="31">
         <f t="shared" si="8"/>
@@ -13128,7 +13164,7 @@
       </c>
       <c r="U37" s="31">
         <f t="shared" si="9"/>
-        <v>2632</v>
+        <v>2874</v>
       </c>
       <c r="V37" s="31">
         <f t="shared" si="9"/>
@@ -13136,7 +13172,7 @@
       </c>
       <c r="W37" s="31">
         <f t="shared" si="9"/>
-        <v>62674</v>
+        <v>65674</v>
       </c>
       <c r="X37" s="31">
         <f t="shared" si="9"/>
@@ -13156,7 +13192,7 @@
       </c>
       <c r="AB37" s="203">
         <f t="shared" si="9"/>
-        <v>205974.25000000003</v>
+        <v>211996.23000000004</v>
       </c>
       <c r="AC37" s="204">
         <f t="shared" si="9"/>
@@ -13164,7 +13200,7 @@
       </c>
       <c r="AD37" s="200">
         <f t="shared" si="9"/>
-        <v>8192.2599999999584</v>
+        <v>2170.2799999999588</v>
       </c>
     </row>
     <row r="41" spans="1:34">
@@ -13187,12 +13223,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:K2"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="AD4:AD18"/>
@@ -13208,6 +13238,12 @@
     <mergeCell ref="AH16:AK16"/>
     <mergeCell ref="AH17:AK17"/>
     <mergeCell ref="AH18:AK18"/>
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
   </mergeCells>
   <conditionalFormatting sqref="AD37">
     <cfRule type="expression" dxfId="1" priority="1">
@@ -21132,34 +21168,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="60.75" customHeight="1">
-      <c r="A1" s="218" t="s">
+      <c r="A1" s="222" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="218"/>
-      <c r="C1" s="218"/>
-      <c r="D1" s="218"/>
-      <c r="E1" s="218"/>
-      <c r="F1" s="218"/>
-      <c r="G1" s="218"/>
-      <c r="H1" s="218"/>
-      <c r="I1" s="218"/>
-      <c r="J1" s="218"/>
-      <c r="K1" s="218"/>
-      <c r="L1" s="218"/>
-      <c r="M1" s="218"/>
-      <c r="N1" s="218"/>
-      <c r="O1" s="218"/>
-      <c r="P1" s="218"/>
-      <c r="Q1" s="218"/>
-      <c r="R1" s="218"/>
-      <c r="S1" s="218"/>
-      <c r="T1" s="218"/>
-      <c r="U1" s="218"/>
-      <c r="V1" s="218"/>
-      <c r="W1" s="218"/>
-      <c r="X1" s="218"/>
-      <c r="Y1" s="218"/>
-      <c r="Z1" s="218"/>
+      <c r="B1" s="222"/>
+      <c r="C1" s="222"/>
+      <c r="D1" s="222"/>
+      <c r="E1" s="222"/>
+      <c r="F1" s="222"/>
+      <c r="G1" s="222"/>
+      <c r="H1" s="222"/>
+      <c r="I1" s="222"/>
+      <c r="J1" s="222"/>
+      <c r="K1" s="222"/>
+      <c r="L1" s="222"/>
+      <c r="M1" s="222"/>
+      <c r="N1" s="222"/>
+      <c r="O1" s="222"/>
+      <c r="P1" s="222"/>
+      <c r="Q1" s="222"/>
+      <c r="R1" s="222"/>
+      <c r="S1" s="222"/>
+      <c r="T1" s="222"/>
+      <c r="U1" s="222"/>
+      <c r="V1" s="222"/>
+      <c r="W1" s="222"/>
+      <c r="X1" s="222"/>
+      <c r="Y1" s="222"/>
+      <c r="Z1" s="222"/>
     </row>
     <row r="2" spans="1:48" ht="45" customHeight="1">
       <c r="A2" s="38" t="s">
@@ -21312,7 +21348,7 @@
         <f>(94085+57723.67)</f>
         <v>151808.67000000001</v>
       </c>
-      <c r="Z3" s="221"/>
+      <c r="Z3" s="220"/>
     </row>
     <row r="4" spans="1:48" ht="15.75">
       <c r="A4" s="52">
@@ -21362,7 +21398,7 @@
       </c>
       <c r="X4" s="50"/>
       <c r="Y4" s="56"/>
-      <c r="Z4" s="221"/>
+      <c r="Z4" s="220"/>
     </row>
     <row r="5" spans="1:48" ht="15.75">
       <c r="A5" s="45">
@@ -21402,7 +21438,7 @@
       </c>
       <c r="X5" s="50"/>
       <c r="Y5" s="56"/>
-      <c r="Z5" s="221"/>
+      <c r="Z5" s="220"/>
     </row>
     <row r="6" spans="1:48" ht="15.75">
       <c r="A6" s="52">
@@ -21443,7 +21479,7 @@
       </c>
       <c r="X6" s="50"/>
       <c r="Y6" s="56"/>
-      <c r="Z6" s="221"/>
+      <c r="Z6" s="220"/>
     </row>
     <row r="7" spans="1:48" ht="15" customHeight="1">
       <c r="A7" s="45">
@@ -21487,7 +21523,7 @@
       </c>
       <c r="X7" s="50"/>
       <c r="Y7" s="56"/>
-      <c r="Z7" s="221"/>
+      <c r="Z7" s="220"/>
     </row>
     <row r="8" spans="1:48" ht="15.75">
       <c r="A8" s="52">
@@ -21529,14 +21565,14 @@
       </c>
       <c r="X8" s="50"/>
       <c r="Y8" s="56"/>
-      <c r="Z8" s="221"/>
-      <c r="AC8" s="222" t="s">
+      <c r="Z8" s="220"/>
+      <c r="AC8" s="221" t="s">
         <v>61</v>
       </c>
-      <c r="AD8" s="222"/>
-      <c r="AE8" s="222"/>
-      <c r="AF8" s="222"/>
-      <c r="AG8" s="222"/>
+      <c r="AD8" s="221"/>
+      <c r="AE8" s="221"/>
+      <c r="AF8" s="221"/>
+      <c r="AG8" s="221"/>
     </row>
     <row r="9" spans="1:48" ht="15.75">
       <c r="A9" s="45">
@@ -21575,12 +21611,12 @@
       </c>
       <c r="X9" s="50"/>
       <c r="Y9" s="56"/>
-      <c r="Z9" s="221"/>
-      <c r="AC9" s="222"/>
-      <c r="AD9" s="222"/>
-      <c r="AE9" s="222"/>
-      <c r="AF9" s="222"/>
-      <c r="AG9" s="222"/>
+      <c r="Z9" s="220"/>
+      <c r="AC9" s="221"/>
+      <c r="AD9" s="221"/>
+      <c r="AE9" s="221"/>
+      <c r="AF9" s="221"/>
+      <c r="AG9" s="221"/>
     </row>
     <row r="10" spans="1:48" ht="15.75">
       <c r="A10" s="52">
@@ -21624,12 +21660,12 @@
       </c>
       <c r="X10" s="50"/>
       <c r="Y10" s="56"/>
-      <c r="Z10" s="221"/>
-      <c r="AC10" s="222"/>
-      <c r="AD10" s="222"/>
-      <c r="AE10" s="222"/>
-      <c r="AF10" s="222"/>
-      <c r="AG10" s="222"/>
+      <c r="Z10" s="220"/>
+      <c r="AC10" s="221"/>
+      <c r="AD10" s="221"/>
+      <c r="AE10" s="221"/>
+      <c r="AF10" s="221"/>
+      <c r="AG10" s="221"/>
     </row>
     <row r="11" spans="1:48" ht="15.75">
       <c r="A11" s="45">
@@ -21669,13 +21705,13 @@
       </c>
       <c r="X11" s="50"/>
       <c r="Y11" s="56"/>
-      <c r="Z11" s="221"/>
-      <c r="AC11" s="219" t="s">
+      <c r="Z11" s="220"/>
+      <c r="AC11" s="218" t="s">
         <v>62</v>
       </c>
-      <c r="AD11" s="219"/>
-      <c r="AE11" s="219"/>
-      <c r="AF11" s="219"/>
+      <c r="AD11" s="218"/>
+      <c r="AE11" s="218"/>
+      <c r="AF11" s="218"/>
       <c r="AG11" s="57">
         <f>Y3+Y14+Y21</f>
         <v>226341.31</v>
@@ -21716,13 +21752,13 @@
       </c>
       <c r="X12" s="50"/>
       <c r="Y12" s="56"/>
-      <c r="Z12" s="221"/>
-      <c r="AC12" s="219" t="s">
+      <c r="Z12" s="220"/>
+      <c r="AC12" s="218" t="s">
         <v>2</v>
       </c>
-      <c r="AD12" s="219"/>
-      <c r="AE12" s="219"/>
-      <c r="AF12" s="219"/>
+      <c r="AD12" s="218"/>
+      <c r="AE12" s="218"/>
+      <c r="AF12" s="218"/>
       <c r="AG12" s="57">
         <f>Y27</f>
         <v>20000</v>
@@ -21767,13 +21803,13 @@
       </c>
       <c r="X13" s="50"/>
       <c r="Y13" s="56"/>
-      <c r="Z13" s="221"/>
-      <c r="AC13" s="219" t="s">
+      <c r="Z13" s="220"/>
+      <c r="AC13" s="218" t="s">
         <v>63</v>
       </c>
-      <c r="AD13" s="219"/>
-      <c r="AE13" s="219"/>
-      <c r="AF13" s="219"/>
+      <c r="AD13" s="218"/>
+      <c r="AE13" s="218"/>
+      <c r="AF13" s="218"/>
       <c r="AG13" s="57">
         <f>Y17+Y19</f>
         <v>25000</v>
@@ -21819,13 +21855,13 @@
       <c r="Y14" s="51">
         <v>37634</v>
       </c>
-      <c r="Z14" s="221"/>
-      <c r="AC14" s="219" t="s">
+      <c r="Z14" s="220"/>
+      <c r="AC14" s="218" t="s">
         <v>64</v>
       </c>
-      <c r="AD14" s="219"/>
-      <c r="AE14" s="219"/>
-      <c r="AF14" s="219"/>
+      <c r="AD14" s="218"/>
+      <c r="AE14" s="218"/>
+      <c r="AF14" s="218"/>
       <c r="AG14" s="57">
         <f>W38</f>
         <v>177971.36</v>
@@ -21875,13 +21911,13 @@
       </c>
       <c r="X15" s="50"/>
       <c r="Y15" s="56"/>
-      <c r="Z15" s="221"/>
-      <c r="AC15" s="219" t="s">
+      <c r="Z15" s="220"/>
+      <c r="AC15" s="218" t="s">
         <v>65</v>
       </c>
-      <c r="AD15" s="219"/>
-      <c r="AE15" s="219"/>
-      <c r="AF15" s="219"/>
+      <c r="AD15" s="218"/>
+      <c r="AE15" s="218"/>
+      <c r="AF15" s="218"/>
       <c r="AG15" s="57">
         <f>SUM(C38:H38)</f>
         <v>55416.04</v>
@@ -21930,13 +21966,13 @@
       </c>
       <c r="X16" s="50"/>
       <c r="Y16" s="56"/>
-      <c r="Z16" s="221"/>
-      <c r="AC16" s="219" t="s">
+      <c r="Z16" s="220"/>
+      <c r="AC16" s="218" t="s">
         <v>85</v>
       </c>
-      <c r="AD16" s="219"/>
-      <c r="AE16" s="219"/>
-      <c r="AF16" s="219"/>
+      <c r="AD16" s="218"/>
+      <c r="AE16" s="218"/>
+      <c r="AF16" s="218"/>
       <c r="AG16" s="57">
         <f>Q38</f>
         <v>27468.98</v>
@@ -21992,7 +22028,7 @@
       <c r="Y17" s="59">
         <v>15000</v>
       </c>
-      <c r="Z17" s="221"/>
+      <c r="Z17" s="220"/>
     </row>
     <row r="18" spans="1:28" ht="15.75">
       <c r="A18" s="52">
@@ -22033,7 +22069,7 @@
       </c>
       <c r="X18" s="50"/>
       <c r="Y18" s="56"/>
-      <c r="Z18" s="221"/>
+      <c r="Z18" s="220"/>
     </row>
     <row r="19" spans="1:28" ht="15.75">
       <c r="A19" s="45">
@@ -22077,7 +22113,7 @@
       <c r="Y19" s="59">
         <v>10000</v>
       </c>
-      <c r="Z19" s="221"/>
+      <c r="Z19" s="220"/>
     </row>
     <row r="20" spans="1:28" ht="14.25" customHeight="1">
       <c r="A20" s="216" t="s">
@@ -22226,7 +22262,7 @@
       <c r="Y21" s="51">
         <v>36898.639999999999</v>
       </c>
-      <c r="Z21" s="221"/>
+      <c r="Z21" s="220"/>
     </row>
     <row r="22" spans="1:28" ht="15.75">
       <c r="A22" s="52">
@@ -22272,7 +22308,7 @@
         <v>23662.84</v>
       </c>
       <c r="Y22" s="56"/>
-      <c r="Z22" s="221"/>
+      <c r="Z22" s="220"/>
       <c r="AB22" s="29"/>
     </row>
     <row r="23" spans="1:28" ht="15.75">
@@ -22316,7 +22352,7 @@
       </c>
       <c r="X23" s="50"/>
       <c r="Y23" s="56"/>
-      <c r="Z23" s="221"/>
+      <c r="Z23" s="220"/>
     </row>
     <row r="24" spans="1:28" ht="15.75">
       <c r="A24" s="52">
@@ -22360,7 +22396,7 @@
       </c>
       <c r="X24" s="50"/>
       <c r="Y24" s="56"/>
-      <c r="Z24" s="221"/>
+      <c r="Z24" s="220"/>
     </row>
     <row r="25" spans="1:28" ht="15.75">
       <c r="A25" s="45">
@@ -22404,7 +22440,7 @@
       </c>
       <c r="X25" s="50"/>
       <c r="Y25" s="56"/>
-      <c r="Z25" s="221"/>
+      <c r="Z25" s="220"/>
     </row>
     <row r="26" spans="1:28" ht="15.75">
       <c r="A26" s="52">
@@ -22443,7 +22479,7 @@
       </c>
       <c r="X26" s="50"/>
       <c r="Y26" s="56"/>
-      <c r="Z26" s="221"/>
+      <c r="Z26" s="220"/>
     </row>
     <row r="27" spans="1:28" ht="15.75">
       <c r="A27" s="45">
@@ -22488,7 +22524,7 @@
       <c r="Y27" s="66">
         <v>20000</v>
       </c>
-      <c r="Z27" s="221"/>
+      <c r="Z27" s="220"/>
     </row>
     <row r="28" spans="1:28" ht="15.75">
       <c r="A28" s="52">
@@ -22530,7 +22566,7 @@
       </c>
       <c r="X28" s="50"/>
       <c r="Y28" s="56"/>
-      <c r="Z28" s="221"/>
+      <c r="Z28" s="220"/>
     </row>
     <row r="29" spans="1:28" ht="15.75">
       <c r="A29" s="45">
@@ -22569,7 +22605,7 @@
       </c>
       <c r="X29" s="50"/>
       <c r="Y29" s="56"/>
-      <c r="Z29" s="221"/>
+      <c r="Z29" s="220"/>
     </row>
     <row r="30" spans="1:28" ht="15.75">
       <c r="A30" s="52">
@@ -22609,7 +22645,7 @@
       </c>
       <c r="X30" s="50"/>
       <c r="Y30" s="56"/>
-      <c r="Z30" s="221"/>
+      <c r="Z30" s="220"/>
     </row>
     <row r="31" spans="1:28" ht="15.75">
       <c r="A31" s="45">
@@ -22644,7 +22680,7 @@
       </c>
       <c r="X31" s="50"/>
       <c r="Y31" s="56"/>
-      <c r="Z31" s="221"/>
+      <c r="Z31" s="220"/>
     </row>
     <row r="32" spans="1:28" ht="15.75">
       <c r="A32" s="52">
@@ -22679,7 +22715,7 @@
       </c>
       <c r="X32" s="50"/>
       <c r="Y32" s="56"/>
-      <c r="Z32" s="221"/>
+      <c r="Z32" s="220"/>
     </row>
     <row r="33" spans="1:26" ht="15.75">
       <c r="A33" s="45">
@@ -22716,7 +22752,7 @@
       <c r="Y33" s="67">
         <v>10000</v>
       </c>
-      <c r="Z33" s="221"/>
+      <c r="Z33" s="220"/>
     </row>
     <row r="34" spans="1:26" ht="15.75">
       <c r="A34" s="52">
@@ -22755,7 +22791,7 @@
       </c>
       <c r="X34" s="50"/>
       <c r="Y34" s="56"/>
-      <c r="Z34" s="221"/>
+      <c r="Z34" s="220"/>
     </row>
     <row r="35" spans="1:26" ht="15.75">
       <c r="A35" s="45">
@@ -22799,7 +22835,7 @@
       </c>
       <c r="X35" s="50"/>
       <c r="Y35" s="56"/>
-      <c r="Z35" s="221"/>
+      <c r="Z35" s="220"/>
     </row>
     <row r="36" spans="1:26" ht="15.75">
       <c r="A36" s="52">
@@ -22840,7 +22876,7 @@
       </c>
       <c r="X36" s="50"/>
       <c r="Y36" s="56"/>
-      <c r="Z36" s="221"/>
+      <c r="Z36" s="220"/>
     </row>
     <row r="37" spans="1:26">
       <c r="A37" s="216" t="s">
@@ -22945,10 +22981,10 @@
       </c>
     </row>
     <row r="38" spans="1:26" ht="31.5" customHeight="1">
-      <c r="A38" s="220" t="s">
+      <c r="A38" s="219" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="220"/>
+      <c r="B38" s="219"/>
       <c r="C38" s="69">
         <f>SUM(C20,C37)</f>
         <v>14335.99</v>
@@ -23060,6 +23096,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="AC11:AF11"/>
+    <mergeCell ref="AC12:AF12"/>
+    <mergeCell ref="AC13:AF13"/>
+    <mergeCell ref="AC14:AF14"/>
     <mergeCell ref="AC15:AF15"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A37:B37"/>
@@ -23068,11 +23109,6 @@
     <mergeCell ref="Z21:Z36"/>
     <mergeCell ref="AC8:AG10"/>
     <mergeCell ref="AC16:AF16"/>
-    <mergeCell ref="A1:Z1"/>
-    <mergeCell ref="AC11:AF11"/>
-    <mergeCell ref="AC12:AF12"/>
-    <mergeCell ref="AC13:AF13"/>
-    <mergeCell ref="AC14:AF14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -23093,78 +23129,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="34.5" customHeight="1">
-      <c r="A1" s="223" t="s">
+      <c r="A1" s="228" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="223"/>
-      <c r="C1" s="223"/>
-      <c r="D1" s="223"/>
-      <c r="E1" s="223"/>
-      <c r="F1" s="223"/>
-      <c r="G1" s="223"/>
-      <c r="H1" s="223"/>
-      <c r="I1" s="223"/>
-      <c r="J1" s="223"/>
-      <c r="K1" s="223"/>
-      <c r="L1" s="223"/>
-      <c r="M1" s="223"/>
-      <c r="N1" s="223"/>
-      <c r="O1" s="223"/>
-      <c r="P1" s="223"/>
-      <c r="Q1" s="223"/>
-      <c r="R1" s="223"/>
-      <c r="S1" s="223"/>
-      <c r="T1" s="223"/>
-      <c r="U1" s="223"/>
-      <c r="V1" s="223"/>
-      <c r="W1" s="223"/>
-      <c r="X1" s="223"/>
-      <c r="Y1" s="223"/>
-      <c r="Z1" s="223"/>
-      <c r="AA1" s="223"/>
-      <c r="AB1" s="223"/>
-      <c r="AC1" s="223"/>
-      <c r="AD1" s="223"/>
+      <c r="B1" s="228"/>
+      <c r="C1" s="228"/>
+      <c r="D1" s="228"/>
+      <c r="E1" s="228"/>
+      <c r="F1" s="228"/>
+      <c r="G1" s="228"/>
+      <c r="H1" s="228"/>
+      <c r="I1" s="228"/>
+      <c r="J1" s="228"/>
+      <c r="K1" s="228"/>
+      <c r="L1" s="228"/>
+      <c r="M1" s="228"/>
+      <c r="N1" s="228"/>
+      <c r="O1" s="228"/>
+      <c r="P1" s="228"/>
+      <c r="Q1" s="228"/>
+      <c r="R1" s="228"/>
+      <c r="S1" s="228"/>
+      <c r="T1" s="228"/>
+      <c r="U1" s="228"/>
+      <c r="V1" s="228"/>
+      <c r="W1" s="228"/>
+      <c r="X1" s="228"/>
+      <c r="Y1" s="228"/>
+      <c r="Z1" s="228"/>
+      <c r="AA1" s="228"/>
+      <c r="AB1" s="228"/>
+      <c r="AC1" s="228"/>
+      <c r="AD1" s="228"/>
     </row>
     <row r="2" spans="1:52" ht="26.25">
-      <c r="A2" s="224"/>
-      <c r="B2" s="225"/>
-      <c r="C2" s="226" t="s">
+      <c r="A2" s="229"/>
+      <c r="B2" s="230"/>
+      <c r="C2" s="231" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="226"/>
-      <c r="E2" s="226"/>
-      <c r="F2" s="226"/>
-      <c r="G2" s="226"/>
-      <c r="H2" s="226"/>
-      <c r="I2" s="226"/>
-      <c r="J2" s="226"/>
-      <c r="K2" s="226"/>
-      <c r="L2" s="227" t="s">
+      <c r="D2" s="231"/>
+      <c r="E2" s="231"/>
+      <c r="F2" s="231"/>
+      <c r="G2" s="231"/>
+      <c r="H2" s="231"/>
+      <c r="I2" s="231"/>
+      <c r="J2" s="231"/>
+      <c r="K2" s="231"/>
+      <c r="L2" s="232" t="s">
         <v>68</v>
       </c>
-      <c r="M2" s="227"/>
-      <c r="N2" s="227"/>
-      <c r="O2" s="227"/>
-      <c r="P2" s="227"/>
-      <c r="Q2" s="227"/>
-      <c r="R2" s="228" t="s">
+      <c r="M2" s="232"/>
+      <c r="N2" s="232"/>
+      <c r="O2" s="232"/>
+      <c r="P2" s="232"/>
+      <c r="Q2" s="232"/>
+      <c r="R2" s="233" t="s">
         <v>69</v>
       </c>
-      <c r="S2" s="228"/>
-      <c r="T2" s="228"/>
-      <c r="U2" s="228"/>
-      <c r="V2" s="228"/>
-      <c r="W2" s="228"/>
-      <c r="X2" s="228"/>
-      <c r="Y2" s="228"/>
-      <c r="Z2" s="228"/>
-      <c r="AA2" s="228"/>
-      <c r="AB2" s="229" t="s">
+      <c r="S2" s="233"/>
+      <c r="T2" s="233"/>
+      <c r="U2" s="233"/>
+      <c r="V2" s="233"/>
+      <c r="W2" s="233"/>
+      <c r="X2" s="233"/>
+      <c r="Y2" s="233"/>
+      <c r="Z2" s="233"/>
+      <c r="AA2" s="233"/>
+      <c r="AB2" s="234" t="s">
         <v>70</v>
       </c>
-      <c r="AC2" s="229"/>
-      <c r="AD2" s="229"/>
+      <c r="AC2" s="234"/>
+      <c r="AD2" s="234"/>
     </row>
     <row r="3" spans="1:52" ht="45" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -23331,7 +23367,7 @@
         <f>37635+40252.26+18817.85</f>
         <v>96705.11</v>
       </c>
-      <c r="AD4" s="233"/>
+      <c r="AD4" s="226"/>
     </row>
     <row r="5" spans="1:52" ht="15.75">
       <c r="A5" s="17">
@@ -23381,7 +23417,7 @@
         <v>16503.13</v>
       </c>
       <c r="AC5" s="21"/>
-      <c r="AD5" s="233"/>
+      <c r="AD5" s="226"/>
     </row>
     <row r="6" spans="1:52" ht="15.75">
       <c r="A6" s="11">
@@ -23424,7 +23460,7 @@
         <v>996.61</v>
       </c>
       <c r="AC6" s="21"/>
-      <c r="AD6" s="233"/>
+      <c r="AD6" s="226"/>
     </row>
     <row r="7" spans="1:52" ht="15.75">
       <c r="A7" s="17">
@@ -23477,7 +23513,7 @@
         <v>5968</v>
       </c>
       <c r="AC7" s="21"/>
-      <c r="AD7" s="233"/>
+      <c r="AD7" s="226"/>
     </row>
     <row r="8" spans="1:52" ht="15" customHeight="1">
       <c r="A8" s="11">
@@ -23523,7 +23559,7 @@
         <v>12168.98</v>
       </c>
       <c r="AC8" s="21"/>
-      <c r="AD8" s="233"/>
+      <c r="AD8" s="226"/>
     </row>
     <row r="9" spans="1:52" ht="15.75">
       <c r="A9" s="17">
@@ -23571,7 +23607,7 @@
         <v>5970</v>
       </c>
       <c r="AC9" s="21"/>
-      <c r="AD9" s="233"/>
+      <c r="AD9" s="226"/>
     </row>
     <row r="10" spans="1:52" ht="15.75">
       <c r="A10" s="11">
@@ -23619,7 +23655,7 @@
         <v>3257</v>
       </c>
       <c r="AC10" s="21"/>
-      <c r="AD10" s="233"/>
+      <c r="AD10" s="226"/>
     </row>
     <row r="11" spans="1:52" ht="15.75">
       <c r="A11" s="17">
@@ -23663,14 +23699,14 @@
         <v>1034</v>
       </c>
       <c r="AC11" s="21"/>
-      <c r="AD11" s="233"/>
-      <c r="AH11" s="234" t="s">
+      <c r="AD11" s="226"/>
+      <c r="AH11" s="227" t="s">
         <v>83</v>
       </c>
-      <c r="AI11" s="234"/>
-      <c r="AJ11" s="234"/>
-      <c r="AK11" s="234"/>
-      <c r="AL11" s="234"/>
+      <c r="AI11" s="227"/>
+      <c r="AJ11" s="227"/>
+      <c r="AK11" s="227"/>
+      <c r="AL11" s="227"/>
     </row>
     <row r="12" spans="1:52" ht="15.75">
       <c r="A12" s="11">
@@ -23717,12 +23753,12 @@
         <v>3586</v>
       </c>
       <c r="AC12" s="21"/>
-      <c r="AD12" s="233"/>
-      <c r="AH12" s="234"/>
-      <c r="AI12" s="234"/>
-      <c r="AJ12" s="234"/>
-      <c r="AK12" s="234"/>
-      <c r="AL12" s="234"/>
+      <c r="AD12" s="226"/>
+      <c r="AH12" s="227"/>
+      <c r="AI12" s="227"/>
+      <c r="AJ12" s="227"/>
+      <c r="AK12" s="227"/>
+      <c r="AL12" s="227"/>
     </row>
     <row r="13" spans="1:52" ht="15.75">
       <c r="A13" s="17">
@@ -23769,12 +23805,12 @@
         <v>5889</v>
       </c>
       <c r="AC13" s="21"/>
-      <c r="AD13" s="233"/>
-      <c r="AH13" s="234"/>
-      <c r="AI13" s="234"/>
-      <c r="AJ13" s="234"/>
-      <c r="AK13" s="234"/>
-      <c r="AL13" s="234"/>
+      <c r="AD13" s="226"/>
+      <c r="AH13" s="227"/>
+      <c r="AI13" s="227"/>
+      <c r="AJ13" s="227"/>
+      <c r="AK13" s="227"/>
+      <c r="AL13" s="227"/>
     </row>
     <row r="14" spans="1:52" ht="18">
       <c r="A14" s="11">
@@ -23820,13 +23856,13 @@
         <v>7092.93</v>
       </c>
       <c r="AC14" s="21"/>
-      <c r="AD14" s="233"/>
-      <c r="AH14" s="230" t="s">
+      <c r="AD14" s="226"/>
+      <c r="AH14" s="223" t="s">
         <v>62</v>
       </c>
-      <c r="AI14" s="230"/>
-      <c r="AJ14" s="230"/>
-      <c r="AK14" s="230"/>
+      <c r="AI14" s="223"/>
+      <c r="AJ14" s="223"/>
+      <c r="AK14" s="223"/>
       <c r="AL14" s="22">
         <f>AC4+AC20</f>
         <v>133443.15</v>
@@ -23884,13 +23920,13 @@
         <v>6644.28</v>
       </c>
       <c r="AC15" s="16"/>
-      <c r="AD15" s="233"/>
-      <c r="AH15" s="230" t="s">
+      <c r="AD15" s="226"/>
+      <c r="AH15" s="223" t="s">
         <v>2</v>
       </c>
-      <c r="AI15" s="230"/>
-      <c r="AJ15" s="230"/>
-      <c r="AK15" s="230"/>
+      <c r="AI15" s="223"/>
+      <c r="AJ15" s="223"/>
+      <c r="AK15" s="223"/>
       <c r="AL15" s="22">
         <f>AC29</f>
         <v>1000</v>
@@ -23945,13 +23981,13 @@
         <v>5105.1899999999996</v>
       </c>
       <c r="AC16" s="21"/>
-      <c r="AD16" s="233"/>
-      <c r="AH16" s="230" t="s">
+      <c r="AD16" s="226"/>
+      <c r="AH16" s="223" t="s">
         <v>63</v>
       </c>
-      <c r="AI16" s="230"/>
-      <c r="AJ16" s="230"/>
-      <c r="AK16" s="230"/>
+      <c r="AI16" s="223"/>
+      <c r="AJ16" s="223"/>
+      <c r="AK16" s="223"/>
       <c r="AL16" s="22">
         <f>AC21+AC34</f>
         <v>11000</v>
@@ -23996,13 +24032,13 @@
         <v>280.97000000000003</v>
       </c>
       <c r="AC17" s="21"/>
-      <c r="AD17" s="233"/>
-      <c r="AH17" s="230" t="s">
+      <c r="AD17" s="226"/>
+      <c r="AH17" s="223" t="s">
         <v>64</v>
       </c>
-      <c r="AI17" s="230"/>
-      <c r="AJ17" s="230"/>
-      <c r="AK17" s="230"/>
+      <c r="AI17" s="223"/>
+      <c r="AJ17" s="223"/>
+      <c r="AK17" s="223"/>
       <c r="AL17" s="22">
         <f>AB36</f>
         <v>146501.73000000001</v>
@@ -24051,23 +24087,23 @@
         <v>956.98</v>
       </c>
       <c r="AC18" s="21"/>
-      <c r="AD18" s="233"/>
-      <c r="AH18" s="230" t="s">
+      <c r="AD18" s="226"/>
+      <c r="AH18" s="223" t="s">
         <v>65</v>
       </c>
-      <c r="AI18" s="230"/>
-      <c r="AJ18" s="230"/>
-      <c r="AK18" s="230"/>
+      <c r="AI18" s="223"/>
+      <c r="AJ18" s="223"/>
+      <c r="AK18" s="223"/>
       <c r="AL18" s="22">
         <f>SUM(C36:K36)</f>
         <v>56967.92</v>
       </c>
     </row>
     <row r="19" spans="1:38" ht="19.5" customHeight="1">
-      <c r="A19" s="231" t="s">
+      <c r="A19" s="224" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="231"/>
+      <c r="B19" s="224"/>
       <c r="C19" s="23">
         <f>SUM(C4:C18)</f>
         <v>1403.89</v>
@@ -24180,12 +24216,12 @@
         <f>AC19-AB19</f>
         <v>4280.0900000000101</v>
       </c>
-      <c r="AH19" s="230" t="s">
+      <c r="AH19" s="223" t="s">
         <v>84</v>
       </c>
-      <c r="AI19" s="230"/>
-      <c r="AJ19" s="230"/>
-      <c r="AK19" s="230"/>
+      <c r="AI19" s="223"/>
+      <c r="AJ19" s="223"/>
+      <c r="AK19" s="223"/>
       <c r="AL19" s="22">
         <f>SUM(L36:Q36)</f>
         <v>31394.13</v>
@@ -24246,13 +24282,13 @@
       <c r="AC20" s="16">
         <v>36738.04</v>
       </c>
-      <c r="AD20" s="233"/>
-      <c r="AH20" s="230" t="s">
+      <c r="AD20" s="226"/>
+      <c r="AH20" s="223" t="s">
         <v>85</v>
       </c>
-      <c r="AI20" s="230"/>
-      <c r="AJ20" s="230"/>
-      <c r="AK20" s="230"/>
+      <c r="AI20" s="223"/>
+      <c r="AJ20" s="223"/>
+      <c r="AK20" s="223"/>
       <c r="AL20" s="22">
         <f>W36</f>
         <v>35678.97</v>
@@ -24307,14 +24343,14 @@
       <c r="AC21" s="37">
         <v>10000</v>
       </c>
-      <c r="AD21" s="233"/>
+      <c r="AD21" s="226"/>
       <c r="AF21" s="29"/>
-      <c r="AH21" s="230" t="s">
+      <c r="AH21" s="223" t="s">
         <v>86</v>
       </c>
-      <c r="AI21" s="230"/>
-      <c r="AJ21" s="230"/>
-      <c r="AK21" s="230"/>
+      <c r="AI21" s="223"/>
+      <c r="AJ21" s="223"/>
+      <c r="AK21" s="223"/>
       <c r="AL21" s="22">
         <f>SUM(U36:V36)</f>
         <v>11008.46</v>
@@ -24357,13 +24393,13 @@
         <v>0</v>
       </c>
       <c r="AC22" s="21"/>
-      <c r="AD22" s="233"/>
-      <c r="AH22" s="230" t="s">
+      <c r="AD22" s="226"/>
+      <c r="AH22" s="223" t="s">
         <v>32</v>
       </c>
-      <c r="AI22" s="230"/>
-      <c r="AJ22" s="230"/>
-      <c r="AK22" s="230"/>
+      <c r="AI22" s="223"/>
+      <c r="AJ22" s="223"/>
+      <c r="AK22" s="223"/>
       <c r="AL22" s="22">
         <f>T36</f>
         <v>0</v>
@@ -24418,13 +24454,13 @@
         <v>6881.28</v>
       </c>
       <c r="AC23" s="21"/>
-      <c r="AD23" s="233"/>
-      <c r="AH23" s="230" t="s">
+      <c r="AD23" s="226"/>
+      <c r="AH23" s="223" t="s">
         <v>87</v>
       </c>
-      <c r="AI23" s="230"/>
-      <c r="AJ23" s="230"/>
-      <c r="AK23" s="230"/>
+      <c r="AI23" s="223"/>
+      <c r="AJ23" s="223"/>
+      <c r="AK23" s="223"/>
       <c r="AL23" s="22">
         <f>X36</f>
         <v>5267.98</v>
@@ -24479,7 +24515,7 @@
         <v>6126.69</v>
       </c>
       <c r="AC24" s="21"/>
-      <c r="AD24" s="233"/>
+      <c r="AD24" s="226"/>
     </row>
     <row r="25" spans="1:38" ht="15.75">
       <c r="A25" s="17">
@@ -24523,7 +24559,7 @@
         <v>7750</v>
       </c>
       <c r="AC25" s="21"/>
-      <c r="AD25" s="233"/>
+      <c r="AD25" s="226"/>
     </row>
     <row r="26" spans="1:38" ht="15.75">
       <c r="A26" s="11">
@@ -24570,7 +24606,7 @@
         <v>2803</v>
       </c>
       <c r="AC26" s="16"/>
-      <c r="AD26" s="233"/>
+      <c r="AD26" s="226"/>
     </row>
     <row r="27" spans="1:38" ht="15.75">
       <c r="A27" s="17">
@@ -24618,7 +24654,7 @@
         <v>2088.96</v>
       </c>
       <c r="AC27" s="21"/>
-      <c r="AD27" s="233"/>
+      <c r="AD27" s="226"/>
     </row>
     <row r="28" spans="1:38" ht="15.75">
       <c r="A28" s="11">
@@ -24664,7 +24700,7 @@
         <v>3468</v>
       </c>
       <c r="AC28" s="21"/>
-      <c r="AD28" s="233"/>
+      <c r="AD28" s="226"/>
     </row>
     <row r="29" spans="1:38" ht="15.75">
       <c r="A29" s="17">
@@ -24717,7 +24753,7 @@
       <c r="AC29" s="21">
         <v>1000</v>
       </c>
-      <c r="AD29" s="233"/>
+      <c r="AD29" s="226"/>
     </row>
     <row r="30" spans="1:38" ht="15.75">
       <c r="A30" s="11">
@@ -24765,7 +24801,7 @@
         <v>4016.5</v>
       </c>
       <c r="AC30" s="21"/>
-      <c r="AD30" s="233"/>
+      <c r="AD30" s="226"/>
     </row>
     <row r="31" spans="1:38" ht="15.75">
       <c r="A31" s="17">
@@ -24809,7 +24845,7 @@
         <v>2801.78</v>
       </c>
       <c r="AC31" s="21"/>
-      <c r="AD31" s="233"/>
+      <c r="AD31" s="226"/>
     </row>
     <row r="32" spans="1:38" ht="15.75">
       <c r="A32" s="11">
@@ -24858,7 +24894,7 @@
         <v>3807.11</v>
       </c>
       <c r="AC32" s="21"/>
-      <c r="AD32" s="233"/>
+      <c r="AD32" s="226"/>
     </row>
     <row r="33" spans="1:30" ht="15.75">
       <c r="A33" s="17">
@@ -24902,7 +24938,7 @@
         <v>675.44</v>
       </c>
       <c r="AC33" s="21"/>
-      <c r="AD33" s="233"/>
+      <c r="AD33" s="226"/>
     </row>
     <row r="34" spans="1:30" ht="15.75">
       <c r="A34" s="11">
@@ -24946,13 +24982,13 @@
       <c r="AC34" s="37">
         <v>1000</v>
       </c>
-      <c r="AD34" s="233"/>
+      <c r="AD34" s="226"/>
     </row>
     <row r="35" spans="1:30" ht="14.25" customHeight="1">
-      <c r="A35" s="231" t="s">
+      <c r="A35" s="224" t="s">
         <v>55</v>
       </c>
-      <c r="B35" s="231"/>
+      <c r="B35" s="224"/>
       <c r="C35" s="23">
         <f t="shared" ref="C35:AC35" si="3">SUM(C20:C34)</f>
         <v>2169.6999999999998</v>
@@ -25067,10 +25103,10 @@
       </c>
     </row>
     <row r="36" spans="1:30" ht="31.5" customHeight="1">
-      <c r="A36" s="232" t="s">
+      <c r="A36" s="225" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="232"/>
+      <c r="B36" s="225"/>
       <c r="C36" s="31">
         <f>SUM(C19,C35)</f>
         <v>3573.59</v>
@@ -25201,6 +25237,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="AH23:AK23"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="A36:B36"/>
@@ -25217,12 +25259,6 @@
     <mergeCell ref="AH16:AK16"/>
     <mergeCell ref="AH17:AK17"/>
     <mergeCell ref="AH18:AK18"/>
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:K2"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -25243,78 +25279,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="34.5" customHeight="1">
-      <c r="A1" s="223" t="s">
+      <c r="A1" s="228" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="223"/>
-      <c r="C1" s="223"/>
-      <c r="D1" s="223"/>
-      <c r="E1" s="223"/>
-      <c r="F1" s="223"/>
-      <c r="G1" s="223"/>
-      <c r="H1" s="223"/>
-      <c r="I1" s="223"/>
-      <c r="J1" s="223"/>
-      <c r="K1" s="223"/>
-      <c r="L1" s="223"/>
-      <c r="M1" s="223"/>
-      <c r="N1" s="223"/>
-      <c r="O1" s="223"/>
-      <c r="P1" s="223"/>
-      <c r="Q1" s="223"/>
-      <c r="R1" s="223"/>
-      <c r="S1" s="223"/>
-      <c r="T1" s="223"/>
-      <c r="U1" s="223"/>
-      <c r="V1" s="223"/>
-      <c r="W1" s="223"/>
-      <c r="X1" s="223"/>
-      <c r="Y1" s="223"/>
-      <c r="Z1" s="223"/>
-      <c r="AA1" s="223"/>
-      <c r="AB1" s="223"/>
-      <c r="AC1" s="223"/>
-      <c r="AD1" s="223"/>
+      <c r="B1" s="228"/>
+      <c r="C1" s="228"/>
+      <c r="D1" s="228"/>
+      <c r="E1" s="228"/>
+      <c r="F1" s="228"/>
+      <c r="G1" s="228"/>
+      <c r="H1" s="228"/>
+      <c r="I1" s="228"/>
+      <c r="J1" s="228"/>
+      <c r="K1" s="228"/>
+      <c r="L1" s="228"/>
+      <c r="M1" s="228"/>
+      <c r="N1" s="228"/>
+      <c r="O1" s="228"/>
+      <c r="P1" s="228"/>
+      <c r="Q1" s="228"/>
+      <c r="R1" s="228"/>
+      <c r="S1" s="228"/>
+      <c r="T1" s="228"/>
+      <c r="U1" s="228"/>
+      <c r="V1" s="228"/>
+      <c r="W1" s="228"/>
+      <c r="X1" s="228"/>
+      <c r="Y1" s="228"/>
+      <c r="Z1" s="228"/>
+      <c r="AA1" s="228"/>
+      <c r="AB1" s="228"/>
+      <c r="AC1" s="228"/>
+      <c r="AD1" s="228"/>
     </row>
     <row r="2" spans="1:52" ht="26.25">
-      <c r="A2" s="224"/>
-      <c r="B2" s="225"/>
-      <c r="C2" s="226" t="s">
+      <c r="A2" s="229"/>
+      <c r="B2" s="230"/>
+      <c r="C2" s="231" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="226"/>
-      <c r="E2" s="226"/>
-      <c r="F2" s="226"/>
-      <c r="G2" s="226"/>
-      <c r="H2" s="226"/>
-      <c r="I2" s="226"/>
-      <c r="J2" s="226"/>
-      <c r="K2" s="226"/>
-      <c r="L2" s="227" t="s">
+      <c r="D2" s="231"/>
+      <c r="E2" s="231"/>
+      <c r="F2" s="231"/>
+      <c r="G2" s="231"/>
+      <c r="H2" s="231"/>
+      <c r="I2" s="231"/>
+      <c r="J2" s="231"/>
+      <c r="K2" s="231"/>
+      <c r="L2" s="232" t="s">
         <v>68</v>
       </c>
-      <c r="M2" s="227"/>
-      <c r="N2" s="227"/>
-      <c r="O2" s="227"/>
-      <c r="P2" s="227"/>
-      <c r="Q2" s="227"/>
-      <c r="R2" s="228" t="s">
+      <c r="M2" s="232"/>
+      <c r="N2" s="232"/>
+      <c r="O2" s="232"/>
+      <c r="P2" s="232"/>
+      <c r="Q2" s="232"/>
+      <c r="R2" s="233" t="s">
         <v>69</v>
       </c>
-      <c r="S2" s="228"/>
-      <c r="T2" s="228"/>
-      <c r="U2" s="228"/>
-      <c r="V2" s="228"/>
-      <c r="W2" s="228"/>
-      <c r="X2" s="228"/>
-      <c r="Y2" s="228"/>
-      <c r="Z2" s="228"/>
-      <c r="AA2" s="228"/>
-      <c r="AB2" s="229" t="s">
+      <c r="S2" s="233"/>
+      <c r="T2" s="233"/>
+      <c r="U2" s="233"/>
+      <c r="V2" s="233"/>
+      <c r="W2" s="233"/>
+      <c r="X2" s="233"/>
+      <c r="Y2" s="233"/>
+      <c r="Z2" s="233"/>
+      <c r="AA2" s="233"/>
+      <c r="AB2" s="234" t="s">
         <v>70</v>
       </c>
-      <c r="AC2" s="229"/>
-      <c r="AD2" s="229"/>
+      <c r="AC2" s="234"/>
+      <c r="AD2" s="234"/>
     </row>
     <row r="3" spans="1:52" ht="45" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -25479,7 +25515,7 @@
         <f>66577.47+18817</f>
         <v>85394.47</v>
       </c>
-      <c r="AD4" s="233"/>
+      <c r="AD4" s="226"/>
     </row>
     <row r="5" spans="1:52" ht="15.75">
       <c r="A5" s="17">
@@ -25534,7 +25570,7 @@
         <v>7116</v>
       </c>
       <c r="AC5" s="165"/>
-      <c r="AD5" s="233"/>
+      <c r="AD5" s="226"/>
     </row>
     <row r="6" spans="1:52" ht="15.75">
       <c r="A6" s="11">
@@ -25582,7 +25618,7 @@
         <v>17146</v>
       </c>
       <c r="AC6" s="165"/>
-      <c r="AD6" s="233"/>
+      <c r="AD6" s="226"/>
     </row>
     <row r="7" spans="1:52" ht="15.75">
       <c r="A7" s="17">
@@ -25639,7 +25675,7 @@
         <v>6206.84</v>
       </c>
       <c r="AC7" s="165"/>
-      <c r="AD7" s="233"/>
+      <c r="AD7" s="226"/>
     </row>
     <row r="8" spans="1:52" ht="15" customHeight="1">
       <c r="A8" s="11">
@@ -25698,7 +25734,7 @@
         <v>8204</v>
       </c>
       <c r="AC8" s="165"/>
-      <c r="AD8" s="233"/>
+      <c r="AD8" s="226"/>
     </row>
     <row r="9" spans="1:52" ht="15.75">
       <c r="A9" s="17">
@@ -25747,7 +25783,7 @@
         <v>8276</v>
       </c>
       <c r="AC9" s="165"/>
-      <c r="AD9" s="233"/>
+      <c r="AD9" s="226"/>
     </row>
     <row r="10" spans="1:52" ht="15.75">
       <c r="A10" s="11">
@@ -25795,7 +25831,7 @@
       <c r="AC10" s="165">
         <v>28225.5</v>
       </c>
-      <c r="AD10" s="233"/>
+      <c r="AD10" s="226"/>
     </row>
     <row r="11" spans="1:52" ht="15.75">
       <c r="A11" s="17">
@@ -25845,14 +25881,14 @@
         <v>5638.53</v>
       </c>
       <c r="AC11" s="165"/>
-      <c r="AD11" s="233"/>
-      <c r="AH11" s="234" t="s">
+      <c r="AD11" s="226"/>
+      <c r="AH11" s="227" t="s">
         <v>83</v>
       </c>
-      <c r="AI11" s="234"/>
-      <c r="AJ11" s="234"/>
-      <c r="AK11" s="234"/>
-      <c r="AL11" s="234"/>
+      <c r="AI11" s="227"/>
+      <c r="AJ11" s="227"/>
+      <c r="AK11" s="227"/>
+      <c r="AL11" s="227"/>
     </row>
     <row r="12" spans="1:52" ht="15.75">
       <c r="A12" s="11">
@@ -25906,12 +25942,12 @@
         <v>33365</v>
       </c>
       <c r="AC12" s="165"/>
-      <c r="AD12" s="233"/>
-      <c r="AH12" s="234"/>
-      <c r="AI12" s="234"/>
-      <c r="AJ12" s="234"/>
-      <c r="AK12" s="234"/>
-      <c r="AL12" s="234"/>
+      <c r="AD12" s="226"/>
+      <c r="AH12" s="227"/>
+      <c r="AI12" s="227"/>
+      <c r="AJ12" s="227"/>
+      <c r="AK12" s="227"/>
+      <c r="AL12" s="227"/>
     </row>
     <row r="13" spans="1:52" ht="15.75">
       <c r="A13" s="17">
@@ -25969,12 +26005,12 @@
         <v>10965.96</v>
       </c>
       <c r="AC13" s="165"/>
-      <c r="AD13" s="233"/>
-      <c r="AH13" s="234"/>
-      <c r="AI13" s="234"/>
-      <c r="AJ13" s="234"/>
-      <c r="AK13" s="234"/>
-      <c r="AL13" s="234"/>
+      <c r="AD13" s="226"/>
+      <c r="AH13" s="227"/>
+      <c r="AI13" s="227"/>
+      <c r="AJ13" s="227"/>
+      <c r="AK13" s="227"/>
+      <c r="AL13" s="227"/>
     </row>
     <row r="14" spans="1:52" ht="18">
       <c r="A14" s="11">
@@ -26022,13 +26058,13 @@
         <v>1614.53</v>
       </c>
       <c r="AC14" s="165"/>
-      <c r="AD14" s="233"/>
-      <c r="AH14" s="230" t="s">
+      <c r="AD14" s="226"/>
+      <c r="AH14" s="223" t="s">
         <v>62</v>
       </c>
-      <c r="AI14" s="230"/>
-      <c r="AJ14" s="230"/>
-      <c r="AK14" s="230"/>
+      <c r="AI14" s="223"/>
+      <c r="AJ14" s="223"/>
+      <c r="AK14" s="223"/>
       <c r="AL14" s="22">
         <f>AC4+AC19+AC23+AC10</f>
         <v>287751.42</v>
@@ -26086,13 +26122,13 @@
         <v>6960.82</v>
       </c>
       <c r="AC15" s="163"/>
-      <c r="AD15" s="233"/>
-      <c r="AH15" s="230" t="s">
+      <c r="AD15" s="226"/>
+      <c r="AH15" s="223" t="s">
         <v>2</v>
       </c>
-      <c r="AI15" s="230"/>
-      <c r="AJ15" s="230"/>
-      <c r="AK15" s="230"/>
+      <c r="AI15" s="223"/>
+      <c r="AJ15" s="223"/>
+      <c r="AK15" s="223"/>
       <c r="AL15" s="22">
         <f>AC20</f>
         <v>1000</v>
@@ -26146,13 +26182,13 @@
       <c r="AC16" s="167">
         <v>5000</v>
       </c>
-      <c r="AD16" s="233"/>
-      <c r="AH16" s="230" t="s">
+      <c r="AD16" s="226"/>
+      <c r="AH16" s="223" t="s">
         <v>63</v>
       </c>
-      <c r="AI16" s="230"/>
-      <c r="AJ16" s="230"/>
-      <c r="AK16" s="230"/>
+      <c r="AI16" s="223"/>
+      <c r="AJ16" s="223"/>
+      <c r="AK16" s="223"/>
       <c r="AL16" s="22">
         <f>AC16+AC28+AC34+AC35</f>
         <v>60000</v>
@@ -26210,7 +26246,7 @@
         <v>5002</v>
       </c>
       <c r="AC17" s="163"/>
-      <c r="AD17" s="233"/>
+      <c r="AD17" s="226"/>
       <c r="AH17" s="235" t="s">
         <v>67</v>
       </c>
@@ -26339,12 +26375,12 @@
         <f>AC18-AB18</f>
         <v>-900.67000000001281</v>
       </c>
-      <c r="AH18" s="230" t="s">
+      <c r="AH18" s="223" t="s">
         <v>84</v>
       </c>
-      <c r="AI18" s="230"/>
-      <c r="AJ18" s="230"/>
-      <c r="AK18" s="230"/>
+      <c r="AI18" s="223"/>
+      <c r="AJ18" s="223"/>
+      <c r="AK18" s="223"/>
       <c r="AL18" s="22">
         <f>SUM(L37:Q37)</f>
         <v>35695</v>
@@ -26398,13 +26434,13 @@
       <c r="AC19" s="16">
         <v>38575.449999999997</v>
       </c>
-      <c r="AD19" s="233"/>
-      <c r="AH19" s="230" t="s">
+      <c r="AD19" s="226"/>
+      <c r="AH19" s="223" t="s">
         <v>85</v>
       </c>
-      <c r="AI19" s="230"/>
-      <c r="AJ19" s="230"/>
-      <c r="AK19" s="230"/>
+      <c r="AI19" s="223"/>
+      <c r="AJ19" s="223"/>
+      <c r="AK19" s="223"/>
       <c r="AL19" s="22">
         <f>W37</f>
         <v>38934</v>
@@ -26461,14 +26497,14 @@
       <c r="AC20" s="21">
         <v>1000</v>
       </c>
-      <c r="AD20" s="233"/>
+      <c r="AD20" s="226"/>
       <c r="AF20" s="29"/>
-      <c r="AH20" s="230" t="s">
+      <c r="AH20" s="223" t="s">
         <v>86</v>
       </c>
-      <c r="AI20" s="230"/>
-      <c r="AJ20" s="230"/>
-      <c r="AK20" s="230"/>
+      <c r="AI20" s="223"/>
+      <c r="AJ20" s="223"/>
+      <c r="AK20" s="223"/>
       <c r="AL20" s="22">
         <f>SUM(U37:V37)</f>
         <v>15264.08</v>
@@ -26514,7 +26550,7 @@
         <v>1980</v>
       </c>
       <c r="AC21" s="21"/>
-      <c r="AD21" s="233"/>
+      <c r="AD21" s="226"/>
       <c r="AH21" s="238" t="s">
         <v>32</v>
       </c>
@@ -26575,7 +26611,7 @@
         <v>3710.54</v>
       </c>
       <c r="AC22" s="21"/>
-      <c r="AD22" s="233"/>
+      <c r="AD22" s="226"/>
       <c r="AH22" s="239"/>
       <c r="AI22" s="239"/>
       <c r="AJ22" s="239"/>
@@ -26631,7 +26667,7 @@
         <f>21986+70637+42933</f>
         <v>135556</v>
       </c>
-      <c r="AD23" s="233"/>
+      <c r="AD23" s="226"/>
     </row>
     <row r="24" spans="1:38" ht="15.75">
       <c r="A24" s="17">
@@ -26691,7 +26727,7 @@
         <v>26293.41</v>
       </c>
       <c r="AC24" s="21"/>
-      <c r="AD24" s="233"/>
+      <c r="AD24" s="226"/>
     </row>
     <row r="25" spans="1:38" ht="15.75">
       <c r="A25" s="11">
@@ -26736,7 +26772,7 @@
         <v>542</v>
       </c>
       <c r="AC25" s="16"/>
-      <c r="AD25" s="233"/>
+      <c r="AD25" s="226"/>
     </row>
     <row r="26" spans="1:38" ht="15.75">
       <c r="A26" s="17">
@@ -26796,7 +26832,7 @@
         <v>5856.07</v>
       </c>
       <c r="AC26" s="21"/>
-      <c r="AD26" s="233"/>
+      <c r="AD26" s="226"/>
     </row>
     <row r="27" spans="1:38" ht="15.75">
       <c r="A27" s="11">
@@ -26850,7 +26886,7 @@
         <v>14081.2</v>
       </c>
       <c r="AC27" s="21"/>
-      <c r="AD27" s="233"/>
+      <c r="AD27" s="226"/>
     </row>
     <row r="28" spans="1:38" ht="15.75">
       <c r="A28" s="17">
@@ -26894,7 +26930,7 @@
       <c r="AC28" s="21">
         <v>20000</v>
       </c>
-      <c r="AD28" s="233"/>
+      <c r="AD28" s="226"/>
     </row>
     <row r="29" spans="1:38" ht="15.75">
       <c r="A29" s="11">
@@ -26943,7 +26979,7 @@
         <v>4019.84</v>
       </c>
       <c r="AC29" s="21"/>
-      <c r="AD29" s="233"/>
+      <c r="AD29" s="226"/>
     </row>
     <row r="30" spans="1:38" ht="15.75">
       <c r="A30" s="17">
@@ -26994,7 +27030,7 @@
         <v>2628.39</v>
       </c>
       <c r="AC30" s="21"/>
-      <c r="AD30" s="233"/>
+      <c r="AD30" s="226"/>
     </row>
     <row r="31" spans="1:38" ht="16.5" thickBot="1">
       <c r="A31" s="139">
@@ -27050,7 +27086,7 @@
         <v>12589</v>
       </c>
       <c r="AC31" s="21"/>
-      <c r="AD31" s="233"/>
+      <c r="AD31" s="226"/>
     </row>
     <row r="32" spans="1:38" ht="15.75">
       <c r="A32" s="147">
@@ -27112,7 +27148,7 @@
         <v>18544.419999999998</v>
       </c>
       <c r="AC32" s="21"/>
-      <c r="AD32" s="233"/>
+      <c r="AD32" s="226"/>
     </row>
     <row r="33" spans="1:34" ht="15.75">
       <c r="A33" s="154">
@@ -27163,7 +27199,7 @@
         <v>9526.09</v>
       </c>
       <c r="AC33" s="21"/>
-      <c r="AD33" s="233"/>
+      <c r="AD33" s="226"/>
     </row>
     <row r="34" spans="1:34" ht="15.75">
       <c r="A34" s="151">
@@ -27225,7 +27261,7 @@
       <c r="AC34" s="21">
         <v>20000</v>
       </c>
-      <c r="AD34" s="233"/>
+      <c r="AD34" s="226"/>
     </row>
     <row r="35" spans="1:34" ht="16.5" thickBot="1">
       <c r="A35" s="158">
@@ -27281,7 +27317,7 @@
       <c r="AC35" s="37">
         <v>15000</v>
       </c>
-      <c r="AD35" s="233"/>
+      <c r="AD35" s="226"/>
     </row>
     <row r="36" spans="1:34" ht="24" customHeight="1">
       <c r="A36" s="240" t="s">
@@ -27403,10 +27439,10 @@
       <c r="AH36" s="162"/>
     </row>
     <row r="37" spans="1:34" ht="31.5" customHeight="1">
-      <c r="A37" s="232" t="s">
+      <c r="A37" s="225" t="s">
         <v>56</v>
       </c>
-      <c r="B37" s="232"/>
+      <c r="B37" s="225"/>
       <c r="C37" s="31">
         <f t="shared" ref="C37:R37" si="7">SUM(C18,C36)</f>
         <v>1423.08</v>
@@ -27537,6 +27573,12 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="AD19:AD35"/>
     <mergeCell ref="AH11:AL13"/>
@@ -27552,12 +27594,6 @@
     <mergeCell ref="AH16:AK16"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="AH18:AK18"/>
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:K2"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Другое/2026/Доходы-Расходы.xlsx
+++ b/Другое/2026/Доходы-Расходы.xlsx
@@ -1,13 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROG\Git\Repository_1\Другое\2026\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10980" tabRatio="672" activeTab="9"/>
   </bookViews>
@@ -23,7 +18,7 @@
     <sheet name="Сентябрь 2026" sheetId="10" r:id="rId9"/>
     <sheet name="Октябрь 2026" sheetId="11" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="125725"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -46,7 +41,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="S3" authorId="0" shapeId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -71,7 +66,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P11" authorId="0" shapeId="0">
+    <comment ref="P11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -96,7 +91,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R16" authorId="0" shapeId="0">
+    <comment ref="R16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -121,7 +116,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P20" authorId="0" shapeId="0">
+    <comment ref="P20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -145,7 +140,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P24" authorId="0" shapeId="0">
+    <comment ref="P24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -169,7 +164,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H25" authorId="0" shapeId="0">
+    <comment ref="H25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -194,7 +189,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J25" authorId="0" shapeId="0">
+    <comment ref="J25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -218,7 +213,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J26" authorId="0" shapeId="0">
+    <comment ref="J26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -242,7 +237,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L26" authorId="0" shapeId="0">
+    <comment ref="L26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -266,7 +261,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P26" authorId="0" shapeId="0">
+    <comment ref="P26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -290,7 +285,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J27" authorId="0" shapeId="0">
+    <comment ref="J27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -324,7 +319,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="R3" authorId="0" shapeId="0">
+    <comment ref="R3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -348,7 +343,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F4" authorId="0" shapeId="0">
+    <comment ref="F4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -372,7 +367,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R4" authorId="0" shapeId="0">
+    <comment ref="R4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -397,7 +392,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0" shapeId="0">
+    <comment ref="S4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -421,7 +416,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T4" authorId="0" shapeId="0">
+    <comment ref="T4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -445,7 +440,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G5" authorId="0" shapeId="0">
+    <comment ref="G5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -469,7 +464,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P5" authorId="0" shapeId="0">
+    <comment ref="P5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -493,7 +488,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P6" authorId="0" shapeId="0">
+    <comment ref="P6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -518,7 +513,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S10" authorId="0" shapeId="0">
+    <comment ref="S10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -542,7 +537,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A11" authorId="0" shapeId="0">
+    <comment ref="A11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -566,7 +561,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R18" authorId="0" shapeId="0">
+    <comment ref="R18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -591,7 +586,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S18" authorId="0" shapeId="0">
+    <comment ref="S18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -615,7 +610,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R19" authorId="0" shapeId="0">
+    <comment ref="R19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -640,7 +635,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S19" authorId="0" shapeId="0">
+    <comment ref="S19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -664,7 +659,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S20" authorId="0" shapeId="0">
+    <comment ref="S20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -688,7 +683,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T20" authorId="0" shapeId="0">
+    <comment ref="T20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -712,7 +707,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S22" authorId="0" shapeId="0">
+    <comment ref="S22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -736,7 +731,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S26" authorId="0" shapeId="0">
+    <comment ref="S26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -770,7 +765,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="Q3" authorId="0" shapeId="0">
+    <comment ref="Q3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -785,7 +780,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0" shapeId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -810,7 +805,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0" shapeId="0">
+    <comment ref="T3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -835,7 +830,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U3" authorId="0" shapeId="0">
+    <comment ref="U3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -859,7 +854,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0" shapeId="0">
+    <comment ref="H4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -883,7 +878,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K4" authorId="0" shapeId="0">
+    <comment ref="K4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -907,7 +902,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N4" authorId="0" shapeId="0">
+    <comment ref="N4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -931,7 +926,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q4" authorId="0" shapeId="0">
+    <comment ref="Q4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -956,7 +951,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0" shapeId="0">
+    <comment ref="S4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -981,7 +976,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U4" authorId="0" shapeId="0">
+    <comment ref="U4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1006,7 +1001,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V4" authorId="0" shapeId="0">
+    <comment ref="V4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1030,7 +1025,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I5" authorId="0" shapeId="0">
+    <comment ref="I5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1055,7 +1050,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S5" authorId="0" shapeId="0">
+    <comment ref="S5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1079,7 +1074,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K6" authorId="0" shapeId="0">
+    <comment ref="K6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1104,7 +1099,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S6" authorId="0" shapeId="0">
+    <comment ref="S6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1129,7 +1124,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H8" authorId="0" shapeId="0">
+    <comment ref="H8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1144,7 +1139,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0">
+    <comment ref="E10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1169,7 +1164,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X11" authorId="0" shapeId="0">
+    <comment ref="X11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1194,7 +1189,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X12" authorId="0" shapeId="0">
+    <comment ref="X12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1218,7 +1213,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H14" authorId="0" shapeId="0">
+    <comment ref="H14" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1243,7 +1238,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H15" authorId="0" shapeId="0">
+    <comment ref="H15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1258,7 +1253,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T15" authorId="0" shapeId="0">
+    <comment ref="T15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1272,7 +1267,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E17" authorId="0" shapeId="0">
+    <comment ref="E17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1296,7 +1291,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q17" authorId="0" shapeId="0">
+    <comment ref="Q17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1320,7 +1315,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S19" authorId="0" shapeId="0">
+    <comment ref="S19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1344,7 +1339,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S21" authorId="0" shapeId="0">
+    <comment ref="S21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1369,7 +1364,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T21" authorId="0" shapeId="0">
+    <comment ref="T21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1393,7 +1388,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F22" authorId="0" shapeId="0">
+    <comment ref="F22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1417,7 +1412,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H22" authorId="0" shapeId="0">
+    <comment ref="H22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1441,7 +1436,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T22" authorId="0" shapeId="0">
+    <comment ref="T22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1465,7 +1460,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E24" authorId="0" shapeId="0">
+    <comment ref="E24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1490,7 +1485,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F25" authorId="0" shapeId="0">
+    <comment ref="F25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1515,7 +1510,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E27" authorId="0" shapeId="0">
+    <comment ref="E27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1540,7 +1535,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H29" authorId="0" shapeId="0">
+    <comment ref="H29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1564,7 +1559,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S29" authorId="0" shapeId="0">
+    <comment ref="S29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1588,7 +1583,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F30" authorId="0" shapeId="0">
+    <comment ref="F30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1612,7 +1607,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X30" authorId="0" shapeId="0">
+    <comment ref="X30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1636,7 +1631,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H31" authorId="0" shapeId="0">
+    <comment ref="H31" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1660,7 +1655,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S33" authorId="0" shapeId="0">
+    <comment ref="S33" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1684,7 +1679,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X35" authorId="0" shapeId="0">
+    <comment ref="X35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1718,7 +1713,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="S3" authorId="0" shapeId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1742,7 +1737,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0" shapeId="0">
+    <comment ref="T3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1767,7 +1762,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0" shapeId="0">
+    <comment ref="H4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1791,7 +1786,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F5" authorId="0" shapeId="0">
+    <comment ref="F5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1815,7 +1810,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S5" authorId="0" shapeId="0">
+    <comment ref="S5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1839,7 +1834,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H6" authorId="0" shapeId="0">
+    <comment ref="H6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1863,7 +1858,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K7" authorId="0" shapeId="0">
+    <comment ref="K7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1887,7 +1882,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X7" authorId="0" shapeId="0">
+    <comment ref="X7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1911,7 +1906,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K8" authorId="0" shapeId="0">
+    <comment ref="K8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1935,7 +1930,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K9" authorId="0" shapeId="0">
+    <comment ref="K9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1959,7 +1954,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F10" authorId="0" shapeId="0">
+    <comment ref="F10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1984,7 +1979,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H11" authorId="0" shapeId="0">
+    <comment ref="H11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2008,7 +2003,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H13" authorId="0" shapeId="0">
+    <comment ref="H13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2033,7 +2028,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q19" authorId="0" shapeId="0">
+    <comment ref="Q19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2057,7 +2052,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S19" authorId="0" shapeId="0">
+    <comment ref="S19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2081,7 +2076,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T20" authorId="0" shapeId="0">
+    <comment ref="T20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2106,7 +2101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H21" authorId="0" shapeId="0">
+    <comment ref="H21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2130,7 +2125,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T21" authorId="0" shapeId="0">
+    <comment ref="T21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2155,7 +2150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X21" authorId="0" shapeId="0">
+    <comment ref="X21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2179,7 +2174,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J24" authorId="0" shapeId="0">
+    <comment ref="J24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2203,7 +2198,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S24" authorId="0" shapeId="0">
+    <comment ref="S24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2227,7 +2222,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V25" authorId="0" shapeId="0">
+    <comment ref="V25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2251,7 +2246,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H27" authorId="0" shapeId="0">
+    <comment ref="H27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2275,7 +2270,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S27" authorId="0" shapeId="0">
+    <comment ref="S27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2299,7 +2294,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H28" authorId="0" shapeId="0">
+    <comment ref="H28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2323,7 +2318,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V28" authorId="0" shapeId="0">
+    <comment ref="V28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2348,7 +2343,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X28" authorId="0" shapeId="0">
+    <comment ref="X28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2372,7 +2367,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E29" authorId="0" shapeId="0">
+    <comment ref="E29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2396,7 +2391,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X29" authorId="0" shapeId="0">
+    <comment ref="X29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2420,7 +2415,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S31" authorId="0" shapeId="0">
+    <comment ref="S31" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2444,7 +2439,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S33" authorId="0" shapeId="0">
+    <comment ref="S33" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2468,7 +2463,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X34" authorId="0" shapeId="0">
+    <comment ref="X34" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2503,7 +2498,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0" shapeId="0">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2527,7 +2522,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0" shapeId="0">
+    <comment ref="H3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2551,7 +2546,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0" shapeId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2575,7 +2570,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0" shapeId="0">
+    <comment ref="T3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2599,7 +2594,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V3" authorId="0" shapeId="0">
+    <comment ref="V3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2623,7 +2618,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0" shapeId="0">
+    <comment ref="H4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2647,7 +2642,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N4" authorId="0" shapeId="0">
+    <comment ref="N4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2671,7 +2666,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q4" authorId="0" shapeId="0">
+    <comment ref="Q4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2695,7 +2690,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0" shapeId="0">
+    <comment ref="S4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2719,7 +2714,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H5" authorId="0" shapeId="0">
+    <comment ref="H5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2743,7 +2738,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T5" authorId="0" shapeId="0">
+    <comment ref="T5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2767,7 +2762,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F6" authorId="0" shapeId="0">
+    <comment ref="F6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2791,7 +2786,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H6" authorId="0" shapeId="0">
+    <comment ref="H6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2815,7 +2810,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T6" authorId="0" shapeId="0">
+    <comment ref="T6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2839,7 +2834,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q7" authorId="0" shapeId="0">
+    <comment ref="Q7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2863,7 +2858,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F8" authorId="0" shapeId="0">
+    <comment ref="F8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2887,7 +2882,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q8" authorId="0" shapeId="0">
+    <comment ref="Q8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2911,7 +2906,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S8" authorId="0" shapeId="0">
+    <comment ref="S8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2935,7 +2930,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q9" authorId="0" shapeId="0">
+    <comment ref="Q9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2959,7 +2954,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X9" authorId="0" shapeId="0">
+    <comment ref="X9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2983,7 +2978,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0">
+    <comment ref="E10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3007,7 +3002,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E11" authorId="0" shapeId="0">
+    <comment ref="E11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3031,7 +3026,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I11" authorId="0" shapeId="0">
+    <comment ref="I11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3055,7 +3050,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q12" authorId="0" shapeId="0">
+    <comment ref="Q12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3080,7 +3075,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q13" authorId="0" shapeId="0">
+    <comment ref="Q13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3104,7 +3099,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S13" authorId="0" shapeId="0">
+    <comment ref="S13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3128,7 +3123,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X14" authorId="0" shapeId="0">
+    <comment ref="X14" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3152,7 +3147,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X16" authorId="0" shapeId="0">
+    <comment ref="X16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3176,7 +3171,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H17" authorId="0" shapeId="0">
+    <comment ref="H17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3201,7 +3196,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S17" authorId="0" shapeId="0">
+    <comment ref="S17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3225,7 +3220,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T17" authorId="0" shapeId="0">
+    <comment ref="T17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3249,7 +3244,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H19" authorId="0" shapeId="0">
+    <comment ref="H19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3273,7 +3268,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N19" authorId="0" shapeId="0">
+    <comment ref="N19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3307,7 +3302,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="Q3" authorId="0" shapeId="0">
+    <comment ref="Q3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3332,7 +3327,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0" shapeId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3356,7 +3351,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0" shapeId="0">
+    <comment ref="H4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3380,7 +3375,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S5" authorId="0" shapeId="0">
+    <comment ref="S5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3405,7 +3400,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V6" authorId="0" shapeId="0">
+    <comment ref="V6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3429,7 +3424,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F7" authorId="0" shapeId="0">
+    <comment ref="F7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3453,7 +3448,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q8" authorId="0" shapeId="0">
+    <comment ref="Q8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3478,7 +3473,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S8" authorId="0" shapeId="0">
+    <comment ref="S8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3503,7 +3498,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S9" authorId="0" shapeId="0">
+    <comment ref="S9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3527,7 +3522,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0">
+    <comment ref="E10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3551,7 +3546,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S10" authorId="0" shapeId="0">
+    <comment ref="S10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3575,7 +3570,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q12" authorId="0" shapeId="0">
+    <comment ref="Q12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3599,7 +3594,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q13" authorId="0" shapeId="0">
+    <comment ref="Q13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3624,7 +3619,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S13" authorId="0" shapeId="0">
+    <comment ref="S13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3648,7 +3643,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y14" authorId="0" shapeId="0">
+    <comment ref="Y14" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3673,7 +3668,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q15" authorId="0" shapeId="0">
+    <comment ref="Q15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3697,7 +3692,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S15" authorId="0" shapeId="0">
+    <comment ref="S15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3721,7 +3716,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E16" authorId="0" shapeId="0">
+    <comment ref="E16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3745,7 +3740,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F16" authorId="0" shapeId="0">
+    <comment ref="F16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3769,7 +3764,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M16" authorId="0" shapeId="0">
+    <comment ref="M16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3794,7 +3789,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T16" authorId="0" shapeId="0">
+    <comment ref="T16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3808,7 +3803,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M17" authorId="0" shapeId="0">
+    <comment ref="M17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3832,7 +3827,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S17" authorId="0" shapeId="0">
+    <comment ref="S17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3856,7 +3851,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T17" authorId="0" shapeId="0">
+    <comment ref="T17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3880,7 +3875,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U17" authorId="0" shapeId="0">
+    <comment ref="U17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3904,7 +3899,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y17" authorId="0" shapeId="0">
+    <comment ref="Y17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3928,7 +3923,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S18" authorId="0" shapeId="0">
+    <comment ref="S18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3952,7 +3947,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U18" authorId="0" shapeId="0">
+    <comment ref="U18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3976,7 +3971,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E19" authorId="0" shapeId="0">
+    <comment ref="E19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4000,7 +3995,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V19" authorId="0" shapeId="0">
+    <comment ref="V19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4024,7 +4019,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y19" authorId="0" shapeId="0">
+    <comment ref="Y19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4038,7 +4033,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F21" authorId="0" shapeId="0">
+    <comment ref="F21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4062,7 +4057,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T21" authorId="0" shapeId="0">
+    <comment ref="T21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4087,7 +4082,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F23" authorId="0" shapeId="0">
+    <comment ref="F23" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4111,7 +4106,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S23" authorId="0" shapeId="0">
+    <comment ref="S23" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4135,7 +4130,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F24" authorId="0" shapeId="0">
+    <comment ref="F24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4159,7 +4154,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H25" authorId="0" shapeId="0">
+    <comment ref="H25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4183,7 +4178,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V25" authorId="0" shapeId="0">
+    <comment ref="V25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4207,7 +4202,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E27" authorId="0" shapeId="0">
+    <comment ref="E27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4231,7 +4226,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V27" authorId="0" shapeId="0">
+    <comment ref="V27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4255,7 +4250,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y27" authorId="0" shapeId="0">
+    <comment ref="Y27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4279,7 +4274,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S28" authorId="0" shapeId="0">
+    <comment ref="S28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4303,7 +4298,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T28" authorId="0" shapeId="0">
+    <comment ref="T28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4327,7 +4322,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q29" authorId="0" shapeId="0">
+    <comment ref="Q29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4351,7 +4346,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F30" authorId="0" shapeId="0">
+    <comment ref="F30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4365,7 +4360,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q30" authorId="0" shapeId="0">
+    <comment ref="Q30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4389,7 +4384,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y33" authorId="0" shapeId="0">
+    <comment ref="Y33" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4404,7 +4399,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S34" authorId="0" shapeId="0">
+    <comment ref="S34" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4419,7 +4414,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T34" authorId="0" shapeId="0">
+    <comment ref="T34" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4433,7 +4428,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E35" authorId="0" shapeId="0">
+    <comment ref="E35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4447,7 +4442,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F35" authorId="0" shapeId="0">
+    <comment ref="F35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4471,7 +4466,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S35" authorId="0" shapeId="0">
+    <comment ref="S35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4496,7 +4491,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H36" authorId="0" shapeId="0">
+    <comment ref="H36" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4520,7 +4515,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S36" authorId="0" shapeId="0">
+    <comment ref="S36" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4554,7 +4549,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="I4" authorId="0" shapeId="0">
+    <comment ref="I4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4568,7 +4563,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O4" authorId="0" shapeId="0">
+    <comment ref="O4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4581,7 +4576,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P4" authorId="0" shapeId="0">
+    <comment ref="P4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4606,7 +4601,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X4" authorId="0" shapeId="0">
+    <comment ref="X4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4620,7 +4615,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L5" authorId="0" shapeId="0">
+    <comment ref="L5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4646,7 +4641,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q5" authorId="0" shapeId="0">
+    <comment ref="Q5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4660,7 +4655,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W5" authorId="0" shapeId="0">
+    <comment ref="W5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4674,7 +4669,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J6" authorId="0" shapeId="0">
+    <comment ref="J6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4698,7 +4693,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I7" authorId="0" shapeId="0">
+    <comment ref="I7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4712,7 +4707,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J7" authorId="0" shapeId="0">
+    <comment ref="J7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4726,7 +4721,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O7" authorId="0" shapeId="0">
+    <comment ref="O7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4740,7 +4735,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z7" authorId="0" shapeId="0">
+    <comment ref="Z7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4755,7 +4750,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J8" authorId="0" shapeId="0">
+    <comment ref="J8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4779,7 +4774,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W8" authorId="0" shapeId="0">
+    <comment ref="W8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4793,7 +4788,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N9" authorId="0" shapeId="0">
+    <comment ref="N9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4807,7 +4802,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P9" authorId="0" shapeId="0">
+    <comment ref="P9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4821,7 +4816,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q10" authorId="0" shapeId="0">
+    <comment ref="Q10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4835,7 +4830,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W10" authorId="0" shapeId="0">
+    <comment ref="W10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4849,7 +4844,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X10" authorId="0" shapeId="0">
+    <comment ref="X10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4873,7 +4868,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W11" authorId="0" shapeId="0">
+    <comment ref="W11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4898,7 +4893,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K12" authorId="0" shapeId="0">
+    <comment ref="K12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4922,7 +4917,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W12" authorId="0" shapeId="0">
+    <comment ref="W12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4946,7 +4941,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I13" authorId="0" shapeId="0">
+    <comment ref="I13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4970,7 +4965,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W13" authorId="0" shapeId="0">
+    <comment ref="W13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4994,7 +4989,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H14" authorId="0" shapeId="0">
+    <comment ref="H14" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5008,7 +5003,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W14" authorId="0" shapeId="0">
+    <comment ref="W14" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5032,7 +5027,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D15" authorId="0" shapeId="0">
+    <comment ref="D15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5046,7 +5041,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J15" authorId="0" shapeId="0">
+    <comment ref="J15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5061,7 +5056,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W15" authorId="0" shapeId="0">
+    <comment ref="W15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5076,7 +5071,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X15" authorId="0" shapeId="0">
+    <comment ref="X15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5090,7 +5085,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z15" authorId="0" shapeId="0">
+    <comment ref="Z15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5104,7 +5099,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I16" authorId="0" shapeId="0">
+    <comment ref="I16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5118,7 +5113,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N16" authorId="0" shapeId="0">
+    <comment ref="N16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5133,7 +5128,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X16" authorId="0" shapeId="0">
+    <comment ref="X16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5147,7 +5142,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X18" authorId="0" shapeId="0">
+    <comment ref="X18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5161,7 +5156,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K20" authorId="0" shapeId="0">
+    <comment ref="K20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5175,7 +5170,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W20" authorId="0" shapeId="0">
+    <comment ref="W20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5190,7 +5185,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I21" authorId="0" shapeId="0">
+    <comment ref="I21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5204,7 +5199,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC21" authorId="0" shapeId="0">
+    <comment ref="AC21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5218,7 +5213,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J23" authorId="0" shapeId="0">
+    <comment ref="J23" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5232,7 +5227,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W23" authorId="0" shapeId="0">
+    <comment ref="W23" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5246,7 +5241,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H24" authorId="0" shapeId="0">
+    <comment ref="H24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5260,7 +5255,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K24" authorId="0" shapeId="0">
+    <comment ref="K24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5284,7 +5279,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K25" authorId="0" shapeId="0">
+    <comment ref="K25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5298,7 +5293,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W25" authorId="0" shapeId="0">
+    <comment ref="W25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5312,7 +5307,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N26" authorId="0" shapeId="0">
+    <comment ref="N26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5326,7 +5321,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W26" authorId="0" shapeId="0">
+    <comment ref="W26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5351,7 +5346,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X26" authorId="0" shapeId="0">
+    <comment ref="X26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5375,7 +5370,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K27" authorId="0" shapeId="0">
+    <comment ref="K27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5389,7 +5384,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X27" authorId="0" shapeId="0">
+    <comment ref="X27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5403,7 +5398,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W28" authorId="0" shapeId="0">
+    <comment ref="W28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5417,7 +5412,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z28" authorId="0" shapeId="0">
+    <comment ref="Z28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5431,7 +5426,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J29" authorId="0" shapeId="0">
+    <comment ref="J29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5455,7 +5450,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z29" authorId="0" shapeId="0">
+    <comment ref="Z29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5469,7 +5464,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC29" authorId="0" shapeId="0">
+    <comment ref="AC29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5483,7 +5478,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J30" authorId="0" shapeId="0">
+    <comment ref="J30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5497,7 +5492,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N30" authorId="0" shapeId="0">
+    <comment ref="N30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5511,7 +5506,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K31" authorId="0" shapeId="0">
+    <comment ref="K31" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5525,7 +5520,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K32" authorId="0" shapeId="0">
+    <comment ref="K32" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5539,7 +5534,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W32" authorId="0" shapeId="0">
+    <comment ref="W32" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5553,7 +5548,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N33" authorId="0" shapeId="0">
+    <comment ref="N33" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5567,7 +5562,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W34" authorId="0" shapeId="0">
+    <comment ref="W34" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5582,7 +5577,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC34" authorId="0" shapeId="0">
+    <comment ref="AC34" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5608,7 +5603,7 @@
     <author>SABEN_MUSIC</author>
   </authors>
   <commentList>
-    <comment ref="X4" authorId="0" shapeId="0">
+    <comment ref="X4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5632,7 +5627,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y4" authorId="0" shapeId="0">
+    <comment ref="Y4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5656,7 +5651,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z4" authorId="0" shapeId="0">
+    <comment ref="Z4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5680,7 +5675,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H5" authorId="0" shapeId="0">
+    <comment ref="H5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5704,7 +5699,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J5" authorId="0" shapeId="0">
+    <comment ref="J5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5728,7 +5723,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M5" authorId="0" shapeId="0">
+    <comment ref="M5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5752,7 +5747,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N5" authorId="0" shapeId="0">
+    <comment ref="N5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5776,7 +5771,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X5" authorId="0" shapeId="0">
+    <comment ref="X5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5800,7 +5795,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I6" authorId="0" shapeId="0">
+    <comment ref="I6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5824,7 +5819,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T6" authorId="0" shapeId="0">
+    <comment ref="T6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5848,7 +5843,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W6" authorId="0" shapeId="0">
+    <comment ref="W6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5872,7 +5867,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K7" authorId="0" shapeId="0">
+    <comment ref="K7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5897,7 +5892,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W7" authorId="0" shapeId="0">
+    <comment ref="W7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5921,7 +5916,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X7" authorId="0" shapeId="0">
+    <comment ref="X7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5945,7 +5940,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y7" authorId="0" shapeId="0">
+    <comment ref="Y7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5969,7 +5964,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H8" authorId="1" shapeId="0">
+    <comment ref="H8" authorId="1">
       <text>
         <r>
           <rPr>
@@ -5994,7 +5989,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K8" authorId="1" shapeId="0">
+    <comment ref="K8" authorId="1">
       <text>
         <r>
           <rPr>
@@ -6008,7 +6003,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M8" authorId="1" shapeId="0">
+    <comment ref="M8" authorId="1">
       <text>
         <r>
           <rPr>
@@ -6022,7 +6017,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O8" authorId="1" shapeId="0">
+    <comment ref="O8" authorId="1">
       <text>
         <r>
           <rPr>
@@ -6036,7 +6031,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W8" authorId="1" shapeId="0">
+    <comment ref="W8" authorId="1">
       <text>
         <r>
           <rPr>
@@ -6050,7 +6045,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K9" authorId="1" shapeId="0">
+    <comment ref="K9" authorId="1">
       <text>
         <r>
           <rPr>
@@ -6074,7 +6069,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W9" authorId="1" shapeId="0">
+    <comment ref="W9" authorId="1">
       <text>
         <r>
           <rPr>
@@ -6088,7 +6083,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N10" authorId="1" shapeId="0">
+    <comment ref="N10" authorId="1">
       <text>
         <r>
           <rPr>
@@ -6112,7 +6107,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K11" authorId="0" shapeId="0">
+    <comment ref="K11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -6137,7 +6132,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N11" authorId="0" shapeId="0">
+    <comment ref="N11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -6161,7 +6156,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z11" authorId="0" shapeId="0">
+    <comment ref="Z11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -6185,7 +6180,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J12" authorId="0" shapeId="0">
+    <comment ref="J12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -6209,7 +6204,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q12" authorId="0" shapeId="0">
+    <comment ref="Q12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -6234,7 +6229,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T12" authorId="0" shapeId="0">
+    <comment ref="T12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -6258,7 +6253,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X12" authorId="0" shapeId="0">
+    <comment ref="X12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -6283,7 +6278,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I13" authorId="0" shapeId="0">
+    <comment ref="I13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -6307,7 +6302,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J13" authorId="0" shapeId="0">
+    <comment ref="J13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -6331,7 +6326,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R13" authorId="0" shapeId="0">
+    <comment ref="R13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -6355,7 +6350,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W13" authorId="0" shapeId="0">
+    <comment ref="W13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -6380,7 +6375,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I15" authorId="0" shapeId="0">
+    <comment ref="I15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -6405,7 +6400,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J15" authorId="0" shapeId="0">
+    <comment ref="J15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -6430,7 +6425,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W15" authorId="0" shapeId="0">
+    <comment ref="W15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -6454,7 +6449,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N16" authorId="0" shapeId="0">
+    <comment ref="N16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -6478,7 +6473,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W16" authorId="0" shapeId="0">
+    <comment ref="W16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -6502,7 +6497,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC16" authorId="0" shapeId="0">
+    <comment ref="AC16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -6526,7 +6521,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M17" authorId="0" shapeId="0">
+    <comment ref="M17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -6550,7 +6545,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N17" authorId="0" shapeId="0">
+    <comment ref="N17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -6574,7 +6569,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q17" authorId="0" shapeId="0">
+    <comment ref="Q17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -6598,7 +6593,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I19" authorId="0" shapeId="0">
+    <comment ref="I19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -6623,7 +6618,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X19" authorId="0" shapeId="0">
+    <comment ref="X19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -6647,7 +6642,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I20" authorId="2" shapeId="0">
+    <comment ref="I20" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6671,7 +6666,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M20" authorId="2" shapeId="0">
+    <comment ref="M20" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6695,7 +6690,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W20" authorId="2" shapeId="0">
+    <comment ref="W20" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6719,7 +6714,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC20" authorId="0" shapeId="0">
+    <comment ref="AC20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -6743,7 +6738,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I21" authorId="2" shapeId="0">
+    <comment ref="I21" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6767,7 +6762,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J22" authorId="2" shapeId="0">
+    <comment ref="J22" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6791,7 +6786,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K22" authorId="2" shapeId="0">
+    <comment ref="K22" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6816,7 +6811,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V22" authorId="2" shapeId="0">
+    <comment ref="V22" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6841,7 +6836,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I23" authorId="2" shapeId="0">
+    <comment ref="I23" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6865,7 +6860,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W23" authorId="2" shapeId="0">
+    <comment ref="W23" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6889,7 +6884,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA23" authorId="2" shapeId="0">
+    <comment ref="AA23" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6913,7 +6908,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC23" authorId="2" shapeId="0">
+    <comment ref="AC23" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6937,7 +6932,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J24" authorId="2" shapeId="0">
+    <comment ref="J24" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6962,7 +6957,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M24" authorId="2" shapeId="0">
+    <comment ref="M24" authorId="2">
       <text>
         <r>
           <rPr>
@@ -6986,7 +6981,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X24" authorId="2" shapeId="0">
+    <comment ref="X24" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7010,7 +7005,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA24" authorId="2" shapeId="0">
+    <comment ref="AA24" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7034,7 +7029,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J26" authorId="2" shapeId="0">
+    <comment ref="J26" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7058,7 +7053,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K26" authorId="2" shapeId="0">
+    <comment ref="K26" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7082,7 +7077,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N26" authorId="2" shapeId="0">
+    <comment ref="N26" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7106,7 +7101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M27" authorId="2" shapeId="0">
+    <comment ref="M27" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7130,7 +7125,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T27" authorId="2" shapeId="0">
+    <comment ref="T27" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7155,7 +7150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W27" authorId="2" shapeId="0">
+    <comment ref="W27" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7179,7 +7174,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC28" authorId="2" shapeId="0">
+    <comment ref="AC28" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7203,7 +7198,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W29" authorId="2" shapeId="0">
+    <comment ref="W29" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7227,7 +7222,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J30" authorId="2" shapeId="0">
+    <comment ref="J30" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7251,7 +7246,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N30" authorId="2" shapeId="0">
+    <comment ref="N30" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7275,7 +7270,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O31" authorId="2" shapeId="0">
+    <comment ref="O31" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7299,7 +7294,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P31" authorId="2" shapeId="0">
+    <comment ref="P31" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7324,7 +7319,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T31" authorId="2" shapeId="0">
+    <comment ref="T31" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7348,7 +7343,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W31" authorId="2" shapeId="0">
+    <comment ref="W31" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7373,7 +7368,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A32" authorId="2" shapeId="0">
+    <comment ref="A32" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7397,7 +7392,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I32" authorId="2" shapeId="0">
+    <comment ref="I32" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7421,7 +7416,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J32" authorId="2" shapeId="0">
+    <comment ref="J32" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7445,7 +7440,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K32" authorId="2" shapeId="0">
+    <comment ref="K32" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7469,7 +7464,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O32" authorId="2" shapeId="0">
+    <comment ref="O32" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7494,7 +7489,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W32" authorId="2" shapeId="0">
+    <comment ref="W32" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7518,7 +7513,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z32" authorId="2" shapeId="0">
+    <comment ref="Z32" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7542,7 +7537,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I33" authorId="2" shapeId="0">
+    <comment ref="I33" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7566,7 +7561,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N33" authorId="2" shapeId="0">
+    <comment ref="N33" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7591,7 +7586,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R33" authorId="2" shapeId="0">
+    <comment ref="R33" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7615,7 +7610,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U33" authorId="2" shapeId="0">
+    <comment ref="U33" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7640,7 +7635,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H34" authorId="2" shapeId="0">
+    <comment ref="H34" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7664,7 +7659,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I34" authorId="2" shapeId="0">
+    <comment ref="I34" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7688,7 +7683,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J34" authorId="2" shapeId="0">
+    <comment ref="J34" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7713,7 +7708,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R34" authorId="2" shapeId="0">
+    <comment ref="R34" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7737,7 +7732,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W34" authorId="2" shapeId="0">
+    <comment ref="W34" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7761,7 +7756,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X34" authorId="2" shapeId="0">
+    <comment ref="X34" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7785,7 +7780,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z34" authorId="2" shapeId="0">
+    <comment ref="Z34" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7809,7 +7804,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC34" authorId="2" shapeId="0">
+    <comment ref="AC34" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7833,7 +7828,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I35" authorId="2" shapeId="0">
+    <comment ref="I35" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7857,7 +7852,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N35" authorId="2" shapeId="0">
+    <comment ref="N35" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7881,7 +7876,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X35" authorId="2" shapeId="0">
+    <comment ref="X35" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7905,7 +7900,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z35" authorId="2" shapeId="0">
+    <comment ref="Z35" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7929,7 +7924,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC35" authorId="2" shapeId="0">
+    <comment ref="AC35" authorId="2">
       <text>
         <r>
           <rPr>
@@ -7965,7 +7960,7 @@
     <author>easob</author>
   </authors>
   <commentList>
-    <comment ref="A4" authorId="0" shapeId="0">
+    <comment ref="A4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -7989,7 +7984,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I4" authorId="0" shapeId="0">
+    <comment ref="I4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8013,7 +8008,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N4" authorId="0" shapeId="0">
+    <comment ref="N4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8037,7 +8032,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U4" authorId="0" shapeId="0">
+    <comment ref="U4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8061,7 +8056,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W4" authorId="0" shapeId="0">
+    <comment ref="W4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8087,7 +8082,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X4" authorId="0" shapeId="0">
+    <comment ref="X4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8111,7 +8106,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I5" authorId="0" shapeId="0">
+    <comment ref="I5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8136,7 +8131,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O5" authorId="0" shapeId="0">
+    <comment ref="O5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8161,7 +8156,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P5" authorId="0" shapeId="0">
+    <comment ref="P5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8185,7 +8180,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U5" authorId="0" shapeId="0">
+    <comment ref="U5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8209,7 +8204,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W5" authorId="0" shapeId="0">
+    <comment ref="W5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8236,7 +8231,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z5" authorId="0" shapeId="0">
+    <comment ref="Z5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8260,7 +8255,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I6" authorId="0" shapeId="0">
+    <comment ref="I6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8284,7 +8279,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q6" authorId="0" shapeId="0">
+    <comment ref="Q6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8308,7 +8303,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X6" authorId="0" shapeId="0">
+    <comment ref="X6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8332,7 +8327,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M7" authorId="0" shapeId="0">
+    <comment ref="M7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8356,7 +8351,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC7" authorId="0" shapeId="0">
+    <comment ref="AC7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8380,7 +8375,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X9" authorId="0" shapeId="0">
+    <comment ref="X9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8405,7 +8400,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0">
+    <comment ref="E10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8429,7 +8424,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W10" authorId="0" shapeId="0">
+    <comment ref="W10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8453,7 +8448,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X10" authorId="0" shapeId="0">
+    <comment ref="X10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8478,7 +8473,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y10" authorId="0" shapeId="0">
+    <comment ref="Y10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8502,7 +8497,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC10" authorId="0" shapeId="0">
+    <comment ref="AC10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8526,7 +8521,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N11" authorId="0" shapeId="0">
+    <comment ref="N11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8550,7 +8545,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X11" authorId="0" shapeId="0">
+    <comment ref="X11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8574,7 +8569,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC11" authorId="0" shapeId="0">
+    <comment ref="AC11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8598,7 +8593,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N12" authorId="0" shapeId="0">
+    <comment ref="N12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8622,7 +8617,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W12" authorId="0" shapeId="0">
+    <comment ref="W12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8647,7 +8642,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X12" authorId="0" shapeId="0">
+    <comment ref="X12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8671,7 +8666,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X13" authorId="0" shapeId="0">
+    <comment ref="X13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8695,7 +8690,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y13" authorId="0" shapeId="0">
+    <comment ref="Y13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8719,7 +8714,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N14" authorId="0" shapeId="0">
+    <comment ref="N14" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8743,7 +8738,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H15" authorId="0" shapeId="0">
+    <comment ref="H15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8767,7 +8762,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N15" authorId="0" shapeId="0">
+    <comment ref="N15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8791,7 +8786,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W15" authorId="0" shapeId="0">
+    <comment ref="W15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8815,7 +8810,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X15" authorId="0" shapeId="0">
+    <comment ref="X15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8839,7 +8834,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H16" authorId="0" shapeId="0">
+    <comment ref="H16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8863,7 +8858,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X16" authorId="0" shapeId="0">
+    <comment ref="X16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8887,7 +8882,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X17" authorId="1" shapeId="0">
+    <comment ref="X17" authorId="1">
       <text>
         <r>
           <rPr>
@@ -8911,7 +8906,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D18" authorId="1" shapeId="0">
+    <comment ref="D18" authorId="1">
       <text>
         <r>
           <rPr>
@@ -8925,7 +8920,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W18" authorId="1" shapeId="0">
+    <comment ref="W18" authorId="1">
       <text>
         <r>
           <rPr>
@@ -8949,7 +8944,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O22" authorId="1" shapeId="0">
+    <comment ref="O22" authorId="1">
       <text>
         <r>
           <rPr>
@@ -8962,7 +8957,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W22" authorId="1" shapeId="0">
+    <comment ref="W22" authorId="1">
       <text>
         <r>
           <rPr>
@@ -8986,7 +8981,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W23" authorId="1" shapeId="0">
+    <comment ref="W23" authorId="1">
       <text>
         <r>
           <rPr>
@@ -9000,7 +8995,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H24" authorId="2" shapeId="0">
+    <comment ref="H24" authorId="2">
       <text>
         <r>
           <rPr>
@@ -9013,7 +9008,134 @@
         </r>
       </text>
     </comment>
-    <comment ref="W34" authorId="1" shapeId="0">
+    <comment ref="I25" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Бон в рябеево
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J25" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Шаурма в хабиби
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N25" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Яндекс плюс</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E26" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Торт в палыче</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K26" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Бабл ти энд поке
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Z26" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Поход в кино на девятую планету
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W27" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">На врача
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H28" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Бабл ти энд поке</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O28" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Ремонт часов
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W34" authorId="1">
       <text>
         <r>
           <rPr>
@@ -9356,11 +9478,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="#\ ##0.00\ &quot;₽&quot;"/>
+    <numFmt numFmtId="164" formatCode="#\ ##0.00\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="52">
+  <fonts count="54">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9753,8 +9875,21 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="40">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -9986,6 +10121,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -10465,7 +10606,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="241">
+  <cellXfs count="242">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10501,39 +10642,39 @@
     <xf numFmtId="0" fontId="11" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="12" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="12" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="15" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="15" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="11" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10542,13 +10683,13 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10557,10 +10698,10 @@
     <xf numFmtId="0" fontId="11" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="16" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="16" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="16" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="16" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10569,77 +10710,77 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="15" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="16" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="16" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="16" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="17" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="11" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="14" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="12" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="16" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="16" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="16" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="16" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="19" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="19" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="16" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="16" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="16" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="16" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="17" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="19" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
@@ -10658,20 +10799,20 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="16" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="16" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="16" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="16" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="20" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="20" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10680,16 +10821,16 @@
     <xf numFmtId="0" fontId="11" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="16" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="16" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="16" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="16" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="12" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="12" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="15" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10698,10 +10839,10 @@
     <xf numFmtId="0" fontId="11" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="15" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="15" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="15" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="15" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10710,10 +10851,10 @@
     <xf numFmtId="0" fontId="11" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="12" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="12" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="12" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="12" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10722,32 +10863,32 @@
     <xf numFmtId="0" fontId="11" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="15" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="15" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="15" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="15" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="20" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="20" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="20" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="20" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="21" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="21" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="16" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="22" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="21" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10777,145 +10918,145 @@
     <xf numFmtId="0" fontId="11" fillId="25" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="25" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="25" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="25" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="25" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="26" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="26" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="27" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="27" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="16" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="16" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="16" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="16" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="27" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="26" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="11" fillId="28" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="27" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="26" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="28" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="20" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="16" fillId="22" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="20" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="16" fillId="22" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="16" fillId="22" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="22" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="29" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="29" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="24" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="24" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="30" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="15" fillId="22" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="30" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="22" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="31" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="11" fillId="10" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="27" fillId="22" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="31" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="10" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="27" fillId="22" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="27" fillId="22" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="27" fillId="22" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="27" fillId="22" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="27" fillId="22" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="30" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="30" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="22" fillId="22" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="22" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="25" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="11" fillId="25" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="25" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="25" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="16" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="11" fillId="16" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="16" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="16" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="32" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="16" fillId="22" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="20" fillId="22" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="32" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="22" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="22" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="29" fillId="22" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="29" fillId="22" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="20" fillId="22" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="22" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="20" fillId="22" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="22" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="33" fillId="34" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="30" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="34" fillId="30" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="34" fillId="30" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="34" fillId="30" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="34" fillId="30" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="34" fillId="30" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="34" fillId="30" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="14" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="34" fillId="14" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="34" fillId="14" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="34" fillId="14" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="34" fillId="14" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="34" fillId="14" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="34" fillId="14" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="35" fillId="26" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="35" fillId="26" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="35" fillId="26" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="36" fillId="26" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="35" fillId="26" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="36" fillId="26" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="34" fillId="32" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="35" fillId="11" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="34" fillId="32" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="35" fillId="11" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="35" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="34" fillId="35" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="34" fillId="35" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="34" fillId="35" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="34" fillId="35" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="34" fillId="35" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="34" fillId="35" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="36" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="34" fillId="36" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="34" fillId="36" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="34" fillId="36" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="34" fillId="36" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="34" fillId="36" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="34" fillId="36" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="34" fillId="35" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="34" fillId="35" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="38" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10924,56 +11065,56 @@
     <xf numFmtId="0" fontId="39" fillId="33" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="40" fillId="33" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="40" fillId="33" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="41" fillId="33" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="41" fillId="33" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="39" fillId="33" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="39" fillId="33" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="42" fillId="33" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="41" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="42" fillId="33" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="41" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="21" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="41" fillId="21" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="41" fillId="21" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="40" fillId="21" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="40" fillId="21" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="43" fillId="21" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="43" fillId="21" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="39" fillId="21" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="39" fillId="21" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="42" fillId="21" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="42" fillId="21" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="39" fillId="22" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="41" fillId="22" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="41" fillId="22" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="43" fillId="22" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="43" fillId="22" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="40" fillId="22" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="40" fillId="22" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="39" fillId="22" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="39" fillId="22" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="42" fillId="22" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="41" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="42" fillId="22" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="41" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="39" fillId="22" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="41" fillId="22" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="39" fillId="22" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="41" fillId="22" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyFill="1"/>
@@ -10981,15 +11122,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="46" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="46" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="46" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="46" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="46" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="46" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="45" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="46" fillId="11" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="46" fillId="11" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="46" fillId="11" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="46" fillId="11" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="37" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -11029,19 +11170,34 @@
     <xf numFmtId="0" fontId="29" fillId="22" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="22" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -11065,20 +11221,14 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -11092,13 +11242,7 @@
     <xf numFmtId="0" fontId="15" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="40" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -11440,7 +11584,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="C4:H17"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -11473,7 +11617,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="3:8" ht="15.75">
+    <row r="5" spans="3:8" ht="16.5">
       <c r="C5" s="196" t="s">
         <v>6</v>
       </c>
@@ -11493,7 +11637,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="3:8" ht="15.75">
+    <row r="6" spans="3:8" ht="16.5">
       <c r="C6" s="196" t="s">
         <v>8</v>
       </c>
@@ -11514,7 +11658,7 @@
         <v>1260.56</v>
       </c>
     </row>
-    <row r="7" spans="3:8" ht="15.75">
+    <row r="7" spans="3:8" ht="16.5">
       <c r="C7" s="196" t="s">
         <v>9</v>
       </c>
@@ -11535,7 +11679,7 @@
         <v>-11931.3</v>
       </c>
     </row>
-    <row r="8" spans="3:8" ht="15.75">
+    <row r="8" spans="3:8" ht="16.5">
       <c r="C8" s="196" t="s">
         <v>10</v>
       </c>
@@ -11556,7 +11700,7 @@
         <v>59.0599999999977</v>
       </c>
     </row>
-    <row r="9" spans="3:8" ht="15.75">
+    <row r="9" spans="3:8" ht="16.5">
       <c r="C9" s="196" t="s">
         <v>11</v>
       </c>
@@ -11581,7 +11725,7 @@
         <v>-2729.0099999999902</v>
       </c>
     </row>
-    <row r="10" spans="3:8" ht="15.75">
+    <row r="10" spans="3:8" ht="16.5">
       <c r="C10" s="196" t="s">
         <v>12</v>
       </c>
@@ -11606,7 +11750,7 @@
         <v>22238.47</v>
       </c>
     </row>
-    <row r="11" spans="3:8" ht="15.75">
+    <row r="11" spans="3:8" ht="16.5">
       <c r="C11" s="196" t="s">
         <v>13</v>
       </c>
@@ -11631,7 +11775,7 @@
         <v>103369.95</v>
       </c>
     </row>
-    <row r="12" spans="3:8" ht="15.75">
+    <row r="12" spans="3:8" ht="16.5">
       <c r="C12" s="196" t="s">
         <v>14</v>
       </c>
@@ -11656,7 +11800,7 @@
         <v>-1058.5799999999899</v>
       </c>
     </row>
-    <row r="13" spans="3:8" ht="15.75">
+    <row r="13" spans="3:8" ht="16.5">
       <c r="C13" s="196" t="s">
         <v>15</v>
       </c>
@@ -11669,7 +11813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="3:8" ht="15.75">
+    <row r="14" spans="3:8" ht="16.5">
       <c r="C14" s="196" t="s">
         <v>16</v>
       </c>
@@ -11682,7 +11826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="3:8" ht="15.75">
+    <row r="15" spans="3:8" ht="16.5">
       <c r="C15" s="196" t="s">
         <v>17</v>
       </c>
@@ -11695,7 +11839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="3:8" ht="15.75">
+    <row r="16" spans="3:8" ht="16.5">
       <c r="C16" s="199" t="s">
         <v>18</v>
       </c>
@@ -11708,7 +11852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="3:8" ht="15.75">
+    <row r="17" spans="3:8" ht="16.5">
       <c r="C17" s="201" t="s">
         <v>19</v>
       </c>
@@ -11741,7 +11885,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AZ41"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -11755,78 +11899,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="34.5" customHeight="1">
-      <c r="A1" s="222" t="s">
+      <c r="A1" s="227" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="222"/>
-      <c r="C1" s="222"/>
-      <c r="D1" s="222"/>
-      <c r="E1" s="222"/>
-      <c r="F1" s="222"/>
-      <c r="G1" s="222"/>
-      <c r="H1" s="222"/>
-      <c r="I1" s="222"/>
-      <c r="J1" s="222"/>
-      <c r="K1" s="222"/>
-      <c r="L1" s="222"/>
-      <c r="M1" s="222"/>
-      <c r="N1" s="222"/>
-      <c r="O1" s="222"/>
-      <c r="P1" s="222"/>
-      <c r="Q1" s="222"/>
-      <c r="R1" s="222"/>
-      <c r="S1" s="222"/>
-      <c r="T1" s="222"/>
-      <c r="U1" s="222"/>
-      <c r="V1" s="222"/>
-      <c r="W1" s="222"/>
-      <c r="X1" s="222"/>
-      <c r="Y1" s="222"/>
-      <c r="Z1" s="222"/>
-      <c r="AA1" s="222"/>
-      <c r="AB1" s="222"/>
-      <c r="AC1" s="222"/>
-      <c r="AD1" s="222"/>
+      <c r="B1" s="227"/>
+      <c r="C1" s="227"/>
+      <c r="D1" s="227"/>
+      <c r="E1" s="227"/>
+      <c r="F1" s="227"/>
+      <c r="G1" s="227"/>
+      <c r="H1" s="227"/>
+      <c r="I1" s="227"/>
+      <c r="J1" s="227"/>
+      <c r="K1" s="227"/>
+      <c r="L1" s="227"/>
+      <c r="M1" s="227"/>
+      <c r="N1" s="227"/>
+      <c r="O1" s="227"/>
+      <c r="P1" s="227"/>
+      <c r="Q1" s="227"/>
+      <c r="R1" s="227"/>
+      <c r="S1" s="227"/>
+      <c r="T1" s="227"/>
+      <c r="U1" s="227"/>
+      <c r="V1" s="227"/>
+      <c r="W1" s="227"/>
+      <c r="X1" s="227"/>
+      <c r="Y1" s="227"/>
+      <c r="Z1" s="227"/>
+      <c r="AA1" s="227"/>
+      <c r="AB1" s="227"/>
+      <c r="AC1" s="227"/>
+      <c r="AD1" s="227"/>
     </row>
     <row r="2" spans="1:52" ht="26.25">
-      <c r="A2" s="223"/>
-      <c r="B2" s="224"/>
-      <c r="C2" s="225" t="s">
+      <c r="A2" s="228"/>
+      <c r="B2" s="229"/>
+      <c r="C2" s="230" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="225"/>
-      <c r="E2" s="225"/>
-      <c r="F2" s="225"/>
-      <c r="G2" s="225"/>
-      <c r="H2" s="225"/>
-      <c r="I2" s="225"/>
-      <c r="J2" s="225"/>
-      <c r="K2" s="225"/>
-      <c r="L2" s="226" t="s">
+      <c r="D2" s="230"/>
+      <c r="E2" s="230"/>
+      <c r="F2" s="230"/>
+      <c r="G2" s="230"/>
+      <c r="H2" s="230"/>
+      <c r="I2" s="230"/>
+      <c r="J2" s="230"/>
+      <c r="K2" s="230"/>
+      <c r="L2" s="231" t="s">
         <v>69</v>
       </c>
-      <c r="M2" s="226"/>
-      <c r="N2" s="226"/>
-      <c r="O2" s="226"/>
-      <c r="P2" s="226"/>
-      <c r="Q2" s="226"/>
-      <c r="R2" s="227" t="s">
+      <c r="M2" s="231"/>
+      <c r="N2" s="231"/>
+      <c r="O2" s="231"/>
+      <c r="P2" s="231"/>
+      <c r="Q2" s="231"/>
+      <c r="R2" s="232" t="s">
         <v>70</v>
       </c>
-      <c r="S2" s="227"/>
-      <c r="T2" s="227"/>
-      <c r="U2" s="227"/>
-      <c r="V2" s="227"/>
-      <c r="W2" s="227"/>
-      <c r="X2" s="227"/>
-      <c r="Y2" s="227"/>
-      <c r="Z2" s="227"/>
-      <c r="AA2" s="227"/>
-      <c r="AB2" s="228" t="s">
+      <c r="S2" s="232"/>
+      <c r="T2" s="232"/>
+      <c r="U2" s="232"/>
+      <c r="V2" s="232"/>
+      <c r="W2" s="232"/>
+      <c r="X2" s="232"/>
+      <c r="Y2" s="232"/>
+      <c r="Z2" s="232"/>
+      <c r="AA2" s="232"/>
+      <c r="AB2" s="233" t="s">
         <v>71</v>
       </c>
-      <c r="AC2" s="228"/>
-      <c r="AD2" s="228"/>
+      <c r="AC2" s="233"/>
+      <c r="AD2" s="233"/>
     </row>
     <row r="3" spans="1:52" ht="45" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -11996,7 +12140,7 @@
       <c r="AC4" s="16">
         <v>142200.85999999999</v>
       </c>
-      <c r="AD4" s="232"/>
+      <c r="AD4" s="225"/>
     </row>
     <row r="5" spans="1:52" ht="15.75">
       <c r="A5" s="17">
@@ -12052,7 +12196,7 @@
         <v>47667</v>
       </c>
       <c r="AC5" s="21"/>
-      <c r="AD5" s="232"/>
+      <c r="AD5" s="225"/>
     </row>
     <row r="6" spans="1:52" ht="15.75">
       <c r="A6" s="22">
@@ -12106,7 +12250,7 @@
         <v>9459</v>
       </c>
       <c r="AC6" s="21"/>
-      <c r="AD6" s="232"/>
+      <c r="AD6" s="225"/>
     </row>
     <row r="7" spans="1:52" ht="15.75">
       <c r="A7" s="26">
@@ -12159,7 +12303,7 @@
       <c r="AC7" s="21">
         <v>2000</v>
       </c>
-      <c r="AD7" s="232"/>
+      <c r="AD7" s="225"/>
     </row>
     <row r="8" spans="1:52" ht="15" customHeight="1">
       <c r="A8" s="31">
@@ -12201,7 +12345,7 @@
         <v>2946.51</v>
       </c>
       <c r="AC8" s="21"/>
-      <c r="AD8" s="232"/>
+      <c r="AD8" s="225"/>
     </row>
     <row r="9" spans="1:52" ht="15.75">
       <c r="A9" s="35">
@@ -12246,7 +12390,7 @@
         <v>1677.84</v>
       </c>
       <c r="AC9" s="21"/>
-      <c r="AD9" s="232"/>
+      <c r="AD9" s="225"/>
     </row>
     <row r="10" spans="1:52" ht="15.75">
       <c r="A10" s="31">
@@ -12312,7 +12456,7 @@
       <c r="AC10" s="21">
         <v>55867</v>
       </c>
-      <c r="AD10" s="232"/>
+      <c r="AD10" s="225"/>
     </row>
     <row r="11" spans="1:52" ht="15.75">
       <c r="A11" s="35">
@@ -12359,14 +12503,14 @@
       <c r="AC11" s="21">
         <v>3000</v>
       </c>
-      <c r="AD11" s="232"/>
-      <c r="AH11" s="233" t="s">
+      <c r="AD11" s="225"/>
+      <c r="AH11" s="226" t="s">
         <v>84</v>
       </c>
-      <c r="AI11" s="233"/>
-      <c r="AJ11" s="233"/>
-      <c r="AK11" s="233"/>
-      <c r="AL11" s="233"/>
+      <c r="AI11" s="226"/>
+      <c r="AJ11" s="226"/>
+      <c r="AK11" s="226"/>
+      <c r="AL11" s="226"/>
     </row>
     <row r="12" spans="1:52" ht="15.75">
       <c r="A12" s="31">
@@ -12415,12 +12559,12 @@
         <v>6686</v>
       </c>
       <c r="AC12" s="21"/>
-      <c r="AD12" s="232"/>
-      <c r="AH12" s="233"/>
-      <c r="AI12" s="233"/>
-      <c r="AJ12" s="233"/>
-      <c r="AK12" s="233"/>
-      <c r="AL12" s="233"/>
+      <c r="AD12" s="225"/>
+      <c r="AH12" s="226"/>
+      <c r="AI12" s="226"/>
+      <c r="AJ12" s="226"/>
+      <c r="AK12" s="226"/>
+      <c r="AL12" s="226"/>
     </row>
     <row r="13" spans="1:52" ht="15.75">
       <c r="A13" s="35">
@@ -12467,12 +12611,12 @@
         <v>3935</v>
       </c>
       <c r="AC13" s="21"/>
-      <c r="AD13" s="232"/>
-      <c r="AH13" s="233"/>
-      <c r="AI13" s="233"/>
-      <c r="AJ13" s="233"/>
-      <c r="AK13" s="233"/>
-      <c r="AL13" s="233"/>
+      <c r="AD13" s="225"/>
+      <c r="AH13" s="226"/>
+      <c r="AI13" s="226"/>
+      <c r="AJ13" s="226"/>
+      <c r="AK13" s="226"/>
+      <c r="AL13" s="226"/>
     </row>
     <row r="14" spans="1:52" ht="18">
       <c r="A14" s="31">
@@ -12513,13 +12657,13 @@
         <v>750</v>
       </c>
       <c r="AC14" s="21"/>
-      <c r="AD14" s="232"/>
-      <c r="AH14" s="229" t="s">
+      <c r="AD14" s="225"/>
+      <c r="AH14" s="222" t="s">
         <v>62</v>
       </c>
-      <c r="AI14" s="229"/>
-      <c r="AJ14" s="229"/>
-      <c r="AK14" s="229"/>
+      <c r="AI14" s="222"/>
+      <c r="AJ14" s="222"/>
+      <c r="AK14" s="222"/>
       <c r="AL14" s="39">
         <f>AC4+AC20+AC24+AC10</f>
         <v>198067.86</v>
@@ -12574,13 +12718,13 @@
         <v>10319</v>
       </c>
       <c r="AC15" s="16"/>
-      <c r="AD15" s="232"/>
-      <c r="AH15" s="229" t="s">
+      <c r="AD15" s="225"/>
+      <c r="AH15" s="222" t="s">
         <v>2</v>
       </c>
-      <c r="AI15" s="229"/>
-      <c r="AJ15" s="229"/>
-      <c r="AK15" s="229"/>
+      <c r="AI15" s="222"/>
+      <c r="AJ15" s="222"/>
+      <c r="AK15" s="222"/>
       <c r="AL15" s="39">
         <f>SUM(AC7,AC11)</f>
         <v>5000</v>
@@ -12635,13 +12779,13 @@
         <v>7901.26</v>
       </c>
       <c r="AC16" s="16"/>
-      <c r="AD16" s="232"/>
-      <c r="AH16" s="229" t="s">
+      <c r="AD16" s="225"/>
+      <c r="AH16" s="222" t="s">
         <v>63</v>
       </c>
-      <c r="AI16" s="229"/>
-      <c r="AJ16" s="229"/>
-      <c r="AK16" s="229"/>
+      <c r="AI16" s="222"/>
+      <c r="AJ16" s="222"/>
+      <c r="AK16" s="222"/>
       <c r="AL16" s="39">
         <v>0</v>
       </c>
@@ -12690,16 +12834,16 @@
         <v>1766.67</v>
       </c>
       <c r="AC17" s="16"/>
-      <c r="AD17" s="232"/>
-      <c r="AH17" s="234" t="s">
+      <c r="AD17" s="225"/>
+      <c r="AH17" s="237" t="s">
         <v>68</v>
       </c>
-      <c r="AI17" s="235"/>
-      <c r="AJ17" s="235"/>
-      <c r="AK17" s="236"/>
+      <c r="AI17" s="238"/>
+      <c r="AJ17" s="238"/>
+      <c r="AK17" s="239"/>
       <c r="AL17" s="39">
         <f>SUM(C37:K37)</f>
-        <v>65098.91</v>
+        <v>65807.89</v>
       </c>
     </row>
     <row r="18" spans="1:38" ht="18">
@@ -12745,23 +12889,23 @@
         <v>20640.400000000001</v>
       </c>
       <c r="AC18" s="16"/>
-      <c r="AD18" s="232"/>
-      <c r="AH18" s="234" t="s">
+      <c r="AD18" s="225"/>
+      <c r="AH18" s="237" t="s">
         <v>85</v>
       </c>
-      <c r="AI18" s="235"/>
-      <c r="AJ18" s="235"/>
-      <c r="AK18" s="236"/>
+      <c r="AI18" s="238"/>
+      <c r="AJ18" s="238"/>
+      <c r="AK18" s="239"/>
       <c r="AL18" s="39">
         <f>SUM(L37:Q37)</f>
-        <v>22101.98</v>
+        <v>23200.98</v>
       </c>
     </row>
     <row r="19" spans="1:38" ht="19.5" customHeight="1">
-      <c r="A19" s="237" t="s">
+      <c r="A19" s="240" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="237"/>
+      <c r="B19" s="240"/>
       <c r="C19" s="40">
         <f>SUM(C4:C18)</f>
         <v>2892.73</v>
@@ -12874,15 +13018,15 @@
         <f>AC19-AB19</f>
         <v>23603.33</v>
       </c>
-      <c r="AH19" s="234" t="s">
+      <c r="AH19" s="237" t="s">
         <v>66</v>
       </c>
-      <c r="AI19" s="235"/>
-      <c r="AJ19" s="235"/>
-      <c r="AK19" s="236"/>
+      <c r="AI19" s="238"/>
+      <c r="AJ19" s="238"/>
+      <c r="AK19" s="239"/>
       <c r="AL19" s="39">
         <f>W37</f>
-        <v>65674</v>
+        <v>67274</v>
       </c>
     </row>
     <row r="20" spans="1:38" ht="18">
@@ -12926,16 +13070,16 @@
       <c r="AC20" s="46">
         <v>0</v>
       </c>
-      <c r="AD20" s="232"/>
-      <c r="AH20" s="234" t="s">
+      <c r="AD20" s="225"/>
+      <c r="AH20" s="237" t="s">
         <v>86</v>
       </c>
-      <c r="AI20" s="235"/>
-      <c r="AJ20" s="235"/>
-      <c r="AK20" s="236"/>
+      <c r="AI20" s="238"/>
+      <c r="AJ20" s="238"/>
+      <c r="AK20" s="239"/>
       <c r="AL20" s="39">
         <f>SUM(U37:V37)</f>
-        <v>6015.03</v>
+        <v>6377.57</v>
       </c>
     </row>
     <row r="21" spans="1:38" ht="18">
@@ -12980,14 +13124,14 @@
         <f>3175.8+7922.85</f>
         <v>11098.65</v>
       </c>
-      <c r="AD21" s="232"/>
+      <c r="AD21" s="225"/>
       <c r="AF21" s="48"/>
-      <c r="AH21" s="238" t="s">
+      <c r="AH21" s="234" t="s">
         <v>32</v>
       </c>
-      <c r="AI21" s="238"/>
-      <c r="AJ21" s="238"/>
-      <c r="AK21" s="238"/>
+      <c r="AI21" s="234"/>
+      <c r="AJ21" s="234"/>
+      <c r="AK21" s="234"/>
       <c r="AL21" s="49">
         <f>T37</f>
         <v>0</v>
@@ -13038,7 +13182,7 @@
         <v>4779.9799999999996</v>
       </c>
       <c r="AC22" s="47"/>
-      <c r="AD22" s="232"/>
+      <c r="AD22" s="225"/>
     </row>
     <row r="23" spans="1:38" ht="18">
       <c r="A23" s="35">
@@ -13082,11 +13226,11 @@
         <v>3933</v>
       </c>
       <c r="AC23" s="47"/>
-      <c r="AD23" s="232"/>
-      <c r="AH23" s="239"/>
-      <c r="AI23" s="239"/>
-      <c r="AJ23" s="239"/>
-      <c r="AK23" s="239"/>
+      <c r="AD23" s="225"/>
+      <c r="AH23" s="235"/>
+      <c r="AI23" s="235"/>
+      <c r="AJ23" s="235"/>
+      <c r="AK23" s="235"/>
       <c r="AL23" s="50"/>
     </row>
     <row r="24" spans="1:38" ht="15.75">
@@ -13136,7 +13280,7 @@
         <v>5930.79</v>
       </c>
       <c r="AC24" s="47"/>
-      <c r="AD24" s="232"/>
+      <c r="AD24" s="225"/>
     </row>
     <row r="25" spans="1:38" ht="15.75">
       <c r="A25" s="35">
@@ -13153,12 +13297,21 @@
       </c>
       <c r="G25" s="37"/>
       <c r="H25" s="37"/>
-      <c r="I25" s="37"/>
-      <c r="J25" s="37"/>
+      <c r="I25" s="37">
+        <f>530+320</f>
+        <v>850</v>
+      </c>
+      <c r="J25" s="37">
+        <f>580</f>
+        <v>580</v>
+      </c>
       <c r="K25" s="37"/>
       <c r="L25" s="37"/>
       <c r="M25" s="37"/>
-      <c r="N25" s="37"/>
+      <c r="N25" s="37">
+        <f>249</f>
+        <v>249</v>
+      </c>
       <c r="O25" s="37"/>
       <c r="P25" s="37"/>
       <c r="Q25" s="37"/>
@@ -13174,10 +13327,10 @@
       <c r="AA25" s="38"/>
       <c r="AB25" s="30">
         <f t="shared" si="5"/>
-        <v>3136.19</v>
+        <v>4815.1900000000005</v>
       </c>
       <c r="AC25" s="47"/>
-      <c r="AD25" s="232"/>
+      <c r="AD25" s="225"/>
     </row>
     <row r="26" spans="1:38" ht="15.75">
       <c r="A26" s="31">
@@ -13188,13 +13341,21 @@
       </c>
       <c r="C26" s="33"/>
       <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
+      <c r="E26" s="33">
+        <f>1850</f>
+        <v>1850</v>
+      </c>
+      <c r="F26" s="33">
+        <v>2017</v>
+      </c>
       <c r="G26" s="33"/>
       <c r="H26" s="33"/>
       <c r="I26" s="33"/>
       <c r="J26" s="33"/>
-      <c r="K26" s="33"/>
+      <c r="K26" s="33">
+        <f>1080</f>
+        <v>1080</v>
+      </c>
       <c r="L26" s="33"/>
       <c r="M26" s="33"/>
       <c r="N26" s="33"/>
@@ -13205,18 +13366,26 @@
       <c r="S26" s="33"/>
       <c r="T26" s="33"/>
       <c r="U26" s="33"/>
-      <c r="V26" s="33"/>
+      <c r="V26" s="33">
+        <f>362.54</f>
+        <v>362.54</v>
+      </c>
       <c r="W26" s="33"/>
-      <c r="X26" s="33"/>
+      <c r="X26" s="33">
+        <v>600</v>
+      </c>
       <c r="Y26" s="33"/>
-      <c r="Z26" s="33"/>
+      <c r="Z26" s="33">
+        <f>550+330</f>
+        <v>880</v>
+      </c>
       <c r="AA26" s="34"/>
       <c r="AB26" s="30">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6789.54</v>
       </c>
       <c r="AC26" s="46"/>
-      <c r="AD26" s="232"/>
+      <c r="AD26" s="225"/>
     </row>
     <row r="27" spans="1:38" ht="15.75">
       <c r="A27" s="35">
@@ -13245,17 +13414,19 @@
       <c r="T27" s="37"/>
       <c r="U27" s="37"/>
       <c r="V27" s="37"/>
-      <c r="W27" s="37"/>
+      <c r="W27" s="37">
+        <v>1600</v>
+      </c>
       <c r="X27" s="37"/>
       <c r="Y27" s="37"/>
       <c r="Z27" s="37"/>
       <c r="AA27" s="38"/>
       <c r="AB27" s="30">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="AC27" s="47"/>
-      <c r="AD27" s="232"/>
+      <c r="AD27" s="225"/>
     </row>
     <row r="28" spans="1:38" ht="15.75">
       <c r="A28" s="31">
@@ -13264,19 +13435,26 @@
       <c r="B28" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="33"/>
+      <c r="C28" s="33">
+        <v>151.97999999999999</v>
+      </c>
       <c r="D28" s="33"/>
       <c r="E28" s="33"/>
       <c r="F28" s="33"/>
       <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
+      <c r="H28" s="33">
+        <f>1180</f>
+        <v>1180</v>
+      </c>
       <c r="I28" s="33"/>
       <c r="J28" s="33"/>
       <c r="K28" s="33"/>
       <c r="L28" s="33"/>
       <c r="M28" s="33"/>
       <c r="N28" s="33"/>
-      <c r="O28" s="33"/>
+      <c r="O28" s="33">
+        <v>850</v>
+      </c>
       <c r="P28" s="33"/>
       <c r="Q28" s="33"/>
       <c r="R28" s="33"/>
@@ -13291,10 +13469,10 @@
       <c r="AA28" s="34"/>
       <c r="AB28" s="30">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2181.98</v>
       </c>
       <c r="AC28" s="47"/>
-      <c r="AD28" s="232"/>
+      <c r="AD28" s="225"/>
     </row>
     <row r="29" spans="1:38" ht="15.75">
       <c r="A29" s="35">
@@ -13306,9 +13484,7 @@
       <c r="C29" s="37"/>
       <c r="D29" s="37"/>
       <c r="E29" s="37"/>
-      <c r="F29" s="51">
-        <v>3500</v>
-      </c>
+      <c r="F29" s="241"/>
       <c r="G29" s="37"/>
       <c r="H29" s="37"/>
       <c r="I29" s="37"/>
@@ -13332,10 +13508,10 @@
       <c r="AA29" s="38"/>
       <c r="AB29" s="30">
         <f t="shared" si="5"/>
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="AC29" s="47"/>
-      <c r="AD29" s="232"/>
+      <c r="AD29" s="225"/>
     </row>
     <row r="30" spans="1:38" ht="15.75">
       <c r="A30" s="31">
@@ -13374,7 +13550,7 @@
         <v>0</v>
       </c>
       <c r="AC30" s="47"/>
-      <c r="AD30" s="232"/>
+      <c r="AD30" s="225"/>
     </row>
     <row r="31" spans="1:38" ht="15.75">
       <c r="A31" s="35">
@@ -13413,7 +13589,7 @@
         <v>0</v>
       </c>
       <c r="AC31" s="47"/>
-      <c r="AD31" s="232"/>
+      <c r="AD31" s="225"/>
     </row>
     <row r="32" spans="1:38" ht="15.75">
       <c r="A32" s="31">
@@ -13452,7 +13628,7 @@
         <v>0</v>
       </c>
       <c r="AC32" s="47"/>
-      <c r="AD32" s="232"/>
+      <c r="AD32" s="225"/>
     </row>
     <row r="33" spans="1:34" ht="15.75">
       <c r="A33" s="35">
@@ -13464,9 +13640,7 @@
       <c r="C33" s="54"/>
       <c r="D33" s="54"/>
       <c r="E33" s="54"/>
-      <c r="F33" s="51">
-        <v>3500</v>
-      </c>
+      <c r="F33" s="241"/>
       <c r="G33" s="54"/>
       <c r="H33" s="54"/>
       <c r="I33" s="54"/>
@@ -13490,10 +13664,10 @@
       <c r="AA33" s="54"/>
       <c r="AB33" s="15">
         <f t="shared" ref="AB33:AB35" si="6">SUM(C33:AA33)</f>
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="AC33" s="47"/>
-      <c r="AD33" s="232"/>
+      <c r="AD33" s="225"/>
     </row>
     <row r="34" spans="1:34" ht="15.75">
       <c r="A34" s="31">
@@ -13534,7 +13708,7 @@
         <v>11525</v>
       </c>
       <c r="AC34" s="47"/>
-      <c r="AD34" s="232"/>
+      <c r="AD34" s="225"/>
     </row>
     <row r="35" spans="1:34" ht="15.75">
       <c r="A35" s="35">
@@ -13573,16 +13747,16 @@
         <v>0</v>
       </c>
       <c r="AC35" s="47"/>
-      <c r="AD35" s="232"/>
+      <c r="AD35" s="225"/>
     </row>
     <row r="36" spans="1:34" ht="24" customHeight="1">
-      <c r="A36" s="240" t="s">
+      <c r="A36" s="236" t="s">
         <v>55</v>
       </c>
-      <c r="B36" s="240"/>
+      <c r="B36" s="236"/>
       <c r="C36" s="56">
         <f t="shared" ref="C36:AC36" si="7">SUM(C20:C35)</f>
-        <v>459.95</v>
+        <v>611.92999999999995</v>
       </c>
       <c r="D36" s="56">
         <f t="shared" si="7"/>
@@ -13590,11 +13764,11 @@
       </c>
       <c r="E36" s="56">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1850</v>
       </c>
       <c r="F36" s="56">
         <f t="shared" si="7"/>
-        <v>15100.91</v>
+        <v>10117.91</v>
       </c>
       <c r="G36" s="56">
         <f t="shared" si="7"/>
@@ -13602,19 +13776,19 @@
       </c>
       <c r="H36" s="56">
         <f t="shared" si="7"/>
-        <v>2600</v>
+        <v>3780</v>
       </c>
       <c r="I36" s="56">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>850</v>
       </c>
       <c r="J36" s="56">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="K36" s="56">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1080</v>
       </c>
       <c r="L36" s="57">
         <f t="shared" si="7"/>
@@ -13626,11 +13800,11 @@
       </c>
       <c r="N36" s="57">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="O36" s="57">
         <f t="shared" si="7"/>
-        <v>299.98</v>
+        <v>1149.98</v>
       </c>
       <c r="P36" s="57">
         <f t="shared" si="7"/>
@@ -13658,15 +13832,15 @@
       </c>
       <c r="V36" s="58">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>362.54</v>
       </c>
       <c r="W36" s="58">
         <f t="shared" si="7"/>
-        <v>16525</v>
+        <v>18125</v>
       </c>
       <c r="X36" s="58">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="Y36" s="58">
         <f t="shared" si="7"/>
@@ -13674,7 +13848,7 @@
       </c>
       <c r="Z36" s="58">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="AA36" s="59">
         <f t="shared" si="7"/>
@@ -13682,7 +13856,7 @@
       </c>
       <c r="AB36" s="43">
         <f t="shared" si="7"/>
-        <v>38789.68</v>
+        <v>44040.2</v>
       </c>
       <c r="AC36" s="44">
         <f t="shared" si="7"/>
@@ -13690,18 +13864,18 @@
       </c>
       <c r="AD36" s="60">
         <f>AC36-AB36</f>
-        <v>-27691.03</v>
+        <v>-32941.549999999996</v>
       </c>
       <c r="AH36" s="48"/>
     </row>
     <row r="37" spans="1:34" ht="31.5" customHeight="1">
-      <c r="A37" s="231" t="s">
+      <c r="A37" s="224" t="s">
         <v>56</v>
       </c>
-      <c r="B37" s="231"/>
+      <c r="B37" s="224"/>
       <c r="C37" s="61">
         <f t="shared" ref="C37:R37" si="8">SUM(C19,C36)</f>
-        <v>3352.68</v>
+        <v>3504.66</v>
       </c>
       <c r="D37" s="61">
         <f t="shared" si="8"/>
@@ -13709,11 +13883,11 @@
       </c>
       <c r="E37" s="61">
         <f t="shared" si="8"/>
-        <v>1850.86</v>
+        <v>3700.8599999999997</v>
       </c>
       <c r="F37" s="61">
         <f t="shared" si="8"/>
-        <v>23355.760000000002</v>
+        <v>18372.760000000002</v>
       </c>
       <c r="G37" s="61">
         <f t="shared" si="8"/>
@@ -13721,19 +13895,19 @@
       </c>
       <c r="H37" s="61">
         <f t="shared" si="8"/>
-        <v>7885</v>
+        <v>9065</v>
       </c>
       <c r="I37" s="61">
         <f t="shared" si="8"/>
-        <v>23855.8</v>
+        <v>24705.8</v>
       </c>
       <c r="J37" s="61">
         <f t="shared" si="8"/>
-        <v>290</v>
+        <v>870</v>
       </c>
       <c r="K37" s="61">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1080</v>
       </c>
       <c r="L37" s="61">
         <f t="shared" si="8"/>
@@ -13745,11 +13919,11 @@
       </c>
       <c r="N37" s="61">
         <f t="shared" si="8"/>
-        <v>2939</v>
+        <v>3188</v>
       </c>
       <c r="O37" s="61">
         <f t="shared" si="8"/>
-        <v>5699.98</v>
+        <v>6549.98</v>
       </c>
       <c r="P37" s="61">
         <f t="shared" si="8"/>
@@ -13774,15 +13948,15 @@
       </c>
       <c r="V37" s="61">
         <f t="shared" si="9"/>
-        <v>2450.0300000000002</v>
+        <v>2812.57</v>
       </c>
       <c r="W37" s="61">
         <f t="shared" si="9"/>
-        <v>65674</v>
+        <v>67274</v>
       </c>
       <c r="X37" s="61">
         <f t="shared" si="9"/>
-        <v>51663.5</v>
+        <v>52263.5</v>
       </c>
       <c r="Y37" s="61">
         <f t="shared" si="9"/>
@@ -13790,7 +13964,7 @@
       </c>
       <c r="Z37" s="61">
         <f t="shared" si="9"/>
-        <v>1000</v>
+        <v>1880</v>
       </c>
       <c r="AA37" s="62">
         <f t="shared" si="9"/>
@@ -13798,7 +13972,7 @@
       </c>
       <c r="AB37" s="63">
         <f t="shared" si="9"/>
-        <v>218254.21</v>
+        <v>223504.72999999998</v>
       </c>
       <c r="AC37" s="64">
         <f t="shared" si="9"/>
@@ -13806,7 +13980,7 @@
       </c>
       <c r="AD37" s="65">
         <f t="shared" si="9"/>
-        <v>-4087.6999999999971</v>
+        <v>-9338.2199999999939</v>
       </c>
     </row>
     <row r="41" spans="1:34">
@@ -13829,6 +14003,12 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="AD4:AD18"/>
@@ -13844,12 +14024,6 @@
     <mergeCell ref="AH16:AK16"/>
     <mergeCell ref="AH17:AK17"/>
     <mergeCell ref="AH18:AK18"/>
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:K2"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
   </mergeCells>
   <conditionalFormatting sqref="AD37">
     <cfRule type="expression" dxfId="1" priority="1">
@@ -13866,7 +14040,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AT35"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -15216,7 +15390,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AT36"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -16578,7 +16752,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AU41"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -18376,7 +18550,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AU40"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -20107,7 +20281,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AU40"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -21762,7 +21936,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AV42"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -21774,34 +21948,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="60.75" customHeight="1">
-      <c r="A1" s="217" t="s">
+      <c r="A1" s="221" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="217"/>
-      <c r="C1" s="217"/>
-      <c r="D1" s="217"/>
-      <c r="E1" s="217"/>
-      <c r="F1" s="217"/>
-      <c r="G1" s="217"/>
-      <c r="H1" s="217"/>
-      <c r="I1" s="217"/>
-      <c r="J1" s="217"/>
-      <c r="K1" s="217"/>
-      <c r="L1" s="217"/>
-      <c r="M1" s="217"/>
-      <c r="N1" s="217"/>
-      <c r="O1" s="217"/>
-      <c r="P1" s="217"/>
-      <c r="Q1" s="217"/>
-      <c r="R1" s="217"/>
-      <c r="S1" s="217"/>
-      <c r="T1" s="217"/>
-      <c r="U1" s="217"/>
-      <c r="V1" s="217"/>
-      <c r="W1" s="217"/>
-      <c r="X1" s="217"/>
-      <c r="Y1" s="217"/>
-      <c r="Z1" s="217"/>
+      <c r="B1" s="221"/>
+      <c r="C1" s="221"/>
+      <c r="D1" s="221"/>
+      <c r="E1" s="221"/>
+      <c r="F1" s="221"/>
+      <c r="G1" s="221"/>
+      <c r="H1" s="221"/>
+      <c r="I1" s="221"/>
+      <c r="J1" s="221"/>
+      <c r="K1" s="221"/>
+      <c r="L1" s="221"/>
+      <c r="M1" s="221"/>
+      <c r="N1" s="221"/>
+      <c r="O1" s="221"/>
+      <c r="P1" s="221"/>
+      <c r="Q1" s="221"/>
+      <c r="R1" s="221"/>
+      <c r="S1" s="221"/>
+      <c r="T1" s="221"/>
+      <c r="U1" s="221"/>
+      <c r="V1" s="221"/>
+      <c r="W1" s="221"/>
+      <c r="X1" s="221"/>
+      <c r="Y1" s="221"/>
+      <c r="Z1" s="221"/>
     </row>
     <row r="2" spans="1:48" ht="45" customHeight="1">
       <c r="A2" s="104" t="s">
@@ -21954,7 +22128,7 @@
         <f>(94085+57723.67)</f>
         <v>151808.67000000001</v>
       </c>
-      <c r="Z3" s="220"/>
+      <c r="Z3" s="219"/>
     </row>
     <row r="4" spans="1:48" ht="15.75">
       <c r="A4" s="117">
@@ -22004,7 +22178,7 @@
       </c>
       <c r="X4" s="90"/>
       <c r="Y4" s="121"/>
-      <c r="Z4" s="220"/>
+      <c r="Z4" s="219"/>
     </row>
     <row r="5" spans="1:48" ht="15.75">
       <c r="A5" s="111">
@@ -22044,7 +22218,7 @@
       </c>
       <c r="X5" s="90"/>
       <c r="Y5" s="121"/>
-      <c r="Z5" s="220"/>
+      <c r="Z5" s="219"/>
     </row>
     <row r="6" spans="1:48" ht="15.75">
       <c r="A6" s="117">
@@ -22085,7 +22259,7 @@
       </c>
       <c r="X6" s="90"/>
       <c r="Y6" s="121"/>
-      <c r="Z6" s="220"/>
+      <c r="Z6" s="219"/>
     </row>
     <row r="7" spans="1:48" ht="15" customHeight="1">
       <c r="A7" s="111">
@@ -22129,7 +22303,7 @@
       </c>
       <c r="X7" s="90"/>
       <c r="Y7" s="121"/>
-      <c r="Z7" s="220"/>
+      <c r="Z7" s="219"/>
     </row>
     <row r="8" spans="1:48" ht="15.75">
       <c r="A8" s="117">
@@ -22171,14 +22345,14 @@
       </c>
       <c r="X8" s="90"/>
       <c r="Y8" s="121"/>
-      <c r="Z8" s="220"/>
-      <c r="AC8" s="221" t="s">
+      <c r="Z8" s="219"/>
+      <c r="AC8" s="220" t="s">
         <v>61</v>
       </c>
-      <c r="AD8" s="221"/>
-      <c r="AE8" s="221"/>
-      <c r="AF8" s="221"/>
-      <c r="AG8" s="221"/>
+      <c r="AD8" s="220"/>
+      <c r="AE8" s="220"/>
+      <c r="AF8" s="220"/>
+      <c r="AG8" s="220"/>
     </row>
     <row r="9" spans="1:48" ht="15.75">
       <c r="A9" s="111">
@@ -22217,12 +22391,12 @@
       </c>
       <c r="X9" s="90"/>
       <c r="Y9" s="121"/>
-      <c r="Z9" s="220"/>
-      <c r="AC9" s="221"/>
-      <c r="AD9" s="221"/>
-      <c r="AE9" s="221"/>
-      <c r="AF9" s="221"/>
-      <c r="AG9" s="221"/>
+      <c r="Z9" s="219"/>
+      <c r="AC9" s="220"/>
+      <c r="AD9" s="220"/>
+      <c r="AE9" s="220"/>
+      <c r="AF9" s="220"/>
+      <c r="AG9" s="220"/>
     </row>
     <row r="10" spans="1:48" ht="15.75">
       <c r="A10" s="117">
@@ -22266,12 +22440,12 @@
       </c>
       <c r="X10" s="90"/>
       <c r="Y10" s="121"/>
-      <c r="Z10" s="220"/>
-      <c r="AC10" s="221"/>
-      <c r="AD10" s="221"/>
-      <c r="AE10" s="221"/>
-      <c r="AF10" s="221"/>
-      <c r="AG10" s="221"/>
+      <c r="Z10" s="219"/>
+      <c r="AC10" s="220"/>
+      <c r="AD10" s="220"/>
+      <c r="AE10" s="220"/>
+      <c r="AF10" s="220"/>
+      <c r="AG10" s="220"/>
     </row>
     <row r="11" spans="1:48" ht="15.75">
       <c r="A11" s="111">
@@ -22311,13 +22485,13 @@
       </c>
       <c r="X11" s="90"/>
       <c r="Y11" s="121"/>
-      <c r="Z11" s="220"/>
-      <c r="AC11" s="218" t="s">
+      <c r="Z11" s="219"/>
+      <c r="AC11" s="217" t="s">
         <v>62</v>
       </c>
-      <c r="AD11" s="218"/>
-      <c r="AE11" s="218"/>
-      <c r="AF11" s="218"/>
+      <c r="AD11" s="217"/>
+      <c r="AE11" s="217"/>
+      <c r="AF11" s="217"/>
       <c r="AG11" s="122">
         <f>Y3+Y14+Y21</f>
         <v>226341.31</v>
@@ -22358,13 +22532,13 @@
       </c>
       <c r="X12" s="90"/>
       <c r="Y12" s="121"/>
-      <c r="Z12" s="220"/>
-      <c r="AC12" s="218" t="s">
+      <c r="Z12" s="219"/>
+      <c r="AC12" s="217" t="s">
         <v>2</v>
       </c>
-      <c r="AD12" s="218"/>
-      <c r="AE12" s="218"/>
-      <c r="AF12" s="218"/>
+      <c r="AD12" s="217"/>
+      <c r="AE12" s="217"/>
+      <c r="AF12" s="217"/>
       <c r="AG12" s="122">
         <f>Y27</f>
         <v>20000</v>
@@ -22409,13 +22583,13 @@
       </c>
       <c r="X13" s="90"/>
       <c r="Y13" s="121"/>
-      <c r="Z13" s="220"/>
-      <c r="AC13" s="218" t="s">
+      <c r="Z13" s="219"/>
+      <c r="AC13" s="217" t="s">
         <v>63</v>
       </c>
-      <c r="AD13" s="218"/>
-      <c r="AE13" s="218"/>
-      <c r="AF13" s="218"/>
+      <c r="AD13" s="217"/>
+      <c r="AE13" s="217"/>
+      <c r="AF13" s="217"/>
       <c r="AG13" s="122">
         <f>Y17+Y19</f>
         <v>25000</v>
@@ -22461,13 +22635,13 @@
       <c r="Y14" s="116">
         <v>37634</v>
       </c>
-      <c r="Z14" s="220"/>
-      <c r="AC14" s="218" t="s">
+      <c r="Z14" s="219"/>
+      <c r="AC14" s="217" t="s">
         <v>64</v>
       </c>
-      <c r="AD14" s="218"/>
-      <c r="AE14" s="218"/>
-      <c r="AF14" s="218"/>
+      <c r="AD14" s="217"/>
+      <c r="AE14" s="217"/>
+      <c r="AF14" s="217"/>
       <c r="AG14" s="122">
         <f>W38</f>
         <v>177971.36</v>
@@ -22517,13 +22691,13 @@
       </c>
       <c r="X15" s="90"/>
       <c r="Y15" s="121"/>
-      <c r="Z15" s="220"/>
-      <c r="AC15" s="218" t="s">
+      <c r="Z15" s="219"/>
+      <c r="AC15" s="217" t="s">
         <v>65</v>
       </c>
-      <c r="AD15" s="218"/>
-      <c r="AE15" s="218"/>
-      <c r="AF15" s="218"/>
+      <c r="AD15" s="217"/>
+      <c r="AE15" s="217"/>
+      <c r="AF15" s="217"/>
       <c r="AG15" s="122">
         <f>SUM(C38:H38)</f>
         <v>55416.04</v>
@@ -22572,13 +22746,13 @@
       </c>
       <c r="X16" s="90"/>
       <c r="Y16" s="121"/>
-      <c r="Z16" s="220"/>
-      <c r="AC16" s="218" t="s">
+      <c r="Z16" s="219"/>
+      <c r="AC16" s="217" t="s">
         <v>66</v>
       </c>
-      <c r="AD16" s="218"/>
-      <c r="AE16" s="218"/>
-      <c r="AF16" s="218"/>
+      <c r="AD16" s="217"/>
+      <c r="AE16" s="217"/>
+      <c r="AF16" s="217"/>
       <c r="AG16" s="122">
         <f>Q38</f>
         <v>27468.98</v>
@@ -22634,7 +22808,7 @@
       <c r="Y17" s="124">
         <v>15000</v>
       </c>
-      <c r="Z17" s="220"/>
+      <c r="Z17" s="219"/>
     </row>
     <row r="18" spans="1:28" ht="15.75">
       <c r="A18" s="117">
@@ -22675,7 +22849,7 @@
       </c>
       <c r="X18" s="90"/>
       <c r="Y18" s="121"/>
-      <c r="Z18" s="220"/>
+      <c r="Z18" s="219"/>
     </row>
     <row r="19" spans="1:28" ht="15.75">
       <c r="A19" s="111">
@@ -22719,7 +22893,7 @@
       <c r="Y19" s="124">
         <v>10000</v>
       </c>
-      <c r="Z19" s="220"/>
+      <c r="Z19" s="219"/>
     </row>
     <row r="20" spans="1:28" ht="14.25" customHeight="1">
       <c r="A20" s="215" t="s">
@@ -22868,7 +23042,7 @@
       <c r="Y21" s="116">
         <v>36898.639999999999</v>
       </c>
-      <c r="Z21" s="220"/>
+      <c r="Z21" s="219"/>
     </row>
     <row r="22" spans="1:28" ht="15.75">
       <c r="A22" s="117">
@@ -22914,7 +23088,7 @@
         <v>23662.84</v>
       </c>
       <c r="Y22" s="121"/>
-      <c r="Z22" s="220"/>
+      <c r="Z22" s="219"/>
       <c r="AB22" s="48"/>
     </row>
     <row r="23" spans="1:28" ht="15.75">
@@ -22958,7 +23132,7 @@
       </c>
       <c r="X23" s="90"/>
       <c r="Y23" s="121"/>
-      <c r="Z23" s="220"/>
+      <c r="Z23" s="219"/>
     </row>
     <row r="24" spans="1:28" ht="15.75">
       <c r="A24" s="117">
@@ -23002,7 +23176,7 @@
       </c>
       <c r="X24" s="90"/>
       <c r="Y24" s="121"/>
-      <c r="Z24" s="220"/>
+      <c r="Z24" s="219"/>
     </row>
     <row r="25" spans="1:28" ht="15.75">
       <c r="A25" s="111">
@@ -23046,7 +23220,7 @@
       </c>
       <c r="X25" s="90"/>
       <c r="Y25" s="121"/>
-      <c r="Z25" s="220"/>
+      <c r="Z25" s="219"/>
     </row>
     <row r="26" spans="1:28" ht="15.75">
       <c r="A26" s="117">
@@ -23085,7 +23259,7 @@
       </c>
       <c r="X26" s="90"/>
       <c r="Y26" s="121"/>
-      <c r="Z26" s="220"/>
+      <c r="Z26" s="219"/>
     </row>
     <row r="27" spans="1:28" ht="15.75">
       <c r="A27" s="111">
@@ -23130,7 +23304,7 @@
       <c r="Y27" s="131">
         <v>20000</v>
       </c>
-      <c r="Z27" s="220"/>
+      <c r="Z27" s="219"/>
     </row>
     <row r="28" spans="1:28" ht="15.75">
       <c r="A28" s="117">
@@ -23172,7 +23346,7 @@
       </c>
       <c r="X28" s="90"/>
       <c r="Y28" s="121"/>
-      <c r="Z28" s="220"/>
+      <c r="Z28" s="219"/>
     </row>
     <row r="29" spans="1:28" ht="15.75">
       <c r="A29" s="111">
@@ -23211,7 +23385,7 @@
       </c>
       <c r="X29" s="90"/>
       <c r="Y29" s="121"/>
-      <c r="Z29" s="220"/>
+      <c r="Z29" s="219"/>
     </row>
     <row r="30" spans="1:28" ht="15.75">
       <c r="A30" s="117">
@@ -23251,7 +23425,7 @@
       </c>
       <c r="X30" s="90"/>
       <c r="Y30" s="121"/>
-      <c r="Z30" s="220"/>
+      <c r="Z30" s="219"/>
     </row>
     <row r="31" spans="1:28" ht="15.75">
       <c r="A31" s="111">
@@ -23286,7 +23460,7 @@
       </c>
       <c r="X31" s="90"/>
       <c r="Y31" s="121"/>
-      <c r="Z31" s="220"/>
+      <c r="Z31" s="219"/>
     </row>
     <row r="32" spans="1:28" ht="15.75">
       <c r="A32" s="117">
@@ -23321,7 +23495,7 @@
       </c>
       <c r="X32" s="90"/>
       <c r="Y32" s="121"/>
-      <c r="Z32" s="220"/>
+      <c r="Z32" s="219"/>
     </row>
     <row r="33" spans="1:26" ht="15.75">
       <c r="A33" s="111">
@@ -23358,7 +23532,7 @@
       <c r="Y33" s="132">
         <v>10000</v>
       </c>
-      <c r="Z33" s="220"/>
+      <c r="Z33" s="219"/>
     </row>
     <row r="34" spans="1:26" ht="15.75">
       <c r="A34" s="117">
@@ -23397,7 +23571,7 @@
       </c>
       <c r="X34" s="90"/>
       <c r="Y34" s="121"/>
-      <c r="Z34" s="220"/>
+      <c r="Z34" s="219"/>
     </row>
     <row r="35" spans="1:26" ht="15.75">
       <c r="A35" s="111">
@@ -23441,7 +23615,7 @@
       </c>
       <c r="X35" s="90"/>
       <c r="Y35" s="121"/>
-      <c r="Z35" s="220"/>
+      <c r="Z35" s="219"/>
     </row>
     <row r="36" spans="1:26" ht="15.75">
       <c r="A36" s="117">
@@ -23482,7 +23656,7 @@
       </c>
       <c r="X36" s="90"/>
       <c r="Y36" s="121"/>
-      <c r="Z36" s="220"/>
+      <c r="Z36" s="219"/>
     </row>
     <row r="37" spans="1:26">
       <c r="A37" s="215" t="s">
@@ -23587,10 +23761,10 @@
       </c>
     </row>
     <row r="38" spans="1:26" ht="31.5" customHeight="1">
-      <c r="A38" s="219" t="s">
+      <c r="A38" s="218" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="219"/>
+      <c r="B38" s="218"/>
       <c r="C38" s="134">
         <f>SUM(C20,C37)</f>
         <v>14335.99</v>
@@ -23702,6 +23876,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="AC11:AF11"/>
+    <mergeCell ref="AC12:AF12"/>
+    <mergeCell ref="AC13:AF13"/>
+    <mergeCell ref="AC14:AF14"/>
     <mergeCell ref="AC15:AF15"/>
     <mergeCell ref="AC16:AF16"/>
     <mergeCell ref="A20:B20"/>
@@ -23710,11 +23889,6 @@
     <mergeCell ref="Z3:Z19"/>
     <mergeCell ref="Z21:Z36"/>
     <mergeCell ref="AC8:AG10"/>
-    <mergeCell ref="A1:Z1"/>
-    <mergeCell ref="AC11:AF11"/>
-    <mergeCell ref="AC12:AF12"/>
-    <mergeCell ref="AC13:AF13"/>
-    <mergeCell ref="AC14:AF14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -23723,7 +23897,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AZ40"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -23735,78 +23909,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="34.5" customHeight="1">
-      <c r="A1" s="222" t="s">
+      <c r="A1" s="227" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="222"/>
-      <c r="C1" s="222"/>
-      <c r="D1" s="222"/>
-      <c r="E1" s="222"/>
-      <c r="F1" s="222"/>
-      <c r="G1" s="222"/>
-      <c r="H1" s="222"/>
-      <c r="I1" s="222"/>
-      <c r="J1" s="222"/>
-      <c r="K1" s="222"/>
-      <c r="L1" s="222"/>
-      <c r="M1" s="222"/>
-      <c r="N1" s="222"/>
-      <c r="O1" s="222"/>
-      <c r="P1" s="222"/>
-      <c r="Q1" s="222"/>
-      <c r="R1" s="222"/>
-      <c r="S1" s="222"/>
-      <c r="T1" s="222"/>
-      <c r="U1" s="222"/>
-      <c r="V1" s="222"/>
-      <c r="W1" s="222"/>
-      <c r="X1" s="222"/>
-      <c r="Y1" s="222"/>
-      <c r="Z1" s="222"/>
-      <c r="AA1" s="222"/>
-      <c r="AB1" s="222"/>
-      <c r="AC1" s="222"/>
-      <c r="AD1" s="222"/>
+      <c r="B1" s="227"/>
+      <c r="C1" s="227"/>
+      <c r="D1" s="227"/>
+      <c r="E1" s="227"/>
+      <c r="F1" s="227"/>
+      <c r="G1" s="227"/>
+      <c r="H1" s="227"/>
+      <c r="I1" s="227"/>
+      <c r="J1" s="227"/>
+      <c r="K1" s="227"/>
+      <c r="L1" s="227"/>
+      <c r="M1" s="227"/>
+      <c r="N1" s="227"/>
+      <c r="O1" s="227"/>
+      <c r="P1" s="227"/>
+      <c r="Q1" s="227"/>
+      <c r="R1" s="227"/>
+      <c r="S1" s="227"/>
+      <c r="T1" s="227"/>
+      <c r="U1" s="227"/>
+      <c r="V1" s="227"/>
+      <c r="W1" s="227"/>
+      <c r="X1" s="227"/>
+      <c r="Y1" s="227"/>
+      <c r="Z1" s="227"/>
+      <c r="AA1" s="227"/>
+      <c r="AB1" s="227"/>
+      <c r="AC1" s="227"/>
+      <c r="AD1" s="227"/>
     </row>
     <row r="2" spans="1:52" ht="26.25">
-      <c r="A2" s="223"/>
-      <c r="B2" s="224"/>
-      <c r="C2" s="225" t="s">
+      <c r="A2" s="228"/>
+      <c r="B2" s="229"/>
+      <c r="C2" s="230" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="225"/>
-      <c r="E2" s="225"/>
-      <c r="F2" s="225"/>
-      <c r="G2" s="225"/>
-      <c r="H2" s="225"/>
-      <c r="I2" s="225"/>
-      <c r="J2" s="225"/>
-      <c r="K2" s="225"/>
-      <c r="L2" s="226" t="s">
+      <c r="D2" s="230"/>
+      <c r="E2" s="230"/>
+      <c r="F2" s="230"/>
+      <c r="G2" s="230"/>
+      <c r="H2" s="230"/>
+      <c r="I2" s="230"/>
+      <c r="J2" s="230"/>
+      <c r="K2" s="230"/>
+      <c r="L2" s="231" t="s">
         <v>69</v>
       </c>
-      <c r="M2" s="226"/>
-      <c r="N2" s="226"/>
-      <c r="O2" s="226"/>
-      <c r="P2" s="226"/>
-      <c r="Q2" s="226"/>
-      <c r="R2" s="227" t="s">
+      <c r="M2" s="231"/>
+      <c r="N2" s="231"/>
+      <c r="O2" s="231"/>
+      <c r="P2" s="231"/>
+      <c r="Q2" s="231"/>
+      <c r="R2" s="232" t="s">
         <v>70</v>
       </c>
-      <c r="S2" s="227"/>
-      <c r="T2" s="227"/>
-      <c r="U2" s="227"/>
-      <c r="V2" s="227"/>
-      <c r="W2" s="227"/>
-      <c r="X2" s="227"/>
-      <c r="Y2" s="227"/>
-      <c r="Z2" s="227"/>
-      <c r="AA2" s="227"/>
-      <c r="AB2" s="228" t="s">
+      <c r="S2" s="232"/>
+      <c r="T2" s="232"/>
+      <c r="U2" s="232"/>
+      <c r="V2" s="232"/>
+      <c r="W2" s="232"/>
+      <c r="X2" s="232"/>
+      <c r="Y2" s="232"/>
+      <c r="Z2" s="232"/>
+      <c r="AA2" s="232"/>
+      <c r="AB2" s="233" t="s">
         <v>71</v>
       </c>
-      <c r="AC2" s="228"/>
-      <c r="AD2" s="228"/>
+      <c r="AC2" s="233"/>
+      <c r="AD2" s="233"/>
     </row>
     <row r="3" spans="1:52" ht="45" customHeight="1">
       <c r="A3" s="67" t="s">
@@ -23973,7 +24147,7 @@
         <f>37635+40252.26+18817.85</f>
         <v>96705.11</v>
       </c>
-      <c r="AD4" s="232"/>
+      <c r="AD4" s="225"/>
     </row>
     <row r="5" spans="1:52" ht="15.75">
       <c r="A5" s="35">
@@ -24023,7 +24197,7 @@
         <v>16503.13</v>
       </c>
       <c r="AC5" s="47"/>
-      <c r="AD5" s="232"/>
+      <c r="AD5" s="225"/>
     </row>
     <row r="6" spans="1:52" ht="15.75">
       <c r="A6" s="31">
@@ -24066,7 +24240,7 @@
         <v>996.61</v>
       </c>
       <c r="AC6" s="47"/>
-      <c r="AD6" s="232"/>
+      <c r="AD6" s="225"/>
     </row>
     <row r="7" spans="1:52" ht="15.75">
       <c r="A7" s="35">
@@ -24119,7 +24293,7 @@
         <v>5968</v>
       </c>
       <c r="AC7" s="47"/>
-      <c r="AD7" s="232"/>
+      <c r="AD7" s="225"/>
     </row>
     <row r="8" spans="1:52" ht="15" customHeight="1">
       <c r="A8" s="31">
@@ -24165,7 +24339,7 @@
         <v>12168.98</v>
       </c>
       <c r="AC8" s="47"/>
-      <c r="AD8" s="232"/>
+      <c r="AD8" s="225"/>
     </row>
     <row r="9" spans="1:52" ht="15.75">
       <c r="A9" s="35">
@@ -24213,7 +24387,7 @@
         <v>5970</v>
       </c>
       <c r="AC9" s="47"/>
-      <c r="AD9" s="232"/>
+      <c r="AD9" s="225"/>
     </row>
     <row r="10" spans="1:52" ht="15.75">
       <c r="A10" s="31">
@@ -24261,7 +24435,7 @@
         <v>3257</v>
       </c>
       <c r="AC10" s="47"/>
-      <c r="AD10" s="232"/>
+      <c r="AD10" s="225"/>
     </row>
     <row r="11" spans="1:52" ht="15.75">
       <c r="A11" s="35">
@@ -24305,14 +24479,14 @@
         <v>1034</v>
       </c>
       <c r="AC11" s="47"/>
-      <c r="AD11" s="232"/>
-      <c r="AH11" s="233" t="s">
+      <c r="AD11" s="225"/>
+      <c r="AH11" s="226" t="s">
         <v>84</v>
       </c>
-      <c r="AI11" s="233"/>
-      <c r="AJ11" s="233"/>
-      <c r="AK11" s="233"/>
-      <c r="AL11" s="233"/>
+      <c r="AI11" s="226"/>
+      <c r="AJ11" s="226"/>
+      <c r="AK11" s="226"/>
+      <c r="AL11" s="226"/>
     </row>
     <row r="12" spans="1:52" ht="15.75">
       <c r="A12" s="31">
@@ -24359,12 +24533,12 @@
         <v>3586</v>
       </c>
       <c r="AC12" s="47"/>
-      <c r="AD12" s="232"/>
-      <c r="AH12" s="233"/>
-      <c r="AI12" s="233"/>
-      <c r="AJ12" s="233"/>
-      <c r="AK12" s="233"/>
-      <c r="AL12" s="233"/>
+      <c r="AD12" s="225"/>
+      <c r="AH12" s="226"/>
+      <c r="AI12" s="226"/>
+      <c r="AJ12" s="226"/>
+      <c r="AK12" s="226"/>
+      <c r="AL12" s="226"/>
     </row>
     <row r="13" spans="1:52" ht="15.75">
       <c r="A13" s="35">
@@ -24411,12 +24585,12 @@
         <v>5889</v>
       </c>
       <c r="AC13" s="47"/>
-      <c r="AD13" s="232"/>
-      <c r="AH13" s="233"/>
-      <c r="AI13" s="233"/>
-      <c r="AJ13" s="233"/>
-      <c r="AK13" s="233"/>
-      <c r="AL13" s="233"/>
+      <c r="AD13" s="225"/>
+      <c r="AH13" s="226"/>
+      <c r="AI13" s="226"/>
+      <c r="AJ13" s="226"/>
+      <c r="AK13" s="226"/>
+      <c r="AL13" s="226"/>
     </row>
     <row r="14" spans="1:52" ht="18">
       <c r="A14" s="31">
@@ -24462,13 +24636,13 @@
         <v>7092.93</v>
       </c>
       <c r="AC14" s="47"/>
-      <c r="AD14" s="232"/>
-      <c r="AH14" s="229" t="s">
+      <c r="AD14" s="225"/>
+      <c r="AH14" s="222" t="s">
         <v>62</v>
       </c>
-      <c r="AI14" s="229"/>
-      <c r="AJ14" s="229"/>
-      <c r="AK14" s="229"/>
+      <c r="AI14" s="222"/>
+      <c r="AJ14" s="222"/>
+      <c r="AK14" s="222"/>
       <c r="AL14" s="39">
         <f>AC4+AC20</f>
         <v>133443.15</v>
@@ -24526,13 +24700,13 @@
         <v>6644.28</v>
       </c>
       <c r="AC15" s="46"/>
-      <c r="AD15" s="232"/>
-      <c r="AH15" s="229" t="s">
+      <c r="AD15" s="225"/>
+      <c r="AH15" s="222" t="s">
         <v>2</v>
       </c>
-      <c r="AI15" s="229"/>
-      <c r="AJ15" s="229"/>
-      <c r="AK15" s="229"/>
+      <c r="AI15" s="222"/>
+      <c r="AJ15" s="222"/>
+      <c r="AK15" s="222"/>
       <c r="AL15" s="39">
         <f>AC29</f>
         <v>1000</v>
@@ -24587,13 +24761,13 @@
         <v>5105.1899999999996</v>
       </c>
       <c r="AC16" s="47"/>
-      <c r="AD16" s="232"/>
-      <c r="AH16" s="229" t="s">
+      <c r="AD16" s="225"/>
+      <c r="AH16" s="222" t="s">
         <v>63</v>
       </c>
-      <c r="AI16" s="229"/>
-      <c r="AJ16" s="229"/>
-      <c r="AK16" s="229"/>
+      <c r="AI16" s="222"/>
+      <c r="AJ16" s="222"/>
+      <c r="AK16" s="222"/>
       <c r="AL16" s="39">
         <f>AC21+AC34</f>
         <v>11000</v>
@@ -24638,13 +24812,13 @@
         <v>280.97000000000003</v>
       </c>
       <c r="AC17" s="47"/>
-      <c r="AD17" s="232"/>
-      <c r="AH17" s="229" t="s">
+      <c r="AD17" s="225"/>
+      <c r="AH17" s="222" t="s">
         <v>64</v>
       </c>
-      <c r="AI17" s="229"/>
-      <c r="AJ17" s="229"/>
-      <c r="AK17" s="229"/>
+      <c r="AI17" s="222"/>
+      <c r="AJ17" s="222"/>
+      <c r="AK17" s="222"/>
       <c r="AL17" s="39">
         <f>AB36</f>
         <v>146501.73000000001</v>
@@ -24693,23 +24867,23 @@
         <v>956.98</v>
       </c>
       <c r="AC18" s="47"/>
-      <c r="AD18" s="232"/>
-      <c r="AH18" s="229" t="s">
+      <c r="AD18" s="225"/>
+      <c r="AH18" s="222" t="s">
         <v>65</v>
       </c>
-      <c r="AI18" s="229"/>
-      <c r="AJ18" s="229"/>
-      <c r="AK18" s="229"/>
+      <c r="AI18" s="222"/>
+      <c r="AJ18" s="222"/>
+      <c r="AK18" s="222"/>
       <c r="AL18" s="39">
         <f>SUM(C36:K36)</f>
         <v>56967.92</v>
       </c>
     </row>
     <row r="19" spans="1:38" ht="19.5" customHeight="1">
-      <c r="A19" s="230" t="s">
+      <c r="A19" s="223" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="230"/>
+      <c r="B19" s="223"/>
       <c r="C19" s="40">
         <f>SUM(C4:C18)</f>
         <v>1403.89</v>
@@ -24822,12 +24996,12 @@
         <f>AC19-AB19</f>
         <v>4280.0900000000101</v>
       </c>
-      <c r="AH19" s="229" t="s">
+      <c r="AH19" s="222" t="s">
         <v>85</v>
       </c>
-      <c r="AI19" s="229"/>
-      <c r="AJ19" s="229"/>
-      <c r="AK19" s="229"/>
+      <c r="AI19" s="222"/>
+      <c r="AJ19" s="222"/>
+      <c r="AK19" s="222"/>
       <c r="AL19" s="39">
         <f>SUM(L36:Q36)</f>
         <v>31394.13</v>
@@ -24888,13 +25062,13 @@
       <c r="AC20" s="46">
         <v>36738.04</v>
       </c>
-      <c r="AD20" s="232"/>
-      <c r="AH20" s="229" t="s">
+      <c r="AD20" s="225"/>
+      <c r="AH20" s="222" t="s">
         <v>66</v>
       </c>
-      <c r="AI20" s="229"/>
-      <c r="AJ20" s="229"/>
-      <c r="AK20" s="229"/>
+      <c r="AI20" s="222"/>
+      <c r="AJ20" s="222"/>
+      <c r="AK20" s="222"/>
       <c r="AL20" s="39">
         <f>W36</f>
         <v>35678.97</v>
@@ -24949,14 +25123,14 @@
       <c r="AC21" s="96">
         <v>10000</v>
       </c>
-      <c r="AD21" s="232"/>
+      <c r="AD21" s="225"/>
       <c r="AF21" s="48"/>
-      <c r="AH21" s="229" t="s">
+      <c r="AH21" s="222" t="s">
         <v>86</v>
       </c>
-      <c r="AI21" s="229"/>
-      <c r="AJ21" s="229"/>
-      <c r="AK21" s="229"/>
+      <c r="AI21" s="222"/>
+      <c r="AJ21" s="222"/>
+      <c r="AK21" s="222"/>
       <c r="AL21" s="39">
         <f>SUM(U36:V36)</f>
         <v>11008.46</v>
@@ -24999,13 +25173,13 @@
         <v>0</v>
       </c>
       <c r="AC22" s="47"/>
-      <c r="AD22" s="232"/>
-      <c r="AH22" s="229" t="s">
+      <c r="AD22" s="225"/>
+      <c r="AH22" s="222" t="s">
         <v>32</v>
       </c>
-      <c r="AI22" s="229"/>
-      <c r="AJ22" s="229"/>
-      <c r="AK22" s="229"/>
+      <c r="AI22" s="222"/>
+      <c r="AJ22" s="222"/>
+      <c r="AK22" s="222"/>
       <c r="AL22" s="39">
         <f>T36</f>
         <v>0</v>
@@ -25060,13 +25234,13 @@
         <v>6881.28</v>
       </c>
       <c r="AC23" s="47"/>
-      <c r="AD23" s="232"/>
-      <c r="AH23" s="229" t="s">
+      <c r="AD23" s="225"/>
+      <c r="AH23" s="222" t="s">
         <v>87</v>
       </c>
-      <c r="AI23" s="229"/>
-      <c r="AJ23" s="229"/>
-      <c r="AK23" s="229"/>
+      <c r="AI23" s="222"/>
+      <c r="AJ23" s="222"/>
+      <c r="AK23" s="222"/>
       <c r="AL23" s="39">
         <f>X36</f>
         <v>5267.98</v>
@@ -25121,7 +25295,7 @@
         <v>6126.69</v>
       </c>
       <c r="AC24" s="47"/>
-      <c r="AD24" s="232"/>
+      <c r="AD24" s="225"/>
     </row>
     <row r="25" spans="1:38" ht="15.75">
       <c r="A25" s="35">
@@ -25165,7 +25339,7 @@
         <v>7750</v>
       </c>
       <c r="AC25" s="47"/>
-      <c r="AD25" s="232"/>
+      <c r="AD25" s="225"/>
     </row>
     <row r="26" spans="1:38" ht="15.75">
       <c r="A26" s="31">
@@ -25212,7 +25386,7 @@
         <v>2803</v>
       </c>
       <c r="AC26" s="46"/>
-      <c r="AD26" s="232"/>
+      <c r="AD26" s="225"/>
     </row>
     <row r="27" spans="1:38" ht="15.75">
       <c r="A27" s="35">
@@ -25260,7 +25434,7 @@
         <v>2088.96</v>
       </c>
       <c r="AC27" s="47"/>
-      <c r="AD27" s="232"/>
+      <c r="AD27" s="225"/>
     </row>
     <row r="28" spans="1:38" ht="15.75">
       <c r="A28" s="31">
@@ -25306,7 +25480,7 @@
         <v>3468</v>
       </c>
       <c r="AC28" s="47"/>
-      <c r="AD28" s="232"/>
+      <c r="AD28" s="225"/>
     </row>
     <row r="29" spans="1:38" ht="15.75">
       <c r="A29" s="35">
@@ -25359,7 +25533,7 @@
       <c r="AC29" s="47">
         <v>1000</v>
       </c>
-      <c r="AD29" s="232"/>
+      <c r="AD29" s="225"/>
     </row>
     <row r="30" spans="1:38" ht="15.75">
       <c r="A30" s="31">
@@ -25407,7 +25581,7 @@
         <v>4016.5</v>
       </c>
       <c r="AC30" s="47"/>
-      <c r="AD30" s="232"/>
+      <c r="AD30" s="225"/>
     </row>
     <row r="31" spans="1:38" ht="15.75">
       <c r="A31" s="35">
@@ -25451,7 +25625,7 @@
         <v>2801.78</v>
       </c>
       <c r="AC31" s="47"/>
-      <c r="AD31" s="232"/>
+      <c r="AD31" s="225"/>
     </row>
     <row r="32" spans="1:38" ht="15.75">
       <c r="A32" s="31">
@@ -25500,7 +25674,7 @@
         <v>3807.11</v>
       </c>
       <c r="AC32" s="47"/>
-      <c r="AD32" s="232"/>
+      <c r="AD32" s="225"/>
     </row>
     <row r="33" spans="1:30" ht="15.75">
       <c r="A33" s="35">
@@ -25544,7 +25718,7 @@
         <v>675.44</v>
       </c>
       <c r="AC33" s="47"/>
-      <c r="AD33" s="232"/>
+      <c r="AD33" s="225"/>
     </row>
     <row r="34" spans="1:30" ht="15.75">
       <c r="A34" s="31">
@@ -25588,13 +25762,13 @@
       <c r="AC34" s="96">
         <v>1000</v>
       </c>
-      <c r="AD34" s="232"/>
+      <c r="AD34" s="225"/>
     </row>
     <row r="35" spans="1:30" ht="14.25" customHeight="1">
-      <c r="A35" s="230" t="s">
+      <c r="A35" s="223" t="s">
         <v>55</v>
       </c>
-      <c r="B35" s="230"/>
+      <c r="B35" s="223"/>
       <c r="C35" s="40">
         <f t="shared" ref="C35:AC35" si="3">SUM(C20:C34)</f>
         <v>2169.6999999999998</v>
@@ -25709,10 +25883,10 @@
       </c>
     </row>
     <row r="36" spans="1:30" ht="31.5" customHeight="1">
-      <c r="A36" s="231" t="s">
+      <c r="A36" s="224" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="231"/>
+      <c r="B36" s="224"/>
       <c r="C36" s="61">
         <f>SUM(C19,C35)</f>
         <v>3573.59</v>
@@ -25843,6 +26017,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="AH23:AK23"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="A36:B36"/>
@@ -25859,12 +26039,6 @@
     <mergeCell ref="AH16:AK16"/>
     <mergeCell ref="AH17:AK17"/>
     <mergeCell ref="AH18:AK18"/>
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:K2"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -25873,7 +26047,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AZ41"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -25885,78 +26059,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="34.5" customHeight="1">
-      <c r="A1" s="222" t="s">
+      <c r="A1" s="227" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="222"/>
-      <c r="C1" s="222"/>
-      <c r="D1" s="222"/>
-      <c r="E1" s="222"/>
-      <c r="F1" s="222"/>
-      <c r="G1" s="222"/>
-      <c r="H1" s="222"/>
-      <c r="I1" s="222"/>
-      <c r="J1" s="222"/>
-      <c r="K1" s="222"/>
-      <c r="L1" s="222"/>
-      <c r="M1" s="222"/>
-      <c r="N1" s="222"/>
-      <c r="O1" s="222"/>
-      <c r="P1" s="222"/>
-      <c r="Q1" s="222"/>
-      <c r="R1" s="222"/>
-      <c r="S1" s="222"/>
-      <c r="T1" s="222"/>
-      <c r="U1" s="222"/>
-      <c r="V1" s="222"/>
-      <c r="W1" s="222"/>
-      <c r="X1" s="222"/>
-      <c r="Y1" s="222"/>
-      <c r="Z1" s="222"/>
-      <c r="AA1" s="222"/>
-      <c r="AB1" s="222"/>
-      <c r="AC1" s="222"/>
-      <c r="AD1" s="222"/>
+      <c r="B1" s="227"/>
+      <c r="C1" s="227"/>
+      <c r="D1" s="227"/>
+      <c r="E1" s="227"/>
+      <c r="F1" s="227"/>
+      <c r="G1" s="227"/>
+      <c r="H1" s="227"/>
+      <c r="I1" s="227"/>
+      <c r="J1" s="227"/>
+      <c r="K1" s="227"/>
+      <c r="L1" s="227"/>
+      <c r="M1" s="227"/>
+      <c r="N1" s="227"/>
+      <c r="O1" s="227"/>
+      <c r="P1" s="227"/>
+      <c r="Q1" s="227"/>
+      <c r="R1" s="227"/>
+      <c r="S1" s="227"/>
+      <c r="T1" s="227"/>
+      <c r="U1" s="227"/>
+      <c r="V1" s="227"/>
+      <c r="W1" s="227"/>
+      <c r="X1" s="227"/>
+      <c r="Y1" s="227"/>
+      <c r="Z1" s="227"/>
+      <c r="AA1" s="227"/>
+      <c r="AB1" s="227"/>
+      <c r="AC1" s="227"/>
+      <c r="AD1" s="227"/>
     </row>
     <row r="2" spans="1:52" ht="26.25">
-      <c r="A2" s="223"/>
-      <c r="B2" s="224"/>
-      <c r="C2" s="225" t="s">
+      <c r="A2" s="228"/>
+      <c r="B2" s="229"/>
+      <c r="C2" s="230" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="225"/>
-      <c r="E2" s="225"/>
-      <c r="F2" s="225"/>
-      <c r="G2" s="225"/>
-      <c r="H2" s="225"/>
-      <c r="I2" s="225"/>
-      <c r="J2" s="225"/>
-      <c r="K2" s="225"/>
-      <c r="L2" s="226" t="s">
+      <c r="D2" s="230"/>
+      <c r="E2" s="230"/>
+      <c r="F2" s="230"/>
+      <c r="G2" s="230"/>
+      <c r="H2" s="230"/>
+      <c r="I2" s="230"/>
+      <c r="J2" s="230"/>
+      <c r="K2" s="230"/>
+      <c r="L2" s="231" t="s">
         <v>69</v>
       </c>
-      <c r="M2" s="226"/>
-      <c r="N2" s="226"/>
-      <c r="O2" s="226"/>
-      <c r="P2" s="226"/>
-      <c r="Q2" s="226"/>
-      <c r="R2" s="227" t="s">
+      <c r="M2" s="231"/>
+      <c r="N2" s="231"/>
+      <c r="O2" s="231"/>
+      <c r="P2" s="231"/>
+      <c r="Q2" s="231"/>
+      <c r="R2" s="232" t="s">
         <v>70</v>
       </c>
-      <c r="S2" s="227"/>
-      <c r="T2" s="227"/>
-      <c r="U2" s="227"/>
-      <c r="V2" s="227"/>
-      <c r="W2" s="227"/>
-      <c r="X2" s="227"/>
-      <c r="Y2" s="227"/>
-      <c r="Z2" s="227"/>
-      <c r="AA2" s="227"/>
-      <c r="AB2" s="228" t="s">
+      <c r="S2" s="232"/>
+      <c r="T2" s="232"/>
+      <c r="U2" s="232"/>
+      <c r="V2" s="232"/>
+      <c r="W2" s="232"/>
+      <c r="X2" s="232"/>
+      <c r="Y2" s="232"/>
+      <c r="Z2" s="232"/>
+      <c r="AA2" s="232"/>
+      <c r="AB2" s="233" t="s">
         <v>71</v>
       </c>
-      <c r="AC2" s="228"/>
-      <c r="AD2" s="228"/>
+      <c r="AC2" s="233"/>
+      <c r="AD2" s="233"/>
     </row>
     <row r="3" spans="1:52" ht="45" customHeight="1">
       <c r="A3" s="67" t="s">
@@ -26121,7 +26295,7 @@
         <f>66577.47+18817</f>
         <v>85394.47</v>
       </c>
-      <c r="AD4" s="232"/>
+      <c r="AD4" s="225"/>
     </row>
     <row r="5" spans="1:52" ht="15.75">
       <c r="A5" s="35">
@@ -26176,7 +26350,7 @@
         <v>7116</v>
       </c>
       <c r="AC5" s="21"/>
-      <c r="AD5" s="232"/>
+      <c r="AD5" s="225"/>
     </row>
     <row r="6" spans="1:52" ht="15.75">
       <c r="A6" s="31">
@@ -26224,7 +26398,7 @@
         <v>17146</v>
       </c>
       <c r="AC6" s="21"/>
-      <c r="AD6" s="232"/>
+      <c r="AD6" s="225"/>
     </row>
     <row r="7" spans="1:52" ht="15.75">
       <c r="A7" s="35">
@@ -26281,7 +26455,7 @@
         <v>6206.84</v>
       </c>
       <c r="AC7" s="21"/>
-      <c r="AD7" s="232"/>
+      <c r="AD7" s="225"/>
     </row>
     <row r="8" spans="1:52" ht="15" customHeight="1">
       <c r="A8" s="31">
@@ -26340,7 +26514,7 @@
         <v>8204</v>
       </c>
       <c r="AC8" s="21"/>
-      <c r="AD8" s="232"/>
+      <c r="AD8" s="225"/>
     </row>
     <row r="9" spans="1:52" ht="15.75">
       <c r="A9" s="35">
@@ -26389,7 +26563,7 @@
         <v>8276</v>
       </c>
       <c r="AC9" s="21"/>
-      <c r="AD9" s="232"/>
+      <c r="AD9" s="225"/>
     </row>
     <row r="10" spans="1:52" ht="15.75">
       <c r="A10" s="31">
@@ -26437,7 +26611,7 @@
       <c r="AC10" s="21">
         <v>28225.5</v>
       </c>
-      <c r="AD10" s="232"/>
+      <c r="AD10" s="225"/>
     </row>
     <row r="11" spans="1:52" ht="15.75">
       <c r="A11" s="35">
@@ -26487,14 +26661,14 @@
         <v>5638.53</v>
       </c>
       <c r="AC11" s="21"/>
-      <c r="AD11" s="232"/>
-      <c r="AH11" s="233" t="s">
+      <c r="AD11" s="225"/>
+      <c r="AH11" s="226" t="s">
         <v>84</v>
       </c>
-      <c r="AI11" s="233"/>
-      <c r="AJ11" s="233"/>
-      <c r="AK11" s="233"/>
-      <c r="AL11" s="233"/>
+      <c r="AI11" s="226"/>
+      <c r="AJ11" s="226"/>
+      <c r="AK11" s="226"/>
+      <c r="AL11" s="226"/>
     </row>
     <row r="12" spans="1:52" ht="15.75">
       <c r="A12" s="31">
@@ -26548,12 +26722,12 @@
         <v>33365</v>
       </c>
       <c r="AC12" s="21"/>
-      <c r="AD12" s="232"/>
-      <c r="AH12" s="233"/>
-      <c r="AI12" s="233"/>
-      <c r="AJ12" s="233"/>
-      <c r="AK12" s="233"/>
-      <c r="AL12" s="233"/>
+      <c r="AD12" s="225"/>
+      <c r="AH12" s="226"/>
+      <c r="AI12" s="226"/>
+      <c r="AJ12" s="226"/>
+      <c r="AK12" s="226"/>
+      <c r="AL12" s="226"/>
     </row>
     <row r="13" spans="1:52" ht="15.75">
       <c r="A13" s="35">
@@ -26611,12 +26785,12 @@
         <v>10965.96</v>
       </c>
       <c r="AC13" s="21"/>
-      <c r="AD13" s="232"/>
-      <c r="AH13" s="233"/>
-      <c r="AI13" s="233"/>
-      <c r="AJ13" s="233"/>
-      <c r="AK13" s="233"/>
-      <c r="AL13" s="233"/>
+      <c r="AD13" s="225"/>
+      <c r="AH13" s="226"/>
+      <c r="AI13" s="226"/>
+      <c r="AJ13" s="226"/>
+      <c r="AK13" s="226"/>
+      <c r="AL13" s="226"/>
     </row>
     <row r="14" spans="1:52" ht="18">
       <c r="A14" s="31">
@@ -26664,13 +26838,13 @@
         <v>1614.53</v>
       </c>
       <c r="AC14" s="21"/>
-      <c r="AD14" s="232"/>
-      <c r="AH14" s="229" t="s">
+      <c r="AD14" s="225"/>
+      <c r="AH14" s="222" t="s">
         <v>62</v>
       </c>
-      <c r="AI14" s="229"/>
-      <c r="AJ14" s="229"/>
-      <c r="AK14" s="229"/>
+      <c r="AI14" s="222"/>
+      <c r="AJ14" s="222"/>
+      <c r="AK14" s="222"/>
       <c r="AL14" s="39">
         <f>AC4+AC19+AC23+AC10</f>
         <v>287751.42</v>
@@ -26728,13 +26902,13 @@
         <v>6960.82</v>
       </c>
       <c r="AC15" s="16"/>
-      <c r="AD15" s="232"/>
-      <c r="AH15" s="229" t="s">
+      <c r="AD15" s="225"/>
+      <c r="AH15" s="222" t="s">
         <v>2</v>
       </c>
-      <c r="AI15" s="229"/>
-      <c r="AJ15" s="229"/>
-      <c r="AK15" s="229"/>
+      <c r="AI15" s="222"/>
+      <c r="AJ15" s="222"/>
+      <c r="AK15" s="222"/>
       <c r="AL15" s="39">
         <f>AC20</f>
         <v>1000</v>
@@ -26788,13 +26962,13 @@
       <c r="AC16" s="76">
         <v>5000</v>
       </c>
-      <c r="AD16" s="232"/>
-      <c r="AH16" s="229" t="s">
+      <c r="AD16" s="225"/>
+      <c r="AH16" s="222" t="s">
         <v>63</v>
       </c>
-      <c r="AI16" s="229"/>
-      <c r="AJ16" s="229"/>
-      <c r="AK16" s="229"/>
+      <c r="AI16" s="222"/>
+      <c r="AJ16" s="222"/>
+      <c r="AK16" s="222"/>
       <c r="AL16" s="39">
         <f>AC16+AC28+AC34+AC35</f>
         <v>60000</v>
@@ -26852,23 +27026,23 @@
         <v>5002</v>
       </c>
       <c r="AC17" s="16"/>
-      <c r="AD17" s="232"/>
-      <c r="AH17" s="234" t="s">
+      <c r="AD17" s="225"/>
+      <c r="AH17" s="237" t="s">
         <v>68</v>
       </c>
-      <c r="AI17" s="235"/>
-      <c r="AJ17" s="235"/>
-      <c r="AK17" s="236"/>
+      <c r="AI17" s="238"/>
+      <c r="AJ17" s="238"/>
+      <c r="AK17" s="239"/>
       <c r="AL17" s="39">
         <f>SUM(C37:K37)</f>
         <v>121331.08</v>
       </c>
     </row>
     <row r="18" spans="1:38" ht="19.5" customHeight="1">
-      <c r="A18" s="237" t="s">
+      <c r="A18" s="240" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="237"/>
+      <c r="B18" s="240"/>
       <c r="C18" s="40">
         <f>SUM(C4:C17)</f>
         <v>129.99</v>
@@ -26981,12 +27155,12 @@
         <f>AC18-AB18</f>
         <v>-900.67000000001303</v>
       </c>
-      <c r="AH18" s="229" t="s">
+      <c r="AH18" s="222" t="s">
         <v>85</v>
       </c>
-      <c r="AI18" s="229"/>
-      <c r="AJ18" s="229"/>
-      <c r="AK18" s="229"/>
+      <c r="AI18" s="222"/>
+      <c r="AJ18" s="222"/>
+      <c r="AK18" s="222"/>
       <c r="AL18" s="39">
         <f>SUM(L37:Q37)</f>
         <v>35695</v>
@@ -27040,13 +27214,13 @@
       <c r="AC19" s="46">
         <v>38575.449999999997</v>
       </c>
-      <c r="AD19" s="232"/>
-      <c r="AH19" s="229" t="s">
+      <c r="AD19" s="225"/>
+      <c r="AH19" s="222" t="s">
         <v>66</v>
       </c>
-      <c r="AI19" s="229"/>
-      <c r="AJ19" s="229"/>
-      <c r="AK19" s="229"/>
+      <c r="AI19" s="222"/>
+      <c r="AJ19" s="222"/>
+      <c r="AK19" s="222"/>
       <c r="AL19" s="39">
         <f>W37</f>
         <v>38934</v>
@@ -27103,14 +27277,14 @@
       <c r="AC20" s="47">
         <v>1000</v>
       </c>
-      <c r="AD20" s="232"/>
+      <c r="AD20" s="225"/>
       <c r="AF20" s="48"/>
-      <c r="AH20" s="229" t="s">
+      <c r="AH20" s="222" t="s">
         <v>86</v>
       </c>
-      <c r="AI20" s="229"/>
-      <c r="AJ20" s="229"/>
-      <c r="AK20" s="229"/>
+      <c r="AI20" s="222"/>
+      <c r="AJ20" s="222"/>
+      <c r="AK20" s="222"/>
       <c r="AL20" s="39">
         <f>SUM(U37:V37)</f>
         <v>15264.08</v>
@@ -27156,13 +27330,13 @@
         <v>1980</v>
       </c>
       <c r="AC21" s="47"/>
-      <c r="AD21" s="232"/>
-      <c r="AH21" s="238" t="s">
+      <c r="AD21" s="225"/>
+      <c r="AH21" s="234" t="s">
         <v>32</v>
       </c>
-      <c r="AI21" s="238"/>
-      <c r="AJ21" s="238"/>
-      <c r="AK21" s="238"/>
+      <c r="AI21" s="234"/>
+      <c r="AJ21" s="234"/>
+      <c r="AK21" s="234"/>
       <c r="AL21" s="49">
         <f>T37</f>
         <v>31093</v>
@@ -27217,11 +27391,11 @@
         <v>3710.54</v>
       </c>
       <c r="AC22" s="47"/>
-      <c r="AD22" s="232"/>
-      <c r="AH22" s="239"/>
-      <c r="AI22" s="239"/>
-      <c r="AJ22" s="239"/>
-      <c r="AK22" s="239"/>
+      <c r="AD22" s="225"/>
+      <c r="AH22" s="235"/>
+      <c r="AI22" s="235"/>
+      <c r="AJ22" s="235"/>
+      <c r="AK22" s="235"/>
       <c r="AL22" s="50"/>
     </row>
     <row r="23" spans="1:38" ht="15.75">
@@ -27273,7 +27447,7 @@
         <f>21986+70637+42933</f>
         <v>135556</v>
       </c>
-      <c r="AD23" s="232"/>
+      <c r="AD23" s="225"/>
     </row>
     <row r="24" spans="1:38" ht="15.75">
       <c r="A24" s="35">
@@ -27333,7 +27507,7 @@
         <v>26293.41</v>
       </c>
       <c r="AC24" s="47"/>
-      <c r="AD24" s="232"/>
+      <c r="AD24" s="225"/>
     </row>
     <row r="25" spans="1:38" ht="15.75">
       <c r="A25" s="31">
@@ -27378,7 +27552,7 @@
         <v>542</v>
       </c>
       <c r="AC25" s="46"/>
-      <c r="AD25" s="232"/>
+      <c r="AD25" s="225"/>
     </row>
     <row r="26" spans="1:38" ht="15.75">
       <c r="A26" s="35">
@@ -27438,7 +27612,7 @@
         <v>5856.07</v>
       </c>
       <c r="AC26" s="47"/>
-      <c r="AD26" s="232"/>
+      <c r="AD26" s="225"/>
     </row>
     <row r="27" spans="1:38" ht="15.75">
       <c r="A27" s="31">
@@ -27492,7 +27666,7 @@
         <v>14081.2</v>
       </c>
       <c r="AC27" s="47"/>
-      <c r="AD27" s="232"/>
+      <c r="AD27" s="225"/>
     </row>
     <row r="28" spans="1:38" ht="15.75">
       <c r="A28" s="35">
@@ -27536,7 +27710,7 @@
       <c r="AC28" s="47">
         <v>20000</v>
       </c>
-      <c r="AD28" s="232"/>
+      <c r="AD28" s="225"/>
     </row>
     <row r="29" spans="1:38" ht="15.75">
       <c r="A29" s="31">
@@ -27585,7 +27759,7 @@
         <v>4019.84</v>
       </c>
       <c r="AC29" s="47"/>
-      <c r="AD29" s="232"/>
+      <c r="AD29" s="225"/>
     </row>
     <row r="30" spans="1:38" ht="15.75">
       <c r="A30" s="35">
@@ -27636,7 +27810,7 @@
         <v>2628.39</v>
       </c>
       <c r="AC30" s="47"/>
-      <c r="AD30" s="232"/>
+      <c r="AD30" s="225"/>
     </row>
     <row r="31" spans="1:38" ht="15.75">
       <c r="A31" s="78">
@@ -27692,7 +27866,7 @@
         <v>12589</v>
       </c>
       <c r="AC31" s="47"/>
-      <c r="AD31" s="232"/>
+      <c r="AD31" s="225"/>
     </row>
     <row r="32" spans="1:38" ht="15.75">
       <c r="A32" s="11">
@@ -27754,7 +27928,7 @@
         <v>18544.419999999998</v>
       </c>
       <c r="AC32" s="47"/>
-      <c r="AD32" s="232"/>
+      <c r="AD32" s="225"/>
     </row>
     <row r="33" spans="1:34" ht="15.75">
       <c r="A33" s="84">
@@ -27805,7 +27979,7 @@
         <v>9526.09</v>
       </c>
       <c r="AC33" s="47"/>
-      <c r="AD33" s="232"/>
+      <c r="AD33" s="225"/>
     </row>
     <row r="34" spans="1:34" ht="15.75">
       <c r="A34" s="88">
@@ -27867,7 +28041,7 @@
       <c r="AC34" s="47">
         <v>20000</v>
       </c>
-      <c r="AD34" s="232"/>
+      <c r="AD34" s="225"/>
     </row>
     <row r="35" spans="1:34" ht="15.75">
       <c r="A35" s="92">
@@ -27923,13 +28097,13 @@
       <c r="AC35" s="96">
         <v>15000</v>
       </c>
-      <c r="AD35" s="232"/>
+      <c r="AD35" s="225"/>
     </row>
     <row r="36" spans="1:34" ht="24" customHeight="1">
-      <c r="A36" s="240" t="s">
+      <c r="A36" s="236" t="s">
         <v>55</v>
       </c>
-      <c r="B36" s="240"/>
+      <c r="B36" s="236"/>
       <c r="C36" s="56">
         <f t="shared" ref="C36:AC36" si="6">SUM(C19:C35)</f>
         <v>1293.0899999999999</v>
@@ -28045,10 +28219,10 @@
       <c r="AH36" s="48"/>
     </row>
     <row r="37" spans="1:34" ht="31.5" customHeight="1">
-      <c r="A37" s="231" t="s">
+      <c r="A37" s="224" t="s">
         <v>56</v>
       </c>
-      <c r="B37" s="231"/>
+      <c r="B37" s="224"/>
       <c r="C37" s="61">
         <f t="shared" ref="C37:R37" si="7">SUM(C18,C36)</f>
         <v>1423.08</v>
@@ -28179,6 +28353,12 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="AD4:AD17"/>
     <mergeCell ref="AD19:AD35"/>
@@ -28194,12 +28374,6 @@
     <mergeCell ref="AH17:AK17"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="AH18:AK18"/>
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:K2"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Другое/2026/Доходы-Расходы.xlsx
+++ b/Другое/2026/Доходы-Расходы.xlsx
@@ -9132,6 +9132,34 @@
           </rPr>
           <t xml:space="preserve">Ремонт часов
 </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N29" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Яндекс Плюс</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W30" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Аня попросила скинуть</t>
         </r>
       </text>
     </comment>
@@ -11131,6 +11159,9 @@
     <xf numFmtId="0" fontId="45" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="46" fillId="11" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="46" fillId="11" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="40" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="37" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -11170,6 +11201,9 @@
     <xf numFmtId="0" fontId="29" fillId="22" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -11180,24 +11214,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -11221,6 +11237,21 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -11240,9 +11271,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="40" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -11899,78 +11927,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="34.5" customHeight="1">
-      <c r="A1" s="227" t="s">
+      <c r="A1" s="223" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="227"/>
-      <c r="C1" s="227"/>
-      <c r="D1" s="227"/>
-      <c r="E1" s="227"/>
-      <c r="F1" s="227"/>
-      <c r="G1" s="227"/>
-      <c r="H1" s="227"/>
-      <c r="I1" s="227"/>
-      <c r="J1" s="227"/>
-      <c r="K1" s="227"/>
-      <c r="L1" s="227"/>
-      <c r="M1" s="227"/>
-      <c r="N1" s="227"/>
-      <c r="O1" s="227"/>
-      <c r="P1" s="227"/>
-      <c r="Q1" s="227"/>
-      <c r="R1" s="227"/>
-      <c r="S1" s="227"/>
-      <c r="T1" s="227"/>
-      <c r="U1" s="227"/>
-      <c r="V1" s="227"/>
-      <c r="W1" s="227"/>
-      <c r="X1" s="227"/>
-      <c r="Y1" s="227"/>
-      <c r="Z1" s="227"/>
-      <c r="AA1" s="227"/>
-      <c r="AB1" s="227"/>
-      <c r="AC1" s="227"/>
-      <c r="AD1" s="227"/>
+      <c r="B1" s="223"/>
+      <c r="C1" s="223"/>
+      <c r="D1" s="223"/>
+      <c r="E1" s="223"/>
+      <c r="F1" s="223"/>
+      <c r="G1" s="223"/>
+      <c r="H1" s="223"/>
+      <c r="I1" s="223"/>
+      <c r="J1" s="223"/>
+      <c r="K1" s="223"/>
+      <c r="L1" s="223"/>
+      <c r="M1" s="223"/>
+      <c r="N1" s="223"/>
+      <c r="O1" s="223"/>
+      <c r="P1" s="223"/>
+      <c r="Q1" s="223"/>
+      <c r="R1" s="223"/>
+      <c r="S1" s="223"/>
+      <c r="T1" s="223"/>
+      <c r="U1" s="223"/>
+      <c r="V1" s="223"/>
+      <c r="W1" s="223"/>
+      <c r="X1" s="223"/>
+      <c r="Y1" s="223"/>
+      <c r="Z1" s="223"/>
+      <c r="AA1" s="223"/>
+      <c r="AB1" s="223"/>
+      <c r="AC1" s="223"/>
+      <c r="AD1" s="223"/>
     </row>
     <row r="2" spans="1:52" ht="26.25">
-      <c r="A2" s="228"/>
-      <c r="B2" s="229"/>
-      <c r="C2" s="230" t="s">
+      <c r="A2" s="224"/>
+      <c r="B2" s="225"/>
+      <c r="C2" s="226" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="230"/>
-      <c r="G2" s="230"/>
-      <c r="H2" s="230"/>
-      <c r="I2" s="230"/>
-      <c r="J2" s="230"/>
-      <c r="K2" s="230"/>
-      <c r="L2" s="231" t="s">
+      <c r="D2" s="226"/>
+      <c r="E2" s="226"/>
+      <c r="F2" s="226"/>
+      <c r="G2" s="226"/>
+      <c r="H2" s="226"/>
+      <c r="I2" s="226"/>
+      <c r="J2" s="226"/>
+      <c r="K2" s="226"/>
+      <c r="L2" s="227" t="s">
         <v>69</v>
       </c>
-      <c r="M2" s="231"/>
-      <c r="N2" s="231"/>
-      <c r="O2" s="231"/>
-      <c r="P2" s="231"/>
-      <c r="Q2" s="231"/>
-      <c r="R2" s="232" t="s">
+      <c r="M2" s="227"/>
+      <c r="N2" s="227"/>
+      <c r="O2" s="227"/>
+      <c r="P2" s="227"/>
+      <c r="Q2" s="227"/>
+      <c r="R2" s="228" t="s">
         <v>70</v>
       </c>
-      <c r="S2" s="232"/>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232"/>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
-      <c r="AA2" s="232"/>
-      <c r="AB2" s="233" t="s">
+      <c r="S2" s="228"/>
+      <c r="T2" s="228"/>
+      <c r="U2" s="228"/>
+      <c r="V2" s="228"/>
+      <c r="W2" s="228"/>
+      <c r="X2" s="228"/>
+      <c r="Y2" s="228"/>
+      <c r="Z2" s="228"/>
+      <c r="AA2" s="228"/>
+      <c r="AB2" s="229" t="s">
         <v>71</v>
       </c>
-      <c r="AC2" s="233"/>
-      <c r="AD2" s="233"/>
+      <c r="AC2" s="229"/>
+      <c r="AD2" s="229"/>
     </row>
     <row r="3" spans="1:52" ht="45" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -12140,7 +12168,7 @@
       <c r="AC4" s="16">
         <v>142200.85999999999</v>
       </c>
-      <c r="AD4" s="225"/>
+      <c r="AD4" s="233"/>
     </row>
     <row r="5" spans="1:52" ht="15.75">
       <c r="A5" s="17">
@@ -12196,7 +12224,7 @@
         <v>47667</v>
       </c>
       <c r="AC5" s="21"/>
-      <c r="AD5" s="225"/>
+      <c r="AD5" s="233"/>
     </row>
     <row r="6" spans="1:52" ht="15.75">
       <c r="A6" s="22">
@@ -12250,7 +12278,7 @@
         <v>9459</v>
       </c>
       <c r="AC6" s="21"/>
-      <c r="AD6" s="225"/>
+      <c r="AD6" s="233"/>
     </row>
     <row r="7" spans="1:52" ht="15.75">
       <c r="A7" s="26">
@@ -12303,7 +12331,7 @@
       <c r="AC7" s="21">
         <v>2000</v>
       </c>
-      <c r="AD7" s="225"/>
+      <c r="AD7" s="233"/>
     </row>
     <row r="8" spans="1:52" ht="15" customHeight="1">
       <c r="A8" s="31">
@@ -12345,7 +12373,7 @@
         <v>2946.51</v>
       </c>
       <c r="AC8" s="21"/>
-      <c r="AD8" s="225"/>
+      <c r="AD8" s="233"/>
     </row>
     <row r="9" spans="1:52" ht="15.75">
       <c r="A9" s="35">
@@ -12390,7 +12418,7 @@
         <v>1677.84</v>
       </c>
       <c r="AC9" s="21"/>
-      <c r="AD9" s="225"/>
+      <c r="AD9" s="233"/>
     </row>
     <row r="10" spans="1:52" ht="15.75">
       <c r="A10" s="31">
@@ -12456,7 +12484,7 @@
       <c r="AC10" s="21">
         <v>55867</v>
       </c>
-      <c r="AD10" s="225"/>
+      <c r="AD10" s="233"/>
     </row>
     <row r="11" spans="1:52" ht="15.75">
       <c r="A11" s="35">
@@ -12503,14 +12531,14 @@
       <c r="AC11" s="21">
         <v>3000</v>
       </c>
-      <c r="AD11" s="225"/>
-      <c r="AH11" s="226" t="s">
+      <c r="AD11" s="233"/>
+      <c r="AH11" s="234" t="s">
         <v>84</v>
       </c>
-      <c r="AI11" s="226"/>
-      <c r="AJ11" s="226"/>
-      <c r="AK11" s="226"/>
-      <c r="AL11" s="226"/>
+      <c r="AI11" s="234"/>
+      <c r="AJ11" s="234"/>
+      <c r="AK11" s="234"/>
+      <c r="AL11" s="234"/>
     </row>
     <row r="12" spans="1:52" ht="15.75">
       <c r="A12" s="31">
@@ -12559,12 +12587,12 @@
         <v>6686</v>
       </c>
       <c r="AC12" s="21"/>
-      <c r="AD12" s="225"/>
-      <c r="AH12" s="226"/>
-      <c r="AI12" s="226"/>
-      <c r="AJ12" s="226"/>
-      <c r="AK12" s="226"/>
-      <c r="AL12" s="226"/>
+      <c r="AD12" s="233"/>
+      <c r="AH12" s="234"/>
+      <c r="AI12" s="234"/>
+      <c r="AJ12" s="234"/>
+      <c r="AK12" s="234"/>
+      <c r="AL12" s="234"/>
     </row>
     <row r="13" spans="1:52" ht="15.75">
       <c r="A13" s="35">
@@ -12611,12 +12639,12 @@
         <v>3935</v>
       </c>
       <c r="AC13" s="21"/>
-      <c r="AD13" s="225"/>
-      <c r="AH13" s="226"/>
-      <c r="AI13" s="226"/>
-      <c r="AJ13" s="226"/>
-      <c r="AK13" s="226"/>
-      <c r="AL13" s="226"/>
+      <c r="AD13" s="233"/>
+      <c r="AH13" s="234"/>
+      <c r="AI13" s="234"/>
+      <c r="AJ13" s="234"/>
+      <c r="AK13" s="234"/>
+      <c r="AL13" s="234"/>
     </row>
     <row r="14" spans="1:52" ht="18">
       <c r="A14" s="31">
@@ -12657,13 +12685,13 @@
         <v>750</v>
       </c>
       <c r="AC14" s="21"/>
-      <c r="AD14" s="225"/>
-      <c r="AH14" s="222" t="s">
+      <c r="AD14" s="233"/>
+      <c r="AH14" s="230" t="s">
         <v>62</v>
       </c>
-      <c r="AI14" s="222"/>
-      <c r="AJ14" s="222"/>
-      <c r="AK14" s="222"/>
+      <c r="AI14" s="230"/>
+      <c r="AJ14" s="230"/>
+      <c r="AK14" s="230"/>
       <c r="AL14" s="39">
         <f>AC4+AC20+AC24+AC10</f>
         <v>198067.86</v>
@@ -12718,13 +12746,13 @@
         <v>10319</v>
       </c>
       <c r="AC15" s="16"/>
-      <c r="AD15" s="225"/>
-      <c r="AH15" s="222" t="s">
+      <c r="AD15" s="233"/>
+      <c r="AH15" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="AI15" s="222"/>
-      <c r="AJ15" s="222"/>
-      <c r="AK15" s="222"/>
+      <c r="AI15" s="230"/>
+      <c r="AJ15" s="230"/>
+      <c r="AK15" s="230"/>
       <c r="AL15" s="39">
         <f>SUM(AC7,AC11)</f>
         <v>5000</v>
@@ -12779,13 +12807,13 @@
         <v>7901.26</v>
       </c>
       <c r="AC16" s="16"/>
-      <c r="AD16" s="225"/>
-      <c r="AH16" s="222" t="s">
+      <c r="AD16" s="233"/>
+      <c r="AH16" s="230" t="s">
         <v>63</v>
       </c>
-      <c r="AI16" s="222"/>
-      <c r="AJ16" s="222"/>
-      <c r="AK16" s="222"/>
+      <c r="AI16" s="230"/>
+      <c r="AJ16" s="230"/>
+      <c r="AK16" s="230"/>
       <c r="AL16" s="39">
         <v>0</v>
       </c>
@@ -12834,13 +12862,13 @@
         <v>1766.67</v>
       </c>
       <c r="AC17" s="16"/>
-      <c r="AD17" s="225"/>
-      <c r="AH17" s="237" t="s">
+      <c r="AD17" s="233"/>
+      <c r="AH17" s="238" t="s">
         <v>68</v>
       </c>
-      <c r="AI17" s="238"/>
-      <c r="AJ17" s="238"/>
-      <c r="AK17" s="239"/>
+      <c r="AI17" s="239"/>
+      <c r="AJ17" s="239"/>
+      <c r="AK17" s="240"/>
       <c r="AL17" s="39">
         <f>SUM(C37:K37)</f>
         <v>65807.89</v>
@@ -12889,23 +12917,23 @@
         <v>20640.400000000001</v>
       </c>
       <c r="AC18" s="16"/>
-      <c r="AD18" s="225"/>
-      <c r="AH18" s="237" t="s">
+      <c r="AD18" s="233"/>
+      <c r="AH18" s="238" t="s">
         <v>85</v>
       </c>
-      <c r="AI18" s="238"/>
-      <c r="AJ18" s="238"/>
-      <c r="AK18" s="239"/>
+      <c r="AI18" s="239"/>
+      <c r="AJ18" s="239"/>
+      <c r="AK18" s="240"/>
       <c r="AL18" s="39">
         <f>SUM(L37:Q37)</f>
-        <v>23200.98</v>
+        <v>24190.98</v>
       </c>
     </row>
     <row r="19" spans="1:38" ht="19.5" customHeight="1">
-      <c r="A19" s="240" t="s">
+      <c r="A19" s="241" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="240"/>
+      <c r="B19" s="241"/>
       <c r="C19" s="40">
         <f>SUM(C4:C18)</f>
         <v>2892.73</v>
@@ -13018,15 +13046,15 @@
         <f>AC19-AB19</f>
         <v>23603.33</v>
       </c>
-      <c r="AH19" s="237" t="s">
+      <c r="AH19" s="238" t="s">
         <v>66</v>
       </c>
-      <c r="AI19" s="238"/>
-      <c r="AJ19" s="238"/>
-      <c r="AK19" s="239"/>
+      <c r="AI19" s="239"/>
+      <c r="AJ19" s="239"/>
+      <c r="AK19" s="240"/>
       <c r="AL19" s="39">
         <f>W37</f>
-        <v>67274</v>
+        <v>68274</v>
       </c>
     </row>
     <row r="20" spans="1:38" ht="18">
@@ -13070,13 +13098,13 @@
       <c r="AC20" s="46">
         <v>0</v>
       </c>
-      <c r="AD20" s="225"/>
-      <c r="AH20" s="237" t="s">
+      <c r="AD20" s="233"/>
+      <c r="AH20" s="238" t="s">
         <v>86</v>
       </c>
-      <c r="AI20" s="238"/>
-      <c r="AJ20" s="238"/>
-      <c r="AK20" s="239"/>
+      <c r="AI20" s="239"/>
+      <c r="AJ20" s="239"/>
+      <c r="AK20" s="240"/>
       <c r="AL20" s="39">
         <f>SUM(U37:V37)</f>
         <v>6377.57</v>
@@ -13124,14 +13152,14 @@
         <f>3175.8+7922.85</f>
         <v>11098.65</v>
       </c>
-      <c r="AD21" s="225"/>
+      <c r="AD21" s="233"/>
       <c r="AF21" s="48"/>
-      <c r="AH21" s="234" t="s">
+      <c r="AH21" s="235" t="s">
         <v>32</v>
       </c>
-      <c r="AI21" s="234"/>
-      <c r="AJ21" s="234"/>
-      <c r="AK21" s="234"/>
+      <c r="AI21" s="235"/>
+      <c r="AJ21" s="235"/>
+      <c r="AK21" s="235"/>
       <c r="AL21" s="49">
         <f>T37</f>
         <v>0</v>
@@ -13182,7 +13210,7 @@
         <v>4779.9799999999996</v>
       </c>
       <c r="AC22" s="47"/>
-      <c r="AD22" s="225"/>
+      <c r="AD22" s="233"/>
     </row>
     <row r="23" spans="1:38" ht="18">
       <c r="A23" s="35">
@@ -13226,11 +13254,11 @@
         <v>3933</v>
       </c>
       <c r="AC23" s="47"/>
-      <c r="AD23" s="225"/>
-      <c r="AH23" s="235"/>
-      <c r="AI23" s="235"/>
-      <c r="AJ23" s="235"/>
-      <c r="AK23" s="235"/>
+      <c r="AD23" s="233"/>
+      <c r="AH23" s="236"/>
+      <c r="AI23" s="236"/>
+      <c r="AJ23" s="236"/>
+      <c r="AK23" s="236"/>
       <c r="AL23" s="50"/>
     </row>
     <row r="24" spans="1:38" ht="15.75">
@@ -13280,7 +13308,7 @@
         <v>5930.79</v>
       </c>
       <c r="AC24" s="47"/>
-      <c r="AD24" s="225"/>
+      <c r="AD24" s="233"/>
     </row>
     <row r="25" spans="1:38" ht="15.75">
       <c r="A25" s="35">
@@ -13330,7 +13358,7 @@
         <v>4815.1900000000005</v>
       </c>
       <c r="AC25" s="47"/>
-      <c r="AD25" s="225"/>
+      <c r="AD25" s="233"/>
     </row>
     <row r="26" spans="1:38" ht="15.75">
       <c r="A26" s="31">
@@ -13385,7 +13413,7 @@
         <v>6789.54</v>
       </c>
       <c r="AC26" s="46"/>
-      <c r="AD26" s="225"/>
+      <c r="AD26" s="233"/>
     </row>
     <row r="27" spans="1:38" ht="15.75">
       <c r="A27" s="35">
@@ -13426,7 +13454,7 @@
         <v>1600</v>
       </c>
       <c r="AC27" s="47"/>
-      <c r="AD27" s="225"/>
+      <c r="AD27" s="233"/>
     </row>
     <row r="28" spans="1:38" ht="15.75">
       <c r="A28" s="31">
@@ -13472,7 +13500,7 @@
         <v>2181.98</v>
       </c>
       <c r="AC28" s="47"/>
-      <c r="AD28" s="225"/>
+      <c r="AD28" s="233"/>
     </row>
     <row r="29" spans="1:38" ht="15.75">
       <c r="A29" s="35">
@@ -13484,7 +13512,7 @@
       <c r="C29" s="37"/>
       <c r="D29" s="37"/>
       <c r="E29" s="37"/>
-      <c r="F29" s="241"/>
+      <c r="F29" s="204"/>
       <c r="G29" s="37"/>
       <c r="H29" s="37"/>
       <c r="I29" s="37"/>
@@ -13492,7 +13520,10 @@
       <c r="K29" s="37"/>
       <c r="L29" s="37"/>
       <c r="M29" s="37"/>
-      <c r="N29" s="37"/>
+      <c r="N29" s="37">
+        <f>990</f>
+        <v>990</v>
+      </c>
       <c r="O29" s="37"/>
       <c r="P29" s="37"/>
       <c r="Q29" s="37"/>
@@ -13508,10 +13539,10 @@
       <c r="AA29" s="38"/>
       <c r="AB29" s="30">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="AC29" s="47"/>
-      <c r="AD29" s="225"/>
+      <c r="AD29" s="233"/>
     </row>
     <row r="30" spans="1:38" ht="15.75">
       <c r="A30" s="31">
@@ -13540,17 +13571,19 @@
       <c r="T30" s="33"/>
       <c r="U30" s="33"/>
       <c r="V30" s="33"/>
-      <c r="W30" s="33"/>
+      <c r="W30" s="33">
+        <v>1000</v>
+      </c>
       <c r="X30" s="33"/>
       <c r="Y30" s="33"/>
       <c r="Z30" s="33"/>
       <c r="AA30" s="34"/>
       <c r="AB30" s="30">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC30" s="47"/>
-      <c r="AD30" s="225"/>
+      <c r="AD30" s="233"/>
     </row>
     <row r="31" spans="1:38" ht="15.75">
       <c r="A31" s="35">
@@ -13589,7 +13622,7 @@
         <v>0</v>
       </c>
       <c r="AC31" s="47"/>
-      <c r="AD31" s="225"/>
+      <c r="AD31" s="233"/>
     </row>
     <row r="32" spans="1:38" ht="15.75">
       <c r="A32" s="31">
@@ -13628,7 +13661,7 @@
         <v>0</v>
       </c>
       <c r="AC32" s="47"/>
-      <c r="AD32" s="225"/>
+      <c r="AD32" s="233"/>
     </row>
     <row r="33" spans="1:34" ht="15.75">
       <c r="A33" s="35">
@@ -13640,7 +13673,7 @@
       <c r="C33" s="54"/>
       <c r="D33" s="54"/>
       <c r="E33" s="54"/>
-      <c r="F33" s="241"/>
+      <c r="F33" s="204"/>
       <c r="G33" s="54"/>
       <c r="H33" s="54"/>
       <c r="I33" s="54"/>
@@ -13667,7 +13700,7 @@
         <v>0</v>
       </c>
       <c r="AC33" s="47"/>
-      <c r="AD33" s="225"/>
+      <c r="AD33" s="233"/>
     </row>
     <row r="34" spans="1:34" ht="15.75">
       <c r="A34" s="31">
@@ -13708,7 +13741,7 @@
         <v>11525</v>
       </c>
       <c r="AC34" s="47"/>
-      <c r="AD34" s="225"/>
+      <c r="AD34" s="233"/>
     </row>
     <row r="35" spans="1:34" ht="15.75">
       <c r="A35" s="35">
@@ -13747,13 +13780,13 @@
         <v>0</v>
       </c>
       <c r="AC35" s="47"/>
-      <c r="AD35" s="225"/>
+      <c r="AD35" s="233"/>
     </row>
     <row r="36" spans="1:34" ht="24" customHeight="1">
-      <c r="A36" s="236" t="s">
+      <c r="A36" s="237" t="s">
         <v>55</v>
       </c>
-      <c r="B36" s="236"/>
+      <c r="B36" s="237"/>
       <c r="C36" s="56">
         <f t="shared" ref="C36:AC36" si="7">SUM(C20:C35)</f>
         <v>611.92999999999995</v>
@@ -13800,7 +13833,7 @@
       </c>
       <c r="N36" s="57">
         <f t="shared" si="7"/>
-        <v>249</v>
+        <v>1239</v>
       </c>
       <c r="O36" s="57">
         <f t="shared" si="7"/>
@@ -13836,7 +13869,7 @@
       </c>
       <c r="W36" s="58">
         <f t="shared" si="7"/>
-        <v>18125</v>
+        <v>19125</v>
       </c>
       <c r="X36" s="58">
         <f t="shared" si="7"/>
@@ -13856,7 +13889,7 @@
       </c>
       <c r="AB36" s="43">
         <f t="shared" si="7"/>
-        <v>44040.2</v>
+        <v>46030.2</v>
       </c>
       <c r="AC36" s="44">
         <f t="shared" si="7"/>
@@ -13864,15 +13897,15 @@
       </c>
       <c r="AD36" s="60">
         <f>AC36-AB36</f>
-        <v>-32941.549999999996</v>
+        <v>-34931.549999999996</v>
       </c>
       <c r="AH36" s="48"/>
     </row>
     <row r="37" spans="1:34" ht="31.5" customHeight="1">
-      <c r="A37" s="224" t="s">
+      <c r="A37" s="232" t="s">
         <v>56</v>
       </c>
-      <c r="B37" s="224"/>
+      <c r="B37" s="232"/>
       <c r="C37" s="61">
         <f t="shared" ref="C37:R37" si="8">SUM(C19,C36)</f>
         <v>3504.66</v>
@@ -13919,7 +13952,7 @@
       </c>
       <c r="N37" s="61">
         <f t="shared" si="8"/>
-        <v>3188</v>
+        <v>4178</v>
       </c>
       <c r="O37" s="61">
         <f t="shared" si="8"/>
@@ -13952,7 +13985,7 @@
       </c>
       <c r="W37" s="61">
         <f t="shared" si="9"/>
-        <v>67274</v>
+        <v>68274</v>
       </c>
       <c r="X37" s="61">
         <f t="shared" si="9"/>
@@ -13972,7 +14005,7 @@
       </c>
       <c r="AB37" s="63">
         <f t="shared" si="9"/>
-        <v>223504.72999999998</v>
+        <v>225494.72999999998</v>
       </c>
       <c r="AC37" s="64">
         <f t="shared" si="9"/>
@@ -13980,7 +14013,7 @@
       </c>
       <c r="AD37" s="65">
         <f t="shared" si="9"/>
-        <v>-9338.2199999999939</v>
+        <v>-11328.219999999994</v>
       </c>
     </row>
     <row r="41" spans="1:34">
@@ -14003,12 +14036,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:K2"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="AD4:AD18"/>
@@ -14024,6 +14051,12 @@
     <mergeCell ref="AH16:AK16"/>
     <mergeCell ref="AH17:AK17"/>
     <mergeCell ref="AH18:AK18"/>
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
   </mergeCells>
   <conditionalFormatting sqref="AD37">
     <cfRule type="expression" dxfId="1" priority="1">
@@ -14050,32 +14083,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="204" t="s">
+      <c r="A1" s="205" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="204"/>
-      <c r="C1" s="204"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="204"/>
-      <c r="F1" s="204"/>
-      <c r="G1" s="204"/>
-      <c r="H1" s="204"/>
-      <c r="I1" s="204"/>
-      <c r="J1" s="204"/>
-      <c r="K1" s="204"/>
-      <c r="L1" s="204"/>
-      <c r="M1" s="204"/>
-      <c r="N1" s="204"/>
-      <c r="O1" s="204"/>
-      <c r="P1" s="204"/>
-      <c r="Q1" s="204"/>
-      <c r="R1" s="204"/>
-      <c r="S1" s="204"/>
-      <c r="T1" s="204"/>
-      <c r="U1" s="204"/>
-      <c r="V1" s="204"/>
-      <c r="W1" s="204"/>
-      <c r="X1" s="204"/>
+      <c r="B1" s="205"/>
+      <c r="C1" s="205"/>
+      <c r="D1" s="205"/>
+      <c r="E1" s="205"/>
+      <c r="F1" s="205"/>
+      <c r="G1" s="205"/>
+      <c r="H1" s="205"/>
+      <c r="I1" s="205"/>
+      <c r="J1" s="205"/>
+      <c r="K1" s="205"/>
+      <c r="L1" s="205"/>
+      <c r="M1" s="205"/>
+      <c r="N1" s="205"/>
+      <c r="O1" s="205"/>
+      <c r="P1" s="205"/>
+      <c r="Q1" s="205"/>
+      <c r="R1" s="205"/>
+      <c r="S1" s="205"/>
+      <c r="T1" s="205"/>
+      <c r="U1" s="205"/>
+      <c r="V1" s="205"/>
+      <c r="W1" s="205"/>
+      <c r="X1" s="205"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="172" t="s">
@@ -15274,10 +15307,10 @@
       </c>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" s="205" t="s">
+      <c r="A31" s="206" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="205"/>
+      <c r="B31" s="206"/>
       <c r="C31" s="192">
         <f>SUM(C3:C30)</f>
         <v>19992.27</v>
@@ -15400,32 +15433,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="206" t="s">
+      <c r="A1" s="207" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="206"/>
-      <c r="C1" s="206"/>
-      <c r="D1" s="206"/>
-      <c r="E1" s="206"/>
-      <c r="F1" s="206"/>
-      <c r="G1" s="206"/>
-      <c r="H1" s="206"/>
-      <c r="I1" s="206"/>
-      <c r="J1" s="206"/>
-      <c r="K1" s="206"/>
-      <c r="L1" s="206"/>
-      <c r="M1" s="206"/>
-      <c r="N1" s="206"/>
-      <c r="O1" s="206"/>
-      <c r="P1" s="206"/>
-      <c r="Q1" s="206"/>
-      <c r="R1" s="206"/>
-      <c r="S1" s="206"/>
-      <c r="T1" s="206"/>
-      <c r="U1" s="206"/>
-      <c r="V1" s="206"/>
-      <c r="W1" s="206"/>
-      <c r="X1" s="206"/>
+      <c r="B1" s="207"/>
+      <c r="C1" s="207"/>
+      <c r="D1" s="207"/>
+      <c r="E1" s="207"/>
+      <c r="F1" s="207"/>
+      <c r="G1" s="207"/>
+      <c r="H1" s="207"/>
+      <c r="I1" s="207"/>
+      <c r="J1" s="207"/>
+      <c r="K1" s="207"/>
+      <c r="L1" s="207"/>
+      <c r="M1" s="207"/>
+      <c r="N1" s="207"/>
+      <c r="O1" s="207"/>
+      <c r="P1" s="207"/>
+      <c r="Q1" s="207"/>
+      <c r="R1" s="207"/>
+      <c r="S1" s="207"/>
+      <c r="T1" s="207"/>
+      <c r="U1" s="207"/>
+      <c r="V1" s="207"/>
+      <c r="W1" s="207"/>
+      <c r="X1" s="207"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="149" t="s">
@@ -16636,10 +16669,10 @@
       <c r="X31" s="166"/>
     </row>
     <row r="32" spans="1:24">
-      <c r="A32" s="207" t="s">
+      <c r="A32" s="208" t="s">
         <v>19</v>
       </c>
-      <c r="B32" s="207"/>
+      <c r="B32" s="208"/>
       <c r="C32" s="165">
         <f>SUM(C3:C31)</f>
         <v>16843.349999999999</v>
@@ -16762,33 +16795,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="206" t="s">
+      <c r="A1" s="207" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="206"/>
-      <c r="C1" s="206"/>
-      <c r="D1" s="206"/>
-      <c r="E1" s="206"/>
-      <c r="F1" s="206"/>
-      <c r="G1" s="206"/>
-      <c r="H1" s="206"/>
-      <c r="I1" s="206"/>
-      <c r="J1" s="206"/>
-      <c r="K1" s="206"/>
-      <c r="L1" s="206"/>
-      <c r="M1" s="206"/>
-      <c r="N1" s="206"/>
-      <c r="O1" s="206"/>
-      <c r="P1" s="206"/>
-      <c r="Q1" s="206"/>
-      <c r="R1" s="206"/>
-      <c r="S1" s="206"/>
-      <c r="T1" s="206"/>
-      <c r="U1" s="206"/>
-      <c r="V1" s="206"/>
-      <c r="W1" s="206"/>
-      <c r="X1" s="206"/>
-      <c r="Y1" s="206"/>
+      <c r="B1" s="207"/>
+      <c r="C1" s="207"/>
+      <c r="D1" s="207"/>
+      <c r="E1" s="207"/>
+      <c r="F1" s="207"/>
+      <c r="G1" s="207"/>
+      <c r="H1" s="207"/>
+      <c r="I1" s="207"/>
+      <c r="J1" s="207"/>
+      <c r="K1" s="207"/>
+      <c r="L1" s="207"/>
+      <c r="M1" s="207"/>
+      <c r="N1" s="207"/>
+      <c r="O1" s="207"/>
+      <c r="P1" s="207"/>
+      <c r="Q1" s="207"/>
+      <c r="R1" s="207"/>
+      <c r="S1" s="207"/>
+      <c r="T1" s="207"/>
+      <c r="U1" s="207"/>
+      <c r="V1" s="207"/>
+      <c r="W1" s="207"/>
+      <c r="X1" s="207"/>
+      <c r="Y1" s="207"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="149" t="s">
@@ -17606,10 +17639,10 @@
       <c r="Y19" s="157"/>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="208" t="s">
+      <c r="A20" s="209" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="209"/>
+      <c r="B20" s="210"/>
       <c r="C20" s="158">
         <f>SUM(C3:C19)</f>
         <v>12278.83</v>
@@ -18329,10 +18362,10 @@
       <c r="Y35" s="157"/>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="208" t="s">
+      <c r="A36" s="209" t="s">
         <v>55</v>
       </c>
-      <c r="B36" s="209"/>
+      <c r="B36" s="210"/>
       <c r="C36" s="158">
         <f>SUM(C21:C35)</f>
         <v>11057.89</v>
@@ -18427,10 +18460,10 @@
       </c>
     </row>
     <row r="37" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A37" s="210" t="s">
+      <c r="A37" s="211" t="s">
         <v>56</v>
       </c>
-      <c r="B37" s="210"/>
+      <c r="B37" s="211"/>
       <c r="C37" s="162">
         <f>SUM(C20,C36)</f>
         <v>23336.720000000001</v>
@@ -18560,33 +18593,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="211" t="s">
+      <c r="A1" s="212" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
-      <c r="I1" s="211"/>
-      <c r="J1" s="211"/>
-      <c r="K1" s="211"/>
-      <c r="L1" s="211"/>
-      <c r="M1" s="211"/>
-      <c r="N1" s="211"/>
-      <c r="O1" s="211"/>
-      <c r="P1" s="211"/>
-      <c r="Q1" s="211"/>
-      <c r="R1" s="211"/>
-      <c r="S1" s="211"/>
-      <c r="T1" s="211"/>
-      <c r="U1" s="211"/>
-      <c r="V1" s="211"/>
-      <c r="W1" s="211"/>
-      <c r="X1" s="211"/>
-      <c r="Y1" s="211"/>
+      <c r="B1" s="212"/>
+      <c r="C1" s="212"/>
+      <c r="D1" s="212"/>
+      <c r="E1" s="212"/>
+      <c r="F1" s="212"/>
+      <c r="G1" s="212"/>
+      <c r="H1" s="212"/>
+      <c r="I1" s="212"/>
+      <c r="J1" s="212"/>
+      <c r="K1" s="212"/>
+      <c r="L1" s="212"/>
+      <c r="M1" s="212"/>
+      <c r="N1" s="212"/>
+      <c r="O1" s="212"/>
+      <c r="P1" s="212"/>
+      <c r="Q1" s="212"/>
+      <c r="R1" s="212"/>
+      <c r="S1" s="212"/>
+      <c r="T1" s="212"/>
+      <c r="U1" s="212"/>
+      <c r="V1" s="212"/>
+      <c r="W1" s="212"/>
+      <c r="X1" s="212"/>
+      <c r="Y1" s="212"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="146" t="s">
@@ -19296,10 +19329,10 @@
       <c r="Y17" s="139"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="212" t="s">
+      <c r="A18" s="213" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="212"/>
+      <c r="B18" s="213"/>
       <c r="C18" s="147">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
         <v>8428.35</v>
@@ -20052,10 +20085,10 @@
       <c r="Y34" s="141"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="212" t="s">
+      <c r="A35" s="213" t="s">
         <v>55</v>
       </c>
-      <c r="B35" s="212"/>
+      <c r="B35" s="213"/>
       <c r="C35" s="147">
         <f>SUM(C19:C34)</f>
         <v>10739.46</v>
@@ -20150,10 +20183,10 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="213" t="s">
+      <c r="A36" s="214" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="213"/>
+      <c r="B36" s="214"/>
       <c r="C36" s="137">
         <f>SUM(C18,C35)</f>
         <v>19167.810000000001</v>
@@ -20291,33 +20324,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="214" t="s">
+      <c r="A1" s="215" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="214"/>
-      <c r="C1" s="214"/>
-      <c r="D1" s="214"/>
-      <c r="E1" s="214"/>
-      <c r="F1" s="214"/>
-      <c r="G1" s="214"/>
-      <c r="H1" s="214"/>
-      <c r="I1" s="214"/>
-      <c r="J1" s="214"/>
-      <c r="K1" s="214"/>
-      <c r="L1" s="214"/>
-      <c r="M1" s="214"/>
-      <c r="N1" s="214"/>
-      <c r="O1" s="214"/>
-      <c r="P1" s="214"/>
-      <c r="Q1" s="214"/>
-      <c r="R1" s="214"/>
-      <c r="S1" s="214"/>
-      <c r="T1" s="214"/>
-      <c r="U1" s="214"/>
-      <c r="V1" s="214"/>
-      <c r="W1" s="214"/>
-      <c r="X1" s="214"/>
-      <c r="Y1" s="214"/>
+      <c r="B1" s="215"/>
+      <c r="C1" s="215"/>
+      <c r="D1" s="215"/>
+      <c r="E1" s="215"/>
+      <c r="F1" s="215"/>
+      <c r="G1" s="215"/>
+      <c r="H1" s="215"/>
+      <c r="I1" s="215"/>
+      <c r="J1" s="215"/>
+      <c r="K1" s="215"/>
+      <c r="L1" s="215"/>
+      <c r="M1" s="215"/>
+      <c r="N1" s="215"/>
+      <c r="O1" s="215"/>
+      <c r="P1" s="215"/>
+      <c r="Q1" s="215"/>
+      <c r="R1" s="215"/>
+      <c r="S1" s="215"/>
+      <c r="T1" s="215"/>
+      <c r="U1" s="215"/>
+      <c r="V1" s="215"/>
+      <c r="W1" s="215"/>
+      <c r="X1" s="215"/>
+      <c r="Y1" s="215"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="104" t="s">
@@ -21056,10 +21089,10 @@
       <c r="Y17" s="139"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="215" t="s">
+      <c r="A18" s="216" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="215"/>
+      <c r="B18" s="216"/>
       <c r="C18" s="125">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
         <v>7904</v>
@@ -21707,10 +21740,10 @@
       <c r="Y34" s="141"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="215" t="s">
+      <c r="A35" s="216" t="s">
         <v>55</v>
       </c>
-      <c r="B35" s="215"/>
+      <c r="B35" s="216"/>
       <c r="C35" s="125">
         <f>SUM(C19:C34)</f>
         <v>0</v>
@@ -21805,10 +21838,10 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="216" t="s">
+      <c r="A36" s="217" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="216"/>
+      <c r="B36" s="217"/>
       <c r="C36" s="145">
         <f>SUM(C18,C35)</f>
         <v>7904</v>
@@ -21948,34 +21981,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="60.75" customHeight="1">
-      <c r="A1" s="221" t="s">
+      <c r="A1" s="218" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="221"/>
-      <c r="C1" s="221"/>
-      <c r="D1" s="221"/>
-      <c r="E1" s="221"/>
-      <c r="F1" s="221"/>
-      <c r="G1" s="221"/>
-      <c r="H1" s="221"/>
-      <c r="I1" s="221"/>
-      <c r="J1" s="221"/>
-      <c r="K1" s="221"/>
-      <c r="L1" s="221"/>
-      <c r="M1" s="221"/>
-      <c r="N1" s="221"/>
-      <c r="O1" s="221"/>
-      <c r="P1" s="221"/>
-      <c r="Q1" s="221"/>
-      <c r="R1" s="221"/>
-      <c r="S1" s="221"/>
-      <c r="T1" s="221"/>
-      <c r="U1" s="221"/>
-      <c r="V1" s="221"/>
-      <c r="W1" s="221"/>
-      <c r="X1" s="221"/>
-      <c r="Y1" s="221"/>
-      <c r="Z1" s="221"/>
+      <c r="B1" s="218"/>
+      <c r="C1" s="218"/>
+      <c r="D1" s="218"/>
+      <c r="E1" s="218"/>
+      <c r="F1" s="218"/>
+      <c r="G1" s="218"/>
+      <c r="H1" s="218"/>
+      <c r="I1" s="218"/>
+      <c r="J1" s="218"/>
+      <c r="K1" s="218"/>
+      <c r="L1" s="218"/>
+      <c r="M1" s="218"/>
+      <c r="N1" s="218"/>
+      <c r="O1" s="218"/>
+      <c r="P1" s="218"/>
+      <c r="Q1" s="218"/>
+      <c r="R1" s="218"/>
+      <c r="S1" s="218"/>
+      <c r="T1" s="218"/>
+      <c r="U1" s="218"/>
+      <c r="V1" s="218"/>
+      <c r="W1" s="218"/>
+      <c r="X1" s="218"/>
+      <c r="Y1" s="218"/>
+      <c r="Z1" s="218"/>
     </row>
     <row r="2" spans="1:48" ht="45" customHeight="1">
       <c r="A2" s="104" t="s">
@@ -22128,7 +22161,7 @@
         <f>(94085+57723.67)</f>
         <v>151808.67000000001</v>
       </c>
-      <c r="Z3" s="219"/>
+      <c r="Z3" s="221"/>
     </row>
     <row r="4" spans="1:48" ht="15.75">
       <c r="A4" s="117">
@@ -22178,7 +22211,7 @@
       </c>
       <c r="X4" s="90"/>
       <c r="Y4" s="121"/>
-      <c r="Z4" s="219"/>
+      <c r="Z4" s="221"/>
     </row>
     <row r="5" spans="1:48" ht="15.75">
       <c r="A5" s="111">
@@ -22218,7 +22251,7 @@
       </c>
       <c r="X5" s="90"/>
       <c r="Y5" s="121"/>
-      <c r="Z5" s="219"/>
+      <c r="Z5" s="221"/>
     </row>
     <row r="6" spans="1:48" ht="15.75">
       <c r="A6" s="117">
@@ -22259,7 +22292,7 @@
       </c>
       <c r="X6" s="90"/>
       <c r="Y6" s="121"/>
-      <c r="Z6" s="219"/>
+      <c r="Z6" s="221"/>
     </row>
     <row r="7" spans="1:48" ht="15" customHeight="1">
       <c r="A7" s="111">
@@ -22303,7 +22336,7 @@
       </c>
       <c r="X7" s="90"/>
       <c r="Y7" s="121"/>
-      <c r="Z7" s="219"/>
+      <c r="Z7" s="221"/>
     </row>
     <row r="8" spans="1:48" ht="15.75">
       <c r="A8" s="117">
@@ -22345,14 +22378,14 @@
       </c>
       <c r="X8" s="90"/>
       <c r="Y8" s="121"/>
-      <c r="Z8" s="219"/>
-      <c r="AC8" s="220" t="s">
+      <c r="Z8" s="221"/>
+      <c r="AC8" s="222" t="s">
         <v>61</v>
       </c>
-      <c r="AD8" s="220"/>
-      <c r="AE8" s="220"/>
-      <c r="AF8" s="220"/>
-      <c r="AG8" s="220"/>
+      <c r="AD8" s="222"/>
+      <c r="AE8" s="222"/>
+      <c r="AF8" s="222"/>
+      <c r="AG8" s="222"/>
     </row>
     <row r="9" spans="1:48" ht="15.75">
       <c r="A9" s="111">
@@ -22391,12 +22424,12 @@
       </c>
       <c r="X9" s="90"/>
       <c r="Y9" s="121"/>
-      <c r="Z9" s="219"/>
-      <c r="AC9" s="220"/>
-      <c r="AD9" s="220"/>
-      <c r="AE9" s="220"/>
-      <c r="AF9" s="220"/>
-      <c r="AG9" s="220"/>
+      <c r="Z9" s="221"/>
+      <c r="AC9" s="222"/>
+      <c r="AD9" s="222"/>
+      <c r="AE9" s="222"/>
+      <c r="AF9" s="222"/>
+      <c r="AG9" s="222"/>
     </row>
     <row r="10" spans="1:48" ht="15.75">
       <c r="A10" s="117">
@@ -22440,12 +22473,12 @@
       </c>
       <c r="X10" s="90"/>
       <c r="Y10" s="121"/>
-      <c r="Z10" s="219"/>
-      <c r="AC10" s="220"/>
-      <c r="AD10" s="220"/>
-      <c r="AE10" s="220"/>
-      <c r="AF10" s="220"/>
-      <c r="AG10" s="220"/>
+      <c r="Z10" s="221"/>
+      <c r="AC10" s="222"/>
+      <c r="AD10" s="222"/>
+      <c r="AE10" s="222"/>
+      <c r="AF10" s="222"/>
+      <c r="AG10" s="222"/>
     </row>
     <row r="11" spans="1:48" ht="15.75">
       <c r="A11" s="111">
@@ -22485,13 +22518,13 @@
       </c>
       <c r="X11" s="90"/>
       <c r="Y11" s="121"/>
-      <c r="Z11" s="219"/>
-      <c r="AC11" s="217" t="s">
+      <c r="Z11" s="221"/>
+      <c r="AC11" s="219" t="s">
         <v>62</v>
       </c>
-      <c r="AD11" s="217"/>
-      <c r="AE11" s="217"/>
-      <c r="AF11" s="217"/>
+      <c r="AD11" s="219"/>
+      <c r="AE11" s="219"/>
+      <c r="AF11" s="219"/>
       <c r="AG11" s="122">
         <f>Y3+Y14+Y21</f>
         <v>226341.31</v>
@@ -22532,13 +22565,13 @@
       </c>
       <c r="X12" s="90"/>
       <c r="Y12" s="121"/>
-      <c r="Z12" s="219"/>
-      <c r="AC12" s="217" t="s">
+      <c r="Z12" s="221"/>
+      <c r="AC12" s="219" t="s">
         <v>2</v>
       </c>
-      <c r="AD12" s="217"/>
-      <c r="AE12" s="217"/>
-      <c r="AF12" s="217"/>
+      <c r="AD12" s="219"/>
+      <c r="AE12" s="219"/>
+      <c r="AF12" s="219"/>
       <c r="AG12" s="122">
         <f>Y27</f>
         <v>20000</v>
@@ -22583,13 +22616,13 @@
       </c>
       <c r="X13" s="90"/>
       <c r="Y13" s="121"/>
-      <c r="Z13" s="219"/>
-      <c r="AC13" s="217" t="s">
+      <c r="Z13" s="221"/>
+      <c r="AC13" s="219" t="s">
         <v>63</v>
       </c>
-      <c r="AD13" s="217"/>
-      <c r="AE13" s="217"/>
-      <c r="AF13" s="217"/>
+      <c r="AD13" s="219"/>
+      <c r="AE13" s="219"/>
+      <c r="AF13" s="219"/>
       <c r="AG13" s="122">
         <f>Y17+Y19</f>
         <v>25000</v>
@@ -22635,13 +22668,13 @@
       <c r="Y14" s="116">
         <v>37634</v>
       </c>
-      <c r="Z14" s="219"/>
-      <c r="AC14" s="217" t="s">
+      <c r="Z14" s="221"/>
+      <c r="AC14" s="219" t="s">
         <v>64</v>
       </c>
-      <c r="AD14" s="217"/>
-      <c r="AE14" s="217"/>
-      <c r="AF14" s="217"/>
+      <c r="AD14" s="219"/>
+      <c r="AE14" s="219"/>
+      <c r="AF14" s="219"/>
       <c r="AG14" s="122">
         <f>W38</f>
         <v>177971.36</v>
@@ -22691,13 +22724,13 @@
       </c>
       <c r="X15" s="90"/>
       <c r="Y15" s="121"/>
-      <c r="Z15" s="219"/>
-      <c r="AC15" s="217" t="s">
+      <c r="Z15" s="221"/>
+      <c r="AC15" s="219" t="s">
         <v>65</v>
       </c>
-      <c r="AD15" s="217"/>
-      <c r="AE15" s="217"/>
-      <c r="AF15" s="217"/>
+      <c r="AD15" s="219"/>
+      <c r="AE15" s="219"/>
+      <c r="AF15" s="219"/>
       <c r="AG15" s="122">
         <f>SUM(C38:H38)</f>
         <v>55416.04</v>
@@ -22746,13 +22779,13 @@
       </c>
       <c r="X16" s="90"/>
       <c r="Y16" s="121"/>
-      <c r="Z16" s="219"/>
-      <c r="AC16" s="217" t="s">
+      <c r="Z16" s="221"/>
+      <c r="AC16" s="219" t="s">
         <v>66</v>
       </c>
-      <c r="AD16" s="217"/>
-      <c r="AE16" s="217"/>
-      <c r="AF16" s="217"/>
+      <c r="AD16" s="219"/>
+      <c r="AE16" s="219"/>
+      <c r="AF16" s="219"/>
       <c r="AG16" s="122">
         <f>Q38</f>
         <v>27468.98</v>
@@ -22808,7 +22841,7 @@
       <c r="Y17" s="124">
         <v>15000</v>
       </c>
-      <c r="Z17" s="219"/>
+      <c r="Z17" s="221"/>
     </row>
     <row r="18" spans="1:28" ht="15.75">
       <c r="A18" s="117">
@@ -22849,7 +22882,7 @@
       </c>
       <c r="X18" s="90"/>
       <c r="Y18" s="121"/>
-      <c r="Z18" s="219"/>
+      <c r="Z18" s="221"/>
     </row>
     <row r="19" spans="1:28" ht="15.75">
       <c r="A19" s="111">
@@ -22893,13 +22926,13 @@
       <c r="Y19" s="124">
         <v>10000</v>
       </c>
-      <c r="Z19" s="219"/>
+      <c r="Z19" s="221"/>
     </row>
     <row r="20" spans="1:28" ht="14.25" customHeight="1">
-      <c r="A20" s="215" t="s">
+      <c r="A20" s="216" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="215"/>
+      <c r="B20" s="216"/>
       <c r="C20" s="125">
         <f t="shared" ref="C20:V20" si="1">SUM(C3:C17)</f>
         <v>10942.99</v>
@@ -23042,7 +23075,7 @@
       <c r="Y21" s="116">
         <v>36898.639999999999</v>
       </c>
-      <c r="Z21" s="219"/>
+      <c r="Z21" s="221"/>
     </row>
     <row r="22" spans="1:28" ht="15.75">
       <c r="A22" s="117">
@@ -23088,7 +23121,7 @@
         <v>23662.84</v>
       </c>
       <c r="Y22" s="121"/>
-      <c r="Z22" s="219"/>
+      <c r="Z22" s="221"/>
       <c r="AB22" s="48"/>
     </row>
     <row r="23" spans="1:28" ht="15.75">
@@ -23132,7 +23165,7 @@
       </c>
       <c r="X23" s="90"/>
       <c r="Y23" s="121"/>
-      <c r="Z23" s="219"/>
+      <c r="Z23" s="221"/>
     </row>
     <row r="24" spans="1:28" ht="15.75">
       <c r="A24" s="117">
@@ -23176,7 +23209,7 @@
       </c>
       <c r="X24" s="90"/>
       <c r="Y24" s="121"/>
-      <c r="Z24" s="219"/>
+      <c r="Z24" s="221"/>
     </row>
     <row r="25" spans="1:28" ht="15.75">
       <c r="A25" s="111">
@@ -23220,7 +23253,7 @@
       </c>
       <c r="X25" s="90"/>
       <c r="Y25" s="121"/>
-      <c r="Z25" s="219"/>
+      <c r="Z25" s="221"/>
     </row>
     <row r="26" spans="1:28" ht="15.75">
       <c r="A26" s="117">
@@ -23259,7 +23292,7 @@
       </c>
       <c r="X26" s="90"/>
       <c r="Y26" s="121"/>
-      <c r="Z26" s="219"/>
+      <c r="Z26" s="221"/>
     </row>
     <row r="27" spans="1:28" ht="15.75">
       <c r="A27" s="111">
@@ -23304,7 +23337,7 @@
       <c r="Y27" s="131">
         <v>20000</v>
       </c>
-      <c r="Z27" s="219"/>
+      <c r="Z27" s="221"/>
     </row>
     <row r="28" spans="1:28" ht="15.75">
       <c r="A28" s="117">
@@ -23346,7 +23379,7 @@
       </c>
       <c r="X28" s="90"/>
       <c r="Y28" s="121"/>
-      <c r="Z28" s="219"/>
+      <c r="Z28" s="221"/>
     </row>
     <row r="29" spans="1:28" ht="15.75">
       <c r="A29" s="111">
@@ -23385,7 +23418,7 @@
       </c>
       <c r="X29" s="90"/>
       <c r="Y29" s="121"/>
-      <c r="Z29" s="219"/>
+      <c r="Z29" s="221"/>
     </row>
     <row r="30" spans="1:28" ht="15.75">
       <c r="A30" s="117">
@@ -23425,7 +23458,7 @@
       </c>
       <c r="X30" s="90"/>
       <c r="Y30" s="121"/>
-      <c r="Z30" s="219"/>
+      <c r="Z30" s="221"/>
     </row>
     <row r="31" spans="1:28" ht="15.75">
       <c r="A31" s="111">
@@ -23460,7 +23493,7 @@
       </c>
       <c r="X31" s="90"/>
       <c r="Y31" s="121"/>
-      <c r="Z31" s="219"/>
+      <c r="Z31" s="221"/>
     </row>
     <row r="32" spans="1:28" ht="15.75">
       <c r="A32" s="117">
@@ -23495,7 +23528,7 @@
       </c>
       <c r="X32" s="90"/>
       <c r="Y32" s="121"/>
-      <c r="Z32" s="219"/>
+      <c r="Z32" s="221"/>
     </row>
     <row r="33" spans="1:26" ht="15.75">
       <c r="A33" s="111">
@@ -23532,7 +23565,7 @@
       <c r="Y33" s="132">
         <v>10000</v>
       </c>
-      <c r="Z33" s="219"/>
+      <c r="Z33" s="221"/>
     </row>
     <row r="34" spans="1:26" ht="15.75">
       <c r="A34" s="117">
@@ -23571,7 +23604,7 @@
       </c>
       <c r="X34" s="90"/>
       <c r="Y34" s="121"/>
-      <c r="Z34" s="219"/>
+      <c r="Z34" s="221"/>
     </row>
     <row r="35" spans="1:26" ht="15.75">
       <c r="A35" s="111">
@@ -23615,7 +23648,7 @@
       </c>
       <c r="X35" s="90"/>
       <c r="Y35" s="121"/>
-      <c r="Z35" s="219"/>
+      <c r="Z35" s="221"/>
     </row>
     <row r="36" spans="1:26" ht="15.75">
       <c r="A36" s="117">
@@ -23656,13 +23689,13 @@
       </c>
       <c r="X36" s="90"/>
       <c r="Y36" s="121"/>
-      <c r="Z36" s="219"/>
+      <c r="Z36" s="221"/>
     </row>
     <row r="37" spans="1:26">
-      <c r="A37" s="215" t="s">
+      <c r="A37" s="216" t="s">
         <v>55</v>
       </c>
-      <c r="B37" s="215"/>
+      <c r="B37" s="216"/>
       <c r="C37" s="125">
         <f>SUM(C21:C36)</f>
         <v>3393</v>
@@ -23761,10 +23794,10 @@
       </c>
     </row>
     <row r="38" spans="1:26" ht="31.5" customHeight="1">
-      <c r="A38" s="218" t="s">
+      <c r="A38" s="220" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="218"/>
+      <c r="B38" s="220"/>
       <c r="C38" s="134">
         <f>SUM(C20,C37)</f>
         <v>14335.99</v>
@@ -23876,11 +23909,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:Z1"/>
-    <mergeCell ref="AC11:AF11"/>
-    <mergeCell ref="AC12:AF12"/>
-    <mergeCell ref="AC13:AF13"/>
-    <mergeCell ref="AC14:AF14"/>
     <mergeCell ref="AC15:AF15"/>
     <mergeCell ref="AC16:AF16"/>
     <mergeCell ref="A20:B20"/>
@@ -23889,6 +23917,11 @@
     <mergeCell ref="Z3:Z19"/>
     <mergeCell ref="Z21:Z36"/>
     <mergeCell ref="AC8:AG10"/>
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="AC11:AF11"/>
+    <mergeCell ref="AC12:AF12"/>
+    <mergeCell ref="AC13:AF13"/>
+    <mergeCell ref="AC14:AF14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -23909,78 +23942,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="34.5" customHeight="1">
-      <c r="A1" s="227" t="s">
+      <c r="A1" s="223" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="227"/>
-      <c r="C1" s="227"/>
-      <c r="D1" s="227"/>
-      <c r="E1" s="227"/>
-      <c r="F1" s="227"/>
-      <c r="G1" s="227"/>
-      <c r="H1" s="227"/>
-      <c r="I1" s="227"/>
-      <c r="J1" s="227"/>
-      <c r="K1" s="227"/>
-      <c r="L1" s="227"/>
-      <c r="M1" s="227"/>
-      <c r="N1" s="227"/>
-      <c r="O1" s="227"/>
-      <c r="P1" s="227"/>
-      <c r="Q1" s="227"/>
-      <c r="R1" s="227"/>
-      <c r="S1" s="227"/>
-      <c r="T1" s="227"/>
-      <c r="U1" s="227"/>
-      <c r="V1" s="227"/>
-      <c r="W1" s="227"/>
-      <c r="X1" s="227"/>
-      <c r="Y1" s="227"/>
-      <c r="Z1" s="227"/>
-      <c r="AA1" s="227"/>
-      <c r="AB1" s="227"/>
-      <c r="AC1" s="227"/>
-      <c r="AD1" s="227"/>
+      <c r="B1" s="223"/>
+      <c r="C1" s="223"/>
+      <c r="D1" s="223"/>
+      <c r="E1" s="223"/>
+      <c r="F1" s="223"/>
+      <c r="G1" s="223"/>
+      <c r="H1" s="223"/>
+      <c r="I1" s="223"/>
+      <c r="J1" s="223"/>
+      <c r="K1" s="223"/>
+      <c r="L1" s="223"/>
+      <c r="M1" s="223"/>
+      <c r="N1" s="223"/>
+      <c r="O1" s="223"/>
+      <c r="P1" s="223"/>
+      <c r="Q1" s="223"/>
+      <c r="R1" s="223"/>
+      <c r="S1" s="223"/>
+      <c r="T1" s="223"/>
+      <c r="U1" s="223"/>
+      <c r="V1" s="223"/>
+      <c r="W1" s="223"/>
+      <c r="X1" s="223"/>
+      <c r="Y1" s="223"/>
+      <c r="Z1" s="223"/>
+      <c r="AA1" s="223"/>
+      <c r="AB1" s="223"/>
+      <c r="AC1" s="223"/>
+      <c r="AD1" s="223"/>
     </row>
     <row r="2" spans="1:52" ht="26.25">
-      <c r="A2" s="228"/>
-      <c r="B2" s="229"/>
-      <c r="C2" s="230" t="s">
+      <c r="A2" s="224"/>
+      <c r="B2" s="225"/>
+      <c r="C2" s="226" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="230"/>
-      <c r="G2" s="230"/>
-      <c r="H2" s="230"/>
-      <c r="I2" s="230"/>
-      <c r="J2" s="230"/>
-      <c r="K2" s="230"/>
-      <c r="L2" s="231" t="s">
+      <c r="D2" s="226"/>
+      <c r="E2" s="226"/>
+      <c r="F2" s="226"/>
+      <c r="G2" s="226"/>
+      <c r="H2" s="226"/>
+      <c r="I2" s="226"/>
+      <c r="J2" s="226"/>
+      <c r="K2" s="226"/>
+      <c r="L2" s="227" t="s">
         <v>69</v>
       </c>
-      <c r="M2" s="231"/>
-      <c r="N2" s="231"/>
-      <c r="O2" s="231"/>
-      <c r="P2" s="231"/>
-      <c r="Q2" s="231"/>
-      <c r="R2" s="232" t="s">
+      <c r="M2" s="227"/>
+      <c r="N2" s="227"/>
+      <c r="O2" s="227"/>
+      <c r="P2" s="227"/>
+      <c r="Q2" s="227"/>
+      <c r="R2" s="228" t="s">
         <v>70</v>
       </c>
-      <c r="S2" s="232"/>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232"/>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
-      <c r="AA2" s="232"/>
-      <c r="AB2" s="233" t="s">
+      <c r="S2" s="228"/>
+      <c r="T2" s="228"/>
+      <c r="U2" s="228"/>
+      <c r="V2" s="228"/>
+      <c r="W2" s="228"/>
+      <c r="X2" s="228"/>
+      <c r="Y2" s="228"/>
+      <c r="Z2" s="228"/>
+      <c r="AA2" s="228"/>
+      <c r="AB2" s="229" t="s">
         <v>71</v>
       </c>
-      <c r="AC2" s="233"/>
-      <c r="AD2" s="233"/>
+      <c r="AC2" s="229"/>
+      <c r="AD2" s="229"/>
     </row>
     <row r="3" spans="1:52" ht="45" customHeight="1">
       <c r="A3" s="67" t="s">
@@ -24147,7 +24180,7 @@
         <f>37635+40252.26+18817.85</f>
         <v>96705.11</v>
       </c>
-      <c r="AD4" s="225"/>
+      <c r="AD4" s="233"/>
     </row>
     <row r="5" spans="1:52" ht="15.75">
       <c r="A5" s="35">
@@ -24197,7 +24230,7 @@
         <v>16503.13</v>
       </c>
       <c r="AC5" s="47"/>
-      <c r="AD5" s="225"/>
+      <c r="AD5" s="233"/>
     </row>
     <row r="6" spans="1:52" ht="15.75">
       <c r="A6" s="31">
@@ -24240,7 +24273,7 @@
         <v>996.61</v>
       </c>
       <c r="AC6" s="47"/>
-      <c r="AD6" s="225"/>
+      <c r="AD6" s="233"/>
     </row>
     <row r="7" spans="1:52" ht="15.75">
       <c r="A7" s="35">
@@ -24293,7 +24326,7 @@
         <v>5968</v>
       </c>
       <c r="AC7" s="47"/>
-      <c r="AD7" s="225"/>
+      <c r="AD7" s="233"/>
     </row>
     <row r="8" spans="1:52" ht="15" customHeight="1">
       <c r="A8" s="31">
@@ -24339,7 +24372,7 @@
         <v>12168.98</v>
       </c>
       <c r="AC8" s="47"/>
-      <c r="AD8" s="225"/>
+      <c r="AD8" s="233"/>
     </row>
     <row r="9" spans="1:52" ht="15.75">
       <c r="A9" s="35">
@@ -24387,7 +24420,7 @@
         <v>5970</v>
       </c>
       <c r="AC9" s="47"/>
-      <c r="AD9" s="225"/>
+      <c r="AD9" s="233"/>
     </row>
     <row r="10" spans="1:52" ht="15.75">
       <c r="A10" s="31">
@@ -24435,7 +24468,7 @@
         <v>3257</v>
       </c>
       <c r="AC10" s="47"/>
-      <c r="AD10" s="225"/>
+      <c r="AD10" s="233"/>
     </row>
     <row r="11" spans="1:52" ht="15.75">
       <c r="A11" s="35">
@@ -24479,14 +24512,14 @@
         <v>1034</v>
       </c>
       <c r="AC11" s="47"/>
-      <c r="AD11" s="225"/>
-      <c r="AH11" s="226" t="s">
+      <c r="AD11" s="233"/>
+      <c r="AH11" s="234" t="s">
         <v>84</v>
       </c>
-      <c r="AI11" s="226"/>
-      <c r="AJ11" s="226"/>
-      <c r="AK11" s="226"/>
-      <c r="AL11" s="226"/>
+      <c r="AI11" s="234"/>
+      <c r="AJ11" s="234"/>
+      <c r="AK11" s="234"/>
+      <c r="AL11" s="234"/>
     </row>
     <row r="12" spans="1:52" ht="15.75">
       <c r="A12" s="31">
@@ -24533,12 +24566,12 @@
         <v>3586</v>
       </c>
       <c r="AC12" s="47"/>
-      <c r="AD12" s="225"/>
-      <c r="AH12" s="226"/>
-      <c r="AI12" s="226"/>
-      <c r="AJ12" s="226"/>
-      <c r="AK12" s="226"/>
-      <c r="AL12" s="226"/>
+      <c r="AD12" s="233"/>
+      <c r="AH12" s="234"/>
+      <c r="AI12" s="234"/>
+      <c r="AJ12" s="234"/>
+      <c r="AK12" s="234"/>
+      <c r="AL12" s="234"/>
     </row>
     <row r="13" spans="1:52" ht="15.75">
       <c r="A13" s="35">
@@ -24585,12 +24618,12 @@
         <v>5889</v>
       </c>
       <c r="AC13" s="47"/>
-      <c r="AD13" s="225"/>
-      <c r="AH13" s="226"/>
-      <c r="AI13" s="226"/>
-      <c r="AJ13" s="226"/>
-      <c r="AK13" s="226"/>
-      <c r="AL13" s="226"/>
+      <c r="AD13" s="233"/>
+      <c r="AH13" s="234"/>
+      <c r="AI13" s="234"/>
+      <c r="AJ13" s="234"/>
+      <c r="AK13" s="234"/>
+      <c r="AL13" s="234"/>
     </row>
     <row r="14" spans="1:52" ht="18">
       <c r="A14" s="31">
@@ -24636,13 +24669,13 @@
         <v>7092.93</v>
       </c>
       <c r="AC14" s="47"/>
-      <c r="AD14" s="225"/>
-      <c r="AH14" s="222" t="s">
+      <c r="AD14" s="233"/>
+      <c r="AH14" s="230" t="s">
         <v>62</v>
       </c>
-      <c r="AI14" s="222"/>
-      <c r="AJ14" s="222"/>
-      <c r="AK14" s="222"/>
+      <c r="AI14" s="230"/>
+      <c r="AJ14" s="230"/>
+      <c r="AK14" s="230"/>
       <c r="AL14" s="39">
         <f>AC4+AC20</f>
         <v>133443.15</v>
@@ -24700,13 +24733,13 @@
         <v>6644.28</v>
       </c>
       <c r="AC15" s="46"/>
-      <c r="AD15" s="225"/>
-      <c r="AH15" s="222" t="s">
+      <c r="AD15" s="233"/>
+      <c r="AH15" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="AI15" s="222"/>
-      <c r="AJ15" s="222"/>
-      <c r="AK15" s="222"/>
+      <c r="AI15" s="230"/>
+      <c r="AJ15" s="230"/>
+      <c r="AK15" s="230"/>
       <c r="AL15" s="39">
         <f>AC29</f>
         <v>1000</v>
@@ -24761,13 +24794,13 @@
         <v>5105.1899999999996</v>
       </c>
       <c r="AC16" s="47"/>
-      <c r="AD16" s="225"/>
-      <c r="AH16" s="222" t="s">
+      <c r="AD16" s="233"/>
+      <c r="AH16" s="230" t="s">
         <v>63</v>
       </c>
-      <c r="AI16" s="222"/>
-      <c r="AJ16" s="222"/>
-      <c r="AK16" s="222"/>
+      <c r="AI16" s="230"/>
+      <c r="AJ16" s="230"/>
+      <c r="AK16" s="230"/>
       <c r="AL16" s="39">
         <f>AC21+AC34</f>
         <v>11000</v>
@@ -24812,13 +24845,13 @@
         <v>280.97000000000003</v>
       </c>
       <c r="AC17" s="47"/>
-      <c r="AD17" s="225"/>
-      <c r="AH17" s="222" t="s">
+      <c r="AD17" s="233"/>
+      <c r="AH17" s="230" t="s">
         <v>64</v>
       </c>
-      <c r="AI17" s="222"/>
-      <c r="AJ17" s="222"/>
-      <c r="AK17" s="222"/>
+      <c r="AI17" s="230"/>
+      <c r="AJ17" s="230"/>
+      <c r="AK17" s="230"/>
       <c r="AL17" s="39">
         <f>AB36</f>
         <v>146501.73000000001</v>
@@ -24867,23 +24900,23 @@
         <v>956.98</v>
       </c>
       <c r="AC18" s="47"/>
-      <c r="AD18" s="225"/>
-      <c r="AH18" s="222" t="s">
+      <c r="AD18" s="233"/>
+      <c r="AH18" s="230" t="s">
         <v>65</v>
       </c>
-      <c r="AI18" s="222"/>
-      <c r="AJ18" s="222"/>
-      <c r="AK18" s="222"/>
+      <c r="AI18" s="230"/>
+      <c r="AJ18" s="230"/>
+      <c r="AK18" s="230"/>
       <c r="AL18" s="39">
         <f>SUM(C36:K36)</f>
         <v>56967.92</v>
       </c>
     </row>
     <row r="19" spans="1:38" ht="19.5" customHeight="1">
-      <c r="A19" s="223" t="s">
+      <c r="A19" s="231" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="223"/>
+      <c r="B19" s="231"/>
       <c r="C19" s="40">
         <f>SUM(C4:C18)</f>
         <v>1403.89</v>
@@ -24996,12 +25029,12 @@
         <f>AC19-AB19</f>
         <v>4280.0900000000101</v>
       </c>
-      <c r="AH19" s="222" t="s">
+      <c r="AH19" s="230" t="s">
         <v>85</v>
       </c>
-      <c r="AI19" s="222"/>
-      <c r="AJ19" s="222"/>
-      <c r="AK19" s="222"/>
+      <c r="AI19" s="230"/>
+      <c r="AJ19" s="230"/>
+      <c r="AK19" s="230"/>
       <c r="AL19" s="39">
         <f>SUM(L36:Q36)</f>
         <v>31394.13</v>
@@ -25062,13 +25095,13 @@
       <c r="AC20" s="46">
         <v>36738.04</v>
       </c>
-      <c r="AD20" s="225"/>
-      <c r="AH20" s="222" t="s">
+      <c r="AD20" s="233"/>
+      <c r="AH20" s="230" t="s">
         <v>66</v>
       </c>
-      <c r="AI20" s="222"/>
-      <c r="AJ20" s="222"/>
-      <c r="AK20" s="222"/>
+      <c r="AI20" s="230"/>
+      <c r="AJ20" s="230"/>
+      <c r="AK20" s="230"/>
       <c r="AL20" s="39">
         <f>W36</f>
         <v>35678.97</v>
@@ -25123,14 +25156,14 @@
       <c r="AC21" s="96">
         <v>10000</v>
       </c>
-      <c r="AD21" s="225"/>
+      <c r="AD21" s="233"/>
       <c r="AF21" s="48"/>
-      <c r="AH21" s="222" t="s">
+      <c r="AH21" s="230" t="s">
         <v>86</v>
       </c>
-      <c r="AI21" s="222"/>
-      <c r="AJ21" s="222"/>
-      <c r="AK21" s="222"/>
+      <c r="AI21" s="230"/>
+      <c r="AJ21" s="230"/>
+      <c r="AK21" s="230"/>
       <c r="AL21" s="39">
         <f>SUM(U36:V36)</f>
         <v>11008.46</v>
@@ -25173,13 +25206,13 @@
         <v>0</v>
       </c>
       <c r="AC22" s="47"/>
-      <c r="AD22" s="225"/>
-      <c r="AH22" s="222" t="s">
+      <c r="AD22" s="233"/>
+      <c r="AH22" s="230" t="s">
         <v>32</v>
       </c>
-      <c r="AI22" s="222"/>
-      <c r="AJ22" s="222"/>
-      <c r="AK22" s="222"/>
+      <c r="AI22" s="230"/>
+      <c r="AJ22" s="230"/>
+      <c r="AK22" s="230"/>
       <c r="AL22" s="39">
         <f>T36</f>
         <v>0</v>
@@ -25234,13 +25267,13 @@
         <v>6881.28</v>
       </c>
       <c r="AC23" s="47"/>
-      <c r="AD23" s="225"/>
-      <c r="AH23" s="222" t="s">
+      <c r="AD23" s="233"/>
+      <c r="AH23" s="230" t="s">
         <v>87</v>
       </c>
-      <c r="AI23" s="222"/>
-      <c r="AJ23" s="222"/>
-      <c r="AK23" s="222"/>
+      <c r="AI23" s="230"/>
+      <c r="AJ23" s="230"/>
+      <c r="AK23" s="230"/>
       <c r="AL23" s="39">
         <f>X36</f>
         <v>5267.98</v>
@@ -25295,7 +25328,7 @@
         <v>6126.69</v>
       </c>
       <c r="AC24" s="47"/>
-      <c r="AD24" s="225"/>
+      <c r="AD24" s="233"/>
     </row>
     <row r="25" spans="1:38" ht="15.75">
       <c r="A25" s="35">
@@ -25339,7 +25372,7 @@
         <v>7750</v>
       </c>
       <c r="AC25" s="47"/>
-      <c r="AD25" s="225"/>
+      <c r="AD25" s="233"/>
     </row>
     <row r="26" spans="1:38" ht="15.75">
       <c r="A26" s="31">
@@ -25386,7 +25419,7 @@
         <v>2803</v>
       </c>
       <c r="AC26" s="46"/>
-      <c r="AD26" s="225"/>
+      <c r="AD26" s="233"/>
     </row>
     <row r="27" spans="1:38" ht="15.75">
       <c r="A27" s="35">
@@ -25434,7 +25467,7 @@
         <v>2088.96</v>
       </c>
       <c r="AC27" s="47"/>
-      <c r="AD27" s="225"/>
+      <c r="AD27" s="233"/>
     </row>
     <row r="28" spans="1:38" ht="15.75">
       <c r="A28" s="31">
@@ -25480,7 +25513,7 @@
         <v>3468</v>
       </c>
       <c r="AC28" s="47"/>
-      <c r="AD28" s="225"/>
+      <c r="AD28" s="233"/>
     </row>
     <row r="29" spans="1:38" ht="15.75">
       <c r="A29" s="35">
@@ -25533,7 +25566,7 @@
       <c r="AC29" s="47">
         <v>1000</v>
       </c>
-      <c r="AD29" s="225"/>
+      <c r="AD29" s="233"/>
     </row>
     <row r="30" spans="1:38" ht="15.75">
       <c r="A30" s="31">
@@ -25581,7 +25614,7 @@
         <v>4016.5</v>
       </c>
       <c r="AC30" s="47"/>
-      <c r="AD30" s="225"/>
+      <c r="AD30" s="233"/>
     </row>
     <row r="31" spans="1:38" ht="15.75">
       <c r="A31" s="35">
@@ -25625,7 +25658,7 @@
         <v>2801.78</v>
       </c>
       <c r="AC31" s="47"/>
-      <c r="AD31" s="225"/>
+      <c r="AD31" s="233"/>
     </row>
     <row r="32" spans="1:38" ht="15.75">
       <c r="A32" s="31">
@@ -25674,7 +25707,7 @@
         <v>3807.11</v>
       </c>
       <c r="AC32" s="47"/>
-      <c r="AD32" s="225"/>
+      <c r="AD32" s="233"/>
     </row>
     <row r="33" spans="1:30" ht="15.75">
       <c r="A33" s="35">
@@ -25718,7 +25751,7 @@
         <v>675.44</v>
       </c>
       <c r="AC33" s="47"/>
-      <c r="AD33" s="225"/>
+      <c r="AD33" s="233"/>
     </row>
     <row r="34" spans="1:30" ht="15.75">
       <c r="A34" s="31">
@@ -25762,13 +25795,13 @@
       <c r="AC34" s="96">
         <v>1000</v>
       </c>
-      <c r="AD34" s="225"/>
+      <c r="AD34" s="233"/>
     </row>
     <row r="35" spans="1:30" ht="14.25" customHeight="1">
-      <c r="A35" s="223" t="s">
+      <c r="A35" s="231" t="s">
         <v>55</v>
       </c>
-      <c r="B35" s="223"/>
+      <c r="B35" s="231"/>
       <c r="C35" s="40">
         <f t="shared" ref="C35:AC35" si="3">SUM(C20:C34)</f>
         <v>2169.6999999999998</v>
@@ -25883,10 +25916,10 @@
       </c>
     </row>
     <row r="36" spans="1:30" ht="31.5" customHeight="1">
-      <c r="A36" s="224" t="s">
+      <c r="A36" s="232" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="224"/>
+      <c r="B36" s="232"/>
       <c r="C36" s="61">
         <f>SUM(C19,C35)</f>
         <v>3573.59</v>
@@ -26017,12 +26050,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:K2"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="AH23:AK23"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="A36:B36"/>
@@ -26039,6 +26066,12 @@
     <mergeCell ref="AH16:AK16"/>
     <mergeCell ref="AH17:AK17"/>
     <mergeCell ref="AH18:AK18"/>
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -26059,78 +26092,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="34.5" customHeight="1">
-      <c r="A1" s="227" t="s">
+      <c r="A1" s="223" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="227"/>
-      <c r="C1" s="227"/>
-      <c r="D1" s="227"/>
-      <c r="E1" s="227"/>
-      <c r="F1" s="227"/>
-      <c r="G1" s="227"/>
-      <c r="H1" s="227"/>
-      <c r="I1" s="227"/>
-      <c r="J1" s="227"/>
-      <c r="K1" s="227"/>
-      <c r="L1" s="227"/>
-      <c r="M1" s="227"/>
-      <c r="N1" s="227"/>
-      <c r="O1" s="227"/>
-      <c r="P1" s="227"/>
-      <c r="Q1" s="227"/>
-      <c r="R1" s="227"/>
-      <c r="S1" s="227"/>
-      <c r="T1" s="227"/>
-      <c r="U1" s="227"/>
-      <c r="V1" s="227"/>
-      <c r="W1" s="227"/>
-      <c r="X1" s="227"/>
-      <c r="Y1" s="227"/>
-      <c r="Z1" s="227"/>
-      <c r="AA1" s="227"/>
-      <c r="AB1" s="227"/>
-      <c r="AC1" s="227"/>
-      <c r="AD1" s="227"/>
+      <c r="B1" s="223"/>
+      <c r="C1" s="223"/>
+      <c r="D1" s="223"/>
+      <c r="E1" s="223"/>
+      <c r="F1" s="223"/>
+      <c r="G1" s="223"/>
+      <c r="H1" s="223"/>
+      <c r="I1" s="223"/>
+      <c r="J1" s="223"/>
+      <c r="K1" s="223"/>
+      <c r="L1" s="223"/>
+      <c r="M1" s="223"/>
+      <c r="N1" s="223"/>
+      <c r="O1" s="223"/>
+      <c r="P1" s="223"/>
+      <c r="Q1" s="223"/>
+      <c r="R1" s="223"/>
+      <c r="S1" s="223"/>
+      <c r="T1" s="223"/>
+      <c r="U1" s="223"/>
+      <c r="V1" s="223"/>
+      <c r="W1" s="223"/>
+      <c r="X1" s="223"/>
+      <c r="Y1" s="223"/>
+      <c r="Z1" s="223"/>
+      <c r="AA1" s="223"/>
+      <c r="AB1" s="223"/>
+      <c r="AC1" s="223"/>
+      <c r="AD1" s="223"/>
     </row>
     <row r="2" spans="1:52" ht="26.25">
-      <c r="A2" s="228"/>
-      <c r="B2" s="229"/>
-      <c r="C2" s="230" t="s">
+      <c r="A2" s="224"/>
+      <c r="B2" s="225"/>
+      <c r="C2" s="226" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="230"/>
-      <c r="G2" s="230"/>
-      <c r="H2" s="230"/>
-      <c r="I2" s="230"/>
-      <c r="J2" s="230"/>
-      <c r="K2" s="230"/>
-      <c r="L2" s="231" t="s">
+      <c r="D2" s="226"/>
+      <c r="E2" s="226"/>
+      <c r="F2" s="226"/>
+      <c r="G2" s="226"/>
+      <c r="H2" s="226"/>
+      <c r="I2" s="226"/>
+      <c r="J2" s="226"/>
+      <c r="K2" s="226"/>
+      <c r="L2" s="227" t="s">
         <v>69</v>
       </c>
-      <c r="M2" s="231"/>
-      <c r="N2" s="231"/>
-      <c r="O2" s="231"/>
-      <c r="P2" s="231"/>
-      <c r="Q2" s="231"/>
-      <c r="R2" s="232" t="s">
+      <c r="M2" s="227"/>
+      <c r="N2" s="227"/>
+      <c r="O2" s="227"/>
+      <c r="P2" s="227"/>
+      <c r="Q2" s="227"/>
+      <c r="R2" s="228" t="s">
         <v>70</v>
       </c>
-      <c r="S2" s="232"/>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232"/>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
-      <c r="AA2" s="232"/>
-      <c r="AB2" s="233" t="s">
+      <c r="S2" s="228"/>
+      <c r="T2" s="228"/>
+      <c r="U2" s="228"/>
+      <c r="V2" s="228"/>
+      <c r="W2" s="228"/>
+      <c r="X2" s="228"/>
+      <c r="Y2" s="228"/>
+      <c r="Z2" s="228"/>
+      <c r="AA2" s="228"/>
+      <c r="AB2" s="229" t="s">
         <v>71</v>
       </c>
-      <c r="AC2" s="233"/>
-      <c r="AD2" s="233"/>
+      <c r="AC2" s="229"/>
+      <c r="AD2" s="229"/>
     </row>
     <row r="3" spans="1:52" ht="45" customHeight="1">
       <c r="A3" s="67" t="s">
@@ -26295,7 +26328,7 @@
         <f>66577.47+18817</f>
         <v>85394.47</v>
       </c>
-      <c r="AD4" s="225"/>
+      <c r="AD4" s="233"/>
     </row>
     <row r="5" spans="1:52" ht="15.75">
       <c r="A5" s="35">
@@ -26350,7 +26383,7 @@
         <v>7116</v>
       </c>
       <c r="AC5" s="21"/>
-      <c r="AD5" s="225"/>
+      <c r="AD5" s="233"/>
     </row>
     <row r="6" spans="1:52" ht="15.75">
       <c r="A6" s="31">
@@ -26398,7 +26431,7 @@
         <v>17146</v>
       </c>
       <c r="AC6" s="21"/>
-      <c r="AD6" s="225"/>
+      <c r="AD6" s="233"/>
     </row>
     <row r="7" spans="1:52" ht="15.75">
       <c r="A7" s="35">
@@ -26455,7 +26488,7 @@
         <v>6206.84</v>
       </c>
       <c r="AC7" s="21"/>
-      <c r="AD7" s="225"/>
+      <c r="AD7" s="233"/>
     </row>
     <row r="8" spans="1:52" ht="15" customHeight="1">
       <c r="A8" s="31">
@@ -26514,7 +26547,7 @@
         <v>8204</v>
       </c>
       <c r="AC8" s="21"/>
-      <c r="AD8" s="225"/>
+      <c r="AD8" s="233"/>
     </row>
     <row r="9" spans="1:52" ht="15.75">
       <c r="A9" s="35">
@@ -26563,7 +26596,7 @@
         <v>8276</v>
       </c>
       <c r="AC9" s="21"/>
-      <c r="AD9" s="225"/>
+      <c r="AD9" s="233"/>
     </row>
     <row r="10" spans="1:52" ht="15.75">
       <c r="A10" s="31">
@@ -26611,7 +26644,7 @@
       <c r="AC10" s="21">
         <v>28225.5</v>
       </c>
-      <c r="AD10" s="225"/>
+      <c r="AD10" s="233"/>
     </row>
     <row r="11" spans="1:52" ht="15.75">
       <c r="A11" s="35">
@@ -26661,14 +26694,14 @@
         <v>5638.53</v>
       </c>
       <c r="AC11" s="21"/>
-      <c r="AD11" s="225"/>
-      <c r="AH11" s="226" t="s">
+      <c r="AD11" s="233"/>
+      <c r="AH11" s="234" t="s">
         <v>84</v>
       </c>
-      <c r="AI11" s="226"/>
-      <c r="AJ11" s="226"/>
-      <c r="AK11" s="226"/>
-      <c r="AL11" s="226"/>
+      <c r="AI11" s="234"/>
+      <c r="AJ11" s="234"/>
+      <c r="AK11" s="234"/>
+      <c r="AL11" s="234"/>
     </row>
     <row r="12" spans="1:52" ht="15.75">
       <c r="A12" s="31">
@@ -26722,12 +26755,12 @@
         <v>33365</v>
       </c>
       <c r="AC12" s="21"/>
-      <c r="AD12" s="225"/>
-      <c r="AH12" s="226"/>
-      <c r="AI12" s="226"/>
-      <c r="AJ12" s="226"/>
-      <c r="AK12" s="226"/>
-      <c r="AL12" s="226"/>
+      <c r="AD12" s="233"/>
+      <c r="AH12" s="234"/>
+      <c r="AI12" s="234"/>
+      <c r="AJ12" s="234"/>
+      <c r="AK12" s="234"/>
+      <c r="AL12" s="234"/>
     </row>
     <row r="13" spans="1:52" ht="15.75">
       <c r="A13" s="35">
@@ -26785,12 +26818,12 @@
         <v>10965.96</v>
       </c>
       <c r="AC13" s="21"/>
-      <c r="AD13" s="225"/>
-      <c r="AH13" s="226"/>
-      <c r="AI13" s="226"/>
-      <c r="AJ13" s="226"/>
-      <c r="AK13" s="226"/>
-      <c r="AL13" s="226"/>
+      <c r="AD13" s="233"/>
+      <c r="AH13" s="234"/>
+      <c r="AI13" s="234"/>
+      <c r="AJ13" s="234"/>
+      <c r="AK13" s="234"/>
+      <c r="AL13" s="234"/>
     </row>
     <row r="14" spans="1:52" ht="18">
       <c r="A14" s="31">
@@ -26838,13 +26871,13 @@
         <v>1614.53</v>
       </c>
       <c r="AC14" s="21"/>
-      <c r="AD14" s="225"/>
-      <c r="AH14" s="222" t="s">
+      <c r="AD14" s="233"/>
+      <c r="AH14" s="230" t="s">
         <v>62</v>
       </c>
-      <c r="AI14" s="222"/>
-      <c r="AJ14" s="222"/>
-      <c r="AK14" s="222"/>
+      <c r="AI14" s="230"/>
+      <c r="AJ14" s="230"/>
+      <c r="AK14" s="230"/>
       <c r="AL14" s="39">
         <f>AC4+AC19+AC23+AC10</f>
         <v>287751.42</v>
@@ -26902,13 +26935,13 @@
         <v>6960.82</v>
       </c>
       <c r="AC15" s="16"/>
-      <c r="AD15" s="225"/>
-      <c r="AH15" s="222" t="s">
+      <c r="AD15" s="233"/>
+      <c r="AH15" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="AI15" s="222"/>
-      <c r="AJ15" s="222"/>
-      <c r="AK15" s="222"/>
+      <c r="AI15" s="230"/>
+      <c r="AJ15" s="230"/>
+      <c r="AK15" s="230"/>
       <c r="AL15" s="39">
         <f>AC20</f>
         <v>1000</v>
@@ -26962,13 +26995,13 @@
       <c r="AC16" s="76">
         <v>5000</v>
       </c>
-      <c r="AD16" s="225"/>
-      <c r="AH16" s="222" t="s">
+      <c r="AD16" s="233"/>
+      <c r="AH16" s="230" t="s">
         <v>63</v>
       </c>
-      <c r="AI16" s="222"/>
-      <c r="AJ16" s="222"/>
-      <c r="AK16" s="222"/>
+      <c r="AI16" s="230"/>
+      <c r="AJ16" s="230"/>
+      <c r="AK16" s="230"/>
       <c r="AL16" s="39">
         <f>AC16+AC28+AC34+AC35</f>
         <v>60000</v>
@@ -27026,23 +27059,23 @@
         <v>5002</v>
       </c>
       <c r="AC17" s="16"/>
-      <c r="AD17" s="225"/>
-      <c r="AH17" s="237" t="s">
+      <c r="AD17" s="233"/>
+      <c r="AH17" s="238" t="s">
         <v>68</v>
       </c>
-      <c r="AI17" s="238"/>
-      <c r="AJ17" s="238"/>
-      <c r="AK17" s="239"/>
+      <c r="AI17" s="239"/>
+      <c r="AJ17" s="239"/>
+      <c r="AK17" s="240"/>
       <c r="AL17" s="39">
         <f>SUM(C37:K37)</f>
         <v>121331.08</v>
       </c>
     </row>
     <row r="18" spans="1:38" ht="19.5" customHeight="1">
-      <c r="A18" s="240" t="s">
+      <c r="A18" s="241" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="240"/>
+      <c r="B18" s="241"/>
       <c r="C18" s="40">
         <f>SUM(C4:C17)</f>
         <v>129.99</v>
@@ -27155,12 +27188,12 @@
         <f>AC18-AB18</f>
         <v>-900.67000000001303</v>
       </c>
-      <c r="AH18" s="222" t="s">
+      <c r="AH18" s="230" t="s">
         <v>85</v>
       </c>
-      <c r="AI18" s="222"/>
-      <c r="AJ18" s="222"/>
-      <c r="AK18" s="222"/>
+      <c r="AI18" s="230"/>
+      <c r="AJ18" s="230"/>
+      <c r="AK18" s="230"/>
       <c r="AL18" s="39">
         <f>SUM(L37:Q37)</f>
         <v>35695</v>
@@ -27214,13 +27247,13 @@
       <c r="AC19" s="46">
         <v>38575.449999999997</v>
       </c>
-      <c r="AD19" s="225"/>
-      <c r="AH19" s="222" t="s">
+      <c r="AD19" s="233"/>
+      <c r="AH19" s="230" t="s">
         <v>66</v>
       </c>
-      <c r="AI19" s="222"/>
-      <c r="AJ19" s="222"/>
-      <c r="AK19" s="222"/>
+      <c r="AI19" s="230"/>
+      <c r="AJ19" s="230"/>
+      <c r="AK19" s="230"/>
       <c r="AL19" s="39">
         <f>W37</f>
         <v>38934</v>
@@ -27277,14 +27310,14 @@
       <c r="AC20" s="47">
         <v>1000</v>
       </c>
-      <c r="AD20" s="225"/>
+      <c r="AD20" s="233"/>
       <c r="AF20" s="48"/>
-      <c r="AH20" s="222" t="s">
+      <c r="AH20" s="230" t="s">
         <v>86</v>
       </c>
-      <c r="AI20" s="222"/>
-      <c r="AJ20" s="222"/>
-      <c r="AK20" s="222"/>
+      <c r="AI20" s="230"/>
+      <c r="AJ20" s="230"/>
+      <c r="AK20" s="230"/>
       <c r="AL20" s="39">
         <f>SUM(U37:V37)</f>
         <v>15264.08</v>
@@ -27330,13 +27363,13 @@
         <v>1980</v>
       </c>
       <c r="AC21" s="47"/>
-      <c r="AD21" s="225"/>
-      <c r="AH21" s="234" t="s">
+      <c r="AD21" s="233"/>
+      <c r="AH21" s="235" t="s">
         <v>32</v>
       </c>
-      <c r="AI21" s="234"/>
-      <c r="AJ21" s="234"/>
-      <c r="AK21" s="234"/>
+      <c r="AI21" s="235"/>
+      <c r="AJ21" s="235"/>
+      <c r="AK21" s="235"/>
       <c r="AL21" s="49">
         <f>T37</f>
         <v>31093</v>
@@ -27391,11 +27424,11 @@
         <v>3710.54</v>
       </c>
       <c r="AC22" s="47"/>
-      <c r="AD22" s="225"/>
-      <c r="AH22" s="235"/>
-      <c r="AI22" s="235"/>
-      <c r="AJ22" s="235"/>
-      <c r="AK22" s="235"/>
+      <c r="AD22" s="233"/>
+      <c r="AH22" s="236"/>
+      <c r="AI22" s="236"/>
+      <c r="AJ22" s="236"/>
+      <c r="AK22" s="236"/>
       <c r="AL22" s="50"/>
     </row>
     <row r="23" spans="1:38" ht="15.75">
@@ -27447,7 +27480,7 @@
         <f>21986+70637+42933</f>
         <v>135556</v>
       </c>
-      <c r="AD23" s="225"/>
+      <c r="AD23" s="233"/>
     </row>
     <row r="24" spans="1:38" ht="15.75">
       <c r="A24" s="35">
@@ -27507,7 +27540,7 @@
         <v>26293.41</v>
       </c>
       <c r="AC24" s="47"/>
-      <c r="AD24" s="225"/>
+      <c r="AD24" s="233"/>
     </row>
     <row r="25" spans="1:38" ht="15.75">
       <c r="A25" s="31">
@@ -27552,7 +27585,7 @@
         <v>542</v>
       </c>
       <c r="AC25" s="46"/>
-      <c r="AD25" s="225"/>
+      <c r="AD25" s="233"/>
     </row>
     <row r="26" spans="1:38" ht="15.75">
       <c r="A26" s="35">
@@ -27612,7 +27645,7 @@
         <v>5856.07</v>
       </c>
       <c r="AC26" s="47"/>
-      <c r="AD26" s="225"/>
+      <c r="AD26" s="233"/>
     </row>
     <row r="27" spans="1:38" ht="15.75">
       <c r="A27" s="31">
@@ -27666,7 +27699,7 @@
         <v>14081.2</v>
       </c>
       <c r="AC27" s="47"/>
-      <c r="AD27" s="225"/>
+      <c r="AD27" s="233"/>
     </row>
     <row r="28" spans="1:38" ht="15.75">
       <c r="A28" s="35">
@@ -27710,7 +27743,7 @@
       <c r="AC28" s="47">
         <v>20000</v>
       </c>
-      <c r="AD28" s="225"/>
+      <c r="AD28" s="233"/>
     </row>
     <row r="29" spans="1:38" ht="15.75">
       <c r="A29" s="31">
@@ -27759,7 +27792,7 @@
         <v>4019.84</v>
       </c>
       <c r="AC29" s="47"/>
-      <c r="AD29" s="225"/>
+      <c r="AD29" s="233"/>
     </row>
     <row r="30" spans="1:38" ht="15.75">
       <c r="A30" s="35">
@@ -27810,7 +27843,7 @@
         <v>2628.39</v>
       </c>
       <c r="AC30" s="47"/>
-      <c r="AD30" s="225"/>
+      <c r="AD30" s="233"/>
     </row>
     <row r="31" spans="1:38" ht="15.75">
       <c r="A31" s="78">
@@ -27866,7 +27899,7 @@
         <v>12589</v>
       </c>
       <c r="AC31" s="47"/>
-      <c r="AD31" s="225"/>
+      <c r="AD31" s="233"/>
     </row>
     <row r="32" spans="1:38" ht="15.75">
       <c r="A32" s="11">
@@ -27928,7 +27961,7 @@
         <v>18544.419999999998</v>
       </c>
       <c r="AC32" s="47"/>
-      <c r="AD32" s="225"/>
+      <c r="AD32" s="233"/>
     </row>
     <row r="33" spans="1:34" ht="15.75">
       <c r="A33" s="84">
@@ -27979,7 +28012,7 @@
         <v>9526.09</v>
       </c>
       <c r="AC33" s="47"/>
-      <c r="AD33" s="225"/>
+      <c r="AD33" s="233"/>
     </row>
     <row r="34" spans="1:34" ht="15.75">
       <c r="A34" s="88">
@@ -28041,7 +28074,7 @@
       <c r="AC34" s="47">
         <v>20000</v>
       </c>
-      <c r="AD34" s="225"/>
+      <c r="AD34" s="233"/>
     </row>
     <row r="35" spans="1:34" ht="15.75">
       <c r="A35" s="92">
@@ -28097,13 +28130,13 @@
       <c r="AC35" s="96">
         <v>15000</v>
       </c>
-      <c r="AD35" s="225"/>
+      <c r="AD35" s="233"/>
     </row>
     <row r="36" spans="1:34" ht="24" customHeight="1">
-      <c r="A36" s="236" t="s">
+      <c r="A36" s="237" t="s">
         <v>55</v>
       </c>
-      <c r="B36" s="236"/>
+      <c r="B36" s="237"/>
       <c r="C36" s="56">
         <f t="shared" ref="C36:AC36" si="6">SUM(C19:C35)</f>
         <v>1293.0899999999999</v>
@@ -28219,10 +28252,10 @@
       <c r="AH36" s="48"/>
     </row>
     <row r="37" spans="1:34" ht="31.5" customHeight="1">
-      <c r="A37" s="224" t="s">
+      <c r="A37" s="232" t="s">
         <v>56</v>
       </c>
-      <c r="B37" s="224"/>
+      <c r="B37" s="232"/>
       <c r="C37" s="61">
         <f t="shared" ref="C37:R37" si="7">SUM(C18,C36)</f>
         <v>1423.08</v>
@@ -28353,12 +28386,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:K2"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="AD4:AD17"/>
     <mergeCell ref="AD19:AD35"/>
@@ -28374,6 +28401,12 @@
     <mergeCell ref="AH17:AK17"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="AH18:AK18"/>
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
